--- a/Client Information App.xlsx
+++ b/Client Information App.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aryte\PycharmProjects\AlucladApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0855D9-C449-4E28-ABDB-E87F481D0E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B3ECF8-2B45-4DE2-A145-F75FE2F87FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="768" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="350">
   <si>
     <t>Ready to dispatch</t>
   </si>
@@ -1349,6 +1349,13 @@
   </si>
   <si>
     <t>status</t>
+  </si>
+  <si>
+    <t>timestamp</t>
+  </si>
+  <si>
+    <t>30/01/2026
+09:55</t>
   </si>
 </sst>
 </file>
@@ -1587,7 +1594,28 @@
     <cellStyle name="Neutral" xfId="1" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="19">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1765,27 +1793,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}" name="Table1" displayName="Table1" ref="A1:P20" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
-  <autoFilter ref="A1:P20" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}"/>
-  <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{867090DC-1FE0-4EF0-A0C0-448920317853}" name="Project" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{ED71812C-E204-4FE0-ADEA-0CD9B3ADA2A3}" name="Project SO" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{32502B80-458D-4EF6-9ABC-03678A6F8302}" name="order_id" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{111DD528-EE5F-4D8B-B63F-9A842570498D}" name="Materials" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{F88C7351-33D9-47AC-88E6-09F8FC43FCF9}" name="status" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{AF541036-9D61-4BFA-9B88-B69C899AAAFF}" name="Phase" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{3C9800BD-A315-48D1-9DB1-AF15B6CE2464}" name="Post Code" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{35381005-95B2-4E9D-9D09-3585A5DE3E35}" name="Delivery Adress" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{21A0DBD3-20BC-48FA-8FF6-DB3AFE9382A5}" name="PO Date" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{3F0B7287-A10E-4CE5-9A48-B72BC577D0D0}" name="Estimated Delivery Date" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{D53CD43D-3F51-4446-BA3F-C95DF42223C1}" name="Current Update" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}" name="Table1" displayName="Table1" ref="A1:Q20" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+  <autoFilter ref="A1:Q20" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}"/>
+  <tableColumns count="17">
+    <tableColumn id="1" xr3:uid="{867090DC-1FE0-4EF0-A0C0-448920317853}" name="Project" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{ED71812C-E204-4FE0-ADEA-0CD9B3ADA2A3}" name="Project SO" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{32502B80-458D-4EF6-9ABC-03678A6F8302}" name="order_id" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{111DD528-EE5F-4D8B-B63F-9A842570498D}" name="Materials" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{F88C7351-33D9-47AC-88E6-09F8FC43FCF9}" name="status" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{AF541036-9D61-4BFA-9B88-B69C899AAAFF}" name="Phase" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{3C9800BD-A315-48D1-9DB1-AF15B6CE2464}" name="Post Code" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{35381005-95B2-4E9D-9D09-3585A5DE3E35}" name="Delivery Adress" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{21A0DBD3-20BC-48FA-8FF6-DB3AFE9382A5}" name="PO Date" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{3F0B7287-A10E-4CE5-9A48-B72BC577D0D0}" name="Estimated Delivery Date" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{D53CD43D-3F51-4446-BA3F-C95DF42223C1}" name="Current Update" dataDxfId="6">
       <calculatedColumnFormula>AVERAGE(L2:N2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{6527AB69-9477-41B6-8941-2FE273E12275}" name="Production" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{6436B5E8-E98E-47E2-B70D-DD9AA467C3A5}" name="PPC" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{D893399C-2909-4B8A-9538-32D22CFA1B25}" name="Dispatch" dataDxfId="2"/>
-    <tableColumn id="15" xr3:uid="{F6302424-51FB-45BD-9F34-61C700C8D161}" name="Welded" dataDxfId="1"/>
-    <tableColumn id="16" xr3:uid="{9BE99484-0D9D-4749-B30B-7C533699CF52}" name="Critical Information" dataDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{6527AB69-9477-41B6-8941-2FE273E12275}" name="Production" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{6436B5E8-E98E-47E2-B70D-DD9AA467C3A5}" name="PPC" dataDxfId="4"/>
+    <tableColumn id="14" xr3:uid="{D893399C-2909-4B8A-9538-32D22CFA1B25}" name="Dispatch" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{F6302424-51FB-45BD-9F34-61C700C8D161}" name="Welded" dataDxfId="2"/>
+    <tableColumn id="16" xr3:uid="{9BE99484-0D9D-4749-B30B-7C533699CF52}" name="Critical Information" dataDxfId="1"/>
+    <tableColumn id="17" xr3:uid="{4C03519C-AB36-480D-97B3-F56FDE4D4B1D}" name="timestamp" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2057,7 +2086,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -2076,9 +2105,10 @@
     <col min="14" max="14" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.85546875" style="12" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="23" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>36</v>
       </c>
@@ -2127,8 +2157,11 @@
       <c r="P1" s="12" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q1" s="12" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>235</v>
       </c>
@@ -2176,8 +2209,9 @@
       <c r="P2" s="36" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+      <c r="Q2" s="16"/>
+    </row>
+    <row r="3" spans="1:17" ht="105" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>272</v>
       </c>
@@ -2218,8 +2252,9 @@
         <v>0.5</v>
       </c>
       <c r="P3" s="16"/>
-    </row>
-    <row r="4" spans="1:16" ht="120" x14ac:dyDescent="0.25">
+      <c r="Q3" s="16"/>
+    </row>
+    <row r="4" spans="1:17" ht="120" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>276</v>
       </c>
@@ -2260,8 +2295,9 @@
         <v>0</v>
       </c>
       <c r="P4" s="16"/>
-    </row>
-    <row r="5" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q4" s="16"/>
+    </row>
+    <row r="5" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>282</v>
       </c>
@@ -2300,8 +2336,9 @@
         <v>0</v>
       </c>
       <c r="P5" s="16"/>
-    </row>
-    <row r="6" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q5" s="16"/>
+    </row>
+    <row r="6" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>159</v>
       </c>
@@ -2343,8 +2380,9 @@
         <v>188</v>
       </c>
       <c r="P6" s="16"/>
-    </row>
-    <row r="7" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q6" s="16"/>
+    </row>
+    <row r="7" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>259</v>
       </c>
@@ -2392,8 +2430,11 @@
       <c r="P7" s="36" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q7" s="36" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>259</v>
       </c>
@@ -2441,8 +2482,9 @@
       <c r="P8" s="36" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q8" s="16"/>
+    </row>
+    <row r="9" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>259</v>
       </c>
@@ -2486,8 +2528,9 @@
         <v>188</v>
       </c>
       <c r="P9" s="16"/>
-    </row>
-    <row r="10" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q9" s="16"/>
+    </row>
+    <row r="10" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>74</v>
       </c>
@@ -2528,8 +2571,9 @@
         <v>0</v>
       </c>
       <c r="P10" s="16"/>
-    </row>
-    <row r="11" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q10" s="16"/>
+    </row>
+    <row r="11" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>281</v>
       </c>
@@ -2573,8 +2617,9 @@
         <v>188</v>
       </c>
       <c r="P11" s="16"/>
-    </row>
-    <row r="12" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q11" s="16"/>
+    </row>
+    <row r="12" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>212</v>
       </c>
@@ -2615,8 +2660,9 @@
         <v>0</v>
       </c>
       <c r="P12" s="16"/>
-    </row>
-    <row r="13" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q12" s="16"/>
+    </row>
+    <row r="13" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>308</v>
       </c>
@@ -2660,8 +2706,9 @@
         <v>188</v>
       </c>
       <c r="P13" s="16"/>
-    </row>
-    <row r="14" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q13" s="16"/>
+    </row>
+    <row r="14" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>315</v>
       </c>
@@ -2705,8 +2752,9 @@
         <v>188</v>
       </c>
       <c r="P14" s="16"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q14" s="16"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>321</v>
       </c>
@@ -2750,8 +2798,9 @@
         <v>188</v>
       </c>
       <c r="P15" s="16"/>
-    </row>
-    <row r="16" spans="1:16" ht="150" x14ac:dyDescent="0.25">
+      <c r="Q15" s="16"/>
+    </row>
+    <row r="16" spans="1:17" ht="150" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>229</v>
       </c>
@@ -2792,8 +2841,9 @@
         <v>0</v>
       </c>
       <c r="P16" s="16"/>
-    </row>
-    <row r="17" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q16" s="16"/>
+    </row>
+    <row r="17" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>97</v>
       </c>
@@ -2837,8 +2887,9 @@
         <v>188</v>
       </c>
       <c r="P17" s="16"/>
-    </row>
-    <row r="18" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q17" s="16"/>
+    </row>
+    <row r="18" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>334</v>
       </c>
@@ -2879,8 +2930,9 @@
         <v>0</v>
       </c>
       <c r="P18" s="16"/>
-    </row>
-    <row r="19" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q18" s="16"/>
+    </row>
+    <row r="19" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>339</v>
       </c>
@@ -2924,8 +2976,9 @@
         <v>188</v>
       </c>
       <c r="P19" s="16"/>
-    </row>
-    <row r="20" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q19" s="16"/>
+    </row>
+    <row r="20" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>259</v>
       </c>
@@ -2966,6 +3019,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/Client Information App.xlsx
+++ b/Client Information App.xlsx
@@ -5,15 +5,15 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aryte\PycharmProjects\AlucladApp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ACL Operation\1. Operation Documents\3. Project Cordination\5. Data Analytics\Power Bi Projects\1. PB2401 Client Information\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B3ECF8-2B45-4DE2-A145-F75FE2F87FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4375D1-9E29-40F4-AA9C-F81814B2EFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="768" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="CRM_main" sheetId="2" r:id="rId1"/>
+    <sheet name="CRM main" sheetId="2" r:id="rId1"/>
     <sheet name="VRP" sheetId="24" r:id="rId2"/>
     <sheet name="Aurora" sheetId="23" r:id="rId3"/>
     <sheet name="Roytec" sheetId="22" r:id="rId4"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="424">
   <si>
     <t>Ready to dispatch</t>
   </si>
@@ -903,18 +903,6 @@
 Embassy Gardens
 29 Nie Elms Lane
 London, SW11 7DP</t>
-  </si>
-  <si>
-    <t>New Swindon College</t>
-  </si>
-  <si>
-    <t>SO-1736</t>
-  </si>
-  <si>
-    <t>PO0189522-1</t>
-  </si>
-  <si>
-    <t>Fins &amp; Subframe Prod. 2</t>
   </si>
   <si>
     <t>SW1X 9HL</t>
@@ -1045,9 +1033,6 @@
     <t xml:space="preserve"> NW12PB</t>
   </si>
   <si>
-    <t>Additional Panels</t>
-  </si>
-  <si>
     <t>Cherry Orchard</t>
   </si>
   <si>
@@ -1075,287 +1060,586 @@
     <t>DA10 0BE</t>
   </si>
   <si>
-    <t>Panoramic</t>
-  </si>
-  <si>
-    <t>SO-1850</t>
-  </si>
-  <si>
-    <t>PAN216</t>
-  </si>
-  <si>
-    <t>NW3 2QX</t>
-  </si>
-  <si>
-    <t>Briggate Leeds</t>
-  </si>
-  <si>
-    <t>SO-1853</t>
-  </si>
-  <si>
-    <t>P6241090</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HG Construction Limited
- Store House Briggate
- 140-142 Briggate Lane
- Rear of House of Fraser, Access via Central Road
- (Opposite Little Tokyo Restaurant)
- Leeds, LS1 6DE
- Ion +44 (0) 7843 117 869</t>
-  </si>
-  <si>
-    <t>LS1 6DE</t>
-  </si>
-  <si>
-    <t>Kings Road Park E2</t>
-  </si>
-  <si>
-    <t>William Street</t>
-  </si>
-  <si>
-    <t>SO-1863</t>
-  </si>
-  <si>
-    <t>SO-1869</t>
-  </si>
-  <si>
-    <t>SO-1870</t>
-  </si>
-  <si>
-    <t>SO-1875</t>
-  </si>
-  <si>
-    <t>WLMS035</t>
-  </si>
-  <si>
-    <t>EBS001</t>
-  </si>
-  <si>
-    <t>Replacment Panels &amp; Pressings</t>
-  </si>
-  <si>
-    <t>Cabinet Prod.2</t>
-  </si>
-  <si>
-    <t>Block B Remaining Cills</t>
-  </si>
-  <si>
-    <t>St George Plc
-Camden Goods Yard
-Chalk Farm Road, Chalk Farm
-Camden Town,London, NW1 8EH
-Kontakt: Arek +44 (0) 7534 515 939</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NW1 8EH</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Powdertech (Corby) Ltd
- 5 Cockerell Rd
- Corby
- NN17 5DU
-Contact: Richard +44 (0) 7977 260 382</t>
-  </si>
-  <si>
-    <t>SO-1876</t>
-  </si>
-  <si>
-    <t>SO-1877</t>
-  </si>
-  <si>
-    <t>SO-1879</t>
-  </si>
-  <si>
-    <t>Perforated Balustrades</t>
-  </si>
-  <si>
-    <t>Rooflight Pressings</t>
-  </si>
-  <si>
-    <t>PO13424-439-JB-KRP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-Lakiernia Sp. z o.o.
-ul. Krzywoustego 1, 84 – 300 Lębork </t>
-  </si>
-  <si>
-    <t>84 – 300</t>
-  </si>
-  <si>
     <t>Critical Information</t>
   </si>
   <si>
-    <t>CW Brackets</t>
-  </si>
-  <si>
-    <t>CW Reinforcments</t>
-  </si>
-  <si>
-    <t>FC Direct Ltd,
-CO GPF Lewis, 
-152 Fleet Road, 
-London, NW3 2QX
-Luis Valle +44 (0) 7765 777 672, 
-Shaun Holland +44 (0) 7846 211 254,  Aaran Barratt +44 (0) 7464 485 453</t>
-  </si>
-  <si>
-    <t>FCS Facades, 
-McAleer &amp; Rushe Contracts UK, 
-10 Fulton Road, Wembley, 
-London, HA9 0GB</t>
-  </si>
-  <si>
-    <t>King Street</t>
-  </si>
-  <si>
-    <t>SO-1880</t>
-  </si>
-  <si>
-    <t>M-CC1084/00071</t>
-  </si>
-  <si>
-    <t>WC2E 8HN</t>
-  </si>
-  <si>
-    <t>26 King Street, London, WC2E 8HN
-Contact: +44 (0) 7540 994 243</t>
-  </si>
-  <si>
-    <t>Vidok Sp. Z.o.o.
-36-054 Mrowla
-Rudna Mala 75</t>
-  </si>
-  <si>
-    <t>Riggid Lorry + Trailer
-Heavy Load</t>
-  </si>
-  <si>
-    <t>Firestone</t>
-  </si>
-  <si>
-    <t>SO-1881</t>
-  </si>
-  <si>
-    <t>M-CC1093/00087</t>
-  </si>
-  <si>
-    <t>Panels</t>
-  </si>
-  <si>
-    <t>TW8 9EP</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> West Cross Industrial Park, Brendford, TW8 9EP
-Contact:  Paul Yates - +44 (0) 7879 882133</t>
-  </si>
-  <si>
-    <t>Kings Road Park E2 (Stavley Road)</t>
-  </si>
-  <si>
-    <t>SO-1882</t>
-  </si>
-  <si>
-    <t>PO30625-458-SRP</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 76 Stavley Road, W4 3HU London</t>
-  </si>
-  <si>
-    <t>W4 3HU</t>
-  </si>
-  <si>
-    <t>SO-1883</t>
-  </si>
-  <si>
-    <t>37-61JA</t>
-  </si>
-  <si>
-    <t>L-Profiles</t>
-  </si>
-  <si>
-    <t>Roytec Ltd c/o RED 
-,Construction Group
-, 5 Simpsons Road, St Marks 
-Square,
- London
- Bromley
- BR2 9AP
-Contact: Oleg +447453009655
-, Andriy +447380330922
-. Nick +07447162592</t>
-  </si>
-  <si>
-    <t>SO-1884</t>
-  </si>
-  <si>
-    <t>Pang - 9765</t>
-  </si>
-  <si>
-    <t>Helena Pang Door Skins</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EK Construction Limited
-143 Ebury Street
- London SW1W 9QN</t>
-  </si>
-  <si>
     <t>Broadway Central 2</t>
   </si>
   <si>
-    <t>SO-1885</t>
-  </si>
-  <si>
-    <t>Panel Hooking System</t>
+    <t>G2 3BW</t>
+  </si>
+  <si>
+    <t>SO-1997</t>
+  </si>
+  <si>
+    <t>EX CW Panels &amp; Pressings</t>
+  </si>
+  <si>
+    <t>Assembly
+CSK Hole</t>
+  </si>
+  <si>
+    <t>Thurrock Power Limited
+Thurrock Flexible Generation
+Station Road
+East Tilbury
+RM18 8QR
+Vlad 07584 078 721</t>
+  </si>
+  <si>
+    <t>Thurrock</t>
+  </si>
+  <si>
+    <t>SO-2002</t>
+  </si>
+  <si>
+    <t>Panel Brackets</t>
+  </si>
+  <si>
+    <t>RM18 8QR</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RM18 8QR</t>
+  </si>
+  <si>
+    <t>Thurrock Power Limited,
+Thurrock Flexible Generation,
+Station Road,
+East Tilbury,
+RM18 8QR
+Vlad +44 (0) 7584 078 721</t>
+  </si>
+  <si>
+    <t>SO-2005</t>
+  </si>
+  <si>
+    <t>Aluworks</t>
+  </si>
+  <si>
+    <t>PO41325-608</t>
+  </si>
+  <si>
+    <t>Aluworks Ltd.
+ Gate 2 Chester House
+ Bentails
+ Basildon
+ SS14 3BG
+Contact: Damian +44 (0)7574 403789</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SS14 3BG</t>
+  </si>
+  <si>
+    <t>Southbank Place</t>
   </si>
   <si>
     <t>McAleer &amp; Rushe Contracts UK Ltd
  (For FCS Facades)
- ,Broadway Central PBSA,
- Renfield Street
+ Southbank Place, Building 5
+ Belvedere Road
+ Southbank SE1 7AF
+Tom Plago +44 (0) 7889 215 253</t>
+  </si>
+  <si>
+    <t>SO-2009</t>
+  </si>
+  <si>
+    <t>Panels Batch 2</t>
+  </si>
+  <si>
+    <t>SE1 7AF</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tetraclad Ltd,</t>
+  </si>
+  <si>
+    <t>DA10 0B</t>
+  </si>
+  <si>
+    <t>St George Plc
+,Camden Goods Yard,
+Chalk Farm Road, Chalk Farm
+,Camden Town,London, NW1 8EH
+Contact: Arek +44 (0) 7534 515 939</t>
+  </si>
+  <si>
+    <t>PO0209992-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tetraclad Ltd,
+ EBBSFLEET GREEN,
+ Site A - Ackers Drive,
+ Ebbsfleet Valley,
+ Kent, DA10 0BE,
+Contact: Ross +44 (0) 7850 985 167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thurrock </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ebbsfleet </t>
+  </si>
+  <si>
+    <t>SO-2018</t>
+  </si>
+  <si>
+    <t>SO-2019</t>
+  </si>
+  <si>
+    <t>Plenums, Ducts &amp; Panels</t>
+  </si>
+  <si>
+    <t>Panel Flashings</t>
+  </si>
+  <si>
+    <t>Yellow Storage Brackets (Batch. 2)</t>
+  </si>
+  <si>
+    <t>Royal Central School</t>
+  </si>
+  <si>
+    <t>RCS003</t>
+  </si>
+  <si>
+    <t>NW3 3HY</t>
+  </si>
+  <si>
+    <t>FC Direct Ltd, Royal Central School of Speech and Drama, Eton Avenue, Belsize Park, London, NW3 3HY
+Luis Valle - +44 (0) 7765 777 672 / Aaran Barratt - +44 (0) 7464 485 453</t>
+  </si>
+  <si>
+    <t>Sinusoidal Panels</t>
+  </si>
+  <si>
+    <t>SO-2022</t>
+  </si>
+  <si>
+    <t>SO-2023</t>
+  </si>
+  <si>
+    <t>E&amp;N GF-L1 Subframe</t>
+  </si>
+  <si>
+    <t>Corner Panel Brackets</t>
+  </si>
+  <si>
+    <t>McAleer &amp; Rushe Contracts UK Ltd
+ (For FCS Facades)
+ ,Broadway Central, PBSA,
+200 Renfield Street,
  Glasgow, G2 3BW
-Contact: Piotr +44 (0) 7471 273 458</t>
-  </si>
-  <si>
-    <t>G2 3BW</t>
-  </si>
-  <si>
-    <t>Slough CDC</t>
-  </si>
-  <si>
-    <t>SO-1886</t>
-  </si>
-  <si>
-    <t>PO00443</t>
+Contact: Jakub +44 (0) 7772 728 234</t>
+  </si>
+  <si>
+    <t>SO-2026</t>
+  </si>
+  <si>
+    <t>SO-2024</t>
+  </si>
+  <si>
+    <t>SO-2025</t>
+  </si>
+  <si>
+    <t>SO-2027</t>
+  </si>
+  <si>
+    <t>SO-2028</t>
+  </si>
+  <si>
+    <t>Additional Panels</t>
+  </si>
+  <si>
+    <t>Windmill Court</t>
+  </si>
+  <si>
+    <t>SO-2029</t>
+  </si>
+  <si>
+    <t>SO-2030</t>
+  </si>
+  <si>
+    <t>SO-2031</t>
+  </si>
+  <si>
+    <t>RCS004</t>
+  </si>
+  <si>
+    <t>McAleer &amp; Rushe Contracts UK Ltd
+(For FCS Facades)
+Stroudley Walk
+E3 3EW
+Jakub - +44 (0) 7772 728 234</t>
+  </si>
+  <si>
+    <t>CSK Holes</t>
+  </si>
+  <si>
+    <t>SO-2032</t>
+  </si>
+  <si>
+    <t>Kingspan Subframe</t>
+  </si>
+  <si>
+    <t>Panels Sub-Frame</t>
+  </si>
+  <si>
+    <t>Bifold Door Factory Ltd.
+, Bingley The Common
+, West Drayton, 
+UB7 7HQ
+Contact: Contact: Harj +44 (0) 7951 893 719</t>
+  </si>
+  <si>
+    <t>Skin Door Panel Deenesh Khoosa</t>
+  </si>
+  <si>
+    <t>Grooves</t>
+  </si>
+  <si>
+    <t>PO0211782-1</t>
+  </si>
+  <si>
+    <t>P.O.WMC003</t>
+  </si>
+  <si>
+    <t>SO-2033</t>
+  </si>
+  <si>
+    <t>HA4 8FG</t>
+  </si>
+  <si>
+    <t>EK Construction Limited
+Windmill Court
+West Way
+Ruislip
+HA4 8FG
+Contact: Sebastian +44 (0) 7851 334 852</t>
+  </si>
+  <si>
+    <t>BS14 1FZ</t>
+  </si>
+  <si>
+    <t>MPB Facades Ltd
+BoKlok Housing Site Office
+Airport Road 
+Bristol 
+BS14 1FZ
+Contact: Martin +44 (0) 7725 900 420</t>
+  </si>
+  <si>
+    <t>Additional Profiles</t>
+  </si>
+  <si>
+    <t>Panels &amp; Vents</t>
+  </si>
+  <si>
+    <t>Backlog of Blades</t>
+  </si>
+  <si>
+    <t>Gutter Flashings</t>
+  </si>
+  <si>
+    <t>L12 Copings</t>
+  </si>
+  <si>
+    <t>SO-2035</t>
+  </si>
+  <si>
+    <t>Corner Brackets</t>
+  </si>
+  <si>
+    <t>SO-2036</t>
+  </si>
+  <si>
+    <t>GF L1 Subframe (Additional Brackets + GF L1 E&amp;N Sub-Frame)</t>
+  </si>
+  <si>
+    <t>Southbank University</t>
+  </si>
+  <si>
+    <t>Melliss Avenue</t>
+  </si>
+  <si>
+    <t>SO-2037</t>
+  </si>
+  <si>
+    <t>SO-2038</t>
+  </si>
+  <si>
+    <t>K2-007</t>
+  </si>
+  <si>
+    <t>SE1 0AA</t>
+  </si>
+  <si>
+    <t>TW9 4BZ</t>
+  </si>
+  <si>
+    <t>McAleer &amp; Rushe Site
+(For FCS Facades)
+Mellis Avenue
+Kew
+TW9 4BZ
+Piotr Slowiak +44 (0) 7968 773 582</t>
+  </si>
+  <si>
+    <t>Mock Up</t>
+  </si>
+  <si>
+    <t>London South Bank University,  
+Building K2, 
+103 Borough Road, 
+London,  
+SE1 0AA
+Contact: Kane Cusens – +44 (0) 7944 431 157</t>
+  </si>
+  <si>
+    <t>Lancelote Pl</t>
+  </si>
+  <si>
+    <t>SO-2039</t>
+  </si>
+  <si>
+    <t>SO-2040</t>
+  </si>
+  <si>
+    <t>PO32-33JA</t>
+  </si>
+  <si>
+    <t>Missing Broken Materials</t>
+  </si>
+  <si>
+    <t>Extra Flashing</t>
+  </si>
+  <si>
+    <t>Roytec Ltd
+27 Passey Place,
+London
+Eltham
+SE9 5DA
+Oleg +44 (0) 7453 009 655
+Nick +44 (0) 7447 162 592
+Jurij +44 (0) 7888 504 050</t>
+  </si>
+  <si>
+    <t>SO-2041</t>
+  </si>
+  <si>
+    <t>L7&amp;8 Flashings</t>
+  </si>
+  <si>
+    <t>SO-2042</t>
+  </si>
+  <si>
+    <t>SO-2043</t>
+  </si>
+  <si>
+    <t>E&amp;N Additional Brackets</t>
+  </si>
+  <si>
+    <t>Mock-Up Subframe</t>
+  </si>
+  <si>
+    <t>SO-2044</t>
+  </si>
+  <si>
+    <t>DT521</t>
+  </si>
+  <si>
+    <t>Template (Cill flashing &amp; Perforated Panel)</t>
+  </si>
+  <si>
+    <t>AJE Facades 
+Clarendon Road Block E3
+C/O St William  , Silsoe road 
+Wood Green 
+ N22 6TR 
+Dragos +44 (0) 7719 309 409</t>
+  </si>
+  <si>
+    <t>Amazon SXW2</t>
+  </si>
+  <si>
+    <t>SO-2045</t>
+  </si>
+  <si>
+    <t>KT13 0YU</t>
+  </si>
+  <si>
+    <t>Fascia Panels Prod. 2</t>
+  </si>
+  <si>
+    <t>SO-2046</t>
+  </si>
+  <si>
+    <t>Fairlie Count Flashings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Group
+Ul. Spółdzielcza 4
+64-111 Lipno </t>
+  </si>
+  <si>
+    <t>CSK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64-111 </t>
+  </si>
+  <si>
+    <t>SO-2047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PO00126-593-9-LD </t>
+  </si>
+  <si>
+    <t>Dock Brackets</t>
+  </si>
+  <si>
+    <t>Rose Court</t>
+  </si>
+  <si>
+    <t>SO-2048</t>
+  </si>
+  <si>
+    <t>PO00499</t>
+  </si>
+  <si>
+    <t>HP13 7PL</t>
+  </si>
+  <si>
+    <t>Kladworx Ltd
+Rose Court
+Wenlock Close
+High Wycombe
+Alfie Kelmendi +44 (0) 7908 701 565</t>
+  </si>
+  <si>
+    <t>SO-2049</t>
+  </si>
+  <si>
+    <t>SO-2050</t>
+  </si>
+  <si>
+    <t>AJE facades 
+C/O Formation 
+58 Cherry orchard 
+Croydon 
+CR0 6BA
+Dragos +44 (0) 7719 309 409</t>
+  </si>
+  <si>
+    <t>CR0 6BA</t>
+  </si>
+  <si>
+    <t>Additional Flashings</t>
+  </si>
+  <si>
+    <t>Cills</t>
+  </si>
+  <si>
+    <t>DT19</t>
+  </si>
+  <si>
+    <t>SO-2051</t>
+  </si>
+  <si>
+    <t>McAleer &amp; Rushe Contracts UK Ltd
+(For FCS Facades)
+1 Church Road
+Tunbridge Wells
+Kent, TN1 1PN
+Kontakt: Pawel +44(0) 7590 056 393 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDC Facilities Ltd 
+Cheshire Storage &amp; Interior Solutions Ltd 
+Amazon SXW2 
+Unit A100 
+Brooklands Business Park 
+Vickers Dr N 
+Weybridge 
+KT13 0YU
+Site contact: Courtney 07904 316867 </t>
+  </si>
+  <si>
+    <t>Upton Hospital CDC</t>
+  </si>
+  <si>
+    <t>SO-2052</t>
+  </si>
+  <si>
+    <t>SO-2053</t>
+  </si>
+  <si>
+    <t>SO-2054</t>
+  </si>
+  <si>
+    <t>SO-2055</t>
+  </si>
+  <si>
+    <t>RCS012</t>
+  </si>
+  <si>
+    <t>PO00500</t>
+  </si>
+  <si>
+    <t>PO41325-695-BYS</t>
+  </si>
+  <si>
+    <t>PO0214960-1</t>
+  </si>
+  <si>
+    <t>Additional Top Hats</t>
+  </si>
+  <si>
+    <t>Fascia &amp; Entrance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Big Yellow Storage  Brackets </t>
+  </si>
+  <si>
+    <t>Missing panels, replacement panels</t>
+  </si>
+  <si>
+    <t>Northwood Garage</t>
+  </si>
+  <si>
+    <t>SO-2056</t>
+  </si>
+  <si>
+    <t>Imphouse Ltd
+Chapel Lane
+Merstone
+Isle of Wight
+PO30  3BZ</t>
+  </si>
+  <si>
+    <t>PO30  3BZ</t>
   </si>
   <si>
     <t>SL1 2BJ</t>
   </si>
   <si>
-    <t>Upton Hospital (CDC)
-, Church Street,
- SLough,
- SL1 2BJ
-Alfie Kelmendi +44 (0) 7908 701565</t>
-  </si>
-  <si>
-    <t>SO-1887</t>
-  </si>
-  <si>
-    <t>Spandrel, Arched &amp; Urban Entrance Panels</t>
-  </si>
-  <si>
-    <t>order_id</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>timestamp</t>
-  </si>
-  <si>
-    <t>30/01/2026
-09:55</t>
+    <t>Kladworx Ltd
+CDCUpton Hospital
+Church Street
+SLough
+Berkshire
+SL1 2BJ
+Alfie Kelmendi
++44 07908 701565</t>
+  </si>
+  <si>
+    <t>Cassette Panels &amp; Sub-Frame</t>
+  </si>
+  <si>
+    <t>SO-2057</t>
+  </si>
+  <si>
+    <t>Door Spandrel Panel</t>
+  </si>
+  <si>
+    <t>Delivered</t>
   </si>
 </sst>
 </file>
@@ -1415,14 +1699,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1439,11 +1722,6 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -1493,11 +1771,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1580,42 +1857,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Neutral" xfId="1" builtinId="28"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <font>
         <b/>
@@ -1793,28 +2043,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}" name="Table1" displayName="Table1" ref="A1:Q20" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:Q20" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}"/>
-  <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{867090DC-1FE0-4EF0-A0C0-448920317853}" name="Project" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{ED71812C-E204-4FE0-ADEA-0CD9B3ADA2A3}" name="Project SO" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{32502B80-458D-4EF6-9ABC-03678A6F8302}" name="order_id" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{111DD528-EE5F-4D8B-B63F-9A842570498D}" name="Materials" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{F88C7351-33D9-47AC-88E6-09F8FC43FCF9}" name="status" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{AF541036-9D61-4BFA-9B88-B69C899AAAFF}" name="Phase" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{3C9800BD-A315-48D1-9DB1-AF15B6CE2464}" name="Post Code" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{35381005-95B2-4E9D-9D09-3585A5DE3E35}" name="Delivery Adress" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{21A0DBD3-20BC-48FA-8FF6-DB3AFE9382A5}" name="PO Date" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{3F0B7287-A10E-4CE5-9A48-B72BC577D0D0}" name="Estimated Delivery Date" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{D53CD43D-3F51-4446-BA3F-C95DF42223C1}" name="Current Update" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}" name="Table1" displayName="Table1" ref="A1:P41" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="A1:P41" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}"/>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{867090DC-1FE0-4EF0-A0C0-448920317853}" name="Project" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{ED71812C-E204-4FE0-ADEA-0CD9B3ADA2A3}" name="Project SO" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{32502B80-458D-4EF6-9ABC-03678A6F8302}" name="Client PO" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{111DD528-EE5F-4D8B-B63F-9A842570498D}" name="Materials" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{F88C7351-33D9-47AC-88E6-09F8FC43FCF9}" name="Status" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{AF541036-9D61-4BFA-9B88-B69C899AAAFF}" name="Phase" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{3C9800BD-A315-48D1-9DB1-AF15B6CE2464}" name="Post Code" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{35381005-95B2-4E9D-9D09-3585A5DE3E35}" name=" Tetraclad Ltd," dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{21A0DBD3-20BC-48FA-8FF6-DB3AFE9382A5}" name="PO Date" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{3F0B7287-A10E-4CE5-9A48-B72BC577D0D0}" name="Estimated Delivery Date" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{D53CD43D-3F51-4446-BA3F-C95DF42223C1}" name="Current Update" dataDxfId="5">
       <calculatedColumnFormula>AVERAGE(L2:N2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{6527AB69-9477-41B6-8941-2FE273E12275}" name="Production" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{6436B5E8-E98E-47E2-B70D-DD9AA467C3A5}" name="PPC" dataDxfId="4"/>
-    <tableColumn id="14" xr3:uid="{D893399C-2909-4B8A-9538-32D22CFA1B25}" name="Dispatch" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{F6302424-51FB-45BD-9F34-61C700C8D161}" name="Welded" dataDxfId="2"/>
-    <tableColumn id="16" xr3:uid="{9BE99484-0D9D-4749-B30B-7C533699CF52}" name="Critical Information" dataDxfId="1"/>
-    <tableColumn id="17" xr3:uid="{4C03519C-AB36-480D-97B3-F56FDE4D4B1D}" name="timestamp" dataDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{6527AB69-9477-41B6-8941-2FE273E12275}" name="Production" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{6436B5E8-E98E-47E2-B70D-DD9AA467C3A5}" name="PPC" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{D893399C-2909-4B8A-9538-32D22CFA1B25}" name="Dispatch" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{F6302424-51FB-45BD-9F34-61C700C8D161}" name="Welded" dataDxfId="1"/>
+    <tableColumn id="16" xr3:uid="{9BE99484-0D9D-4749-B30B-7C533699CF52}" name="Critical Information" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2086,7 +2335,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -2105,10 +2354,9 @@
     <col min="14" max="14" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.85546875" style="12" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="23" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>36</v>
       </c>
@@ -2116,13 +2364,13 @@
         <v>35</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>346</v>
+        <v>34</v>
       </c>
       <c r="D1" s="12" t="s">
         <v>33</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>347</v>
+        <v>32</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>31</v>
@@ -2131,7 +2379,7 @@
         <v>30</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>29</v>
+        <v>290</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>28</v>
@@ -2155,41 +2403,36 @@
         <v>187</v>
       </c>
       <c r="P1" s="12" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q1" s="12" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>237</v>
+        <v>270</v>
+      </c>
+      <c r="C2" s="15">
+        <v>2517</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="E2" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="12"/>
-      <c r="G2" t="s">
-        <v>197</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="I2" s="3">
-        <v>45811</v>
-      </c>
-      <c r="J2" s="14">
-        <v>45916</v>
-      </c>
+      <c r="G2" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="I2" s="14">
+        <v>45987</v>
+      </c>
+      <c r="J2" s="14"/>
       <c r="K2" s="23">
         <f t="shared" ref="K2" si="0">AVERAGE(L2:N2)</f>
         <v>3.3333333333333335E-3</v>
@@ -2206,830 +2449,1721 @@
       <c r="O2" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="P2" s="36" t="s">
-        <v>314</v>
-      </c>
-      <c r="Q2" s="16"/>
-    </row>
-    <row r="3" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+      <c r="P2" s="34" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>119</v>
+        <v>301</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>3</v>
       </c>
       <c r="F3" s="12"/>
       <c r="G3" s="12" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="I3" s="14">
-        <v>45875</v>
+        <v>45995</v>
       </c>
       <c r="J3" s="14"/>
       <c r="K3" s="23">
         <f t="shared" ref="K3" si="1">AVERAGE(L3:N3)</f>
-        <v>0.83333333333333337</v>
+        <v>3.3333333333333335E-3</v>
       </c>
       <c r="L3" s="23">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="M3" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" s="23">
-        <v>0.5</v>
+        <v>0</v>
+      </c>
+      <c r="O3" s="12" t="s">
+        <v>188</v>
       </c>
       <c r="P3" s="16"/>
-      <c r="Q3" s="16"/>
-    </row>
-    <row r="4" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:16" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="E4" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="E4" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="12" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="I4" s="14">
-        <v>45877</v>
+        <v>46000</v>
       </c>
       <c r="J4" s="14"/>
-      <c r="K4" s="23">
+      <c r="K4" s="32">
         <f t="shared" ref="K4" si="2">AVERAGE(L4:N4)</f>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L4" s="23">
+      <c r="L4" s="32">
         <v>0.01</v>
       </c>
-      <c r="M4" s="23">
-        <v>0</v>
-      </c>
-      <c r="N4" s="23">
+      <c r="M4" s="32">
+        <v>0</v>
+      </c>
+      <c r="N4" s="32">
         <v>0</v>
       </c>
       <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-    </row>
-    <row r="5" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:16" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>287</v>
+        <v>297</v>
+      </c>
+      <c r="C5" s="15">
+        <v>2622</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="E5" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="G5" s="12" t="s">
+        <v>155</v>
+      </c>
       <c r="H5" s="24" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I5" s="14">
-        <v>45888</v>
+        <v>46009</v>
       </c>
       <c r="J5" s="14"/>
-      <c r="K5" s="23">
-        <f t="shared" ref="K5:K7" si="3">AVERAGE(L5:N5)</f>
+      <c r="K5" s="32">
+        <f t="shared" ref="K5:K6" si="3">AVERAGE(L5:N5)</f>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L5" s="23">
+      <c r="L5" s="32">
         <v>0.01</v>
       </c>
-      <c r="M5" s="23">
-        <v>0</v>
-      </c>
-      <c r="N5" s="23">
-        <v>0</v>
+      <c r="M5" s="32">
+        <v>0</v>
+      </c>
+      <c r="N5" s="32">
+        <v>0</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>188</v>
       </c>
       <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-    </row>
-    <row r="6" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:16" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>159</v>
+        <v>295</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>288</v>
+        <v>298</v>
+      </c>
+      <c r="C6" s="15">
+        <v>2633</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="E6" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="E6" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="G6" s="12" t="s">
+        <v>278</v>
+      </c>
       <c r="H6" s="24" t="s">
-        <v>333</v>
+        <v>279</v>
       </c>
       <c r="I6" s="14">
-        <v>45890</v>
+        <v>46013</v>
       </c>
       <c r="J6" s="14"/>
-      <c r="K6" s="23">
+      <c r="K6" s="32">
         <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L6" s="23">
+      <c r="L6" s="32">
         <v>0.01</v>
       </c>
-      <c r="M6" s="23">
-        <v>0</v>
-      </c>
-      <c r="N6" s="23">
-        <v>0</v>
-      </c>
-      <c r="O6" s="12" t="s">
-        <v>188</v>
+      <c r="M6" s="32">
+        <v>0</v>
+      </c>
+      <c r="N6" s="32">
+        <v>0</v>
       </c>
       <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-    </row>
-    <row r="7" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:16" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>259</v>
+        <v>302</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="C7" s="15">
-        <v>2126</v>
+        <v>312</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>303</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="E7" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="E7" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="12" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="I7" s="14">
-        <v>45891</v>
-      </c>
-      <c r="J7" s="14">
-        <v>45916</v>
-      </c>
-      <c r="K7" s="23">
-        <f t="shared" si="3"/>
-        <v>0.18666666666666668</v>
-      </c>
-      <c r="L7" s="23">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="M7" s="23">
-        <v>0</v>
-      </c>
-      <c r="N7" s="23">
-        <v>0</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="P7" s="36" t="s">
-        <v>314</v>
-      </c>
-      <c r="Q7" s="36" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>46030</v>
+      </c>
+      <c r="J7" s="14"/>
+      <c r="K7" s="32">
+        <f t="shared" ref="K7" si="4">AVERAGE(L7:N7)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L7" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M7" s="32">
+        <v>0</v>
+      </c>
+      <c r="N7" s="32">
+        <v>0</v>
+      </c>
+      <c r="P7" s="16"/>
+    </row>
+    <row r="8" spans="1:16" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="C8" s="15">
-        <v>2136</v>
+        <v>2661</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="E8" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="E8" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="12" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="I8" s="14">
-        <v>45896</v>
-      </c>
-      <c r="J8" s="14">
-        <v>45916</v>
-      </c>
-      <c r="K8" s="23">
-        <f>AVERAGE(L8:N8)</f>
-        <v>0.14666666666666667</v>
-      </c>
-      <c r="L8" s="23">
-        <v>0.44</v>
-      </c>
-      <c r="M8" s="23">
-        <v>0</v>
-      </c>
-      <c r="N8" s="23">
+        <v>46030</v>
+      </c>
+      <c r="J8" s="14"/>
+      <c r="K8" s="32">
+        <f t="shared" ref="K8:K9" si="5">AVERAGE(L8:N8)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L8" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M8" s="32">
+        <v>0</v>
+      </c>
+      <c r="N8" s="32">
         <v>0</v>
       </c>
       <c r="O8" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="P8" s="36" t="s">
-        <v>314</v>
-      </c>
-      <c r="Q8" s="16"/>
-    </row>
-    <row r="9" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+      <c r="P8" s="16"/>
+    </row>
+    <row r="9" spans="1:16" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="C9" s="15">
-        <v>2137</v>
+        <v>2662</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="E9" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="E9" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="H9" s="35" t="s">
-        <v>313</v>
+        <v>269</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>311</v>
       </c>
       <c r="I9" s="14">
-        <v>45896</v>
+        <v>46030</v>
       </c>
       <c r="J9" s="14"/>
-      <c r="K9" s="23">
-        <f>AVERAGE(L9:N9)</f>
+      <c r="K9" s="32">
+        <f t="shared" si="5"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L9" s="23">
+      <c r="L9" s="32">
         <v>0.01</v>
       </c>
-      <c r="M9" s="23">
-        <v>0</v>
-      </c>
-      <c r="N9" s="23">
+      <c r="M9" s="32">
+        <v>0</v>
+      </c>
+      <c r="N9" s="32">
         <v>0</v>
       </c>
       <c r="O9" s="12" t="s">
         <v>188</v>
       </c>
       <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-    </row>
-    <row r="10" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:16" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="C10" s="15">
-        <v>2147</v>
+        <v>2671</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="E10" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="E10" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="12"/>
-      <c r="G10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>307</v>
+      <c r="G10" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>323</v>
       </c>
       <c r="I10" s="14">
-        <v>45902</v>
+        <v>46031</v>
       </c>
       <c r="J10" s="14"/>
-      <c r="K10" s="23">
-        <f t="shared" ref="K10:K12" si="4">AVERAGE(L10:N10)</f>
+      <c r="K10" s="32">
+        <f t="shared" ref="K10:K13" si="6">AVERAGE(L10:N10)</f>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L10" s="23">
+      <c r="L10" s="32">
         <v>0.01</v>
       </c>
-      <c r="M10" s="23">
-        <v>0</v>
-      </c>
-      <c r="N10" s="23">
-        <v>0</v>
-      </c>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-    </row>
-    <row r="11" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="M10" s="32">
+        <v>0</v>
+      </c>
+      <c r="N10" s="32">
+        <v>0</v>
+      </c>
+      <c r="O10" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P10" s="16" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>300</v>
+        <v>314</v>
+      </c>
+      <c r="C11" s="15">
+        <v>2672</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="E11" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="E11" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="12"/>
-      <c r="G11" s="34" t="s">
+      <c r="G11" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="I11" s="14">
+        <v>46031</v>
+      </c>
+      <c r="J11" s="14"/>
+      <c r="K11" s="32">
+        <f t="shared" si="6"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L11" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M11" s="32">
+        <v>0</v>
+      </c>
+      <c r="N11" s="32">
+        <v>0</v>
+      </c>
+      <c r="P11" s="16"/>
+    </row>
+    <row r="12" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="H11" s="35" t="s">
-        <v>301</v>
-      </c>
-      <c r="I11" s="14">
-        <v>45902</v>
-      </c>
-      <c r="J11" s="14"/>
-      <c r="K11" s="23">
-        <f t="shared" si="4"/>
+      <c r="B12" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="I12" s="14">
+        <v>46030</v>
+      </c>
+      <c r="J12" s="14"/>
+      <c r="K12" s="32">
+        <f t="shared" si="6"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L11" s="23">
+      <c r="L12" s="32">
         <v>0.01</v>
       </c>
-      <c r="M11" s="23">
-        <v>0</v>
-      </c>
-      <c r="N11" s="23">
-        <v>0</v>
-      </c>
-      <c r="O11" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-    </row>
-    <row r="12" spans="1:17" ht="75" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="C12" s="15">
-        <v>2151</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="12"/>
-      <c r="G12" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="H12" s="28" t="s">
-        <v>255</v>
-      </c>
-      <c r="I12" s="14">
-        <v>45902</v>
-      </c>
-      <c r="J12" s="14"/>
-      <c r="K12" s="23">
-        <f t="shared" si="4"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L12" s="23">
-        <v>0.01</v>
-      </c>
-      <c r="M12" s="23">
-        <v>0</v>
-      </c>
-      <c r="N12" s="23">
+      <c r="M12" s="32">
+        <v>0</v>
+      </c>
+      <c r="N12" s="32">
         <v>0</v>
       </c>
       <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-    </row>
-    <row r="13" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:16" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>308</v>
+        <v>97</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>310</v>
+        <v>316</v>
+      </c>
+      <c r="C13" s="15">
+        <v>1711019</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="E13" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="E13" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="12" t="s">
-        <v>311</v>
+        <v>98</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="I13" s="14">
-        <v>45905</v>
+        <v>46031</v>
       </c>
       <c r="J13" s="14"/>
-      <c r="K13" s="23">
-        <f t="shared" ref="K13" si="5">AVERAGE(L13:N13)</f>
+      <c r="K13" s="32">
+        <f t="shared" si="6"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L13" s="23">
+      <c r="L13" s="32">
         <v>0.01</v>
       </c>
-      <c r="M13" s="23">
-        <v>0</v>
-      </c>
-      <c r="N13" s="23">
+      <c r="M13" s="32">
+        <v>0</v>
+      </c>
+      <c r="N13" s="32">
         <v>0</v>
       </c>
       <c r="O13" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-    </row>
-    <row r="14" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+      <c r="P13" s="16" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>315</v>
+        <v>217</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>317</v>
+        <v>319</v>
+      </c>
+      <c r="C14" s="15">
+        <v>53</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="E14" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="E14" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="12" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="H14" s="24" t="s">
+        <v>337</v>
+      </c>
+      <c r="I14" s="14">
+        <v>46034</v>
+      </c>
+      <c r="J14" s="14"/>
+      <c r="K14" s="32">
+        <f t="shared" ref="K14:K16" si="7">AVERAGE(L14:N14)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L14" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M14" s="32">
+        <v>0</v>
+      </c>
+      <c r="N14" s="32">
+        <v>0</v>
+      </c>
+      <c r="P14" s="16"/>
+    </row>
+    <row r="15" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="I14" s="14">
-        <v>45905</v>
-      </c>
-      <c r="J14" s="14"/>
-      <c r="K14" s="23">
-        <f t="shared" ref="K14" si="6">AVERAGE(L14:N14)</f>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L14" s="23">
-        <v>0.01</v>
-      </c>
-      <c r="M14" s="23">
-        <v>0</v>
-      </c>
-      <c r="N14" s="23">
-        <v>0</v>
-      </c>
-      <c r="O14" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>321</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>322</v>
-      </c>
       <c r="C15" s="15" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>3</v>
+        <v>339</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>423</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12" t="s">
-        <v>325</v>
+        <v>291</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>324</v>
+        <v>265</v>
       </c>
       <c r="I15" s="14">
-        <v>45905</v>
-      </c>
-      <c r="J15" s="14"/>
-      <c r="K15" s="23">
-        <f t="shared" ref="K15" si="7">AVERAGE(L15:N15)</f>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L15" s="23">
-        <v>0.01</v>
-      </c>
-      <c r="M15" s="23">
-        <v>0</v>
-      </c>
-      <c r="N15" s="23">
-        <v>0</v>
+        <v>46034</v>
+      </c>
+      <c r="J15" s="14">
+        <v>46063</v>
+      </c>
+      <c r="K15" s="32">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="L15" s="32">
+        <v>1</v>
+      </c>
+      <c r="M15" s="32">
+        <v>1</v>
+      </c>
+      <c r="N15" s="32">
+        <v>1</v>
       </c>
       <c r="O15" s="12" t="s">
         <v>188</v>
       </c>
       <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-    </row>
-    <row r="16" spans="1:17" ht="150" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:16" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>229</v>
+        <v>318</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="E16" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E16" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="12" t="s">
-        <v>232</v>
+        <v>334</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="I16" s="14">
-        <v>45908</v>
+        <v>46034</v>
       </c>
       <c r="J16" s="14"/>
-      <c r="K16" s="23">
-        <f t="shared" ref="K16" si="8">AVERAGE(L16:N16)</f>
+      <c r="K16" s="32">
+        <f t="shared" si="7"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L16" s="23">
+      <c r="L16" s="32">
         <v>0.01</v>
       </c>
-      <c r="M16" s="23">
-        <v>0</v>
-      </c>
-      <c r="N16" s="23">
-        <v>0</v>
+      <c r="M16" s="32">
+        <v>0</v>
+      </c>
+      <c r="N16" s="32">
+        <v>0</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>188</v>
       </c>
       <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-    </row>
-    <row r="17" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:16" ht="90" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>97</v>
+        <v>285</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>331</v>
+        <v>325</v>
+      </c>
+      <c r="C17" s="15">
+        <v>2687</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>332</v>
-      </c>
-      <c r="E17" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="E17" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F17" s="12"/>
-      <c r="G17" t="s">
-        <v>98</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>99</v>
+      <c r="G17" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>286</v>
       </c>
       <c r="I17" s="14">
-        <v>45908</v>
+        <v>46035</v>
       </c>
       <c r="J17" s="14"/>
-      <c r="K17" s="23">
-        <f t="shared" ref="K17" si="9">AVERAGE(L17:N17)</f>
+      <c r="K17" s="32">
+        <f t="shared" ref="K17:K18" si="8">AVERAGE(L17:N17)</f>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L17" s="23">
+      <c r="L17" s="32">
         <v>0.01</v>
       </c>
-      <c r="M17" s="23">
-        <v>0</v>
-      </c>
-      <c r="N17" s="23">
+      <c r="M17" s="32">
+        <v>0</v>
+      </c>
+      <c r="N17" s="32">
         <v>0</v>
       </c>
       <c r="O17" s="12" t="s">
         <v>188</v>
       </c>
       <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-    </row>
-    <row r="18" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:16" ht="90" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>334</v>
+        <v>285</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C18" s="15">
-        <v>2183</v>
+        <v>2690</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="E18" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="E18" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="12" t="s">
-        <v>338</v>
+        <v>289</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>337</v>
+        <v>286</v>
       </c>
       <c r="I18" s="14">
-        <v>45909</v>
+        <v>46035</v>
       </c>
       <c r="J18" s="14"/>
-      <c r="K18" s="23">
-        <f t="shared" ref="K18:K19" si="10">AVERAGE(L18:N18)</f>
+      <c r="K18" s="32">
+        <f t="shared" si="8"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L18" s="23">
+      <c r="L18" s="32">
         <v>0.01</v>
       </c>
-      <c r="M18" s="23">
-        <v>0</v>
-      </c>
-      <c r="N18" s="23">
-        <v>0</v>
+      <c r="M18" s="32">
+        <v>0</v>
+      </c>
+      <c r="N18" s="32">
+        <v>0</v>
+      </c>
+      <c r="O18" s="12" t="s">
+        <v>188</v>
       </c>
       <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-    </row>
-    <row r="19" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:16" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>339</v>
+        <v>268</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>341</v>
+        <v>343</v>
+      </c>
+      <c r="C19" s="15">
+        <v>2711</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E19" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="E19" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="12" t="s">
-        <v>342</v>
+        <v>269</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>343</v>
+        <v>311</v>
       </c>
       <c r="I19" s="14">
-        <v>45910</v>
+        <v>46037</v>
       </c>
       <c r="J19" s="14"/>
-      <c r="K19" s="23">
-        <f t="shared" si="10"/>
+      <c r="K19" s="32">
+        <f t="shared" ref="K19" si="9">AVERAGE(L19:N19)</f>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="32">
         <v>0.01</v>
       </c>
-      <c r="M19" s="16">
-        <v>0</v>
-      </c>
-      <c r="N19" s="16">
-        <v>0</v>
-      </c>
-      <c r="O19" s="12" t="s">
-        <v>188</v>
+      <c r="M19" s="32">
+        <v>0</v>
+      </c>
+      <c r="N19" s="32">
+        <v>0</v>
       </c>
       <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-    </row>
-    <row r="20" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:16" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C20" s="15">
-        <v>2190</v>
+        <v>2721</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>345</v>
-      </c>
-      <c r="E20" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="E20" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="12" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="I20" s="14">
-        <v>45910</v>
+        <v>46037</v>
       </c>
       <c r="J20" s="14"/>
-      <c r="K20" s="23">
-        <f t="shared" ref="K20" si="11">AVERAGE(L20:N20)</f>
+      <c r="K20" s="32">
+        <f t="shared" ref="K20" si="10">AVERAGE(L20:N20)</f>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="32">
         <v>0.01</v>
       </c>
-      <c r="M20" s="16">
-        <v>0</v>
-      </c>
-      <c r="N20" s="16">
-        <v>0</v>
+      <c r="M20" s="32">
+        <v>0</v>
+      </c>
+      <c r="N20" s="32">
+        <v>0</v>
+      </c>
+      <c r="O20" s="12" t="s">
+        <v>188</v>
       </c>
       <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
+    </row>
+    <row r="21" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="H21" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="I21" s="14">
+        <v>46038</v>
+      </c>
+      <c r="J21" s="14"/>
+      <c r="K21" s="32">
+        <f t="shared" ref="K21:K22" si="11">AVERAGE(L21:N21)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L21" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M21" s="32">
+        <v>0</v>
+      </c>
+      <c r="N21" s="32">
+        <v>0</v>
+      </c>
+      <c r="P21" s="16"/>
+    </row>
+    <row r="22" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="C22" s="15">
+        <v>2746</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>354</v>
+      </c>
+      <c r="I22" s="14">
+        <v>46042</v>
+      </c>
+      <c r="J22" s="14"/>
+      <c r="K22" s="32">
+        <f t="shared" si="11"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L22" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M22" s="32">
+        <v>0</v>
+      </c>
+      <c r="N22" s="32">
+        <v>0</v>
+      </c>
+      <c r="O22" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P22" s="16"/>
+    </row>
+    <row r="23" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="C23" s="15">
+        <v>2706</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H23" s="24" t="s">
+        <v>323</v>
+      </c>
+      <c r="I23" s="14">
+        <v>46036</v>
+      </c>
+      <c r="J23" s="14"/>
+      <c r="K23" s="32">
+        <f t="shared" ref="K23:K24" si="12">AVERAGE(L23:N23)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L23" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M23" s="32">
+        <v>0</v>
+      </c>
+      <c r="N23" s="32">
+        <v>0</v>
+      </c>
+      <c r="O23" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P23" s="16"/>
+    </row>
+    <row r="24" spans="1:16" ht="120" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>363</v>
+      </c>
+      <c r="I24" s="14">
+        <v>46043</v>
+      </c>
+      <c r="J24" s="14"/>
+      <c r="K24" s="32">
+        <f t="shared" si="12"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L24" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M24" s="32">
+        <v>0</v>
+      </c>
+      <c r="N24" s="32">
+        <v>0</v>
+      </c>
+      <c r="P24" s="16"/>
+    </row>
+    <row r="25" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="C25" s="15">
+        <v>2781</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="H25" s="24" t="s">
+        <v>399</v>
+      </c>
+      <c r="I25" s="14">
+        <v>46045</v>
+      </c>
+      <c r="J25" s="14"/>
+      <c r="K25" s="32">
+        <f t="shared" ref="K25" si="13">AVERAGE(L25:N25)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L25" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M25" s="32">
+        <v>0</v>
+      </c>
+      <c r="N25" s="32">
+        <v>0</v>
+      </c>
+      <c r="O25" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P25" s="16"/>
+    </row>
+    <row r="26" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="C26" s="15">
+        <v>2787</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="H26" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="I26" s="14">
+        <v>46045</v>
+      </c>
+      <c r="J26" s="14"/>
+      <c r="K26" s="32">
+        <f t="shared" ref="K26:K27" si="14">AVERAGE(L26:N26)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L26" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M26" s="32">
+        <v>0</v>
+      </c>
+      <c r="N26" s="32">
+        <v>0</v>
+      </c>
+      <c r="O26" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P26" s="16"/>
+    </row>
+    <row r="27" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="C27" s="15">
+        <v>2800</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="H27" s="24" t="s">
+        <v>354</v>
+      </c>
+      <c r="I27" s="14">
+        <v>46049</v>
+      </c>
+      <c r="J27" s="14"/>
+      <c r="K27" s="32">
+        <f t="shared" si="14"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L27" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M27" s="32">
+        <v>0</v>
+      </c>
+      <c r="N27" s="32">
+        <v>0</v>
+      </c>
+      <c r="P27" s="16"/>
+    </row>
+    <row r="28" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="H28" s="24" t="s">
+        <v>373</v>
+      </c>
+      <c r="I28" s="14">
+        <v>46050</v>
+      </c>
+      <c r="J28" s="14"/>
+      <c r="K28" s="32">
+        <f t="shared" ref="K28" si="15">AVERAGE(L28:N28)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L28" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M28" s="32">
+        <v>0</v>
+      </c>
+      <c r="N28" s="32">
+        <v>0</v>
+      </c>
+      <c r="O28" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P28" s="16"/>
+    </row>
+    <row r="29" spans="1:16" ht="150" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="H29" s="24" t="s">
+        <v>400</v>
+      </c>
+      <c r="I29" s="14">
+        <v>46051</v>
+      </c>
+      <c r="J29" s="14"/>
+      <c r="K29" s="32">
+        <f t="shared" ref="K29" si="16">AVERAGE(L29:N29)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L29" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M29" s="32">
+        <v>0</v>
+      </c>
+      <c r="N29" s="32">
+        <v>0</v>
+      </c>
+      <c r="P29" s="16"/>
+    </row>
+    <row r="30" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="C30" s="15">
+        <v>2814</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" s="24" t="s">
+        <v>323</v>
+      </c>
+      <c r="I30" s="14">
+        <v>46051</v>
+      </c>
+      <c r="J30" s="14"/>
+      <c r="K30" s="32">
+        <f t="shared" ref="K30" si="17">AVERAGE(L30:N30)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L30" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M30" s="32">
+        <v>0</v>
+      </c>
+      <c r="N30" s="32">
+        <v>0</v>
+      </c>
+      <c r="P30" s="16"/>
+    </row>
+    <row r="31" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="H31" s="24" t="s">
+        <v>380</v>
+      </c>
+      <c r="I31" s="14">
+        <v>46055</v>
+      </c>
+      <c r="J31" s="14"/>
+      <c r="K31" s="32">
+        <f t="shared" ref="K31" si="18">AVERAGE(L31:N31)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L31" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M31" s="32">
+        <v>0</v>
+      </c>
+      <c r="N31" s="32">
+        <v>0</v>
+      </c>
+      <c r="O31" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="P31" s="16"/>
+    </row>
+    <row r="32" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="H32" s="24" t="s">
+        <v>390</v>
+      </c>
+      <c r="I32" s="14">
+        <v>46055</v>
+      </c>
+      <c r="J32" s="14"/>
+      <c r="K32" s="32">
+        <f t="shared" ref="K32" si="19">AVERAGE(L32:N32)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L32" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M32" s="32">
+        <v>0</v>
+      </c>
+      <c r="N32" s="32">
+        <v>0</v>
+      </c>
+      <c r="O32" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P32" s="16"/>
+    </row>
+    <row r="33" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="C33" s="15">
+        <v>2836</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="H33" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="I33" s="14">
+        <v>46056</v>
+      </c>
+      <c r="J33" s="14"/>
+      <c r="K33" s="32">
+        <f t="shared" ref="K33:K34" si="20">AVERAGE(L33:N33)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L33" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M33" s="32">
+        <v>0</v>
+      </c>
+      <c r="N33" s="32">
+        <v>0</v>
+      </c>
+      <c r="P33" s="16"/>
+    </row>
+    <row r="34" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="H34" s="24" t="s">
+        <v>393</v>
+      </c>
+      <c r="I34" s="14">
+        <v>46056</v>
+      </c>
+      <c r="J34" s="14"/>
+      <c r="K34" s="32">
+        <f t="shared" si="20"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L34" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M34" s="32">
+        <v>0</v>
+      </c>
+      <c r="N34" s="32">
+        <v>0</v>
+      </c>
+      <c r="O34" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="P34" s="16"/>
+    </row>
+    <row r="35" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="H35" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="I35" s="14">
+        <v>46058</v>
+      </c>
+      <c r="J35" s="14"/>
+      <c r="K35" s="32">
+        <f t="shared" ref="K35:K39" si="21">AVERAGE(L35:N35)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L35" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M35" s="32">
+        <v>0</v>
+      </c>
+      <c r="N35" s="32">
+        <v>0</v>
+      </c>
+      <c r="P35" s="16"/>
+    </row>
+    <row r="36" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="C36" s="15">
+        <v>2858</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="H36" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="I36" s="14">
+        <v>46059</v>
+      </c>
+      <c r="J36" s="14"/>
+      <c r="K36" s="32">
+        <f t="shared" si="21"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L36" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M36" s="32">
+        <v>0</v>
+      </c>
+      <c r="N36" s="32">
+        <v>0</v>
+      </c>
+      <c r="O36" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P36" s="16"/>
+    </row>
+    <row r="37" spans="1:16" ht="120" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="H37" s="24" t="s">
+        <v>419</v>
+      </c>
+      <c r="I37" s="14">
+        <v>46059</v>
+      </c>
+      <c r="J37" s="14"/>
+      <c r="K37" s="32">
+        <f t="shared" si="21"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L37" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M37" s="32">
+        <v>0</v>
+      </c>
+      <c r="N37" s="32">
+        <v>0</v>
+      </c>
+      <c r="O37" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P37" s="16"/>
+    </row>
+    <row r="38" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="H38" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="I38" s="14">
+        <v>46059</v>
+      </c>
+      <c r="J38" s="14"/>
+      <c r="K38" s="32">
+        <f t="shared" si="21"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L38" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M38" s="32">
+        <v>0</v>
+      </c>
+      <c r="N38" s="32">
+        <v>0</v>
+      </c>
+      <c r="P38" s="16"/>
+    </row>
+    <row r="39" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="H39" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="I39" s="14">
+        <v>46059</v>
+      </c>
+      <c r="J39" s="14"/>
+      <c r="K39" s="32">
+        <f t="shared" si="21"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L39" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M39" s="32">
+        <v>0</v>
+      </c>
+      <c r="N39" s="32">
+        <v>0</v>
+      </c>
+      <c r="P39" s="16"/>
+    </row>
+    <row r="40" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="H40" s="24" t="s">
+        <v>416</v>
+      </c>
+      <c r="I40" s="14"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="32">
+        <f t="shared" ref="K40" si="22">AVERAGE(L40:N40)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L40" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M40" s="32">
+        <v>0</v>
+      </c>
+      <c r="N40" s="32">
+        <v>0</v>
+      </c>
+      <c r="P40" s="16"/>
+    </row>
+    <row r="41" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="A41" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="C41" s="15">
+        <v>2863</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="H41" s="24" t="s">
+        <v>399</v>
+      </c>
+      <c r="I41" s="14">
+        <v>46062</v>
+      </c>
+      <c r="J41" s="14"/>
+      <c r="K41" s="32">
+        <f t="shared" ref="K41" si="23">AVERAGE(L41:N41)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L41" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M41" s="32">
+        <v>0</v>
+      </c>
+      <c r="N41" s="32">
+        <v>0</v>
+      </c>
+      <c r="P41" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{26F360D1-F7D8-4390-9C80-BDD8F9AF104F}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3054,7 +4188,7 @@
     <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="240" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="165" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>107</v>
       </c>
@@ -3081,7 +4215,7 @@
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="1">
-        <f t="shared" ref="K1" si="0">AVERAGE(L1:N1)</f>
+        <f>AVERAGE(L1:N1)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L1" s="1">
@@ -3094,7 +4228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="150" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="165" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>107</v>
       </c>
@@ -3234,29 +4368,29 @@
         <v>209</v>
       </c>
       <c r="H9" s="28" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="150" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="180" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="G11" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3297,7 +4431,7 @@
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="1">
-        <f t="shared" ref="K1" si="0">AVERAGE(L1:N1)</f>
+        <f>AVERAGE(L1:N1)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L1" s="1">
@@ -3398,7 +4532,7 @@
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="1">
-        <f t="shared" ref="K1:K2" si="0">AVERAGE(L1:N1)</f>
+        <f>AVERAGE(L1:N1)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L1" s="1">
@@ -3438,7 +4572,7 @@
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(L2:N2)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L2" s="1">
@@ -3477,7 +4611,7 @@
         <v>45715</v>
       </c>
       <c r="K3" s="1">
-        <f t="shared" ref="K3" si="1">AVERAGE(L3:N3)</f>
+        <f>AVERAGE(L3:N3)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L3" s="1">
@@ -3506,10 +4640,10 @@
     </row>
     <row r="5" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="G5" s="18" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3523,7 +4657,7 @@
   <dimension ref="A1:N1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="135" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="150" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>68</v>
       </c>
@@ -3550,7 +4684,7 @@
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="1">
-        <f t="shared" ref="K1" si="0">AVERAGE(L1:N1)</f>
+        <f>AVERAGE(L1:N1)</f>
         <v>0</v>
       </c>
       <c r="L1" s="1">
@@ -3603,7 +4737,7 @@
         <v>45576</v>
       </c>
       <c r="K1" s="1">
-        <f t="shared" ref="K1" si="0">AVERAGE(L1:N1)</f>
+        <f>AVERAGE(L1:N1)</f>
         <v>1.6666666666666666E-2</v>
       </c>
       <c r="L1" s="1">
@@ -3676,7 +4810,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817F5A1D-BC75-4FA1-87DF-3A3A945A281D}">
   <sheetPr codeName="Sheet12"/>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
@@ -3735,7 +4869,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>51</v>
       </c>
@@ -3777,7 +4911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>52</v>
       </c>
@@ -3819,7 +4953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -3846,7 +4980,7 @@
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="1">
-        <f t="shared" ref="K5" si="0">AVERAGE(L5:N5)</f>
+        <f>AVERAGE(L5:N5)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L5" s="1">
@@ -3859,7 +4993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="135" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>113</v>
       </c>
@@ -3901,7 +5035,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -3943,7 +5077,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>52</v>
       </c>
@@ -3985,7 +5119,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="135" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>210</v>
       </c>
@@ -3996,7 +5130,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="150" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>211</v>
       </c>
@@ -4027,7 +5161,7 @@
         <v>215</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="I11" t="s">
         <v>216</v>
@@ -4036,7 +5170,7 @@
         <v>45804</v>
       </c>
       <c r="K11" s="1">
-        <f t="shared" ref="K11" si="1">AVERAGE(L11:N11)</f>
+        <f>AVERAGE(L11:N11)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L11" s="1">
@@ -4048,6 +5182,51 @@
       <c r="N11" s="1">
         <v>0</v>
       </c>
+    </row>
+    <row r="12" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+      <c r="A12" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="B12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C12">
+        <v>2547</v>
+      </c>
+      <c r="D12" t="s">
+        <v>276</v>
+      </c>
+      <c r="E12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" t="s">
+        <v>277</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I12" s="3">
+        <v>45993</v>
+      </c>
+      <c r="J12" s="3">
+        <v>46003</v>
+      </c>
+      <c r="K12" s="1">
+        <f>AVERAGE(L12:N12)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H17" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4271,13 +5450,13 @@
     </row>
     <row r="7" spans="1:23" ht="195" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -4450,38 +5629,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44653D23-C67E-4CA8-ABB7-D3B8921C4390}">
+  <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" ht="150" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E1" s="30" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="18"/>
       <c r="G1" s="18" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="H1" s="26" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="I1" s="31">
         <v>45853</v>
       </c>
       <c r="J1" s="31"/>
       <c r="K1" s="32">
-        <f t="shared" ref="K1" si="0">AVERAGE(L1:N1)</f>
+        <f>AVERAGE(L1:N1)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L1" s="32">
@@ -4661,7 +5841,7 @@
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="16">
-        <f t="shared" ref="K5" si="0">AVERAGE(L5:N5)</f>
+        <f>AVERAGE(L5:N5)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L5" s="16">
@@ -4915,10 +6095,10 @@
     </row>
     <row r="3" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="G3" s="18" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -4928,18 +6108,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE3D3346-1B18-4457-8F16-B2D49D7FEC34}">
+  <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" ht="105" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="270" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D1" s="12"/>
       <c r="E1" s="22" t="s">
@@ -4947,15 +6128,15 @@
       </c>
       <c r="F1" s="12"/>
       <c r="G1" s="12" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="H1" s="24" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I1" s="14"/>
       <c r="J1" s="14"/>
       <c r="K1" s="23">
-        <f t="shared" ref="K1" si="0">AVERAGE(L1:N1)</f>
+        <f>AVERAGE(L1:N1)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L1" s="23">
@@ -4976,6 +6157,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7238AED6-2070-4724-B092-F36A90711D6D}">
+  <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5016,12 +6198,12 @@
         <v>232</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="16">
-        <f t="shared" ref="K1" si="0">AVERAGE(L1:N1)</f>
+        <f>AVERAGE(L1:N1)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L1" s="16">
@@ -5037,18 +6219,18 @@
     </row>
     <row r="2" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="G2" s="20" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="105" x14ac:dyDescent="0.25">
       <c r="G3" s="20" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -5058,6 +6240,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA38C61B-46D5-4EDA-ACDD-706BC2FB7AE6}">
+  <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5088,7 +6271,7 @@
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="16">
-        <f t="shared" ref="K1" si="0">AVERAGE(L1:N1)</f>
+        <f>AVERAGE(L1:N1)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L1" s="16">
@@ -5109,6 +6292,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E216D8F-1A92-41EC-B1E9-352A8F5FBBC6}">
+  <sheetPr codeName="Sheet22"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5168,7 +6352,7 @@
       </c>
       <c r="P1" s="3"/>
       <c r="Q1" s="10">
-        <f t="shared" ref="Q1" si="0">AVERAGE(R1:T1)</f>
+        <f>AVERAGE(R1:T1)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="R1" s="10">
@@ -5232,7 +6416,7 @@
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="1">
-        <f t="shared" ref="K1" si="0">AVERAGE(L1:N1)</f>
+        <f>AVERAGE(L1:N1)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L1" s="1">
@@ -5256,7 +6440,7 @@
   <dimension ref="A1:N1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="165" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>122</v>
       </c>

--- a/Client Information App.xlsx
+++ b/Client Information App.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ACL Operation\1. Operation Documents\3. Project Cordination\5. Data Analytics\Power Bi Projects\1. PB2401 Client Information\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aryte\PycharmProjects\AlucladApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4375D1-9E29-40F4-AA9C-F81814B2EFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8A6DCF-C95E-45F4-8AB1-B380F5786414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="768" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="427">
   <si>
     <t>Ready to dispatch</t>
   </si>
@@ -1148,9 +1148,6 @@
   </si>
   <si>
     <t>SE1 7AF</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tetraclad Ltd,</t>
   </si>
   <si>
     <t>DA10 0B</t>
@@ -1640,6 +1637,19 @@
   </si>
   <si>
     <t>Delivered</t>
+  </si>
+  <si>
+    <t>order_id</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>timestamp</t>
+  </si>
+  <si>
+    <t>10/02/2026
+09:29</t>
   </si>
 </sst>
 </file>
@@ -1774,7 +1784,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1861,11 +1871,35 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="19">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2043,27 +2077,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}" name="Table1" displayName="Table1" ref="A1:P41" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
-  <autoFilter ref="A1:P41" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}"/>
-  <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{867090DC-1FE0-4EF0-A0C0-448920317853}" name="Project" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{ED71812C-E204-4FE0-ADEA-0CD9B3ADA2A3}" name="Project SO" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{32502B80-458D-4EF6-9ABC-03678A6F8302}" name="Client PO" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{111DD528-EE5F-4D8B-B63F-9A842570498D}" name="Materials" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{F88C7351-33D9-47AC-88E6-09F8FC43FCF9}" name="Status" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{AF541036-9D61-4BFA-9B88-B69C899AAAFF}" name="Phase" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{3C9800BD-A315-48D1-9DB1-AF15B6CE2464}" name="Post Code" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{35381005-95B2-4E9D-9D09-3585A5DE3E35}" name=" Tetraclad Ltd," dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{21A0DBD3-20BC-48FA-8FF6-DB3AFE9382A5}" name="PO Date" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{3F0B7287-A10E-4CE5-9A48-B72BC577D0D0}" name="Estimated Delivery Date" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{D53CD43D-3F51-4446-BA3F-C95DF42223C1}" name="Current Update" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}" name="Table1" displayName="Table1" ref="A1:Q41" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+  <autoFilter ref="A1:Q41" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}"/>
+  <tableColumns count="17">
+    <tableColumn id="1" xr3:uid="{867090DC-1FE0-4EF0-A0C0-448920317853}" name="Project" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{ED71812C-E204-4FE0-ADEA-0CD9B3ADA2A3}" name="Project SO" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{32502B80-458D-4EF6-9ABC-03678A6F8302}" name="order_id" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{111DD528-EE5F-4D8B-B63F-9A842570498D}" name="Materials" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{F88C7351-33D9-47AC-88E6-09F8FC43FCF9}" name="status" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{AF541036-9D61-4BFA-9B88-B69C899AAAFF}" name="Phase" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{3C9800BD-A315-48D1-9DB1-AF15B6CE2464}" name="Post Code" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{35381005-95B2-4E9D-9D09-3585A5DE3E35}" name="Delivery Adress" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{21A0DBD3-20BC-48FA-8FF6-DB3AFE9382A5}" name="PO Date" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{3F0B7287-A10E-4CE5-9A48-B72BC577D0D0}" name="Estimated Delivery Date" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{D53CD43D-3F51-4446-BA3F-C95DF42223C1}" name="Current Update" dataDxfId="6">
       <calculatedColumnFormula>AVERAGE(L2:N2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{6527AB69-9477-41B6-8941-2FE273E12275}" name="Production" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{6436B5E8-E98E-47E2-B70D-DD9AA467C3A5}" name="PPC" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{D893399C-2909-4B8A-9538-32D22CFA1B25}" name="Dispatch" dataDxfId="2"/>
-    <tableColumn id="15" xr3:uid="{F6302424-51FB-45BD-9F34-61C700C8D161}" name="Welded" dataDxfId="1"/>
-    <tableColumn id="16" xr3:uid="{9BE99484-0D9D-4749-B30B-7C533699CF52}" name="Critical Information" dataDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{6527AB69-9477-41B6-8941-2FE273E12275}" name="Production" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{6436B5E8-E98E-47E2-B70D-DD9AA467C3A5}" name="PPC" dataDxfId="4"/>
+    <tableColumn id="14" xr3:uid="{D893399C-2909-4B8A-9538-32D22CFA1B25}" name="Dispatch" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{F6302424-51FB-45BD-9F34-61C700C8D161}" name="Welded" dataDxfId="2"/>
+    <tableColumn id="16" xr3:uid="{9BE99484-0D9D-4749-B30B-7C533699CF52}" name="Critical Information" dataDxfId="1"/>
+    <tableColumn id="17" xr3:uid="{294DD3E6-5EEC-42DD-AE99-1AC9AB8E1DEE}" name="timestamp" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2335,7 +2370,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -2354,9 +2389,10 @@
     <col min="14" max="14" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.85546875" style="12" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="23" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>36</v>
       </c>
@@ -2364,13 +2400,13 @@
         <v>35</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>34</v>
+        <v>423</v>
       </c>
       <c r="D1" s="12" t="s">
         <v>33</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>32</v>
+        <v>424</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>31</v>
@@ -2379,7 +2415,7 @@
         <v>30</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>290</v>
+        <v>29</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>28</v>
@@ -2405,8 +2441,11 @@
       <c r="P1" s="12" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q1" s="12" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>255</v>
       </c>
@@ -2427,7 +2466,7 @@
         <v>155</v>
       </c>
       <c r="H2" s="24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I2" s="14">
         <v>45987</v>
@@ -2452,8 +2491,9 @@
       <c r="P2" s="34" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q2" s="16"/>
+    </row>
+    <row r="3" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>281</v>
       </c>
@@ -2464,7 +2504,7 @@
         <v>282</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>3</v>
@@ -2497,8 +2537,9 @@
         <v>188</v>
       </c>
       <c r="P3" s="16"/>
-    </row>
-    <row r="4" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q3" s="16"/>
+    </row>
+    <row r="4" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>264</v>
       </c>
@@ -2506,7 +2547,7 @@
         <v>287</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>288</v>
@@ -2516,10 +2557,10 @@
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I4" s="14">
         <v>46000</v>
@@ -2539,19 +2580,20 @@
         <v>0</v>
       </c>
       <c r="P4" s="16"/>
-    </row>
-    <row r="5" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q4" s="16"/>
+    </row>
+    <row r="5" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>255</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C5" s="15">
         <v>2622</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E5" s="20" t="s">
         <v>3</v>
@@ -2561,7 +2603,7 @@
         <v>155</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I5" s="14">
         <v>46009</v>
@@ -2584,19 +2626,20 @@
         <v>188</v>
       </c>
       <c r="P5" s="16"/>
-    </row>
-    <row r="6" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q5" s="16"/>
+    </row>
+    <row r="6" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C6" s="15">
         <v>2633</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>3</v>
@@ -2626,29 +2669,30 @@
         <v>0</v>
       </c>
       <c r="P6" s="16"/>
-    </row>
-    <row r="7" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q6" s="16"/>
+    </row>
+    <row r="7" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>303</v>
-      </c>
       <c r="D7" s="12" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="H7" s="24" t="s">
         <v>304</v>
-      </c>
-      <c r="H7" s="24" t="s">
-        <v>305</v>
       </c>
       <c r="I7" s="14">
         <v>46030</v>
@@ -2668,19 +2712,20 @@
         <v>0</v>
       </c>
       <c r="P7" s="16"/>
-    </row>
-    <row r="8" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q7" s="16"/>
+    </row>
+    <row r="8" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>268</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C8" s="15">
         <v>2661</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>3</v>
@@ -2690,7 +2735,7 @@
         <v>269</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I8" s="14">
         <v>46030</v>
@@ -2713,19 +2758,20 @@
         <v>188</v>
       </c>
       <c r="P8" s="16"/>
-    </row>
-    <row r="9" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q8" s="16"/>
+    </row>
+    <row r="9" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>268</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C9" s="15">
         <v>2662</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>3</v>
@@ -2735,7 +2781,7 @@
         <v>269</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I9" s="14">
         <v>46030</v>
@@ -2758,19 +2804,20 @@
         <v>188</v>
       </c>
       <c r="P9" s="16"/>
-    </row>
-    <row r="10" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q9" s="16"/>
+    </row>
+    <row r="10" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C10" s="15">
         <v>2671</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>3</v>
@@ -2780,7 +2827,7 @@
         <v>53</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I10" s="14">
         <v>46031</v>
@@ -2803,21 +2850,22 @@
         <v>188</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+      <c r="Q10" s="16"/>
+    </row>
+    <row r="11" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>268</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C11" s="15">
         <v>2672</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E11" s="20" t="s">
         <v>3</v>
@@ -2827,7 +2875,7 @@
         <v>269</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I11" s="14">
         <v>46031</v>
@@ -2847,29 +2895,30 @@
         <v>0</v>
       </c>
       <c r="P11" s="16"/>
-    </row>
-    <row r="12" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q11" s="16"/>
+    </row>
+    <row r="12" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E12" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="H12" s="24" t="s">
         <v>304</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>305</v>
       </c>
       <c r="I12" s="14">
         <v>46030</v>
@@ -2889,19 +2938,20 @@
         <v>0</v>
       </c>
       <c r="P12" s="16"/>
-    </row>
-    <row r="13" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q12" s="16"/>
+    </row>
+    <row r="13" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>97</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C13" s="15">
         <v>1711019</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E13" s="20" t="s">
         <v>3</v>
@@ -2911,7 +2961,7 @@
         <v>98</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I13" s="14">
         <v>46031</v>
@@ -2934,31 +2984,32 @@
         <v>188</v>
       </c>
       <c r="P13" s="16" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="Q13" s="16"/>
+    </row>
+    <row r="14" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>217</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C14" s="15">
         <v>53</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E14" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="H14" s="24" t="s">
         <v>336</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>337</v>
       </c>
       <c r="I14" s="14">
         <v>46034</v>
@@ -2978,26 +3029,27 @@
         <v>0</v>
       </c>
       <c r="P14" s="16"/>
-    </row>
-    <row r="15" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q14" s="16"/>
+    </row>
+    <row r="15" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H15" s="24" t="s">
         <v>265</v>
@@ -3025,29 +3077,32 @@
         <v>188</v>
       </c>
       <c r="P15" s="16"/>
-    </row>
-    <row r="16" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q15" s="36" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E16" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="H16" s="24" t="s">
         <v>334</v>
-      </c>
-      <c r="H16" s="24" t="s">
-        <v>335</v>
       </c>
       <c r="I16" s="14">
         <v>46034</v>
@@ -3070,19 +3125,20 @@
         <v>188</v>
       </c>
       <c r="P16" s="16"/>
-    </row>
-    <row r="17" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q16" s="16"/>
+    </row>
+    <row r="17" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>285</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C17" s="15">
         <v>2687</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E17" s="20" t="s">
         <v>3</v>
@@ -3115,19 +3171,20 @@
         <v>188</v>
       </c>
       <c r="P17" s="16"/>
-    </row>
-    <row r="18" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q17" s="16"/>
+    </row>
+    <row r="18" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>285</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C18" s="15">
         <v>2690</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E18" s="20" t="s">
         <v>3</v>
@@ -3160,19 +3217,20 @@
         <v>188</v>
       </c>
       <c r="P18" s="16"/>
-    </row>
-    <row r="19" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q18" s="16"/>
+    </row>
+    <row r="19" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>268</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C19" s="15">
         <v>2711</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E19" s="20" t="s">
         <v>3</v>
@@ -3182,7 +3240,7 @@
         <v>269</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I19" s="14">
         <v>46037</v>
@@ -3202,19 +3260,20 @@
         <v>0</v>
       </c>
       <c r="P19" s="16"/>
-    </row>
-    <row r="20" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q19" s="16"/>
+    </row>
+    <row r="20" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>268</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C20" s="15">
         <v>2721</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E20" s="20" t="s">
         <v>3</v>
@@ -3224,7 +3283,7 @@
         <v>269</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I20" s="14">
         <v>46037</v>
@@ -3247,16 +3306,17 @@
         <v>188</v>
       </c>
       <c r="P20" s="16"/>
-    </row>
-    <row r="21" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+      <c r="Q20" s="16"/>
+    </row>
+    <row r="21" spans="1:17" ht="105" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>106</v>
@@ -3266,10 +3326,10 @@
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="12" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I21" s="14">
         <v>46038</v>
@@ -3289,29 +3349,30 @@
         <v>0</v>
       </c>
       <c r="P21" s="16"/>
-    </row>
-    <row r="22" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q21" s="16"/>
+    </row>
+    <row r="22" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C22" s="15">
         <v>2746</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E22" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="H22" s="24" t="s">
         <v>353</v>
-      </c>
-      <c r="H22" s="24" t="s">
-        <v>354</v>
       </c>
       <c r="I22" s="14">
         <v>46042</v>
@@ -3334,19 +3395,20 @@
         <v>188</v>
       </c>
       <c r="P22" s="16"/>
-    </row>
-    <row r="23" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q22" s="16"/>
+    </row>
+    <row r="23" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C23" s="15">
         <v>2706</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E23" s="20" t="s">
         <v>3</v>
@@ -3356,7 +3418,7 @@
         <v>53</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I23" s="14">
         <v>46036</v>
@@ -3379,19 +3441,20 @@
         <v>188</v>
       </c>
       <c r="P23" s="16"/>
-    </row>
-    <row r="24" spans="1:16" ht="120" x14ac:dyDescent="0.25">
+      <c r="Q23" s="16"/>
+    </row>
+    <row r="24" spans="1:17" ht="120" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B24" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="C24" s="15" t="s">
-        <v>360</v>
-      </c>
       <c r="D24" s="12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E24" s="20" t="s">
         <v>3</v>
@@ -3401,7 +3464,7 @@
         <v>238</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I24" s="14">
         <v>46043</v>
@@ -3421,19 +3484,20 @@
         <v>0</v>
       </c>
       <c r="P24" s="16"/>
-    </row>
-    <row r="25" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q24" s="16"/>
+    </row>
+    <row r="25" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>91</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C25" s="15">
         <v>2781</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E25" s="20" t="s">
         <v>3</v>
@@ -3443,7 +3507,7 @@
         <v>157</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I25" s="14">
         <v>46045</v>
@@ -3466,19 +3530,20 @@
         <v>188</v>
       </c>
       <c r="P25" s="16"/>
-    </row>
-    <row r="26" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q25" s="16"/>
+    </row>
+    <row r="26" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>268</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C26" s="15">
         <v>2787</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E26" s="20" t="s">
         <v>3</v>
@@ -3488,7 +3553,7 @@
         <v>269</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I26" s="14">
         <v>46045</v>
@@ -3511,29 +3576,30 @@
         <v>188</v>
       </c>
       <c r="P26" s="16"/>
-    </row>
-    <row r="27" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q26" s="16"/>
+    </row>
+    <row r="27" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C27" s="15">
         <v>2800</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E27" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F27" s="12"/>
       <c r="G27" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="H27" s="24" t="s">
         <v>353</v>
-      </c>
-      <c r="H27" s="24" t="s">
-        <v>354</v>
       </c>
       <c r="I27" s="14">
         <v>46049</v>
@@ -3553,19 +3619,20 @@
         <v>0</v>
       </c>
       <c r="P27" s="16"/>
-    </row>
-    <row r="28" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q27" s="16"/>
+    </row>
+    <row r="28" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>17</v>
       </c>
       <c r="B28" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="C28" s="15" t="s">
         <v>370</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="D28" s="12" t="s">
         <v>371</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>372</v>
       </c>
       <c r="E28" s="20" t="s">
         <v>3</v>
@@ -3575,7 +3642,7 @@
         <v>189</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I28" s="14">
         <v>46050</v>
@@ -3598,29 +3665,30 @@
         <v>188</v>
       </c>
       <c r="P28" s="16"/>
-    </row>
-    <row r="29" spans="1:16" ht="150" x14ac:dyDescent="0.25">
+      <c r="Q28" s="16"/>
+    </row>
+    <row r="29" spans="1:17" ht="150" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B29" s="12" t="s">
         <v>374</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>375</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>67</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E29" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F29" s="12"/>
       <c r="G29" s="12" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H29" s="24" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I29" s="14">
         <v>46051</v>
@@ -3640,19 +3708,20 @@
         <v>0</v>
       </c>
       <c r="P29" s="16"/>
-    </row>
-    <row r="30" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q29" s="16"/>
+    </row>
+    <row r="30" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C30" s="15">
         <v>2814</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E30" s="20" t="s">
         <v>3</v>
@@ -3662,7 +3731,7 @@
         <v>53</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I30" s="14">
         <v>46051</v>
@@ -3682,29 +3751,30 @@
         <v>0</v>
       </c>
       <c r="P30" s="16"/>
-    </row>
-    <row r="31" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q30" s="16"/>
+    </row>
+    <row r="31" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
         <v>281</v>
       </c>
       <c r="B31" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="C31" s="15" t="s">
         <v>383</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="D31" s="12" t="s">
         <v>384</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>385</v>
       </c>
       <c r="E31" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F31" s="12"/>
       <c r="G31" s="12" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I31" s="14">
         <v>46055</v>
@@ -3724,19 +3794,20 @@
         <v>0</v>
       </c>
       <c r="O31" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="P31" s="16"/>
-    </row>
-    <row r="32" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q31" s="16"/>
+    </row>
+    <row r="32" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="B32" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="C32" s="15" t="s">
         <v>387</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>388</v>
       </c>
       <c r="D32" s="12" t="s">
         <v>87</v>
@@ -3746,10 +3817,10 @@
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="H32" s="24" t="s">
         <v>389</v>
-      </c>
-      <c r="H32" s="24" t="s">
-        <v>390</v>
       </c>
       <c r="I32" s="14">
         <v>46055</v>
@@ -3772,19 +3843,20 @@
         <v>188</v>
       </c>
       <c r="P32" s="16"/>
-    </row>
-    <row r="33" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q32" s="16"/>
+    </row>
+    <row r="33" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C33" s="15">
         <v>2836</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E33" s="20" t="s">
         <v>3</v>
@@ -3814,29 +3886,30 @@
         <v>0</v>
       </c>
       <c r="P33" s="16"/>
-    </row>
-    <row r="34" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q33" s="16"/>
+    </row>
+    <row r="34" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>261</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E34" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F34" s="12"/>
       <c r="G34" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H34" s="24" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I34" s="14">
         <v>46056</v>
@@ -3856,32 +3929,33 @@
         <v>0</v>
       </c>
       <c r="O34" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="P34" s="16"/>
-    </row>
-    <row r="35" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q34" s="16"/>
+    </row>
+    <row r="35" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E35" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F35" s="12"/>
       <c r="G35" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="H35" s="24" t="s">
         <v>304</v>
-      </c>
-      <c r="H35" s="24" t="s">
-        <v>305</v>
       </c>
       <c r="I35" s="14">
         <v>46058</v>
@@ -3901,19 +3975,20 @@
         <v>0</v>
       </c>
       <c r="P35" s="16"/>
-    </row>
-    <row r="36" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q35" s="16"/>
+    </row>
+    <row r="36" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C36" s="15">
         <v>2858</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E36" s="20" t="s">
         <v>3</v>
@@ -3946,29 +4021,30 @@
         <v>188</v>
       </c>
       <c r="P36" s="16"/>
-    </row>
-    <row r="37" spans="1:16" ht="120" x14ac:dyDescent="0.25">
+      <c r="Q36" s="16"/>
+    </row>
+    <row r="37" spans="1:17" ht="120" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E37" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F37" s="12"/>
       <c r="G37" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="H37" s="24" t="s">
         <v>418</v>
-      </c>
-      <c r="H37" s="24" t="s">
-        <v>419</v>
       </c>
       <c r="I37" s="14">
         <v>46059</v>
@@ -3991,19 +4067,20 @@
         <v>188</v>
       </c>
       <c r="P37" s="16"/>
-    </row>
-    <row r="38" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q37" s="16"/>
+    </row>
+    <row r="38" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
         <v>281</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>3</v>
@@ -4033,26 +4110,27 @@
         <v>0</v>
       </c>
       <c r="P38" s="16"/>
-    </row>
-    <row r="39" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q38" s="16"/>
+    </row>
+    <row r="39" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
         <v>264</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F39" s="12"/>
       <c r="G39" s="12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H39" s="24" t="s">
         <v>265</v>
@@ -4075,29 +4153,30 @@
         <v>0</v>
       </c>
       <c r="P39" s="16"/>
-    </row>
-    <row r="40" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q39" s="16"/>
+    </row>
+    <row r="40" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="B40" s="12" t="s">
         <v>414</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>415</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>67</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F40" s="12"/>
       <c r="G40" s="12" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14"/>
@@ -4115,19 +4194,20 @@
         <v>0</v>
       </c>
       <c r="P40" s="16"/>
-    </row>
-    <row r="41" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q40" s="16"/>
+    </row>
+    <row r="41" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
         <v>91</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C41" s="15">
         <v>2863</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E41" s="20" t="s">
         <v>3</v>
@@ -4137,7 +4217,7 @@
         <v>157</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I41" s="14">
         <v>46062</v>
@@ -4157,6 +4237,7 @@
         <v>0</v>
       </c>
       <c r="P41" s="16"/>
+      <c r="Q41" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/Client Information App.xlsx
+++ b/Client Information App.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aryte\PycharmProjects\AlucladApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8A6DCF-C95E-45F4-8AB1-B380F5786414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85FC15B6-CF43-4527-8BD7-859EE4DD43DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="768" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="428">
   <si>
     <t>Ready to dispatch</t>
   </si>
@@ -1650,6 +1650,9 @@
   <si>
     <t>10/02/2026
 09:29</t>
+  </si>
+  <si>
+    <t>Delivery Address</t>
   </si>
 </sst>
 </file>
@@ -2087,7 +2090,7 @@
     <tableColumn id="5" xr3:uid="{F88C7351-33D9-47AC-88E6-09F8FC43FCF9}" name="status" dataDxfId="12"/>
     <tableColumn id="6" xr3:uid="{AF541036-9D61-4BFA-9B88-B69C899AAAFF}" name="Phase" dataDxfId="11"/>
     <tableColumn id="7" xr3:uid="{3C9800BD-A315-48D1-9DB1-AF15B6CE2464}" name="Post Code" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{35381005-95B2-4E9D-9D09-3585A5DE3E35}" name="Delivery Adress" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{35381005-95B2-4E9D-9D09-3585A5DE3E35}" name="Delivery Address" dataDxfId="9"/>
     <tableColumn id="9" xr3:uid="{21A0DBD3-20BC-48FA-8FF6-DB3AFE9382A5}" name="PO Date" dataDxfId="8"/>
     <tableColumn id="10" xr3:uid="{3F0B7287-A10E-4CE5-9A48-B72BC577D0D0}" name="Estimated Delivery Date" dataDxfId="7"/>
     <tableColumn id="11" xr3:uid="{D53CD43D-3F51-4446-BA3F-C95DF42223C1}" name="Current Update" dataDxfId="6">
@@ -2415,7 +2418,7 @@
         <v>30</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>29</v>
+        <v>427</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>28</v>

--- a/Client Information App.xlsx
+++ b/Client Information App.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aryte\PycharmProjects\AlucladApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85FC15B6-CF43-4527-8BD7-859EE4DD43DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E35F3484-2BB6-4314-85D4-19BFC157A1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="768" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1648,11 +1648,11 @@
     <t>timestamp</t>
   </si>
   <si>
+    <t>Delivery Address</t>
+  </si>
+  <si>
     <t>10/02/2026
-09:29</t>
-  </si>
-  <si>
-    <t>Delivery Address</t>
+08:34</t>
   </si>
 </sst>
 </file>
@@ -2418,7 +2418,7 @@
         <v>30</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>28</v>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="P15" s="16"/>
       <c r="Q15" s="36" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="90" x14ac:dyDescent="0.25">

--- a/Client Information App.xlsx
+++ b/Client Information App.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aryte\PycharmProjects\AlucladApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E35F3484-2BB6-4314-85D4-19BFC157A1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C433A25D-CB6D-4C09-9606-256ACEC2DF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="768" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="431">
   <si>
     <t>Ready to dispatch</t>
   </si>
@@ -1653,6 +1653,16 @@
   <si>
     <t>10/02/2026
 08:34</t>
+  </si>
+  <si>
+    <t>SO-2058</t>
+  </si>
+  <si>
+    <t>Infills - Various Cladding</t>
+  </si>
+  <si>
+    <t>11/02/2026
+07:15</t>
   </si>
 </sst>
 </file>
@@ -2080,8 +2090,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}" name="Table1" displayName="Table1" ref="A1:Q41" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:Q41" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}" name="Table1" displayName="Table1" ref="A1:Q42" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+  <autoFilter ref="A1:Q42" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{867090DC-1FE0-4EF0-A0C0-448920317853}" name="Project" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{ED71812C-E204-4FE0-ADEA-0CD9B3ADA2A3}" name="Project SO" dataDxfId="15"/>
@@ -2373,7 +2383,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -2957,7 +2967,7 @@
         <v>328</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="12" t="s">
@@ -2989,7 +2999,9 @@
       <c r="P13" s="16" t="s">
         <v>329</v>
       </c>
-      <c r="Q13" s="16"/>
+      <c r="Q13" s="36" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="14" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
@@ -4241,6 +4253,52 @@
       </c>
       <c r="P41" s="16"/>
       <c r="Q41" s="16"/>
+    </row>
+    <row r="42" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="C42" s="15">
+        <v>2872</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="H42" s="24" t="s">
+        <v>291</v>
+      </c>
+      <c r="I42" s="14">
+        <v>46062</v>
+      </c>
+      <c r="J42" s="14"/>
+      <c r="K42" s="32">
+        <f t="shared" ref="K42" si="24">AVERAGE(L42:N42)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L42" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M42" s="32">
+        <v>0</v>
+      </c>
+      <c r="N42" s="32">
+        <v>0</v>
+      </c>
+      <c r="O42" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P42" s="16"/>
+      <c r="Q42" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/Client Information App.xlsx
+++ b/Client Information App.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aryte\PycharmProjects\AlucladApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C433A25D-CB6D-4C09-9606-256ACEC2DF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338F5147-18EF-4491-91B1-32467026D017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="768" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="445">
   <si>
     <t>Ready to dispatch</t>
   </si>
@@ -1663,6 +1663,59 @@
   <si>
     <t>11/02/2026
 07:15</t>
+  </si>
+  <si>
+    <t>Corinthian House</t>
+  </si>
+  <si>
+    <t>SO-2059</t>
+  </si>
+  <si>
+    <t>P.O.CHC002</t>
+  </si>
+  <si>
+    <t>Perforated Panels</t>
+  </si>
+  <si>
+    <t>CR0 2BX</t>
+  </si>
+  <si>
+    <t>EK Construction Limited / TBL Roofing Limited
+Corinthian House
+17 Lansdowne Road
+Croydon
+CR0 2BX
+Sebastian, +44 (0) 7851 334 852</t>
+  </si>
+  <si>
+    <t>The Paddock</t>
+  </si>
+  <si>
+    <t>SO-2060</t>
+  </si>
+  <si>
+    <t>PO00501</t>
+  </si>
+  <si>
+    <t>PO3 5PL</t>
+  </si>
+  <si>
+    <t>Dale Crowsley- E9C39A64
+ship2me, Unit 1 Quadra Point,
+Sharps Close, Anchorage Park,
+Portsmouth, PO3 5PL
+Dale Crowsley
+07781 132223</t>
+  </si>
+  <si>
+    <t>SO-2061</t>
+  </si>
+  <si>
+    <t>P.O.CHC003</t>
+  </si>
+  <si>
+    <t>11/02/2026
+8:55</t>
   </si>
 </sst>
 </file>
@@ -1748,7 +1801,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1793,11 +1846,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1886,6 +1948,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2090,8 +2158,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}" name="Table1" displayName="Table1" ref="A1:Q42" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:Q42" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}" name="Table1" displayName="Table1" ref="A1:Q45" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+  <autoFilter ref="A1:Q45" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{867090DC-1FE0-4EF0-A0C0-448920317853}" name="Project" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{ED71812C-E204-4FE0-ADEA-0CD9B3ADA2A3}" name="Project SO" dataDxfId="15"/>
@@ -2383,7 +2451,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -4282,7 +4350,7 @@
       </c>
       <c r="J42" s="14"/>
       <c r="K42" s="32">
-        <f t="shared" ref="K42" si="24">AVERAGE(L42:N42)</f>
+        <f t="shared" ref="K42:K45" si="24">AVERAGE(L42:N42)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L42" s="32">
@@ -4299,6 +4367,134 @@
       </c>
       <c r="P42" s="16"/>
       <c r="Q42" s="16"/>
+    </row>
+    <row r="43" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="E43" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="H43" s="24" t="s">
+        <v>436</v>
+      </c>
+      <c r="I43" s="14">
+        <v>46063</v>
+      </c>
+      <c r="J43" s="14"/>
+      <c r="K43" s="38">
+        <f t="shared" si="24"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L43" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M43" s="38">
+        <v>0</v>
+      </c>
+      <c r="N43" s="38">
+        <v>0</v>
+      </c>
+      <c r="O43" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P43" s="16"/>
+      <c r="Q43" s="16"/>
+    </row>
+    <row r="44" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="D44" s="12"/>
+      <c r="E44" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="H44" s="24" t="s">
+        <v>441</v>
+      </c>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="38">
+        <f t="shared" si="24"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L44" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M44" s="38">
+        <v>0</v>
+      </c>
+      <c r="N44" s="38">
+        <v>0</v>
+      </c>
+      <c r="P44" s="16"/>
+      <c r="Q44" s="16"/>
+    </row>
+    <row r="45" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E45" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="H45" s="24" t="s">
+        <v>436</v>
+      </c>
+      <c r="I45" s="14"/>
+      <c r="J45" s="14"/>
+      <c r="K45" s="38">
+        <f t="shared" si="24"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L45" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M45" s="38">
+        <v>0</v>
+      </c>
+      <c r="N45" s="38">
+        <v>0</v>
+      </c>
+      <c r="P45" s="16"/>
+      <c r="Q45" s="34" t="s">
+        <v>444</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/Client Information App.xlsx
+++ b/Client Information App.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aryte\PycharmProjects\AlucladApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338F5147-18EF-4491-91B1-32467026D017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC47CF9-E339-40B4-92C8-CD2DA6353FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="768" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="623">
   <si>
     <t>Ready to dispatch</t>
   </si>
@@ -1133,23 +1133,6 @@
     <t>Southbank Place</t>
   </si>
   <si>
-    <t>McAleer &amp; Rushe Contracts UK Ltd
- (For FCS Facades)
- Southbank Place, Building 5
- Belvedere Road
- Southbank SE1 7AF
-Tom Plago +44 (0) 7889 215 253</t>
-  </si>
-  <si>
-    <t>SO-2009</t>
-  </si>
-  <si>
-    <t>Panels Batch 2</t>
-  </si>
-  <si>
-    <t>SE1 7AF</t>
-  </si>
-  <si>
     <t>DA10 0B</t>
   </si>
   <si>
@@ -1160,33 +1143,7 @@
 Contact: Arek +44 (0) 7534 515 939</t>
   </si>
   <si>
-    <t>PO0209992-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tetraclad Ltd,
- EBBSFLEET GREEN,
- Site A - Ackers Drive,
- Ebbsfleet Valley,
- Kent, DA10 0BE,
-Contact: Ross +44 (0) 7850 985 167</t>
-  </si>
-  <si>
     <t xml:space="preserve">Thurrock </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ebbsfleet </t>
-  </si>
-  <si>
-    <t>SO-2018</t>
-  </si>
-  <si>
-    <t>SO-2019</t>
-  </si>
-  <si>
-    <t>Plenums, Ducts &amp; Panels</t>
-  </si>
-  <si>
-    <t>Panel Flashings</t>
   </si>
   <si>
     <t>Yellow Storage Brackets (Batch. 2)</t>
@@ -1206,18 +1163,6 @@
   </si>
   <si>
     <t>Sinusoidal Panels</t>
-  </si>
-  <si>
-    <t>SO-2022</t>
-  </si>
-  <si>
-    <t>SO-2023</t>
-  </si>
-  <si>
-    <t>E&amp;N GF-L1 Subframe</t>
-  </si>
-  <si>
-    <t>Corner Panel Brackets</t>
   </si>
   <si>
     <t>McAleer &amp; Rushe Contracts UK Ltd
@@ -1231,36 +1176,6 @@
     <t>SO-2026</t>
   </si>
   <si>
-    <t>SO-2024</t>
-  </si>
-  <si>
-    <t>SO-2025</t>
-  </si>
-  <si>
-    <t>SO-2027</t>
-  </si>
-  <si>
-    <t>SO-2028</t>
-  </si>
-  <si>
-    <t>Additional Panels</t>
-  </si>
-  <si>
-    <t>Windmill Court</t>
-  </si>
-  <si>
-    <t>SO-2029</t>
-  </si>
-  <si>
-    <t>SO-2030</t>
-  </si>
-  <si>
-    <t>SO-2031</t>
-  </si>
-  <si>
-    <t>RCS004</t>
-  </si>
-  <si>
     <t>McAleer &amp; Rushe Contracts UK Ltd
 (For FCS Facades)
 Stroudley Walk
@@ -1268,77 +1183,6 @@
 Jakub - +44 (0) 7772 728 234</t>
   </si>
   <si>
-    <t>CSK Holes</t>
-  </si>
-  <si>
-    <t>SO-2032</t>
-  </si>
-  <si>
-    <t>Kingspan Subframe</t>
-  </si>
-  <si>
-    <t>Panels Sub-Frame</t>
-  </si>
-  <si>
-    <t>Bifold Door Factory Ltd.
-, Bingley The Common
-, West Drayton, 
-UB7 7HQ
-Contact: Contact: Harj +44 (0) 7951 893 719</t>
-  </si>
-  <si>
-    <t>Skin Door Panel Deenesh Khoosa</t>
-  </si>
-  <si>
-    <t>Grooves</t>
-  </si>
-  <si>
-    <t>PO0211782-1</t>
-  </si>
-  <si>
-    <t>P.O.WMC003</t>
-  </si>
-  <si>
-    <t>SO-2033</t>
-  </si>
-  <si>
-    <t>HA4 8FG</t>
-  </si>
-  <si>
-    <t>EK Construction Limited
-Windmill Court
-West Way
-Ruislip
-HA4 8FG
-Contact: Sebastian +44 (0) 7851 334 852</t>
-  </si>
-  <si>
-    <t>BS14 1FZ</t>
-  </si>
-  <si>
-    <t>MPB Facades Ltd
-BoKlok Housing Site Office
-Airport Road 
-Bristol 
-BS14 1FZ
-Contact: Martin +44 (0) 7725 900 420</t>
-  </si>
-  <si>
-    <t>Additional Profiles</t>
-  </si>
-  <si>
-    <t>Panels &amp; Vents</t>
-  </si>
-  <si>
-    <t>Backlog of Blades</t>
-  </si>
-  <si>
-    <t>Gutter Flashings</t>
-  </si>
-  <si>
-    <t>L12 Copings</t>
-  </si>
-  <si>
     <t>SO-2035</t>
   </si>
   <si>
@@ -1351,22 +1195,10 @@
     <t>GF L1 Subframe (Additional Brackets + GF L1 E&amp;N Sub-Frame)</t>
   </si>
   <si>
-    <t>Southbank University</t>
-  </si>
-  <si>
     <t>Melliss Avenue</t>
   </si>
   <si>
-    <t>SO-2037</t>
-  </si>
-  <si>
     <t>SO-2038</t>
-  </si>
-  <si>
-    <t>K2-007</t>
-  </si>
-  <si>
-    <t>SE1 0AA</t>
   </si>
   <si>
     <t>TW9 4BZ</t>
@@ -1383,42 +1215,6 @@
     <t>Mock Up</t>
   </si>
   <si>
-    <t>London South Bank University,  
-Building K2, 
-103 Borough Road, 
-London,  
-SE1 0AA
-Contact: Kane Cusens – +44 (0) 7944 431 157</t>
-  </si>
-  <si>
-    <t>Lancelote Pl</t>
-  </si>
-  <si>
-    <t>SO-2039</t>
-  </si>
-  <si>
-    <t>SO-2040</t>
-  </si>
-  <si>
-    <t>PO32-33JA</t>
-  </si>
-  <si>
-    <t>Missing Broken Materials</t>
-  </si>
-  <si>
-    <t>Extra Flashing</t>
-  </si>
-  <si>
-    <t>Roytec Ltd
-27 Passey Place,
-London
-Eltham
-SE9 5DA
-Oleg +44 (0) 7453 009 655
-Nick +44 (0) 7447 162 592
-Jurij +44 (0) 7888 504 050</t>
-  </si>
-  <si>
     <t>SO-2041</t>
   </si>
   <si>
@@ -1502,13 +1298,6 @@
   </si>
   <si>
     <t>HP13 7PL</t>
-  </si>
-  <si>
-    <t>Kladworx Ltd
-Rose Court
-Wenlock Close
-High Wycombe
-Alfie Kelmendi +44 (0) 7908 701 565</t>
   </si>
   <si>
     <t>SO-2049</t>
@@ -1604,13 +1393,6 @@
     <t>SO-2056</t>
   </si>
   <si>
-    <t>Imphouse Ltd
-Chapel Lane
-Merstone
-Isle of Wight
-PO30  3BZ</t>
-  </si>
-  <si>
     <t>PO30  3BZ</t>
   </si>
   <si>
@@ -1636,9 +1418,6 @@
     <t>Door Spandrel Panel</t>
   </si>
   <si>
-    <t>Delivered</t>
-  </si>
-  <si>
     <t>order_id</t>
   </si>
   <si>
@@ -1717,12 +1496,814 @@
     <t>11/02/2026
 8:55</t>
   </si>
+  <si>
+    <t xml:space="preserve"> (For FCS Facades)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ,Broadway Central, PBSA,</t>
+  </si>
+  <si>
+    <t>200 Renfield Street,</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Glasgow, G2 3BW</t>
+  </si>
+  <si>
+    <t>Contact: Jakub +44 (0) 7772 728 234</t>
+  </si>
+  <si>
+    <t>Kladworx Ltd
+Rose Court
+Wenlock Close
+High Wycombe
+HP13 7PL
+Alfie Kelmendi +44 (0) 7908 701 565</t>
+  </si>
+  <si>
+    <t>Imphouse Ltd
+Chapel Lane
+Merstone
+Isle of Wight
+PO30  3BZ
+Mike +44 (0) 7966 279 880</t>
+  </si>
+  <si>
+    <t>Louvre Brise Soleil</t>
+  </si>
+  <si>
+    <t>SO-2062</t>
+  </si>
+  <si>
+    <t>P29950S</t>
+  </si>
+  <si>
+    <t>Extra Cill &amp; Panel</t>
+  </si>
+  <si>
+    <t>C/o Fleetwood Architectural Aluminium
+Union Square
+Stoddart Street
+Shieldfield
+NE2 1BS
+Seb +44 (0) 7903 098 924</t>
+  </si>
+  <si>
+    <t>SO-2063</t>
+  </si>
+  <si>
+    <t>PO41325-708-BYS</t>
+  </si>
+  <si>
+    <t>Brackets GF (BYS)</t>
+  </si>
+  <si>
+    <t>SO-2064</t>
+  </si>
+  <si>
+    <t>PO41325-709-BYS</t>
+  </si>
+  <si>
+    <t>Corner Brackets (BYS)</t>
+  </si>
+  <si>
+    <t>SO-2065</t>
+  </si>
+  <si>
+    <t>PO41325-711-BYS</t>
+  </si>
+  <si>
+    <t>Extra Brackets (BYS)</t>
+  </si>
+  <si>
+    <t>SO-2066</t>
+  </si>
+  <si>
+    <t>Soffit Panels</t>
+  </si>
+  <si>
+    <t>Lyndhurst Road</t>
+  </si>
+  <si>
+    <t>SO-2067</t>
+  </si>
+  <si>
+    <t>PO00502</t>
+  </si>
+  <si>
+    <t>Lindfield Place, 22 Lyndhurst
+Rd, Worthing, BN11 2DF
+Alfie +44 (0) 7908 701 565</t>
+  </si>
+  <si>
+    <t>SO-2068</t>
+  </si>
+  <si>
+    <t>SO-2069</t>
+  </si>
+  <si>
+    <t>Minories</t>
+  </si>
+  <si>
+    <t>SO-2070</t>
+  </si>
+  <si>
+    <t>TW4 6DH</t>
+  </si>
+  <si>
+    <t>FCS Facades
+The Ranch
+Next to Heathrow Gymnastics
+back of CB Hounslow
+TW4 6DH
+Piotr +44 (0) 7471 273 458</t>
+  </si>
+  <si>
+    <t>Aberdeen Lane</t>
+  </si>
+  <si>
+    <t>SO-2071</t>
+  </si>
+  <si>
+    <t>Coping Support</t>
+  </si>
+  <si>
+    <t>N5 2EJ</t>
+  </si>
+  <si>
+    <t>McAleer &amp; Rushe Contracts UK Ltd
+(For FCS Facades)
+Aberdeen Lane
+Islington
+N5 2EJ
+Pawel +44 (0) 7971 679 193</t>
+  </si>
+  <si>
+    <t>SO-2072</t>
+  </si>
+  <si>
+    <t>Angle with PCV Block</t>
+  </si>
+  <si>
+    <t>Talbot Mill</t>
+  </si>
+  <si>
+    <t>SO-2073</t>
+  </si>
+  <si>
+    <t>Sub-Frame Mill 1</t>
+  </si>
+  <si>
+    <t>44 Ellesmere Street, Manchester, M15 4JY
+Contact: Callum +44 (0) 7787 155 920
+ +44 (0) 1246 588 334</t>
+  </si>
+  <si>
+    <t>Sub-Frame Mill 2</t>
+  </si>
+  <si>
+    <t>SO-2074</t>
+  </si>
+  <si>
+    <t>Damaged Panel</t>
+  </si>
+  <si>
+    <t>SO-2075</t>
+  </si>
+  <si>
+    <t>Termination Bar</t>
+  </si>
+  <si>
+    <t>London Duck</t>
+  </si>
+  <si>
+    <t>SO-2076</t>
+  </si>
+  <si>
+    <t>Sub-Frame New Building</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EW1 2SF</t>
+  </si>
+  <si>
+    <t>St George North london Ltd
+(For FCS Facades)
+London Dock
+St George Construction Site
+Pennington Street, EW1 2SF
+Arek 07534 515 939</t>
+  </si>
+  <si>
+    <t>SO-2077</t>
+  </si>
+  <si>
+    <t>Substation Flashing</t>
+  </si>
+  <si>
+    <t>Selly Oak</t>
+  </si>
+  <si>
+    <t>SO-2078</t>
+  </si>
+  <si>
+    <t>Block A Plenums</t>
+  </si>
+  <si>
+    <t>B29 6SJ</t>
+  </si>
+  <si>
+    <t>McAleer &amp; Rushe Site
+(For FCS Facades)
+1 Chapel Lane
+Selly Oak
+B29 6SJ
+Ruslan +44 (0) 7896 059 740</t>
+  </si>
+  <si>
+    <t>Richmond Mews</t>
+  </si>
+  <si>
+    <t>SO-2079</t>
+  </si>
+  <si>
+    <t>PO00504</t>
+  </si>
+  <si>
+    <t>SE6 3JH</t>
+  </si>
+  <si>
+    <t>1 – 8 Richmond Mews
+Fordmill Road
+London
+SE6 3JH
+Contact – Alfie 07908 701565</t>
+  </si>
+  <si>
+    <t>SO-2080</t>
+  </si>
+  <si>
+    <t>Spandrel Panels</t>
+  </si>
+  <si>
+    <t>SO-2081</t>
+  </si>
+  <si>
+    <t>Brackets &amp; Flashings</t>
+  </si>
+  <si>
+    <t>SO-2082</t>
+  </si>
+  <si>
+    <t>PO41325-740-BYS</t>
+  </si>
+  <si>
+    <t>Yellow Storage Brackets - Revision C04</t>
+  </si>
+  <si>
+    <t>SO-2083</t>
+  </si>
+  <si>
+    <t>PO41325-744-BYS</t>
+  </si>
+  <si>
+    <t>YS - Bracket and Flashing</t>
+  </si>
+  <si>
+    <t>Gun Wharf</t>
+  </si>
+  <si>
+    <t>SO-2084</t>
+  </si>
+  <si>
+    <t>PO00505</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PO1 3TZ</t>
+  </si>
+  <si>
+    <t>Gun Quays,
+ Park Road,
+ Portsmouth,
+ PO1 3TZ
+Alan Davies +44 (0) 7834 198 845</t>
+  </si>
+  <si>
+    <t>SO-2085</t>
+  </si>
+  <si>
+    <t>Plenums for brick</t>
+  </si>
+  <si>
+    <t>SO-2086</t>
+  </si>
+  <si>
+    <t>Blk B Window Brackets</t>
+  </si>
+  <si>
+    <t>SO-2087</t>
+  </si>
+  <si>
+    <t>DT53</t>
+  </si>
+  <si>
+    <t>SO-2089</t>
+  </si>
+  <si>
+    <t>Panels Mill 1</t>
+  </si>
+  <si>
+    <t>SO-2089.1</t>
+  </si>
+  <si>
+    <t>Panels Mill 2</t>
+  </si>
+  <si>
+    <t>SO-2090</t>
+  </si>
+  <si>
+    <t>Last CW Flashings</t>
+  </si>
+  <si>
+    <t>V. Lema Prebook</t>
+  </si>
+  <si>
+    <t>Kennington</t>
+  </si>
+  <si>
+    <t>SO-2092</t>
+  </si>
+  <si>
+    <t>CP595</t>
+  </si>
+  <si>
+    <t>Panels</t>
+  </si>
+  <si>
+    <t>SE11 5SY</t>
+  </si>
+  <si>
+    <t>8A Harleyford Street
+Oval
+London
+SE11 5SY
+Richard +44 (0) 7854 920 942</t>
+  </si>
+  <si>
+    <t>SO-2094</t>
+  </si>
+  <si>
+    <t>External Flashings</t>
+  </si>
+  <si>
+    <t>SO-2095</t>
+  </si>
+  <si>
+    <t>SO-2096</t>
+  </si>
+  <si>
+    <t>DT66</t>
+  </si>
+  <si>
+    <t>Reveals Brackets</t>
+  </si>
+  <si>
+    <t>Bosden Stockport</t>
+  </si>
+  <si>
+    <t>SO-2097</t>
+  </si>
+  <si>
+    <t>Fins</t>
+  </si>
+  <si>
+    <t>SK3 8AB</t>
+  </si>
+  <si>
+    <t>Oak Construction 
+Delivery Gate
+Mulberry Mount Street
+Stockport
+SK3 8AB</t>
+  </si>
+  <si>
+    <t>SO-2097.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canopy </t>
+  </si>
+  <si>
+    <t>Greenwich Millennium Village</t>
+  </si>
+  <si>
+    <t>SO-2098</t>
+  </si>
+  <si>
+    <t>V-Groove Panels</t>
+  </si>
+  <si>
+    <t>SE10 0JT</t>
+  </si>
+  <si>
+    <t>McAleer &amp; Rushe Site
+(For FCS Facades)
+Greenwich Millennium Village
+Plots 401 &amp; 403
+SE10 0JT
+Piotr +44 (0) 7471 273 458</t>
+  </si>
+  <si>
+    <t>London Dock</t>
+  </si>
+  <si>
+    <t>SO-2099</t>
+  </si>
+  <si>
+    <t>BR14 Brackets</t>
+  </si>
+  <si>
+    <t>SO-2100</t>
+  </si>
+  <si>
+    <t>Plenums</t>
+  </si>
+  <si>
+    <t>SO-2101</t>
+  </si>
+  <si>
+    <t>Final Brackets</t>
+  </si>
+  <si>
+    <t>SO-2102</t>
+  </si>
+  <si>
+    <t>Door Brackets</t>
+  </si>
+  <si>
+    <t>Mellis Avenue</t>
+  </si>
+  <si>
+    <t>SO-2103</t>
+  </si>
+  <si>
+    <t>Plenums for Brick</t>
+  </si>
+  <si>
+    <t>SO-2104</t>
+  </si>
+  <si>
+    <t>DT78</t>
+  </si>
+  <si>
+    <t>Brackets Prod. 2</t>
+  </si>
+  <si>
+    <t>SO-2105</t>
+  </si>
+  <si>
+    <t>L2 Subframe</t>
+  </si>
+  <si>
+    <t>SO-2106</t>
+  </si>
+  <si>
+    <t>DT81</t>
+  </si>
+  <si>
+    <t>Brackets Prod. 3</t>
+  </si>
+  <si>
+    <t>SO-2107</t>
+  </si>
+  <si>
+    <t>Plates for Doors</t>
+  </si>
+  <si>
+    <t>SO-2108</t>
+  </si>
+  <si>
+    <t>Dummy Plenums</t>
+  </si>
+  <si>
+    <t>SO-2109</t>
+  </si>
+  <si>
+    <t>P.O.CHC009</t>
+  </si>
+  <si>
+    <t>Extra Panels &amp; Renew Corner</t>
+  </si>
+  <si>
+    <t>SO-2110</t>
+  </si>
+  <si>
+    <t>Coping</t>
+  </si>
+  <si>
+    <t>SO-2111</t>
+  </si>
+  <si>
+    <t>P. Klubowicz Prebook</t>
+  </si>
+  <si>
+    <t>Wensleydale Av</t>
+  </si>
+  <si>
+    <t>SO-2112</t>
+  </si>
+  <si>
+    <t>Flat panels</t>
+  </si>
+  <si>
+    <t>N1 5QJ</t>
+  </si>
+  <si>
+    <t>Flat 9
+28–36 Orsman Road
+London
+N1 5QJ
+Victor +44 (0) 7979 368 584</t>
+  </si>
+  <si>
+    <t>SO-2113</t>
+  </si>
+  <si>
+    <t>Brackets &amp; Shims</t>
+  </si>
+  <si>
+    <t>A.Szyposz &amp; W.Damski Prebook</t>
+  </si>
+  <si>
+    <t>SO-2114</t>
+  </si>
+  <si>
+    <t>SO-2115</t>
+  </si>
+  <si>
+    <t>SO-2116</t>
+  </si>
+  <si>
+    <t>Subframe -Brackets &amp; Top Hats</t>
+  </si>
+  <si>
+    <t>SO-2117</t>
+  </si>
+  <si>
+    <t>Block B HDPE Blocks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BS14 1FZ </t>
+  </si>
+  <si>
+    <t>MPB Facades Ltd
+BoKlok Housing Site Office
+Airport Road 
+Bristol 
+BS14 1FZ 
+What3words/// Maple.bronze.corner
+Martin 07725900420</t>
+  </si>
+  <si>
+    <t>UB8 2XW</t>
+  </si>
+  <si>
+    <t>Sarogirg Ltd
+Wellington House 
+4-10 Cowley Road 
+Uxbridge 
+UB8 2XW
+Contact: Andrian 07438888813</t>
+  </si>
+  <si>
+    <t>SO-2118</t>
+  </si>
+  <si>
+    <t>Block B HDPE Blocks Prod. 2</t>
+  </si>
+  <si>
+    <t>SO-2119</t>
+  </si>
+  <si>
+    <t>DT96</t>
+  </si>
+  <si>
+    <t>T-Rails</t>
+  </si>
+  <si>
+    <t>SO-2120</t>
+  </si>
+  <si>
+    <t>CW Brackets L5-7</t>
+  </si>
+  <si>
+    <t>SO-2121</t>
+  </si>
+  <si>
+    <t>Block C Copings</t>
+  </si>
+  <si>
+    <t>SO-2122</t>
+  </si>
+  <si>
+    <t>Block C Cladding</t>
+  </si>
+  <si>
+    <t>SO-2123</t>
+  </si>
+  <si>
+    <t>SO-2124</t>
+  </si>
+  <si>
+    <t>CA2919</t>
+  </si>
+  <si>
+    <t>Block B Panels</t>
+  </si>
+  <si>
+    <t>Lancelote Pl (Lancaster Road)</t>
+  </si>
+  <si>
+    <t>SO-2125</t>
+  </si>
+  <si>
+    <t>Lancaster Road Panels</t>
+  </si>
+  <si>
+    <t>W11 1QJ</t>
+  </si>
+  <si>
+    <t>39 Lancaster Road
+W11 1QJ
+Noel +44 (0) 7580 181 106</t>
+  </si>
+  <si>
+    <t>SO-2126</t>
+  </si>
+  <si>
+    <t>Block B Flat Wall Panels</t>
+  </si>
+  <si>
+    <t>SO-2127</t>
+  </si>
+  <si>
+    <t>Plenums Prod. 2</t>
+  </si>
+  <si>
+    <t>SO-2128</t>
+  </si>
+  <si>
+    <t>PO00519</t>
+  </si>
+  <si>
+    <t>Upstands</t>
+  </si>
+  <si>
+    <t>1 – 8 Richmond Mews
+Fordmill Road
+London
+SE6 3JH
+Contact – Peter 07309 102159</t>
+  </si>
+  <si>
+    <t>SO-2129</t>
+  </si>
+  <si>
+    <t>Slatted Panel Tubes</t>
+  </si>
+  <si>
+    <t>SO-2130</t>
+  </si>
+  <si>
+    <t>CA2920</t>
+  </si>
+  <si>
+    <t>Block B Panels Prod. 2</t>
+  </si>
+  <si>
+    <t>SO-2131</t>
+  </si>
+  <si>
+    <t>June Site</t>
+  </si>
+  <si>
+    <t>SO-2132</t>
+  </si>
+  <si>
+    <t>Gough Street</t>
+  </si>
+  <si>
+    <t>SO-2133</t>
+  </si>
+  <si>
+    <t>P1 Understructure</t>
+  </si>
+  <si>
+    <t>McAleer &amp; Rushe Site
+(For FCS Facades)
+Gough Street
+Birmingham, B1 1HN
+Ruslan +44 (0) 7896 059 740</t>
+  </si>
+  <si>
+    <t>SO-2134</t>
+  </si>
+  <si>
+    <t>Additional Coping</t>
+  </si>
+  <si>
+    <t>McAleer &amp; Rushe Contracts UK Ltd
+(For FCS Facades)
+Southbank Place, Building 5
+Belvedere Road
+Southbank SE1 7AF
+Tom Plago 07889 215 253</t>
+  </si>
+  <si>
+    <t>SO-2135</t>
+  </si>
+  <si>
+    <t>Blk B Plenums</t>
+  </si>
+  <si>
+    <t>Parts Delivery
+Level 1 Priority</t>
+  </si>
+  <si>
+    <t>SO-2136</t>
+  </si>
+  <si>
+    <t>Blk A CW Brackets</t>
+  </si>
+  <si>
+    <t>SO-2137</t>
+  </si>
+  <si>
+    <t>CA2922</t>
+  </si>
+  <si>
+    <t>Block B Panels Prod. 3</t>
+  </si>
+  <si>
+    <t>SO-2138</t>
+  </si>
+  <si>
+    <t>P2 Understructure</t>
+  </si>
+  <si>
+    <t>SO-2139</t>
+  </si>
+  <si>
+    <t>CW Spandrels &amp; Trays</t>
+  </si>
+  <si>
+    <t>SO-2140</t>
+  </si>
+  <si>
+    <t>G3&amp;G4 L0-3 Brackets</t>
+  </si>
+  <si>
+    <t>SO-2141</t>
+  </si>
+  <si>
+    <t>SO-2142</t>
+  </si>
+  <si>
+    <t>SO-2143</t>
+  </si>
+  <si>
+    <t>DT112</t>
+  </si>
+  <si>
+    <t>SO-2144</t>
+  </si>
+  <si>
+    <t>SO-2145</t>
+  </si>
+  <si>
+    <t>SO-2146</t>
+  </si>
+  <si>
+    <t>SO-2147</t>
+  </si>
+  <si>
+    <t>SO-2148</t>
+  </si>
+  <si>
+    <t>SO-2149</t>
+  </si>
+  <si>
+    <t>SO-2150</t>
+  </si>
+  <si>
+    <t>SO-2151</t>
+  </si>
+  <si>
+    <t>SO-2152</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1780,8 +2361,15 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1798,6 +2386,11 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -1856,10 +2449,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1955,8 +2549,12 @@
     <xf numFmtId="9" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Neutral" xfId="1" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="19">
@@ -1982,6 +2580,9 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -2000,6 +2601,172 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="13" formatCode="0%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2044,101 +2811,6 @@
         <charset val="238"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2158,28 +2830,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}" name="Table1" displayName="Table1" ref="A1:Q45" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:Q45" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}" name="Table1" displayName="Table1" ref="A1:Q122" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+  <autoFilter ref="A1:Q122" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{867090DC-1FE0-4EF0-A0C0-448920317853}" name="Project" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{ED71812C-E204-4FE0-ADEA-0CD9B3ADA2A3}" name="Project SO" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{32502B80-458D-4EF6-9ABC-03678A6F8302}" name="order_id" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{111DD528-EE5F-4D8B-B63F-9A842570498D}" name="Materials" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{F88C7351-33D9-47AC-88E6-09F8FC43FCF9}" name="status" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{AF541036-9D61-4BFA-9B88-B69C899AAAFF}" name="Phase" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{3C9800BD-A315-48D1-9DB1-AF15B6CE2464}" name="Post Code" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{35381005-95B2-4E9D-9D09-3585A5DE3E35}" name="Delivery Address" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{21A0DBD3-20BC-48FA-8FF6-DB3AFE9382A5}" name="PO Date" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{3F0B7287-A10E-4CE5-9A48-B72BC577D0D0}" name="Estimated Delivery Date" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{D53CD43D-3F51-4446-BA3F-C95DF42223C1}" name="Current Update" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{867090DC-1FE0-4EF0-A0C0-448920317853}" name="Project" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{ED71812C-E204-4FE0-ADEA-0CD9B3ADA2A3}" name="Project SO" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{32502B80-458D-4EF6-9ABC-03678A6F8302}" name="order_id" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{111DD528-EE5F-4D8B-B63F-9A842570498D}" name="Materials" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{F88C7351-33D9-47AC-88E6-09F8FC43FCF9}" name="status" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{AF541036-9D61-4BFA-9B88-B69C899AAAFF}" name="Phase" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{3C9800BD-A315-48D1-9DB1-AF15B6CE2464}" name="Post Code" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{35381005-95B2-4E9D-9D09-3585A5DE3E35}" name="Delivery Address" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{21A0DBD3-20BC-48FA-8FF6-DB3AFE9382A5}" name="PO Date" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{3F0B7287-A10E-4CE5-9A48-B72BC577D0D0}" name="Estimated Delivery Date" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{D53CD43D-3F51-4446-BA3F-C95DF42223C1}" name="Current Update" dataDxfId="5">
       <calculatedColumnFormula>AVERAGE(L2:N2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{6527AB69-9477-41B6-8941-2FE273E12275}" name="Production" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{6436B5E8-E98E-47E2-B70D-DD9AA467C3A5}" name="PPC" dataDxfId="4"/>
-    <tableColumn id="14" xr3:uid="{D893399C-2909-4B8A-9538-32D22CFA1B25}" name="Dispatch" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{F6302424-51FB-45BD-9F34-61C700C8D161}" name="Welded" dataDxfId="2"/>
-    <tableColumn id="16" xr3:uid="{9BE99484-0D9D-4749-B30B-7C533699CF52}" name="Critical Information" dataDxfId="1"/>
-    <tableColumn id="17" xr3:uid="{294DD3E6-5EEC-42DD-AE99-1AC9AB8E1DEE}" name="timestamp" dataDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{6527AB69-9477-41B6-8941-2FE273E12275}" name="Production" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{6436B5E8-E98E-47E2-B70D-DD9AA467C3A5}" name="PPC" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{D893399C-2909-4B8A-9538-32D22CFA1B25}" name="Dispatch" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{F6302424-51FB-45BD-9F34-61C700C8D161}" name="Welded" dataDxfId="1"/>
+    <tableColumn id="16" xr3:uid="{9BE99484-0D9D-4749-B30B-7C533699CF52}" name="Critical Information" dataDxfId="0"/>
+    <tableColumn id="17" xr3:uid="{294DD3E6-5EEC-42DD-AE99-1AC9AB8E1DEE}" name="timestamp" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2451,7 +3123,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:Q122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -2481,13 +3153,13 @@
         <v>35</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>423</v>
+        <v>364</v>
       </c>
       <c r="D1" s="12" t="s">
         <v>33</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>424</v>
+        <v>365</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>31</v>
@@ -2496,7 +3168,7 @@
         <v>30</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>426</v>
+        <v>367</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>28</v>
@@ -2523,10 +3195,10 @@
         <v>267</v>
       </c>
       <c r="Q1" s="12" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>255</v>
       </c>
@@ -2547,14 +3219,14 @@
         <v>155</v>
       </c>
       <c r="H2" s="24" t="s">
-        <v>291</v>
+        <v>386</v>
       </c>
       <c r="I2" s="14">
         <v>45987</v>
       </c>
       <c r="J2" s="14"/>
       <c r="K2" s="23">
-        <f t="shared" ref="K2" si="0">AVERAGE(L2:N2)</f>
+        <f t="shared" ref="K2:K65" si="0">AVERAGE(L2:N2)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L2" s="23">
@@ -2574,7 +3246,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>281</v>
       </c>
@@ -2585,7 +3257,7 @@
         <v>282</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>3</v>
@@ -2595,14 +3267,14 @@
         <v>284</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>283</v>
+        <v>387</v>
       </c>
       <c r="I3" s="14">
         <v>45995</v>
       </c>
       <c r="J3" s="14"/>
       <c r="K3" s="23">
-        <f t="shared" ref="K3" si="1">AVERAGE(L3:N3)</f>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L3" s="23">
@@ -2620,35 +3292,35 @@
       <c r="P3" s="16"/>
       <c r="Q3" s="16"/>
     </row>
-    <row r="4" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E4" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="12" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="I4" s="14">
-        <v>46000</v>
+        <v>46030</v>
       </c>
       <c r="J4" s="14"/>
       <c r="K4" s="32">
-        <f t="shared" ref="K4" si="2">AVERAGE(L4:N4)</f>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L4" s="32">
@@ -2663,35 +3335,35 @@
       <c r="P4" s="16"/>
       <c r="Q4" s="16"/>
     </row>
-    <row r="5" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C5" s="15">
-        <v>2622</v>
+        <v>2711</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E5" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="12" t="s">
-        <v>155</v>
+        <v>269</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>291</v>
+        <v>389</v>
       </c>
       <c r="I5" s="14">
-        <v>46009</v>
+        <v>46037</v>
       </c>
       <c r="J5" s="14"/>
       <c r="K5" s="32">
-        <f t="shared" ref="K5:K6" si="3">AVERAGE(L5:N5)</f>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L5" s="32">
@@ -2702,42 +3374,39 @@
       </c>
       <c r="N5" s="32">
         <v>0</v>
-      </c>
-      <c r="O5" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="16"/>
     </row>
-    <row r="6" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C6" s="15">
-        <v>2633</v>
+        <v>2721</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="12" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>279</v>
+        <v>390</v>
       </c>
       <c r="I6" s="14">
-        <v>46013</v>
+        <v>46037</v>
       </c>
       <c r="J6" s="14"/>
       <c r="K6" s="32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L6" s="32">
@@ -2748,39 +3417,42 @@
       </c>
       <c r="N6" s="32">
         <v>0</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>188</v>
       </c>
       <c r="P6" s="16"/>
       <c r="Q6" s="16"/>
     </row>
-    <row r="7" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>302</v>
+        <v>303</v>
+      </c>
+      <c r="C7" s="15">
+        <v>2746</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="12" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I7" s="14">
-        <v>46030</v>
+        <v>46042</v>
       </c>
       <c r="J7" s="14"/>
       <c r="K7" s="32">
-        <f t="shared" ref="K7" si="4">AVERAGE(L7:N7)</f>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L7" s="32">
@@ -2791,19 +3463,22 @@
       </c>
       <c r="N7" s="32">
         <v>0</v>
+      </c>
+      <c r="O7" s="12" t="s">
+        <v>188</v>
       </c>
       <c r="P7" s="16"/>
       <c r="Q7" s="16"/>
     </row>
     <row r="8" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>268</v>
+        <v>91</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C8" s="15">
-        <v>2661</v>
+        <v>2781</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>308</v>
@@ -2813,17 +3488,17 @@
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="12" t="s">
-        <v>269</v>
+        <v>157</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>310</v>
+        <v>341</v>
       </c>
       <c r="I8" s="14">
-        <v>46030</v>
+        <v>46045</v>
       </c>
       <c r="J8" s="14"/>
       <c r="K8" s="32">
-        <f t="shared" ref="K8:K9" si="5">AVERAGE(L8:N8)</f>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L8" s="32">
@@ -2846,13 +3521,13 @@
         <v>268</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C9" s="15">
-        <v>2662</v>
+        <v>2787</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>3</v>
@@ -2862,14 +3537,14 @@
         <v>269</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="I9" s="14">
-        <v>46030</v>
+        <v>46045</v>
       </c>
       <c r="J9" s="14"/>
       <c r="K9" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L9" s="32">
@@ -2887,35 +3562,35 @@
       <c r="P9" s="16"/>
       <c r="Q9" s="16"/>
     </row>
-    <row r="10" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>51</v>
+        <v>302</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="C10" s="15">
+        <v>2800</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>312</v>
-      </c>
-      <c r="C10" s="15">
-        <v>2671</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>316</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="12" t="s">
-        <v>53</v>
+        <v>304</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="I10" s="14">
-        <v>46031</v>
+        <v>46049</v>
       </c>
       <c r="J10" s="14"/>
       <c r="K10" s="32">
-        <f t="shared" ref="K10:K13" si="6">AVERAGE(L10:N10)</f>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L10" s="32">
@@ -2927,43 +3602,38 @@
       <c r="N10" s="32">
         <v>0</v>
       </c>
-      <c r="O10" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="P10" s="16" t="s">
-        <v>323</v>
-      </c>
+      <c r="P10" s="16"/>
       <c r="Q10" s="16"/>
     </row>
     <row r="11" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>268</v>
+        <v>17</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="C11" s="15">
-        <v>2672</v>
+      <c r="C11" s="15" t="s">
+        <v>314</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="E11" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="12" t="s">
-        <v>269</v>
+        <v>189</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="I11" s="14">
-        <v>46031</v>
+        <v>46050</v>
       </c>
       <c r="J11" s="14"/>
       <c r="K11" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L11" s="32">
@@ -2974,39 +3644,42 @@
       </c>
       <c r="N11" s="32">
         <v>0</v>
+      </c>
+      <c r="O11" s="12" t="s">
+        <v>188</v>
       </c>
       <c r="P11" s="16"/>
       <c r="Q11" s="16"/>
     </row>
-    <row r="12" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="150" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>321</v>
+        <v>67</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="E12" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="12" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>304</v>
+        <v>342</v>
       </c>
       <c r="I12" s="14">
-        <v>46030</v>
+        <v>46051</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L12" s="32">
@@ -3021,35 +3694,35 @@
       <c r="P12" s="16"/>
       <c r="Q12" s="16"/>
     </row>
-    <row r="13" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C13" s="15">
-        <v>1711019</v>
+        <v>2814</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="12" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>327</v>
+        <v>297</v>
       </c>
       <c r="I13" s="14">
-        <v>46031</v>
+        <v>46051</v>
       </c>
       <c r="J13" s="14"/>
       <c r="K13" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L13" s="32">
@@ -3061,45 +3734,40 @@
       <c r="N13" s="32">
         <v>0</v>
       </c>
-      <c r="O13" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="P13" s="16" t="s">
-        <v>329</v>
-      </c>
+      <c r="P13" s="16"/>
       <c r="Q13" s="36" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>217</v>
+        <v>281</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="C14" s="15">
-        <v>53</v>
+        <v>326</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>327</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="E14" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="12" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="I14" s="14">
-        <v>46034</v>
+        <v>46055</v>
       </c>
       <c r="J14" s="14"/>
       <c r="K14" s="32">
-        <f t="shared" ref="K14:K16" si="7">AVERAGE(L14:N14)</f>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L14" s="32">
@@ -3110,89 +3778,90 @@
       </c>
       <c r="N14" s="32">
         <v>0</v>
+      </c>
+      <c r="O14" s="12" t="s">
+        <v>324</v>
       </c>
       <c r="P14" s="16"/>
       <c r="Q14" s="16"/>
     </row>
     <row r="15" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>295</v>
+        <v>329</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>338</v>
+        <v>87</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>422</v>
+        <v>3</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12" t="s">
-        <v>290</v>
+        <v>332</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>265</v>
+        <v>391</v>
       </c>
       <c r="I15" s="14">
-        <v>46034</v>
-      </c>
-      <c r="J15" s="14">
-        <v>46063</v>
-      </c>
+        <v>46055</v>
+      </c>
+      <c r="J15" s="14"/>
       <c r="K15" s="32">
-        <f t="shared" si="7"/>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
       </c>
       <c r="L15" s="32">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="M15" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" s="12" t="s">
         <v>188</v>
       </c>
       <c r="P15" s="16"/>
       <c r="Q15" s="36" t="s">
-        <v>427</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>317</v>
+        <v>288</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>331</v>
+        <v>333</v>
+      </c>
+      <c r="C16" s="15">
+        <v>2836</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E16" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="12" t="s">
-        <v>333</v>
+        <v>278</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>334</v>
+        <v>279</v>
       </c>
       <c r="I16" s="14">
-        <v>46034</v>
+        <v>46056</v>
       </c>
       <c r="J16" s="14"/>
       <c r="K16" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L16" s="32">
@@ -3203,42 +3872,39 @@
       </c>
       <c r="N16" s="32">
         <v>0</v>
-      </c>
-      <c r="O16" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="P16" s="16"/>
       <c r="Q16" s="16"/>
     </row>
     <row r="17" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>324</v>
-      </c>
-      <c r="C17" s="15">
-        <v>2687</v>
+        <v>334</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>339</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E17" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="12" t="s">
-        <v>289</v>
+        <v>336</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>286</v>
+        <v>335</v>
       </c>
       <c r="I17" s="14">
-        <v>46035</v>
+        <v>46056</v>
       </c>
       <c r="J17" s="14"/>
       <c r="K17" s="32">
-        <f t="shared" ref="K17:K18" si="8">AVERAGE(L17:N17)</f>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L17" s="32">
@@ -3251,40 +3917,40 @@
         <v>0</v>
       </c>
       <c r="O17" s="12" t="s">
-        <v>188</v>
+        <v>324</v>
       </c>
       <c r="P17" s="16"/>
       <c r="Q17" s="16"/>
     </row>
-    <row r="18" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>332</v>
-      </c>
-      <c r="C18" s="15">
-        <v>2690</v>
+        <v>340</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>348</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="E18" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="12" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="I18" s="14">
-        <v>46035</v>
+        <v>46058</v>
       </c>
       <c r="J18" s="14"/>
       <c r="K18" s="32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L18" s="32">
@@ -3295,42 +3961,39 @@
       </c>
       <c r="N18" s="32">
         <v>0</v>
-      </c>
-      <c r="O18" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="P18" s="16"/>
       <c r="Q18" s="16"/>
     </row>
     <row r="19" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C19" s="15">
-        <v>2711</v>
+        <v>2858</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="E19" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="12" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>310</v>
+        <v>279</v>
       </c>
       <c r="I19" s="14">
-        <v>46037</v>
+        <v>46059</v>
       </c>
       <c r="J19" s="14"/>
       <c r="K19" s="32">
-        <f t="shared" ref="K19" si="9">AVERAGE(L19:N19)</f>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L19" s="32">
@@ -3341,39 +4004,42 @@
       </c>
       <c r="N19" s="32">
         <v>0</v>
+      </c>
+      <c r="O19" s="12" t="s">
+        <v>188</v>
       </c>
       <c r="P19" s="16"/>
       <c r="Q19" s="16"/>
     </row>
-    <row r="20" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" ht="120" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>268</v>
+        <v>343</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="C20" s="15">
-        <v>2721</v>
+        <v>345</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>349</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="E20" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="12" t="s">
-        <v>269</v>
+        <v>359</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="I20" s="14">
-        <v>46037</v>
+        <v>46059</v>
       </c>
       <c r="J20" s="14"/>
       <c r="K20" s="32">
-        <f t="shared" ref="K20" si="10">AVERAGE(L20:N20)</f>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L20" s="32">
@@ -3391,35 +4057,35 @@
       <c r="P20" s="16"/>
       <c r="Q20" s="16"/>
     </row>
-    <row r="21" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>346</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>348</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>350</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>106</v>
+        <v>354</v>
       </c>
       <c r="E21" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="12" t="s">
-        <v>351</v>
+        <v>284</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>355</v>
+        <v>283</v>
       </c>
       <c r="I21" s="14">
-        <v>46038</v>
+        <v>46059</v>
       </c>
       <c r="J21" s="14"/>
       <c r="K21" s="32">
-        <f t="shared" ref="K21:K22" si="11">AVERAGE(L21:N21)</f>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L21" s="32">
@@ -3436,33 +4102,33 @@
     </row>
     <row r="22" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="B22" s="12" t="s">
-        <v>349</v>
-      </c>
-      <c r="C22" s="15">
-        <v>2746</v>
+      <c r="C22" s="15" t="s">
+        <v>351</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E22" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="12" t="s">
-        <v>352</v>
+        <v>286</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>353</v>
+        <v>265</v>
       </c>
       <c r="I22" s="14">
-        <v>46042</v>
+        <v>46059</v>
       </c>
       <c r="J22" s="14"/>
       <c r="K22" s="32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L22" s="32">
@@ -3473,42 +4139,37 @@
       </c>
       <c r="N22" s="32">
         <v>0</v>
-      </c>
-      <c r="O22" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="P22" s="16"/>
       <c r="Q22" s="16"/>
     </row>
-    <row r="23" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>51</v>
+        <v>356</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="C23" s="15">
-        <v>2706</v>
+      <c r="C23" s="15" t="s">
+        <v>67</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E23" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F23" s="12"/>
       <c r="G23" s="12" t="s">
-        <v>53</v>
+        <v>358</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>322</v>
-      </c>
-      <c r="I23" s="14">
-        <v>46036</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="I23" s="14"/>
       <c r="J23" s="14"/>
       <c r="K23" s="32">
-        <f t="shared" ref="K23:K24" si="12">AVERAGE(L23:N23)</f>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L23" s="32">
@@ -3519,42 +4180,39 @@
       </c>
       <c r="N23" s="32">
         <v>0</v>
-      </c>
-      <c r="O23" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="P23" s="16"/>
       <c r="Q23" s="16"/>
     </row>
-    <row r="24" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>356</v>
+        <v>91</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>359</v>
+        <v>362</v>
+      </c>
+      <c r="C24" s="15">
+        <v>2863</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E24" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F24" s="12"/>
       <c r="G24" s="12" t="s">
-        <v>238</v>
+        <v>157</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="I24" s="14">
-        <v>46043</v>
+        <v>46062</v>
       </c>
       <c r="J24" s="14"/>
       <c r="K24" s="32">
-        <f t="shared" si="12"/>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L24" s="32">
@@ -3569,44 +4227,44 @@
       <c r="P24" s="16"/>
       <c r="Q24" s="16"/>
     </row>
-    <row r="25" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>91</v>
+        <v>255</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C25" s="15">
-        <v>2781</v>
+        <v>2872</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="E25" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="E25" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>398</v>
+        <v>287</v>
       </c>
       <c r="I25" s="14">
-        <v>46045</v>
+        <v>46062</v>
       </c>
       <c r="J25" s="14"/>
-      <c r="K25" s="32">
-        <f t="shared" ref="K25" si="13">AVERAGE(L25:N25)</f>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L25" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M25" s="32">
-        <v>0</v>
-      </c>
-      <c r="N25" s="32">
+      <c r="K25" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L25" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M25" s="38">
+        <v>0</v>
+      </c>
+      <c r="N25" s="38">
         <v>0</v>
       </c>
       <c r="O25" s="12" t="s">
@@ -3615,44 +4273,44 @@
       <c r="P25" s="16"/>
       <c r="Q25" s="16"/>
     </row>
-    <row r="26" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="105" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>268</v>
+        <v>372</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="C26" s="15">
-        <v>2787</v>
+        <v>373</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>374</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="E26" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="E26" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="12" t="s">
-        <v>269</v>
+        <v>376</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>310</v>
+        <v>377</v>
       </c>
       <c r="I26" s="14">
-        <v>46045</v>
+        <v>46063</v>
       </c>
       <c r="J26" s="14"/>
-      <c r="K26" s="32">
-        <f t="shared" ref="K26:K27" si="14">AVERAGE(L26:N26)</f>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L26" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M26" s="32">
-        <v>0</v>
-      </c>
-      <c r="N26" s="32">
+      <c r="K26" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L26" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M26" s="38">
+        <v>0</v>
+      </c>
+      <c r="N26" s="38">
         <v>0</v>
       </c>
       <c r="O26" s="12" t="s">
@@ -3663,398 +4321,374 @@
     </row>
     <row r="27" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>347</v>
+        <v>378</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="C27" s="15">
-        <v>2800</v>
+        <v>379</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>380</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="E27" s="20" t="s">
+        <v>393</v>
+      </c>
+      <c r="E27" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F27" s="12"/>
       <c r="G27" s="12" t="s">
-        <v>352</v>
+        <v>381</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>353</v>
+        <v>382</v>
       </c>
       <c r="I27" s="14">
-        <v>46049</v>
+        <v>46063</v>
       </c>
       <c r="J27" s="14"/>
-      <c r="K27" s="32">
-        <f t="shared" si="14"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L27" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M27" s="32">
-        <v>0</v>
-      </c>
-      <c r="N27" s="32">
+      <c r="K27" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L27" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M27" s="38">
+        <v>0</v>
+      </c>
+      <c r="N27" s="38">
         <v>0</v>
       </c>
       <c r="P27" s="16"/>
       <c r="Q27" s="16"/>
     </row>
-    <row r="28" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="105" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>17</v>
+        <v>372</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="E28" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="E28" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F28" s="12"/>
       <c r="G28" s="12" t="s">
-        <v>189</v>
+        <v>376</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="I28" s="14">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="J28" s="14"/>
-      <c r="K28" s="32">
-        <f t="shared" ref="K28" si="15">AVERAGE(L28:N28)</f>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L28" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M28" s="32">
-        <v>0</v>
-      </c>
-      <c r="N28" s="32">
-        <v>0</v>
-      </c>
-      <c r="O28" s="12" t="s">
-        <v>188</v>
+      <c r="K28" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L28" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M28" s="38">
+        <v>0</v>
+      </c>
+      <c r="N28" s="38">
+        <v>0</v>
       </c>
       <c r="P28" s="16"/>
       <c r="Q28" s="16"/>
     </row>
-    <row r="29" spans="1:17" ht="150" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" ht="105" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>373</v>
+        <v>148</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>67</v>
+        <v>395</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="E29" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="E29" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F29" s="12"/>
       <c r="G29" s="12" t="s">
-        <v>375</v>
+        <v>153</v>
       </c>
       <c r="H29" s="24" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I29" s="14">
-        <v>46051</v>
+        <v>46065</v>
       </c>
       <c r="J29" s="14"/>
-      <c r="K29" s="32">
-        <f t="shared" ref="K29" si="16">AVERAGE(L29:N29)</f>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L29" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M29" s="32">
-        <v>0</v>
-      </c>
-      <c r="N29" s="32">
+      <c r="K29" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L29" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M29" s="38">
+        <v>0</v>
+      </c>
+      <c r="N29" s="38">
         <v>0</v>
       </c>
       <c r="P29" s="16"/>
       <c r="Q29" s="16"/>
     </row>
-    <row r="30" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>51</v>
+        <v>281</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="C30" s="15">
-        <v>2814</v>
+        <v>398</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>399</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="E30" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="E30" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="12" t="s">
-        <v>53</v>
+        <v>284</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>322</v>
-      </c>
-      <c r="I30" s="14">
-        <v>46051</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="I30" s="14"/>
       <c r="J30" s="14"/>
-      <c r="K30" s="32">
-        <f t="shared" ref="K30" si="17">AVERAGE(L30:N30)</f>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L30" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M30" s="32">
-        <v>0</v>
-      </c>
-      <c r="N30" s="32">
+      <c r="K30" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L30" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M30" s="38">
+        <v>0</v>
+      </c>
+      <c r="N30" s="38">
         <v>0</v>
       </c>
       <c r="P30" s="16"/>
       <c r="Q30" s="16"/>
     </row>
-    <row r="31" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
         <v>281</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="E31" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="E31" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F31" s="12"/>
       <c r="G31" s="12" t="s">
-        <v>381</v>
+        <v>284</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>379</v>
-      </c>
-      <c r="I31" s="14">
-        <v>46055</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="I31" s="14"/>
       <c r="J31" s="14"/>
-      <c r="K31" s="32">
-        <f t="shared" ref="K31" si="18">AVERAGE(L31:N31)</f>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L31" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M31" s="32">
-        <v>0</v>
-      </c>
-      <c r="N31" s="32">
-        <v>0</v>
-      </c>
-      <c r="O31" s="12" t="s">
-        <v>380</v>
+      <c r="K31" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L31" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M31" s="38">
+        <v>0</v>
+      </c>
+      <c r="N31" s="38">
+        <v>0</v>
       </c>
       <c r="P31" s="16"/>
       <c r="Q31" s="16"/>
     </row>
-    <row r="32" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>385</v>
+        <v>281</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E32" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="E32" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="12" t="s">
-        <v>388</v>
+        <v>284</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>389</v>
-      </c>
-      <c r="I32" s="14">
-        <v>46055</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="I32" s="14"/>
       <c r="J32" s="14"/>
-      <c r="K32" s="32">
-        <f t="shared" ref="K32" si="19">AVERAGE(L32:N32)</f>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L32" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M32" s="32">
-        <v>0</v>
-      </c>
-      <c r="N32" s="32">
-        <v>0</v>
-      </c>
-      <c r="O32" s="12" t="s">
-        <v>188</v>
+      <c r="K32" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L32" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M32" s="38">
+        <v>0</v>
+      </c>
+      <c r="N32" s="38">
+        <v>0</v>
       </c>
       <c r="P32" s="16"/>
       <c r="Q32" s="16"/>
     </row>
-    <row r="33" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>294</v>
+        <v>51</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>390</v>
+        <v>407</v>
       </c>
       <c r="C33" s="15">
-        <v>2836</v>
+        <v>2904</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="E33" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E33" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F33" s="12"/>
       <c r="G33" s="12" t="s">
-        <v>278</v>
+        <v>53</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="I33" s="14">
-        <v>46056</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="I33" s="14"/>
       <c r="J33" s="14"/>
-      <c r="K33" s="32">
-        <f t="shared" ref="K33:K34" si="20">AVERAGE(L33:N33)</f>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L33" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M33" s="32">
-        <v>0</v>
-      </c>
-      <c r="N33" s="32">
+      <c r="K33" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L33" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M33" s="38">
+        <v>0</v>
+      </c>
+      <c r="N33" s="38">
         <v>0</v>
       </c>
       <c r="P33" s="16"/>
       <c r="Q33" s="16"/>
     </row>
-    <row r="34" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>261</v>
+        <v>409</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="E34" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E34" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F34" s="12"/>
       <c r="G34" s="12" t="s">
-        <v>393</v>
+        <v>185</v>
       </c>
       <c r="H34" s="24" t="s">
-        <v>392</v>
-      </c>
-      <c r="I34" s="14">
-        <v>46056</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="I34" s="14"/>
       <c r="J34" s="14"/>
-      <c r="K34" s="32">
-        <f t="shared" si="20"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L34" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M34" s="32">
-        <v>0</v>
-      </c>
-      <c r="N34" s="32">
-        <v>0</v>
-      </c>
-      <c r="O34" s="12" t="s">
-        <v>380</v>
+      <c r="K34" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L34" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M34" s="38">
+        <v>0</v>
+      </c>
+      <c r="N34" s="38">
+        <v>0</v>
       </c>
       <c r="P34" s="16"/>
       <c r="Q34" s="16"/>
     </row>
-    <row r="35" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>301</v>
+        <v>274</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>397</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>405</v>
+        <v>413</v>
+      </c>
+      <c r="C35" s="15">
+        <v>2912</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>409</v>
-      </c>
-      <c r="E35" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E35" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F35" s="12"/>
       <c r="G35" s="12" t="s">
-        <v>303</v>
+        <v>278</v>
       </c>
       <c r="H35" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="I35" s="14">
-        <v>46058</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="I35" s="14"/>
       <c r="J35" s="14"/>
-      <c r="K35" s="32">
-        <f t="shared" ref="K35:K39" si="21">AVERAGE(L35:N35)</f>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L35" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M35" s="32">
-        <v>0</v>
-      </c>
-      <c r="N35" s="32">
+      <c r="K35" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L35" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M35" s="38">
+        <v>0</v>
+      </c>
+      <c r="N35" s="38">
         <v>0</v>
       </c>
       <c r="P35" s="16"/>
@@ -4062,64 +4696,59 @@
     </row>
     <row r="36" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>294</v>
+        <v>91</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="C36" s="15">
-        <v>2858</v>
+        <v>2913</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="E36" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E36" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F36" s="12"/>
       <c r="G36" s="12" t="s">
-        <v>278</v>
+        <v>157</v>
       </c>
       <c r="H36" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="I36" s="14">
-        <v>46059</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="I36" s="14"/>
       <c r="J36" s="14"/>
-      <c r="K36" s="32">
-        <f t="shared" si="21"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L36" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M36" s="32">
-        <v>0</v>
-      </c>
-      <c r="N36" s="32">
-        <v>0</v>
-      </c>
-      <c r="O36" s="12" t="s">
-        <v>188</v>
+      <c r="K36" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L36" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M36" s="38">
+        <v>0</v>
+      </c>
+      <c r="N36" s="38">
+        <v>0</v>
       </c>
       <c r="P36" s="16"/>
       <c r="Q36" s="16"/>
     </row>
-    <row r="37" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>402</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>406</v>
+        <v>416</v>
+      </c>
+      <c r="C37" s="15">
+        <v>2914</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="E37" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="E37" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F37" s="12"/>
@@ -4129,194 +4758,183 @@
       <c r="H37" s="24" t="s">
         <v>418</v>
       </c>
-      <c r="I37" s="14">
-        <v>46059</v>
-      </c>
+      <c r="I37" s="14"/>
       <c r="J37" s="14"/>
-      <c r="K37" s="32">
-        <f t="shared" si="21"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L37" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M37" s="32">
-        <v>0</v>
-      </c>
-      <c r="N37" s="32">
-        <v>0</v>
-      </c>
-      <c r="O37" s="12" t="s">
-        <v>188</v>
+      <c r="K37" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L37" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M37" s="38">
+        <v>0</v>
+      </c>
+      <c r="N37" s="38">
+        <v>0</v>
       </c>
       <c r="P37" s="16"/>
       <c r="Q37" s="16"/>
     </row>
     <row r="38" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>281</v>
+        <v>419</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>403</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>407</v>
+        <v>420</v>
+      </c>
+      <c r="C38" s="15">
+        <v>2917</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>411</v>
-      </c>
-      <c r="E38" s="20" t="s">
+        <v>421</v>
+      </c>
+      <c r="E38" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F38" s="12"/>
       <c r="G38" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="H38" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="I38" s="14">
-        <v>46059</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="I38" s="14"/>
       <c r="J38" s="14"/>
-      <c r="K38" s="32">
-        <f t="shared" si="21"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L38" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M38" s="32">
-        <v>0</v>
-      </c>
-      <c r="N38" s="32">
+      <c r="K38" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L38" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M38" s="38">
+        <v>0</v>
+      </c>
+      <c r="N38" s="38">
         <v>0</v>
       </c>
       <c r="P38" s="16"/>
       <c r="Q38" s="16"/>
     </row>
-    <row r="39" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>404</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>408</v>
+        <v>424</v>
+      </c>
+      <c r="C39" s="15">
+        <v>2928</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="E39" s="20" t="s">
+        <v>425</v>
+      </c>
+      <c r="E39" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F39" s="12"/>
       <c r="G39" s="12" t="s">
-        <v>290</v>
+        <v>155</v>
       </c>
       <c r="H39" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="I39" s="14">
-        <v>46059</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="I39" s="14"/>
       <c r="J39" s="14"/>
-      <c r="K39" s="32">
-        <f t="shared" si="21"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L39" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M39" s="32">
-        <v>0</v>
-      </c>
-      <c r="N39" s="32">
+      <c r="K39" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L39" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M39" s="38">
+        <v>0</v>
+      </c>
+      <c r="N39" s="38">
         <v>0</v>
       </c>
       <c r="P39" s="16"/>
       <c r="Q39" s="16"/>
     </row>
-    <row r="40" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>67</v>
+        <v>427</v>
+      </c>
+      <c r="C40" s="15">
+        <v>5320</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>419</v>
-      </c>
-      <c r="E40" s="20" t="s">
+        <v>428</v>
+      </c>
+      <c r="E40" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F40" s="12"/>
       <c r="G40" s="12" t="s">
-        <v>416</v>
+        <v>127</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14"/>
-      <c r="K40" s="32">
-        <f t="shared" ref="K40" si="22">AVERAGE(L40:N40)</f>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L40" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M40" s="32">
-        <v>0</v>
-      </c>
-      <c r="N40" s="32">
+      <c r="K40" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L40" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M40" s="38">
+        <v>0</v>
+      </c>
+      <c r="N40" s="38">
         <v>0</v>
       </c>
       <c r="P40" s="16"/>
       <c r="Q40" s="16"/>
     </row>
-    <row r="41" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>91</v>
+        <v>426</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="C41" s="15">
-        <v>2863</v>
+        <v>5320</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="E41" s="20" t="s">
+        <v>430</v>
+      </c>
+      <c r="E41" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F41" s="12"/>
       <c r="G41" s="12" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>398</v>
-      </c>
-      <c r="I41" s="14">
-        <v>46062</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="I41" s="14"/>
       <c r="J41" s="14"/>
-      <c r="K41" s="32">
-        <f t="shared" ref="K41" si="23">AVERAGE(L41:N41)</f>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L41" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M41" s="32">
-        <v>0</v>
-      </c>
-      <c r="N41" s="32">
+      <c r="K41" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L41" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M41" s="38">
+        <v>0</v>
+      </c>
+      <c r="N41" s="38">
         <v>0</v>
       </c>
       <c r="P41" s="16"/>
@@ -4324,59 +4942,54 @@
     </row>
     <row r="42" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>255</v>
+        <v>51</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C42" s="15">
-        <v>2872</v>
+        <v>2940</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>429</v>
-      </c>
-      <c r="E42" s="20" t="s">
+        <v>432</v>
+      </c>
+      <c r="E42" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F42" s="12"/>
       <c r="G42" s="12" t="s">
-        <v>155</v>
+        <v>53</v>
       </c>
       <c r="H42" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="I42" s="14">
-        <v>46062</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="I42" s="14"/>
       <c r="J42" s="14"/>
-      <c r="K42" s="32">
-        <f t="shared" ref="K42:K45" si="24">AVERAGE(L42:N42)</f>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L42" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M42" s="32">
-        <v>0</v>
-      </c>
-      <c r="N42" s="32">
-        <v>0</v>
-      </c>
-      <c r="O42" s="12" t="s">
-        <v>188</v>
+      <c r="K42" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L42" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M42" s="38">
+        <v>0</v>
+      </c>
+      <c r="N42" s="38">
+        <v>0</v>
       </c>
       <c r="P42" s="16"/>
       <c r="Q42" s="16"/>
     </row>
-    <row r="43" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>432</v>
-      </c>
-      <c r="C43" s="15" t="s">
         <v>433</v>
+      </c>
+      <c r="C43" s="15">
+        <v>5321</v>
       </c>
       <c r="D43" s="12" t="s">
         <v>434</v>
@@ -4386,17 +4999,15 @@
       </c>
       <c r="F43" s="12"/>
       <c r="G43" s="12" t="s">
-        <v>435</v>
+        <v>127</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>436</v>
-      </c>
-      <c r="I43" s="14">
-        <v>46063</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="I43" s="14"/>
       <c r="J43" s="14"/>
       <c r="K43" s="38">
-        <f t="shared" si="24"/>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L43" s="38">
@@ -4407,38 +5018,37 @@
       </c>
       <c r="N43" s="38">
         <v>0</v>
-      </c>
-      <c r="O43" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="P43" s="16"/>
       <c r="Q43" s="16"/>
     </row>
     <row r="44" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="C44" s="15">
+        <v>2946</v>
+      </c>
+      <c r="D44" s="12" t="s">
         <v>437</v>
       </c>
-      <c r="B44" s="12" t="s">
-        <v>438</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="D44" s="12"/>
       <c r="E44" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F44" s="12"/>
       <c r="G44" s="12" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14"/>
       <c r="K44" s="38">
-        <f t="shared" si="24"/>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L44" s="38">
@@ -4453,33 +5063,33 @@
       <c r="P44" s="16"/>
       <c r="Q44" s="16"/>
     </row>
-    <row r="45" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>431</v>
+        <v>91</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="C45" s="15" t="s">
-        <v>443</v>
+        <v>440</v>
+      </c>
+      <c r="C45" s="15">
+        <v>2963</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>184</v>
+        <v>441</v>
       </c>
       <c r="E45" s="37" t="s">
         <v>3</v>
       </c>
       <c r="F45" s="12"/>
       <c r="G45" s="12" t="s">
-        <v>435</v>
+        <v>157</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>436</v>
+        <v>341</v>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14"/>
       <c r="K45" s="38">
-        <f t="shared" si="24"/>
+        <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L45" s="38">
@@ -4493,7 +5103,3217 @@
       </c>
       <c r="P45" s="16"/>
       <c r="Q45" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="C46" s="15">
+        <v>2978</v>
+      </c>
+      <c r="D46" s="12" t="s">
         <v>444</v>
+      </c>
+      <c r="E46" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="H46" s="24" t="s">
+        <v>446</v>
+      </c>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L46" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M46" s="38">
+        <v>0</v>
+      </c>
+      <c r="N46" s="38">
+        <v>0</v>
+      </c>
+      <c r="O46" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P46" s="16"/>
+      <c r="Q46" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A47" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E47" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="H47" s="24" t="s">
+        <v>451</v>
+      </c>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L47" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M47" s="38">
+        <v>0</v>
+      </c>
+      <c r="N47" s="38">
+        <v>0</v>
+      </c>
+      <c r="P47" s="16"/>
+      <c r="Q47" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A48" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="C48" s="15">
+        <v>2976</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="E48" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H48" s="24" t="s">
+        <v>297</v>
+      </c>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L48" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M48" s="38">
+        <v>0</v>
+      </c>
+      <c r="N48" s="38">
+        <v>0</v>
+      </c>
+      <c r="P48" s="16"/>
+      <c r="Q48" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A49" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="C49" s="15">
+        <v>2986</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="E49" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="H49" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L49" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M49" s="38">
+        <v>0</v>
+      </c>
+      <c r="N49" s="38">
+        <v>0</v>
+      </c>
+      <c r="O49" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P49" s="16"/>
+      <c r="Q49" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="E50" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="H50" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L50" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M50" s="38">
+        <v>0</v>
+      </c>
+      <c r="N50" s="38">
+        <v>0</v>
+      </c>
+      <c r="O50" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P50" s="16"/>
+      <c r="Q50" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>460</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="E51" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="H51" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L51" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M51" s="38">
+        <v>0</v>
+      </c>
+      <c r="N51" s="38">
+        <v>0</v>
+      </c>
+      <c r="P51" s="16"/>
+      <c r="Q51" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="E52" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L52" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M52" s="38">
+        <v>0</v>
+      </c>
+      <c r="N52" s="38">
+        <v>0</v>
+      </c>
+      <c r="P52" s="16"/>
+      <c r="Q52" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="C53" s="15">
+        <v>3023</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="E53" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="H53" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L53" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M53" s="38">
+        <v>0</v>
+      </c>
+      <c r="N53" s="38">
+        <v>0</v>
+      </c>
+      <c r="O53" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P53" s="16"/>
+      <c r="Q53" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="C54" s="15">
+        <v>3030</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="E54" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="H54" s="24" t="s">
+        <v>446</v>
+      </c>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L54" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M54" s="38">
+        <v>0</v>
+      </c>
+      <c r="N54" s="38">
+        <v>0</v>
+      </c>
+      <c r="P54" s="16"/>
+      <c r="Q54" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A55" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>471</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="E55" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="H55" s="24" t="s">
+        <v>335</v>
+      </c>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L55" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M55" s="38">
+        <v>0</v>
+      </c>
+      <c r="N55" s="38">
+        <v>0</v>
+      </c>
+      <c r="P55" s="16"/>
+      <c r="Q55" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="C56" s="15">
+        <v>5333</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="E56" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="H56" s="24" t="s">
+        <v>429</v>
+      </c>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L56" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M56" s="38">
+        <v>0</v>
+      </c>
+      <c r="N56" s="38">
+        <v>0</v>
+      </c>
+      <c r="P56" s="16"/>
+      <c r="Q56" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+      <c r="A57" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="C57" s="15">
+        <v>5333</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="E57" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="H57" s="24" t="s">
+        <v>429</v>
+      </c>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L57" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M57" s="38">
+        <v>0</v>
+      </c>
+      <c r="N57" s="38">
+        <v>0</v>
+      </c>
+      <c r="P57" s="16"/>
+      <c r="Q57" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="C58" s="15">
+        <v>3044</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="E58" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="H58" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L58" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M58" s="38">
+        <v>0</v>
+      </c>
+      <c r="N58" s="38">
+        <v>0</v>
+      </c>
+      <c r="P58" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q58" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A59" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="E59" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="H59" s="24" t="s">
+        <v>485</v>
+      </c>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L59" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M59" s="38">
+        <v>0</v>
+      </c>
+      <c r="N59" s="38">
+        <v>0</v>
+      </c>
+      <c r="P59" s="16"/>
+      <c r="Q59" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A60" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="C60" s="15">
+        <v>3090</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="E60" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="H60" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L60" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M60" s="38">
+        <v>0</v>
+      </c>
+      <c r="N60" s="38">
+        <v>0</v>
+      </c>
+      <c r="O60" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P60" s="16"/>
+      <c r="Q60" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A61" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>488</v>
+      </c>
+      <c r="C61" s="15">
+        <v>3096</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E61" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="H61" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L61" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M61" s="38">
+        <v>0</v>
+      </c>
+      <c r="N61" s="38">
+        <v>0</v>
+      </c>
+      <c r="P61" s="16"/>
+      <c r="Q61" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="E62" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="H62" s="24" t="s">
+        <v>335</v>
+      </c>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+      <c r="K62" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L62" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M62" s="38">
+        <v>0</v>
+      </c>
+      <c r="N62" s="38">
+        <v>0</v>
+      </c>
+      <c r="P62" s="16"/>
+      <c r="Q62" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="C63" s="15">
+        <v>10001</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>494</v>
+      </c>
+      <c r="E63" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12" t="s">
+        <v>495</v>
+      </c>
+      <c r="H63" s="24" t="s">
+        <v>496</v>
+      </c>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L63" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M63" s="38">
+        <v>0</v>
+      </c>
+      <c r="N63" s="38">
+        <v>0</v>
+      </c>
+      <c r="P63" s="16"/>
+      <c r="Q63" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="C64" s="15">
+        <v>10001</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="E64" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12" t="s">
+        <v>495</v>
+      </c>
+      <c r="H64" s="24" t="s">
+        <v>496</v>
+      </c>
+      <c r="I64" s="14"/>
+      <c r="J64" s="14"/>
+      <c r="K64" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L64" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M64" s="38">
+        <v>0</v>
+      </c>
+      <c r="N64" s="38">
+        <v>0</v>
+      </c>
+      <c r="P64" s="16"/>
+      <c r="Q64" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A65" s="12" t="s">
+        <v>499</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>500</v>
+      </c>
+      <c r="C65" s="15">
+        <v>3107</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="E65" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="H65" s="24" t="s">
+        <v>503</v>
+      </c>
+      <c r="I65" s="14"/>
+      <c r="J65" s="14"/>
+      <c r="K65" s="38">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L65" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M65" s="38">
+        <v>0</v>
+      </c>
+      <c r="N65" s="38">
+        <v>0</v>
+      </c>
+      <c r="P65" s="16"/>
+      <c r="Q65" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A66" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="C66" s="15">
+        <v>3110</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="E66" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="H66" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="I66" s="14"/>
+      <c r="J66" s="14"/>
+      <c r="K66" s="38">
+        <f t="shared" ref="K66:K122" si="1">AVERAGE(L66:N66)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L66" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M66" s="38">
+        <v>0</v>
+      </c>
+      <c r="N66" s="38">
+        <v>0</v>
+      </c>
+      <c r="P66" s="16"/>
+      <c r="Q66" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A67" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>507</v>
+      </c>
+      <c r="C67" s="15">
+        <v>3111</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>508</v>
+      </c>
+      <c r="E67" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="H67" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="I67" s="14"/>
+      <c r="J67" s="14"/>
+      <c r="K67" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L67" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M67" s="38">
+        <v>0</v>
+      </c>
+      <c r="N67" s="38">
+        <v>0</v>
+      </c>
+      <c r="O67" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P67" s="16"/>
+      <c r="Q67" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="C68" s="15">
+        <v>3128</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="E68" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="H68" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+      <c r="K68" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L68" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M68" s="38">
+        <v>0</v>
+      </c>
+      <c r="N68" s="38">
+        <v>0</v>
+      </c>
+      <c r="O68" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P68" s="16"/>
+      <c r="Q68" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A69" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="B69" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="C69" s="15">
+        <v>3153</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>512</v>
+      </c>
+      <c r="E69" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="H69" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14"/>
+      <c r="K69" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L69" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M69" s="38">
+        <v>0</v>
+      </c>
+      <c r="N69" s="38">
+        <v>0</v>
+      </c>
+      <c r="P69" s="16"/>
+      <c r="Q69" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A70" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="C70" s="15">
+        <v>3160</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="E70" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="H70" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14"/>
+      <c r="K70" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L70" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M70" s="38">
+        <v>0</v>
+      </c>
+      <c r="N70" s="38">
+        <v>0</v>
+      </c>
+      <c r="P70" s="16"/>
+      <c r="Q70" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A71" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>518</v>
+      </c>
+      <c r="E71" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F71" s="12"/>
+      <c r="G71" s="20" t="s">
+        <v>336</v>
+      </c>
+      <c r="H71" s="25" t="s">
+        <v>335</v>
+      </c>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+      <c r="K71" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L71" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M71" s="38">
+        <v>0</v>
+      </c>
+      <c r="N71" s="38">
+        <v>0</v>
+      </c>
+      <c r="P71" s="16"/>
+      <c r="Q71" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A72" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>519</v>
+      </c>
+      <c r="C72" s="15">
+        <v>3179</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>520</v>
+      </c>
+      <c r="E72" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="H72" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+      <c r="K72" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L72" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M72" s="38">
+        <v>0</v>
+      </c>
+      <c r="N72" s="38">
+        <v>0</v>
+      </c>
+      <c r="P72" s="16"/>
+      <c r="Q72" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A73" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>522</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>523</v>
+      </c>
+      <c r="E73" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="H73" s="24" t="s">
+        <v>335</v>
+      </c>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+      <c r="K73" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L73" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M73" s="38">
+        <v>0</v>
+      </c>
+      <c r="N73" s="38">
+        <v>0</v>
+      </c>
+      <c r="P73" s="16"/>
+      <c r="Q73" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A74" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="C74" s="15">
+        <v>3190</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="E74" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="H74" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+      <c r="K74" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L74" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M74" s="38">
+        <v>0</v>
+      </c>
+      <c r="N74" s="38">
+        <v>0</v>
+      </c>
+      <c r="P74" s="16"/>
+      <c r="Q74" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A75" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>526</v>
+      </c>
+      <c r="C75" s="15">
+        <v>3197</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>527</v>
+      </c>
+      <c r="E75" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="H75" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="I75" s="14"/>
+      <c r="J75" s="14"/>
+      <c r="K75" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L75" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M75" s="38">
+        <v>0</v>
+      </c>
+      <c r="N75" s="38">
+        <v>0</v>
+      </c>
+      <c r="P75" s="16"/>
+      <c r="Q75" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>528</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>529</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="E76" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F76" s="12"/>
+      <c r="G76" s="20" t="s">
+        <v>376</v>
+      </c>
+      <c r="H76" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="I76" s="14"/>
+      <c r="J76" s="14"/>
+      <c r="K76" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L76" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M76" s="38">
+        <v>0</v>
+      </c>
+      <c r="N76" s="38">
+        <v>0</v>
+      </c>
+      <c r="P76" s="16"/>
+      <c r="Q76" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A77" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>531</v>
+      </c>
+      <c r="C77" s="15">
+        <v>3213</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>532</v>
+      </c>
+      <c r="E77" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F77" s="12"/>
+      <c r="G77" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H77" s="24" t="s">
+        <v>297</v>
+      </c>
+      <c r="I77" s="14"/>
+      <c r="J77" s="14"/>
+      <c r="K77" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L77" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M77" s="38">
+        <v>0</v>
+      </c>
+      <c r="N77" s="38">
+        <v>0</v>
+      </c>
+      <c r="P77" s="16"/>
+      <c r="Q77" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A78" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="C78" s="15">
+        <v>3220</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="E78" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F78" s="12"/>
+      <c r="G78" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="H78" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="I78" s="14"/>
+      <c r="J78" s="14"/>
+      <c r="K78" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L78" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M78" s="38">
+        <v>0</v>
+      </c>
+      <c r="N78" s="38">
+        <v>0</v>
+      </c>
+      <c r="P78" s="16" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q78" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A79" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="C79" s="15"/>
+      <c r="D79" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="E79" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F79" s="12"/>
+      <c r="G79" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="H79" s="39" t="s">
+        <v>539</v>
+      </c>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14"/>
+      <c r="K79" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L79" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M79" s="38">
+        <v>0</v>
+      </c>
+      <c r="N79" s="38">
+        <v>0</v>
+      </c>
+      <c r="P79" s="16"/>
+      <c r="Q79" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A80" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>540</v>
+      </c>
+      <c r="C80" s="15">
+        <v>3226</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="E80" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F80" s="12"/>
+      <c r="G80" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="H80" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="I80" s="14"/>
+      <c r="J80" s="14"/>
+      <c r="K80" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L80" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M80" s="38">
+        <v>0</v>
+      </c>
+      <c r="N80" s="38">
+        <v>0</v>
+      </c>
+      <c r="P80" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="Q80" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A81" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>543</v>
+      </c>
+      <c r="C81" s="15">
+        <v>3231</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="E81" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="H81" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="I81" s="14"/>
+      <c r="J81" s="14"/>
+      <c r="K81" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L81" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M81" s="38">
+        <v>0</v>
+      </c>
+      <c r="N81" s="38">
+        <v>0</v>
+      </c>
+      <c r="P81" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q81" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A82" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>544</v>
+      </c>
+      <c r="C82" s="15">
+        <v>3236</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E82" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F82" s="12"/>
+      <c r="G82" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="H82" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="I82" s="14"/>
+      <c r="J82" s="14"/>
+      <c r="K82" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L82" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M82" s="38">
+        <v>0</v>
+      </c>
+      <c r="N82" s="38">
+        <v>0</v>
+      </c>
+      <c r="P82" s="16" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q82" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A83" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="B83" s="12" t="s">
+        <v>545</v>
+      </c>
+      <c r="C83" s="15">
+        <v>3240</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="E83" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="I83" s="14"/>
+      <c r="J83" s="14"/>
+      <c r="K83" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L83" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M83" s="38">
+        <v>0</v>
+      </c>
+      <c r="N83" s="38">
+        <v>0</v>
+      </c>
+      <c r="P83" s="16"/>
+      <c r="Q83" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A84" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="B84" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="C84" s="15">
+        <v>3242</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="E84" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="H84" s="24" t="s">
+        <v>446</v>
+      </c>
+      <c r="I84" s="14"/>
+      <c r="J84" s="14"/>
+      <c r="K84" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L84" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M84" s="38">
+        <v>0</v>
+      </c>
+      <c r="N84" s="38">
+        <v>0</v>
+      </c>
+      <c r="P84" s="16"/>
+      <c r="Q84" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+      <c r="A85" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B85" s="12"/>
+      <c r="C85" s="15"/>
+      <c r="D85" s="12"/>
+      <c r="E85" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="H85" s="24" t="s">
+        <v>550</v>
+      </c>
+      <c r="I85" s="14"/>
+      <c r="J85" s="14"/>
+      <c r="K85" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L85" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M85" s="38">
+        <v>0</v>
+      </c>
+      <c r="N85" s="38">
+        <v>0</v>
+      </c>
+      <c r="P85" s="16"/>
+      <c r="Q85" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+      <c r="A86" s="12"/>
+      <c r="B86" s="12"/>
+      <c r="C86" s="15"/>
+      <c r="D86" s="12"/>
+      <c r="E86" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F86" s="12"/>
+      <c r="G86" s="12" t="s">
+        <v>551</v>
+      </c>
+      <c r="H86" s="24" t="s">
+        <v>552</v>
+      </c>
+      <c r="I86" s="14"/>
+      <c r="J86" s="14"/>
+      <c r="K86" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L86" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M86" s="38">
+        <v>0</v>
+      </c>
+      <c r="N86" s="38">
+        <v>0</v>
+      </c>
+      <c r="P86" s="16"/>
+      <c r="Q86" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A87" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="B87" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="C87" s="15">
+        <v>3241</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>554</v>
+      </c>
+      <c r="E87" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="H87" s="24" t="s">
+        <v>446</v>
+      </c>
+      <c r="I87" s="14"/>
+      <c r="J87" s="14"/>
+      <c r="K87" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L87" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M87" s="38">
+        <v>0</v>
+      </c>
+      <c r="N87" s="38">
+        <v>0</v>
+      </c>
+      <c r="P87" s="16"/>
+      <c r="Q87" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A88" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B88" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="C88" s="15" t="s">
+        <v>556</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="E88" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="H88" s="24" t="s">
+        <v>335</v>
+      </c>
+      <c r="I88" s="14"/>
+      <c r="J88" s="14"/>
+      <c r="K88" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L88" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M88" s="38">
+        <v>0</v>
+      </c>
+      <c r="N88" s="38">
+        <v>0</v>
+      </c>
+      <c r="P88" s="16"/>
+      <c r="Q88" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A89" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="C89" s="15">
+        <v>3273</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="E89" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="12"/>
+      <c r="G89" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="H89" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="I89" s="14"/>
+      <c r="J89" s="14"/>
+      <c r="K89" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L89" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M89" s="38">
+        <v>0</v>
+      </c>
+      <c r="N89" s="38">
+        <v>0</v>
+      </c>
+      <c r="P89" s="16"/>
+      <c r="Q89" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A90" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="B90" s="12" t="s">
+        <v>560</v>
+      </c>
+      <c r="C90" s="15">
+        <v>3276</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="E90" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F90" s="12"/>
+      <c r="G90" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="I90" s="14"/>
+      <c r="J90" s="14"/>
+      <c r="K90" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L90" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M90" s="38">
+        <v>0</v>
+      </c>
+      <c r="N90" s="38">
+        <v>0</v>
+      </c>
+      <c r="P90" s="16"/>
+      <c r="Q90" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A91" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>562</v>
+      </c>
+      <c r="C91" s="15">
+        <v>3282</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="E91" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="12"/>
+      <c r="G91" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="I91" s="14"/>
+      <c r="J91" s="14"/>
+      <c r="K91" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L91" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M91" s="38">
+        <v>0</v>
+      </c>
+      <c r="N91" s="38">
+        <v>0</v>
+      </c>
+      <c r="P91" s="16"/>
+      <c r="Q91" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A92" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="B92" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="C92" s="15">
+        <v>3283</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="E92" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F92" s="12"/>
+      <c r="G92" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="I92" s="14"/>
+      <c r="J92" s="14"/>
+      <c r="K92" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L92" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M92" s="38">
+        <v>0</v>
+      </c>
+      <c r="N92" s="38">
+        <v>0</v>
+      </c>
+      <c r="P92" s="16"/>
+      <c r="Q92" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A93" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="C93" s="15" t="s">
+        <v>566</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="E93" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F93" s="12"/>
+      <c r="G93" s="12"/>
+      <c r="H93" s="24" t="s">
+        <v>335</v>
+      </c>
+      <c r="I93" s="14"/>
+      <c r="J93" s="14"/>
+      <c r="K93" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L93" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M93" s="38">
+        <v>0</v>
+      </c>
+      <c r="N93" s="38">
+        <v>0</v>
+      </c>
+      <c r="P93" s="16"/>
+      <c r="Q93" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+      <c r="A94" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="C94" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="E94" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12" t="s">
+        <v>571</v>
+      </c>
+      <c r="H94" s="24" t="s">
+        <v>572</v>
+      </c>
+      <c r="I94" s="14"/>
+      <c r="J94" s="14"/>
+      <c r="K94" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L94" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M94" s="38">
+        <v>0</v>
+      </c>
+      <c r="N94" s="38">
+        <v>0</v>
+      </c>
+      <c r="P94" s="16"/>
+      <c r="Q94" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A95" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="B95" s="12" t="s">
+        <v>573</v>
+      </c>
+      <c r="C95" s="15">
+        <v>3292</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>574</v>
+      </c>
+      <c r="E95" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F95" s="12"/>
+      <c r="G95" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="I95" s="14"/>
+      <c r="J95" s="14"/>
+      <c r="K95" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L95" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M95" s="38">
+        <v>0</v>
+      </c>
+      <c r="N95" s="38">
+        <v>0</v>
+      </c>
+      <c r="P95" s="16"/>
+      <c r="Q95" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A96" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>575</v>
+      </c>
+      <c r="C96" s="15">
+        <v>3294</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>576</v>
+      </c>
+      <c r="E96" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="H96" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="I96" s="14"/>
+      <c r="J96" s="14"/>
+      <c r="K96" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L96" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M96" s="38">
+        <v>0</v>
+      </c>
+      <c r="N96" s="38">
+        <v>0</v>
+      </c>
+      <c r="P96" s="16"/>
+      <c r="Q96" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A97" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>577</v>
+      </c>
+      <c r="C97" s="15" t="s">
+        <v>578</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>579</v>
+      </c>
+      <c r="E97" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="H97" s="24" t="s">
+        <v>580</v>
+      </c>
+      <c r="I97" s="14"/>
+      <c r="J97" s="14"/>
+      <c r="K97" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L97" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M97" s="38">
+        <v>0</v>
+      </c>
+      <c r="N97" s="38">
+        <v>0</v>
+      </c>
+      <c r="P97" s="16"/>
+      <c r="Q97" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A98" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="B98" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="C98" s="15">
+        <v>3300</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>582</v>
+      </c>
+      <c r="E98" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F98" s="12"/>
+      <c r="G98" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="I98" s="14"/>
+      <c r="J98" s="14"/>
+      <c r="K98" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L98" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M98" s="38">
+        <v>0</v>
+      </c>
+      <c r="N98" s="38">
+        <v>0</v>
+      </c>
+      <c r="P98" s="16"/>
+      <c r="Q98" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A99" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="C99" s="15" t="s">
+        <v>584</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>585</v>
+      </c>
+      <c r="E99" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12"/>
+      <c r="H99" s="24" t="s">
+        <v>335</v>
+      </c>
+      <c r="I99" s="14"/>
+      <c r="J99" s="14"/>
+      <c r="K99" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L99" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M99" s="38">
+        <v>0</v>
+      </c>
+      <c r="N99" s="38">
+        <v>0</v>
+      </c>
+      <c r="P99" s="16"/>
+      <c r="Q99" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A100" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B100" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="C100" s="15">
+        <v>3333</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E100" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="12"/>
+      <c r="G100" s="12"/>
+      <c r="H100" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="I100" s="14"/>
+      <c r="J100" s="14"/>
+      <c r="K100" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L100" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M100" s="38">
+        <v>0</v>
+      </c>
+      <c r="N100" s="38">
+        <v>0</v>
+      </c>
+      <c r="P100" s="16" t="s">
+        <v>587</v>
+      </c>
+      <c r="Q100" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A101" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="B101" s="12" t="s">
+        <v>588</v>
+      </c>
+      <c r="C101" s="15">
+        <v>3336</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="E101" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="12"/>
+      <c r="G101" s="12"/>
+      <c r="H101" s="24" t="s">
+        <v>446</v>
+      </c>
+      <c r="I101" s="14"/>
+      <c r="J101" s="14"/>
+      <c r="K101" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L101" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M101" s="38">
+        <v>0</v>
+      </c>
+      <c r="N101" s="38">
+        <v>0</v>
+      </c>
+      <c r="P101" s="16"/>
+      <c r="Q101" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A102" s="12" t="s">
+        <v>589</v>
+      </c>
+      <c r="B102" s="12" t="s">
+        <v>590</v>
+      </c>
+      <c r="C102" s="15">
+        <v>3339</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="E102" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F102" s="12"/>
+      <c r="G102" s="12"/>
+      <c r="H102" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="I102"/>
+      <c r="J102"/>
+      <c r="K102" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L102" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M102" s="38">
+        <v>0</v>
+      </c>
+      <c r="N102" s="38">
+        <v>0</v>
+      </c>
+      <c r="P102" s="16"/>
+      <c r="Q102" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A103" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="B103" s="12" t="s">
+        <v>593</v>
+      </c>
+      <c r="C103" s="15">
+        <v>3341</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>594</v>
+      </c>
+      <c r="E103" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F103" s="12"/>
+      <c r="G103" s="12"/>
+      <c r="H103" s="24" t="s">
+        <v>595</v>
+      </c>
+      <c r="I103" s="14"/>
+      <c r="J103" s="14"/>
+      <c r="K103" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L103" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M103" s="38">
+        <v>0</v>
+      </c>
+      <c r="N103" s="38">
+        <v>0</v>
+      </c>
+      <c r="P103" s="16"/>
+      <c r="Q103" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A104" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="B104" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="C104" s="15">
+        <v>3356</v>
+      </c>
+      <c r="D104" s="12" t="s">
+        <v>597</v>
+      </c>
+      <c r="E104" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F104" s="12"/>
+      <c r="G104" s="12"/>
+      <c r="H104" s="24" t="s">
+        <v>446</v>
+      </c>
+      <c r="I104" s="14"/>
+      <c r="J104" s="14"/>
+      <c r="K104" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L104" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M104" s="38">
+        <v>0</v>
+      </c>
+      <c r="N104" s="38">
+        <v>0</v>
+      </c>
+      <c r="P104" s="34" t="s">
+        <v>598</v>
+      </c>
+      <c r="Q104" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A105" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="B105" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="C105" s="15">
+        <v>3357</v>
+      </c>
+      <c r="D105" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="E105" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F105" s="12"/>
+      <c r="G105" s="12"/>
+      <c r="H105" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="I105" s="14"/>
+      <c r="J105" s="14"/>
+      <c r="K105" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L105" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M105" s="38">
+        <v>0</v>
+      </c>
+      <c r="N105" s="38">
+        <v>0</v>
+      </c>
+      <c r="P105" s="16"/>
+      <c r="Q105" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A106" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B106" s="12" t="s">
+        <v>601</v>
+      </c>
+      <c r="C106" s="15" t="s">
+        <v>602</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>603</v>
+      </c>
+      <c r="E106" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F106" s="12"/>
+      <c r="G106" s="12"/>
+      <c r="H106" s="24" t="s">
+        <v>335</v>
+      </c>
+      <c r="I106" s="14"/>
+      <c r="J106" s="14"/>
+      <c r="K106" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L106" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M106" s="38">
+        <v>0</v>
+      </c>
+      <c r="N106" s="38">
+        <v>0</v>
+      </c>
+      <c r="P106" s="16"/>
+      <c r="Q106" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A107" s="12" t="s">
+        <v>589</v>
+      </c>
+      <c r="B107" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="C107" s="15">
+        <v>3374</v>
+      </c>
+      <c r="D107" s="12" t="s">
+        <v>605</v>
+      </c>
+      <c r="E107" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F107" s="12"/>
+      <c r="G107" s="12"/>
+      <c r="H107" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="I107" s="14"/>
+      <c r="J107" s="14"/>
+      <c r="K107" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L107" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M107" s="38">
+        <v>0</v>
+      </c>
+      <c r="N107" s="38">
+        <v>0</v>
+      </c>
+      <c r="P107" s="16"/>
+      <c r="Q107" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A108" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="B108" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="C108" s="15">
+        <v>3382</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>607</v>
+      </c>
+      <c r="E108" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F108" s="12"/>
+      <c r="G108" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="H108" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="I108" s="14"/>
+      <c r="J108" s="14"/>
+      <c r="K108" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L108" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M108" s="38">
+        <v>0</v>
+      </c>
+      <c r="N108" s="38">
+        <v>0</v>
+      </c>
+      <c r="P108" s="16"/>
+      <c r="Q108" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A109" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="B109" s="12" t="s">
+        <v>608</v>
+      </c>
+      <c r="C109" s="15">
+        <v>3391</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>609</v>
+      </c>
+      <c r="E109" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F109" s="12"/>
+      <c r="G109" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="H109" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="I109" s="14"/>
+      <c r="J109" s="14"/>
+      <c r="K109" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L109" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M109" s="38">
+        <v>0</v>
+      </c>
+      <c r="N109" s="38">
+        <v>0</v>
+      </c>
+      <c r="P109" s="16"/>
+      <c r="Q109" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A110" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="B110" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="C110" s="15">
+        <v>3387</v>
+      </c>
+      <c r="D110" s="12"/>
+      <c r="E110" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F110" s="12"/>
+      <c r="G110" s="12"/>
+      <c r="H110" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="I110" s="14"/>
+      <c r="J110" s="14"/>
+      <c r="K110" s="38">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L110" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="M110" s="38">
+        <v>0</v>
+      </c>
+      <c r="N110" s="38">
+        <v>0</v>
+      </c>
+      <c r="P110" s="16"/>
+      <c r="Q110" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A111" s="12" t="s">
+        <v>589</v>
+      </c>
+      <c r="B111" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="C111" s="15">
+        <v>3396</v>
+      </c>
+      <c r="D111" s="12"/>
+      <c r="E111" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F111" s="12"/>
+      <c r="G111" s="20"/>
+      <c r="H111" s="25" t="s">
+        <v>592</v>
+      </c>
+      <c r="I111" s="14"/>
+      <c r="J111" s="14"/>
+      <c r="K111" s="32">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L111" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M111" s="32">
+        <v>0</v>
+      </c>
+      <c r="N111" s="32">
+        <v>0</v>
+      </c>
+      <c r="P111" s="16"/>
+      <c r="Q111" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A112" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B112" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="C112" s="15" t="s">
+        <v>613</v>
+      </c>
+      <c r="D112" s="12"/>
+      <c r="E112" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F112" s="12"/>
+      <c r="G112" s="12"/>
+      <c r="H112" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="I112" s="14"/>
+      <c r="J112" s="14"/>
+      <c r="K112" s="32">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L112" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M112" s="32">
+        <v>0</v>
+      </c>
+      <c r="N112" s="32">
+        <v>0</v>
+      </c>
+      <c r="P112" s="16"/>
+      <c r="Q112" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A113" s="12" t="s">
+        <v>499</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>614</v>
+      </c>
+      <c r="C113" s="15">
+        <v>3414</v>
+      </c>
+      <c r="D113" s="12"/>
+      <c r="E113" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F113" s="12"/>
+      <c r="G113" s="12"/>
+      <c r="H113" s="26" t="s">
+        <v>503</v>
+      </c>
+      <c r="I113" s="14"/>
+      <c r="J113" s="14"/>
+      <c r="K113" s="32">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L113" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M113" s="32">
+        <v>0</v>
+      </c>
+      <c r="N113" s="32">
+        <v>0</v>
+      </c>
+      <c r="P113" s="16"/>
+      <c r="Q113" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A114" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B114" s="12" t="s">
+        <v>615</v>
+      </c>
+      <c r="C114" s="15">
+        <v>3421</v>
+      </c>
+      <c r="D114" s="12"/>
+      <c r="E114" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F114" s="12"/>
+      <c r="G114" s="12"/>
+      <c r="H114" s="25" t="s">
+        <v>295</v>
+      </c>
+      <c r="I114" s="14"/>
+      <c r="J114" s="14"/>
+      <c r="K114" s="32">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L114" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M114" s="32">
+        <v>0</v>
+      </c>
+      <c r="N114" s="32">
+        <v>0</v>
+      </c>
+      <c r="P114" s="16"/>
+      <c r="Q114" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A115" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="B115" s="12" t="s">
+        <v>616</v>
+      </c>
+      <c r="C115" s="15">
+        <v>3423</v>
+      </c>
+      <c r="D115" s="12"/>
+      <c r="E115" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F115" s="12"/>
+      <c r="G115" s="12"/>
+      <c r="H115" s="26" t="s">
+        <v>423</v>
+      </c>
+      <c r="I115" s="14"/>
+      <c r="J115" s="14"/>
+      <c r="K115" s="32">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L115" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M115" s="32">
+        <v>0</v>
+      </c>
+      <c r="N115" s="32">
+        <v>0</v>
+      </c>
+      <c r="P115" s="16"/>
+      <c r="Q115" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A116" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="B116" s="12" t="s">
+        <v>617</v>
+      </c>
+      <c r="C116" s="15">
+        <v>3427</v>
+      </c>
+      <c r="D116" s="12"/>
+      <c r="E116" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F116" s="12"/>
+      <c r="G116" s="12"/>
+      <c r="H116" s="26" t="s">
+        <v>439</v>
+      </c>
+      <c r="I116" s="14"/>
+      <c r="J116" s="14"/>
+      <c r="K116" s="32">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L116" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M116" s="32">
+        <v>0</v>
+      </c>
+      <c r="N116" s="32">
+        <v>0</v>
+      </c>
+      <c r="P116" s="16"/>
+      <c r="Q116" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A117" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="B117" s="12" t="s">
+        <v>618</v>
+      </c>
+      <c r="C117" s="15">
+        <v>3433</v>
+      </c>
+      <c r="D117" s="12"/>
+      <c r="E117" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F117" s="12"/>
+      <c r="G117" s="12"/>
+      <c r="H117" s="26" t="s">
+        <v>439</v>
+      </c>
+      <c r="I117" s="14"/>
+      <c r="J117" s="14"/>
+      <c r="K117" s="32">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L117" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M117" s="32">
+        <v>0</v>
+      </c>
+      <c r="N117" s="32">
+        <v>0</v>
+      </c>
+      <c r="P117" s="16"/>
+      <c r="Q117" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A118" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="B118" s="12" t="s">
+        <v>619</v>
+      </c>
+      <c r="C118" s="15"/>
+      <c r="D118" s="12"/>
+      <c r="E118" s="12"/>
+      <c r="F118" s="12"/>
+      <c r="G118" s="12"/>
+      <c r="H118" s="24"/>
+      <c r="I118" s="14"/>
+      <c r="J118" s="14"/>
+      <c r="K118" s="32">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L118" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M118" s="32">
+        <v>0</v>
+      </c>
+      <c r="N118" s="32">
+        <v>0</v>
+      </c>
+      <c r="P118" s="16"/>
+      <c r="Q118" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A119" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="B119" s="12" t="s">
+        <v>620</v>
+      </c>
+      <c r="C119" s="15"/>
+      <c r="D119" s="12"/>
+      <c r="E119" s="12"/>
+      <c r="F119" s="12"/>
+      <c r="G119" s="12"/>
+      <c r="H119" s="24"/>
+      <c r="I119" s="14"/>
+      <c r="J119" s="14"/>
+      <c r="K119" s="32">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L119" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M119" s="32">
+        <v>0</v>
+      </c>
+      <c r="N119" s="32">
+        <v>0</v>
+      </c>
+      <c r="P119" s="16"/>
+      <c r="Q119" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A120" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B120" s="12" t="s">
+        <v>621</v>
+      </c>
+      <c r="C120" s="15"/>
+      <c r="D120" s="12"/>
+      <c r="E120" s="12"/>
+      <c r="F120" s="12"/>
+      <c r="G120" s="12"/>
+      <c r="H120" s="24"/>
+      <c r="I120" s="14"/>
+      <c r="J120" s="14"/>
+      <c r="K120" s="32">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L120" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M120" s="32">
+        <v>0</v>
+      </c>
+      <c r="N120" s="32">
+        <v>0</v>
+      </c>
+      <c r="P120" s="16"/>
+      <c r="Q120" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A121" s="12"/>
+      <c r="B121" s="12" t="s">
+        <v>622</v>
+      </c>
+      <c r="C121" s="15"/>
+      <c r="D121" s="12"/>
+      <c r="E121" s="12"/>
+      <c r="F121" s="12"/>
+      <c r="G121" s="12"/>
+      <c r="H121" s="24"/>
+      <c r="I121" s="14"/>
+      <c r="J121" s="14"/>
+      <c r="K121" s="16" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L121" s="16"/>
+      <c r="M121" s="16"/>
+      <c r="N121" s="16"/>
+      <c r="P121" s="16"/>
+      <c r="Q121" s="34" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A122" s="12"/>
+      <c r="B122" s="12"/>
+      <c r="C122" s="15"/>
+      <c r="D122" s="12"/>
+      <c r="E122" s="12"/>
+      <c r="F122" s="12"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="24"/>
+      <c r="I122" s="14"/>
+      <c r="J122" s="14"/>
+      <c r="K122" s="16" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L122" s="16"/>
+      <c r="M122" s="16"/>
+      <c r="N122" s="16"/>
+      <c r="P122" s="16"/>
+      <c r="Q122" s="34" t="s">
+        <v>385</v>
       </c>
     </row>
   </sheetData>

--- a/Client Information App.xlsx
+++ b/Client Information App.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aryte\PycharmProjects\AlucladApp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\06 Operation\1. Operation Documents\3. Project Cordination\5. Data Analytics\Power Bi Projects\1. PB2401 Client Information\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC47CF9-E339-40B4-92C8-CD2DA6353FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D0425E-BBD9-42C4-B0C4-135CDED41D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="768" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="768" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CRM main" sheetId="2" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="553">
   <si>
     <t>Ready to dispatch</t>
   </si>
@@ -1069,16 +1069,6 @@
     <t>G2 3BW</t>
   </si>
   <si>
-    <t>SO-1997</t>
-  </si>
-  <si>
-    <t>EX CW Panels &amp; Pressings</t>
-  </si>
-  <si>
-    <t>Assembly
-CSK Hole</t>
-  </si>
-  <si>
     <t>Thurrock Power Limited
 Thurrock Flexible Generation
 Station Road
@@ -1099,24 +1089,7 @@
     <t>RM18 8QR</t>
   </si>
   <si>
-    <t xml:space="preserve"> RM18 8QR</t>
-  </si>
-  <si>
-    <t>Thurrock Power Limited,
-Thurrock Flexible Generation,
-Station Road,
-East Tilbury,
-RM18 8QR
-Vlad +44 (0) 7584 078 721</t>
-  </si>
-  <si>
-    <t>SO-2005</t>
-  </si>
-  <si>
     <t>Aluworks</t>
-  </si>
-  <si>
-    <t>PO41325-608</t>
   </si>
   <si>
     <t>Aluworks Ltd.
@@ -1133,36 +1106,11 @@
     <t>Southbank Place</t>
   </si>
   <si>
-    <t>DA10 0B</t>
-  </si>
-  <si>
     <t>St George Plc
 ,Camden Goods Yard,
 Chalk Farm Road, Chalk Farm
 ,Camden Town,London, NW1 8EH
 Contact: Arek +44 (0) 7534 515 939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thurrock </t>
-  </si>
-  <si>
-    <t>Yellow Storage Brackets (Batch. 2)</t>
-  </si>
-  <si>
-    <t>Royal Central School</t>
-  </si>
-  <si>
-    <t>RCS003</t>
-  </si>
-  <si>
-    <t>NW3 3HY</t>
-  </si>
-  <si>
-    <t>FC Direct Ltd, Royal Central School of Speech and Drama, Eton Avenue, Belsize Park, London, NW3 3HY
-Luis Valle - +44 (0) 7765 777 672 / Aaran Barratt - +44 (0) 7464 485 453</t>
-  </si>
-  <si>
-    <t>Sinusoidal Panels</t>
   </si>
   <si>
     <t>McAleer &amp; Rushe Contracts UK Ltd
@@ -1173,9 +1121,6 @@
 Contact: Jakub +44 (0) 7772 728 234</t>
   </si>
   <si>
-    <t>SO-2026</t>
-  </si>
-  <si>
     <t>McAleer &amp; Rushe Contracts UK Ltd
 (For FCS Facades)
 Stroudley Walk
@@ -1183,22 +1128,7 @@
 Jakub - +44 (0) 7772 728 234</t>
   </si>
   <si>
-    <t>SO-2035</t>
-  </si>
-  <si>
-    <t>Corner Brackets</t>
-  </si>
-  <si>
-    <t>SO-2036</t>
-  </si>
-  <si>
-    <t>GF L1 Subframe (Additional Brackets + GF L1 E&amp;N Sub-Frame)</t>
-  </si>
-  <si>
     <t>Melliss Avenue</t>
-  </si>
-  <si>
-    <t>SO-2038</t>
   </si>
   <si>
     <t>TW9 4BZ</t>
@@ -1212,100 +1142,6 @@
 Piotr Slowiak +44 (0) 7968 773 582</t>
   </si>
   <si>
-    <t>Mock Up</t>
-  </si>
-  <si>
-    <t>SO-2041</t>
-  </si>
-  <si>
-    <t>L7&amp;8 Flashings</t>
-  </si>
-  <si>
-    <t>SO-2042</t>
-  </si>
-  <si>
-    <t>SO-2043</t>
-  </si>
-  <si>
-    <t>E&amp;N Additional Brackets</t>
-  </si>
-  <si>
-    <t>Mock-Up Subframe</t>
-  </si>
-  <si>
-    <t>SO-2044</t>
-  </si>
-  <si>
-    <t>DT521</t>
-  </si>
-  <si>
-    <t>Template (Cill flashing &amp; Perforated Panel)</t>
-  </si>
-  <si>
-    <t>AJE Facades 
-Clarendon Road Block E3
-C/O St William  , Silsoe road 
-Wood Green 
- N22 6TR 
-Dragos +44 (0) 7719 309 409</t>
-  </si>
-  <si>
-    <t>Amazon SXW2</t>
-  </si>
-  <si>
-    <t>SO-2045</t>
-  </si>
-  <si>
-    <t>KT13 0YU</t>
-  </si>
-  <si>
-    <t>Fascia Panels Prod. 2</t>
-  </si>
-  <si>
-    <t>SO-2046</t>
-  </si>
-  <si>
-    <t>Fairlie Count Flashings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Group
-Ul. Spółdzielcza 4
-64-111 Lipno </t>
-  </si>
-  <si>
-    <t>CSK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64-111 </t>
-  </si>
-  <si>
-    <t>SO-2047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO00126-593-9-LD </t>
-  </si>
-  <si>
-    <t>Dock Brackets</t>
-  </si>
-  <si>
-    <t>Rose Court</t>
-  </si>
-  <si>
-    <t>SO-2048</t>
-  </si>
-  <si>
-    <t>PO00499</t>
-  </si>
-  <si>
-    <t>HP13 7PL</t>
-  </si>
-  <si>
-    <t>SO-2049</t>
-  </si>
-  <si>
-    <t>SO-2050</t>
-  </si>
-  <si>
     <t>AJE facades 
 C/O Formation 
 58 Cherry orchard 
@@ -1317,16 +1153,7 @@
     <t>CR0 6BA</t>
   </si>
   <si>
-    <t>Additional Flashings</t>
-  </si>
-  <si>
     <t>Cills</t>
-  </si>
-  <si>
-    <t>DT19</t>
-  </si>
-  <si>
-    <t>SO-2051</t>
   </si>
   <si>
     <t>McAleer &amp; Rushe Contracts UK Ltd
@@ -1337,87 +1164,6 @@
 Kontakt: Pawel +44(0) 7590 056 393 </t>
   </si>
   <si>
-    <t xml:space="preserve">EDC Facilities Ltd 
-Cheshire Storage &amp; Interior Solutions Ltd 
-Amazon SXW2 
-Unit A100 
-Brooklands Business Park 
-Vickers Dr N 
-Weybridge 
-KT13 0YU
-Site contact: Courtney 07904 316867 </t>
-  </si>
-  <si>
-    <t>Upton Hospital CDC</t>
-  </si>
-  <si>
-    <t>SO-2052</t>
-  </si>
-  <si>
-    <t>SO-2053</t>
-  </si>
-  <si>
-    <t>SO-2054</t>
-  </si>
-  <si>
-    <t>SO-2055</t>
-  </si>
-  <si>
-    <t>RCS012</t>
-  </si>
-  <si>
-    <t>PO00500</t>
-  </si>
-  <si>
-    <t>PO41325-695-BYS</t>
-  </si>
-  <si>
-    <t>PO0214960-1</t>
-  </si>
-  <si>
-    <t>Additional Top Hats</t>
-  </si>
-  <si>
-    <t>Fascia &amp; Entrance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Big Yellow Storage  Brackets </t>
-  </si>
-  <si>
-    <t>Missing panels, replacement panels</t>
-  </si>
-  <si>
-    <t>Northwood Garage</t>
-  </si>
-  <si>
-    <t>SO-2056</t>
-  </si>
-  <si>
-    <t>PO30  3BZ</t>
-  </si>
-  <si>
-    <t>SL1 2BJ</t>
-  </si>
-  <si>
-    <t>Kladworx Ltd
-CDCUpton Hospital
-Church Street
-SLough
-Berkshire
-SL1 2BJ
-Alfie Kelmendi
-+44 07908 701565</t>
-  </si>
-  <si>
-    <t>Cassette Panels &amp; Sub-Frame</t>
-  </si>
-  <si>
-    <t>SO-2057</t>
-  </si>
-  <si>
-    <t>Door Spandrel Panel</t>
-  </si>
-  <si>
     <t>order_id</t>
   </si>
   <si>
@@ -1430,27 +1176,7 @@
     <t>Delivery Address</t>
   </si>
   <si>
-    <t>10/02/2026
-08:34</t>
-  </si>
-  <si>
-    <t>SO-2058</t>
-  </si>
-  <si>
-    <t>Infills - Various Cladding</t>
-  </si>
-  <si>
-    <t>11/02/2026
-07:15</t>
-  </si>
-  <si>
     <t>Corinthian House</t>
-  </si>
-  <si>
-    <t>SO-2059</t>
-  </si>
-  <si>
-    <t>P.O.CHC002</t>
   </si>
   <si>
     <t>Perforated Panels</t>
@@ -1467,164 +1193,11 @@
 Sebastian, +44 (0) 7851 334 852</t>
   </si>
   <si>
-    <t>The Paddock</t>
-  </si>
-  <si>
-    <t>SO-2060</t>
-  </si>
-  <si>
-    <t>PO00501</t>
-  </si>
-  <si>
-    <t>PO3 5PL</t>
-  </si>
-  <si>
-    <t>Dale Crowsley- E9C39A64
-ship2me, Unit 1 Quadra Point,
-Sharps Close, Anchorage Park,
-Portsmouth, PO3 5PL
-Dale Crowsley
-07781 132223</t>
-  </si>
-  <si>
-    <t>SO-2061</t>
-  </si>
-  <si>
-    <t>P.O.CHC003</t>
-  </si>
-  <si>
     <t>11/02/2026
 8:55</t>
   </si>
   <si>
-    <t xml:space="preserve"> (For FCS Facades)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ,Broadway Central, PBSA,</t>
-  </si>
-  <si>
-    <t>200 Renfield Street,</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Glasgow, G2 3BW</t>
-  </si>
-  <si>
-    <t>Contact: Jakub +44 (0) 7772 728 234</t>
-  </si>
-  <si>
-    <t>Kladworx Ltd
-Rose Court
-Wenlock Close
-High Wycombe
-HP13 7PL
-Alfie Kelmendi +44 (0) 7908 701 565</t>
-  </si>
-  <si>
-    <t>Imphouse Ltd
-Chapel Lane
-Merstone
-Isle of Wight
-PO30  3BZ
-Mike +44 (0) 7966 279 880</t>
-  </si>
-  <si>
-    <t>Louvre Brise Soleil</t>
-  </si>
-  <si>
-    <t>SO-2062</t>
-  </si>
-  <si>
-    <t>P29950S</t>
-  </si>
-  <si>
-    <t>Extra Cill &amp; Panel</t>
-  </si>
-  <si>
-    <t>C/o Fleetwood Architectural Aluminium
-Union Square
-Stoddart Street
-Shieldfield
-NE2 1BS
-Seb +44 (0) 7903 098 924</t>
-  </si>
-  <si>
-    <t>SO-2063</t>
-  </si>
-  <si>
-    <t>PO41325-708-BYS</t>
-  </si>
-  <si>
-    <t>Brackets GF (BYS)</t>
-  </si>
-  <si>
-    <t>SO-2064</t>
-  </si>
-  <si>
-    <t>PO41325-709-BYS</t>
-  </si>
-  <si>
-    <t>Corner Brackets (BYS)</t>
-  </si>
-  <si>
-    <t>SO-2065</t>
-  </si>
-  <si>
-    <t>PO41325-711-BYS</t>
-  </si>
-  <si>
-    <t>Extra Brackets (BYS)</t>
-  </si>
-  <si>
-    <t>SO-2066</t>
-  </si>
-  <si>
-    <t>Soffit Panels</t>
-  </si>
-  <si>
-    <t>Lyndhurst Road</t>
-  </si>
-  <si>
-    <t>SO-2067</t>
-  </si>
-  <si>
-    <t>PO00502</t>
-  </si>
-  <si>
-    <t>Lindfield Place, 22 Lyndhurst
-Rd, Worthing, BN11 2DF
-Alfie +44 (0) 7908 701 565</t>
-  </si>
-  <si>
-    <t>SO-2068</t>
-  </si>
-  <si>
-    <t>SO-2069</t>
-  </si>
-  <si>
-    <t>Minories</t>
-  </si>
-  <si>
-    <t>SO-2070</t>
-  </si>
-  <si>
-    <t>TW4 6DH</t>
-  </si>
-  <si>
-    <t>FCS Facades
-The Ranch
-Next to Heathrow Gymnastics
-back of CB Hounslow
-TW4 6DH
-Piotr +44 (0) 7471 273 458</t>
-  </si>
-  <si>
     <t>Aberdeen Lane</t>
-  </si>
-  <si>
-    <t>SO-2071</t>
-  </si>
-  <si>
-    <t>Coping Support</t>
   </si>
   <si>
     <t>N5 2EJ</t>
@@ -1638,27 +1211,12 @@
 Pawel +44 (0) 7971 679 193</t>
   </si>
   <si>
-    <t>SO-2072</t>
-  </si>
-  <si>
-    <t>Angle with PCV Block</t>
-  </si>
-  <si>
     <t>Talbot Mill</t>
-  </si>
-  <si>
-    <t>SO-2073</t>
-  </si>
-  <si>
-    <t>Sub-Frame Mill 1</t>
   </si>
   <si>
     <t>44 Ellesmere Street, Manchester, M15 4JY
 Contact: Callum +44 (0) 7787 155 920
  +44 (0) 1246 588 334</t>
-  </si>
-  <si>
-    <t>Sub-Frame Mill 2</t>
   </si>
   <si>
     <t>SO-2074</t>
@@ -2293,10 +1851,203 @@
     <t>SO-2150</t>
   </si>
   <si>
-    <t>SO-2151</t>
-  </si>
-  <si>
     <t>SO-2152</t>
+  </si>
+  <si>
+    <t>Various</t>
+  </si>
+  <si>
+    <t>SO-2153</t>
+  </si>
+  <si>
+    <t>DT127</t>
+  </si>
+  <si>
+    <t>Block B Panels Prod. 4</t>
+  </si>
+  <si>
+    <t>SO-2154</t>
+  </si>
+  <si>
+    <t>Block B Copings</t>
+  </si>
+  <si>
+    <t>SO-2155</t>
+  </si>
+  <si>
+    <t>Additional Plenums</t>
+  </si>
+  <si>
+    <t>White Lodge</t>
+  </si>
+  <si>
+    <t>SO-2156</t>
+  </si>
+  <si>
+    <t>CM.9662.0539</t>
+  </si>
+  <si>
+    <t>Spigot plates and brackets</t>
+  </si>
+  <si>
+    <t>NR4 6DG</t>
+  </si>
+  <si>
+    <t>Unit 45 
+White Lodge Trading Estate 
+NR4 6DG
+Chris Mann +44 (0) 1603 327 373</t>
+  </si>
+  <si>
+    <t>SO-2157</t>
+  </si>
+  <si>
+    <t>Window Brackets</t>
+  </si>
+  <si>
+    <t>SO-2158</t>
+  </si>
+  <si>
+    <t>Curved Wall Profiles &amp; 009</t>
+  </si>
+  <si>
+    <t>SO-2159</t>
+  </si>
+  <si>
+    <t>Elm Lane Fire Station</t>
+  </si>
+  <si>
+    <t>SO-2160</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P1115 - 1006</t>
+  </si>
+  <si>
+    <t>Framing</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> O&amp;P Construction Ltd (Sparta Clad)
+Elm Lane Fire Station 
+Sheffield
+S5 7TW
+Gavin Bailey 07719711503</t>
+  </si>
+  <si>
+    <t>SO-2161</t>
+  </si>
+  <si>
+    <t>Wellington House</t>
+  </si>
+  <si>
+    <t>SO-2162</t>
+  </si>
+  <si>
+    <t>Claddings</t>
+  </si>
+  <si>
+    <t>SO-2163</t>
+  </si>
+  <si>
+    <t>Block C Additions Copings</t>
+  </si>
+  <si>
+    <t>SO-2164</t>
+  </si>
+  <si>
+    <t>Daniele Squarci &amp; Luisella Quirito</t>
+  </si>
+  <si>
+    <t>Bifold Door Factory Ltd.
+, Bingley The Common
+, West Drayton, 
+UB7 7HQ
+Contact: Contact: Harj +44 (0) 7951 893 719</t>
+  </si>
+  <si>
+    <t>SO-2165</t>
+  </si>
+  <si>
+    <t>Projection Window</t>
+  </si>
+  <si>
+    <t>8A Harleyford Street
+Oval
+London
+SE11 5SY
+Cristi +44 (0)7743 949 805</t>
+  </si>
+  <si>
+    <t>Kings Road Park</t>
+  </si>
+  <si>
+    <t>SO-2166</t>
+  </si>
+  <si>
+    <t>SO-2167</t>
+  </si>
+  <si>
+    <t>Spandrels Block A CW</t>
+  </si>
+  <si>
+    <t>SO-2168</t>
+  </si>
+  <si>
+    <t>SO-2169</t>
+  </si>
+  <si>
+    <t>SO-2170</t>
+  </si>
+  <si>
+    <t>SO-2171</t>
+  </si>
+  <si>
+    <t>Additional Top Hats L5&amp;L6</t>
+  </si>
+  <si>
+    <t>Colonnade Soffit Panels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windows Plenums </t>
+  </si>
+  <si>
+    <t>DT155</t>
+  </si>
+  <si>
+    <t>SO-2172</t>
+  </si>
+  <si>
+    <t>HM0321</t>
+  </si>
+  <si>
+    <t>PO58325-927-KRP</t>
+  </si>
+  <si>
+    <t>09/06/2026
+11:09</t>
+  </si>
+  <si>
+    <t>76d11:Sparta Clad0</t>
+  </si>
+  <si>
+    <t>097
+11:01</t>
+  </si>
+  <si>
+    <t>8C-11:i2</t>
+  </si>
+  <si>
+    <t>091
+11:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   1Ce11:04</t>
+  </si>
+  <si>
+    <t>1
+11:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pu11:06</t>
   </si>
 </sst>
 </file>
@@ -2453,7 +2204,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2540,9 +2291,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2558,6 +2306,27 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="19">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2790,27 +2559,6 @@
         <charset val="238"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2830,28 +2578,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}" name="Table1" displayName="Table1" ref="A1:Q122" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:Q122" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}" name="Table1" displayName="Table1" ref="A1:Q100" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+  <autoFilter ref="A1:Q100" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{867090DC-1FE0-4EF0-A0C0-448920317853}" name="Project" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{ED71812C-E204-4FE0-ADEA-0CD9B3ADA2A3}" name="Project SO" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{32502B80-458D-4EF6-9ABC-03678A6F8302}" name="order_id" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{111DD528-EE5F-4D8B-B63F-9A842570498D}" name="Materials" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{F88C7351-33D9-47AC-88E6-09F8FC43FCF9}" name="status" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{AF541036-9D61-4BFA-9B88-B69C899AAAFF}" name="Phase" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{3C9800BD-A315-48D1-9DB1-AF15B6CE2464}" name="Post Code" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{35381005-95B2-4E9D-9D09-3585A5DE3E35}" name="Delivery Address" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{21A0DBD3-20BC-48FA-8FF6-DB3AFE9382A5}" name="PO Date" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{3F0B7287-A10E-4CE5-9A48-B72BC577D0D0}" name="Estimated Delivery Date" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{D53CD43D-3F51-4446-BA3F-C95DF42223C1}" name="Current Update" dataDxfId="5">
+    <tableColumn id="1" xr3:uid="{867090DC-1FE0-4EF0-A0C0-448920317853}" name="Project" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{ED71812C-E204-4FE0-ADEA-0CD9B3ADA2A3}" name="Project SO" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{32502B80-458D-4EF6-9ABC-03678A6F8302}" name="order_id" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{111DD528-EE5F-4D8B-B63F-9A842570498D}" name="Materials" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{F88C7351-33D9-47AC-88E6-09F8FC43FCF9}" name="status" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{AF541036-9D61-4BFA-9B88-B69C899AAAFF}" name="Phase" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{3C9800BD-A315-48D1-9DB1-AF15B6CE2464}" name="Post Code" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{35381005-95B2-4E9D-9D09-3585A5DE3E35}" name="Delivery Address" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{21A0DBD3-20BC-48FA-8FF6-DB3AFE9382A5}" name="PO Date" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{3F0B7287-A10E-4CE5-9A48-B72BC577D0D0}" name="Estimated Delivery Date" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{D53CD43D-3F51-4446-BA3F-C95DF42223C1}" name="Current Update" dataDxfId="6">
       <calculatedColumnFormula>AVERAGE(L2:N2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{6527AB69-9477-41B6-8941-2FE273E12275}" name="Production" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{6436B5E8-E98E-47E2-B70D-DD9AA467C3A5}" name="PPC" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{D893399C-2909-4B8A-9538-32D22CFA1B25}" name="Dispatch" dataDxfId="2"/>
-    <tableColumn id="15" xr3:uid="{F6302424-51FB-45BD-9F34-61C700C8D161}" name="Welded" dataDxfId="1"/>
-    <tableColumn id="16" xr3:uid="{9BE99484-0D9D-4749-B30B-7C533699CF52}" name="Critical Information" dataDxfId="0"/>
-    <tableColumn id="17" xr3:uid="{294DD3E6-5EEC-42DD-AE99-1AC9AB8E1DEE}" name="timestamp" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{6527AB69-9477-41B6-8941-2FE273E12275}" name="Production" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{6436B5E8-E98E-47E2-B70D-DD9AA467C3A5}" name="PPC" dataDxfId="4"/>
+    <tableColumn id="14" xr3:uid="{D893399C-2909-4B8A-9538-32D22CFA1B25}" name="Dispatch" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{F6302424-51FB-45BD-9F34-61C700C8D161}" name="Welded" dataDxfId="2"/>
+    <tableColumn id="16" xr3:uid="{9BE99484-0D9D-4749-B30B-7C533699CF52}" name="Critical Information" dataDxfId="1"/>
+    <tableColumn id="17" xr3:uid="{294DD3E6-5EEC-42DD-AE99-1AC9AB8E1DEE}" name="timestamp" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3123,7 +2871,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:Q122"/>
+  <dimension ref="A1:Q100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -3153,13 +2901,13 @@
         <v>35</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>364</v>
+        <v>289</v>
       </c>
       <c r="D1" s="12" t="s">
         <v>33</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>365</v>
+        <v>290</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>31</v>
@@ -3168,7 +2916,7 @@
         <v>30</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>367</v>
+        <v>292</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>28</v>
@@ -3195,925 +2943,894 @@
         <v>267</v>
       </c>
       <c r="Q1" s="12" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>255</v>
+        <v>51</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c r="C2" s="15">
-        <v>2517</v>
+        <v>2940</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="E2" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="E2" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12" t="s">
-        <v>155</v>
+        <v>53</v>
       </c>
       <c r="H2" s="24" t="s">
-        <v>386</v>
-      </c>
-      <c r="I2" s="14">
-        <v>45987</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="I2" s="14"/>
       <c r="J2" s="14"/>
-      <c r="K2" s="23">
-        <f t="shared" ref="K2:K65" si="0">AVERAGE(L2:N2)</f>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L2" s="23">
-        <v>0.01</v>
-      </c>
-      <c r="M2" s="23">
-        <v>0</v>
-      </c>
-      <c r="N2" s="23">
-        <v>0</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="P2" s="34" t="s">
-        <v>272</v>
-      </c>
+      <c r="K2" s="37">
+        <f t="shared" ref="K2:K25" si="0">AVERAGE(L2:N2)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L2" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M2" s="37">
+        <v>0</v>
+      </c>
+      <c r="N2" s="37">
+        <v>0</v>
+      </c>
+      <c r="P2" s="16"/>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>282</v>
+        <v>305</v>
+      </c>
+      <c r="C3" s="15">
+        <v>5321</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="E3" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="E3" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="12"/>
       <c r="G3" s="12" t="s">
-        <v>284</v>
+        <v>127</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>387</v>
-      </c>
-      <c r="I3" s="14">
-        <v>45995</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="I3" s="14"/>
       <c r="J3" s="14"/>
-      <c r="K3" s="23">
+      <c r="K3" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L3" s="23">
-        <v>0.01</v>
-      </c>
-      <c r="M3" s="23">
-        <v>0</v>
-      </c>
-      <c r="N3" s="23">
-        <v>0</v>
-      </c>
-      <c r="O3" s="12" t="s">
-        <v>188</v>
+      <c r="L3" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M3" s="37">
+        <v>0</v>
+      </c>
+      <c r="N3" s="37">
+        <v>0</v>
       </c>
       <c r="P3" s="16"/>
       <c r="Q3" s="16"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>291</v>
+        <v>308</v>
+      </c>
+      <c r="C4" s="15">
+        <v>2946</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="E4" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="E4" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="12" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>388</v>
-      </c>
-      <c r="I4" s="14">
-        <v>46030</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="I4" s="14"/>
       <c r="J4" s="14"/>
-      <c r="K4" s="32">
+      <c r="K4" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L4" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M4" s="32">
-        <v>0</v>
-      </c>
-      <c r="N4" s="32">
+      <c r="L4" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M4" s="37">
+        <v>0</v>
+      </c>
+      <c r="N4" s="37">
         <v>0</v>
       </c>
       <c r="P4" s="16"/>
       <c r="Q4" s="16"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>268</v>
+        <v>91</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="C5" s="15">
-        <v>2711</v>
+        <v>2963</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E5" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="E5" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="12" t="s">
-        <v>269</v>
+        <v>157</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>389</v>
-      </c>
-      <c r="I5" s="14">
-        <v>46037</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="I5" s="14"/>
       <c r="J5" s="14"/>
-      <c r="K5" s="32">
+      <c r="K5" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L5" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M5" s="32">
-        <v>0</v>
-      </c>
-      <c r="N5" s="32">
+      <c r="L5" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M5" s="37">
+        <v>0</v>
+      </c>
+      <c r="N5" s="37">
         <v>0</v>
       </c>
       <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q5" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>268</v>
+        <v>314</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="C6" s="15">
-        <v>2721</v>
+        <v>2978</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="E6" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="E6" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="12" t="s">
-        <v>269</v>
+        <v>317</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>390</v>
-      </c>
-      <c r="I6" s="14">
-        <v>46037</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="I6" s="14"/>
       <c r="J6" s="14"/>
-      <c r="K6" s="32">
+      <c r="K6" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L6" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M6" s="32">
-        <v>0</v>
-      </c>
-      <c r="N6" s="32">
+      <c r="L6" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M6" s="37">
+        <v>0</v>
+      </c>
+      <c r="N6" s="37">
         <v>0</v>
       </c>
       <c r="O6" s="12" t="s">
         <v>188</v>
       </c>
       <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-    </row>
-    <row r="7" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q6" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>303</v>
-      </c>
-      <c r="C7" s="15">
-        <v>2746</v>
+        <v>320</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>321</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="E7" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="12" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>305</v>
-      </c>
-      <c r="I7" s="14">
-        <v>46042</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="I7" s="14"/>
       <c r="J7" s="14"/>
-      <c r="K7" s="32">
+      <c r="K7" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L7" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M7" s="32">
-        <v>0</v>
-      </c>
-      <c r="N7" s="32">
-        <v>0</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>188</v>
+      <c r="L7" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M7" s="37">
+        <v>0</v>
+      </c>
+      <c r="N7" s="37">
+        <v>0</v>
       </c>
       <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-    </row>
-    <row r="8" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q7" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="C8" s="15">
-        <v>2781</v>
+        <v>2976</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="E8" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="E8" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="12" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>341</v>
-      </c>
-      <c r="I8" s="14">
-        <v>46045</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="I8" s="14"/>
       <c r="J8" s="14"/>
-      <c r="K8" s="32">
+      <c r="K8" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L8" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M8" s="32">
-        <v>0</v>
-      </c>
-      <c r="N8" s="32">
-        <v>0</v>
-      </c>
-      <c r="O8" s="12" t="s">
-        <v>188</v>
+      <c r="L8" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M8" s="37">
+        <v>0</v>
+      </c>
+      <c r="N8" s="37">
+        <v>0</v>
       </c>
       <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
+      <c r="Q8" s="34" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="9" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>268</v>
+        <v>91</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="C9" s="15">
-        <v>2787</v>
+        <v>2986</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="E9" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="E9" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12" t="s">
-        <v>269</v>
+        <v>157</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>295</v>
-      </c>
-      <c r="I9" s="14">
-        <v>46045</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="I9" s="14"/>
       <c r="J9" s="14"/>
-      <c r="K9" s="32">
+      <c r="K9" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L9" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M9" s="32">
-        <v>0</v>
-      </c>
-      <c r="N9" s="32">
+      <c r="L9" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M9" s="37">
+        <v>0</v>
+      </c>
+      <c r="N9" s="37">
         <v>0</v>
       </c>
       <c r="O9" s="12" t="s">
         <v>188</v>
       </c>
       <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
+      <c r="Q9" s="34" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="10" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>302</v>
+        <v>275</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="C10" s="15">
-        <v>2800</v>
+        <v>328</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>329</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="E10" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="E10" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="12" t="s">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>305</v>
-      </c>
-      <c r="I10" s="14">
-        <v>46049</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="I10" s="14"/>
       <c r="J10" s="14"/>
-      <c r="K10" s="32">
+      <c r="K10" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L10" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M10" s="32">
-        <v>0</v>
-      </c>
-      <c r="N10" s="32">
-        <v>0</v>
+      <c r="L10" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M10" s="37">
+        <v>0</v>
+      </c>
+      <c r="N10" s="37">
+        <v>0</v>
+      </c>
+      <c r="O10" s="12" t="s">
+        <v>188</v>
       </c>
       <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
+      <c r="Q10" s="34" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="11" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>17</v>
+        <v>275</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="E11" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="E11" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="12" t="s">
-        <v>189</v>
+        <v>277</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>316</v>
-      </c>
-      <c r="I11" s="14">
-        <v>46050</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="I11" s="14"/>
       <c r="J11" s="14"/>
-      <c r="K11" s="32">
+      <c r="K11" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L11" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M11" s="32">
-        <v>0</v>
-      </c>
-      <c r="N11" s="32">
-        <v>0</v>
-      </c>
-      <c r="O11" s="12" t="s">
-        <v>188</v>
+      <c r="L11" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M11" s="37">
+        <v>0</v>
+      </c>
+      <c r="N11" s="37">
+        <v>0</v>
       </c>
       <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-    </row>
-    <row r="12" spans="1:17" ht="150" x14ac:dyDescent="0.25">
+      <c r="Q11" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>67</v>
+        <v>336</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="E12" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="E12" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>342</v>
-      </c>
-      <c r="I12" s="14">
-        <v>46051</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="I12" s="14"/>
       <c r="J12" s="14"/>
-      <c r="K12" s="32">
+      <c r="K12" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L12" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M12" s="32">
-        <v>0</v>
-      </c>
-      <c r="N12" s="32">
+      <c r="L12" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M12" s="37">
+        <v>0</v>
+      </c>
+      <c r="N12" s="37">
         <v>0</v>
       </c>
       <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-    </row>
-    <row r="13" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q12" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>51</v>
+        <v>282</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="C13" s="15">
-        <v>2814</v>
+        <v>3023</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="E13" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="E13" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="12" t="s">
-        <v>53</v>
+        <v>283</v>
       </c>
       <c r="H13" s="24" t="s">
+        <v>284</v>
+      </c>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="37">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L13" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M13" s="37">
+        <v>0</v>
+      </c>
+      <c r="N13" s="37">
+        <v>0</v>
+      </c>
+      <c r="O13" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="34" t="s">
         <v>297</v>
       </c>
-      <c r="I13" s="14">
-        <v>46051</v>
-      </c>
-      <c r="J13" s="14"/>
-      <c r="K13" s="32">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L13" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M13" s="32">
-        <v>0</v>
-      </c>
-      <c r="N13" s="32">
-        <v>0</v>
-      </c>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="36" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>281</v>
+        <v>314</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>327</v>
+        <v>341</v>
+      </c>
+      <c r="C14" s="15">
+        <v>3030</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="E14" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="E14" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="12" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>323</v>
-      </c>
-      <c r="I14" s="14">
-        <v>46055</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="I14" s="14"/>
       <c r="J14" s="14"/>
-      <c r="K14" s="32">
+      <c r="K14" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L14" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M14" s="32">
-        <v>0</v>
-      </c>
-      <c r="N14" s="32">
-        <v>0</v>
-      </c>
-      <c r="O14" s="12" t="s">
-        <v>324</v>
+      <c r="L14" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M14" s="37">
+        <v>0</v>
+      </c>
+      <c r="N14" s="37">
+        <v>0</v>
       </c>
       <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
+      <c r="Q14" s="34" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="15" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>329</v>
+        <v>261</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E15" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="E15" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12" t="s">
-        <v>332</v>
+        <v>286</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>391</v>
-      </c>
-      <c r="I15" s="14">
-        <v>46055</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="I15" s="14"/>
       <c r="J15" s="14"/>
-      <c r="K15" s="32">
+      <c r="K15" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L15" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M15" s="32">
-        <v>0</v>
-      </c>
-      <c r="N15" s="32">
-        <v>0</v>
-      </c>
-      <c r="O15" s="12" t="s">
-        <v>188</v>
+      <c r="L15" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M15" s="37">
+        <v>0</v>
+      </c>
+      <c r="N15" s="37">
+        <v>0</v>
       </c>
       <c r="P15" s="16"/>
-      <c r="Q15" s="36" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q15" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="C16" s="15">
-        <v>2836</v>
+        <v>5333</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>337</v>
-      </c>
-      <c r="E16" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="E16" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="12" t="s">
-        <v>278</v>
+        <v>127</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="I16" s="14">
-        <v>46056</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="I16" s="14"/>
       <c r="J16" s="14"/>
-      <c r="K16" s="32">
+      <c r="K16" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L16" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M16" s="32">
-        <v>0</v>
-      </c>
-      <c r="N16" s="32">
+      <c r="L16" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M16" s="37">
+        <v>0</v>
+      </c>
+      <c r="N16" s="37">
         <v>0</v>
       </c>
       <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-    </row>
-    <row r="17" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q16" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>261</v>
+        <v>301</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>334</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>339</v>
+        <v>347</v>
+      </c>
+      <c r="C17" s="15">
+        <v>5333</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="E17" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="E17" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="12" t="s">
-        <v>336</v>
+        <v>127</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>335</v>
-      </c>
-      <c r="I17" s="14">
-        <v>46056</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="I17" s="14"/>
       <c r="J17" s="14"/>
-      <c r="K17" s="32">
+      <c r="K17" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L17" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M17" s="32">
-        <v>0</v>
-      </c>
-      <c r="N17" s="32">
-        <v>0</v>
-      </c>
-      <c r="O17" s="12" t="s">
-        <v>324</v>
+      <c r="L17" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M17" s="37">
+        <v>0</v>
+      </c>
+      <c r="N17" s="37">
+        <v>0</v>
       </c>
       <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
+      <c r="Q17" s="34" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="18" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>290</v>
+        <v>255</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>348</v>
+        <v>349</v>
+      </c>
+      <c r="C18" s="15">
+        <v>3044</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="E18" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="E18" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="12" t="s">
-        <v>292</v>
+        <v>155</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="I18" s="14">
-        <v>46058</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="I18" s="14"/>
       <c r="J18" s="14"/>
-      <c r="K18" s="32">
+      <c r="K18" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L18" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M18" s="32">
-        <v>0</v>
-      </c>
-      <c r="N18" s="32">
-        <v>0</v>
-      </c>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-    </row>
-    <row r="19" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="L18" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M18" s="37">
+        <v>0</v>
+      </c>
+      <c r="N18" s="37">
+        <v>0</v>
+      </c>
+      <c r="P18" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q18" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>288</v>
+        <v>352</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="C19" s="15">
-        <v>2858</v>
+        <v>353</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>354</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>337</v>
-      </c>
-      <c r="E19" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="E19" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="12" t="s">
-        <v>278</v>
+        <v>356</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="I19" s="14">
-        <v>46059</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="I19" s="14"/>
       <c r="J19" s="14"/>
-      <c r="K19" s="32">
+      <c r="K19" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L19" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M19" s="32">
-        <v>0</v>
-      </c>
-      <c r="N19" s="32">
-        <v>0</v>
-      </c>
-      <c r="O19" s="12" t="s">
-        <v>188</v>
+      <c r="L19" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M19" s="37">
+        <v>0</v>
+      </c>
+      <c r="N19" s="37">
+        <v>0</v>
       </c>
       <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-    </row>
-    <row r="20" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+      <c r="Q19" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>343</v>
+        <v>255</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>345</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>349</v>
+        <v>358</v>
+      </c>
+      <c r="C20" s="15">
+        <v>3090</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="E20" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="E20" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="12" t="s">
-        <v>359</v>
+        <v>155</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>360</v>
-      </c>
-      <c r="I20" s="14">
-        <v>46059</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="I20" s="14"/>
       <c r="J20" s="14"/>
-      <c r="K20" s="32">
+      <c r="K20" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L20" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M20" s="32">
-        <v>0</v>
-      </c>
-      <c r="N20" s="32">
+      <c r="L20" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M20" s="37">
+        <v>0</v>
+      </c>
+      <c r="N20" s="37">
         <v>0</v>
       </c>
       <c r="O20" s="12" t="s">
         <v>188</v>
       </c>
       <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
-    </row>
-    <row r="21" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q20" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>281</v>
+        <v>255</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>350</v>
+        <v>360</v>
+      </c>
+      <c r="C21" s="15">
+        <v>3096</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="E21" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="12" t="s">
-        <v>284</v>
+        <v>155</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="I21" s="14">
-        <v>46059</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="I21" s="14"/>
       <c r="J21" s="14"/>
-      <c r="K21" s="32">
+      <c r="K21" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L21" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M21" s="32">
-        <v>0</v>
-      </c>
-      <c r="N21" s="32">
+      <c r="L21" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M21" s="37">
+        <v>0</v>
+      </c>
+      <c r="N21" s="37">
         <v>0</v>
       </c>
       <c r="P21" s="16"/>
-      <c r="Q21" s="16"/>
+      <c r="Q21" s="34" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="22" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="E22" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="E22" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F22" s="12"/>
@@ -4121,4200 +3838,3233 @@
         <v>286</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="I22" s="14">
-        <v>46059</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="I22" s="14"/>
       <c r="J22" s="14"/>
-      <c r="K22" s="32">
+      <c r="K22" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L22" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M22" s="32">
-        <v>0</v>
-      </c>
-      <c r="N22" s="32">
+      <c r="L22" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M22" s="37">
+        <v>0</v>
+      </c>
+      <c r="N22" s="37">
         <v>0</v>
       </c>
       <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
-    </row>
-    <row r="23" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q22" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>357</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>67</v>
+        <v>365</v>
+      </c>
+      <c r="C23" s="15">
+        <v>10001</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="E23" s="20" t="s">
+        <v>366</v>
+      </c>
+      <c r="E23" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F23" s="12"/>
       <c r="G23" s="12" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>392</v>
+        <v>368</v>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14"/>
-      <c r="K23" s="32">
+      <c r="K23" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L23" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M23" s="32">
-        <v>0</v>
-      </c>
-      <c r="N23" s="32">
+      <c r="L23" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M23" s="37">
+        <v>0</v>
+      </c>
+      <c r="N23" s="37">
         <v>0</v>
       </c>
       <c r="P23" s="16"/>
-      <c r="Q23" s="16"/>
-    </row>
-    <row r="24" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q23" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>91</v>
+        <v>364</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C24" s="15">
-        <v>2863</v>
+        <v>10001</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="E24" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="E24" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F24" s="12"/>
       <c r="G24" s="12" t="s">
-        <v>157</v>
+        <v>367</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>341</v>
-      </c>
-      <c r="I24" s="14">
-        <v>46062</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="32">
+      <c r="K24" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L24" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M24" s="32">
-        <v>0</v>
-      </c>
-      <c r="N24" s="32">
+      <c r="L24" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M24" s="37">
+        <v>0</v>
+      </c>
+      <c r="N24" s="37">
         <v>0</v>
       </c>
       <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-    </row>
-    <row r="25" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q24" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>255</v>
+        <v>371</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C25" s="15">
-        <v>2872</v>
+        <v>3107</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="E25" s="37" t="s">
+        <v>373</v>
+      </c>
+      <c r="E25" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="12" t="s">
-        <v>155</v>
+        <v>374</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="I25" s="14">
-        <v>46062</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="I25" s="14"/>
       <c r="J25" s="14"/>
-      <c r="K25" s="38">
+      <c r="K25" s="37">
         <f t="shared" si="0"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L25" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M25" s="38">
-        <v>0</v>
-      </c>
-      <c r="N25" s="38">
-        <v>0</v>
-      </c>
-      <c r="O25" s="12" t="s">
-        <v>188</v>
+      <c r="L25" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M25" s="37">
+        <v>0</v>
+      </c>
+      <c r="N25" s="37">
+        <v>0</v>
       </c>
       <c r="P25" s="16"/>
-      <c r="Q25" s="16"/>
-    </row>
-    <row r="26" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+      <c r="Q25" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>374</v>
+        <v>377</v>
+      </c>
+      <c r="C26" s="15">
+        <v>3110</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="E26" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="E26" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="12" t="s">
-        <v>376</v>
+        <v>310</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>377</v>
-      </c>
-      <c r="I26" s="14">
-        <v>46063</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="I26" s="14"/>
       <c r="J26" s="14"/>
-      <c r="K26" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L26" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M26" s="38">
-        <v>0</v>
-      </c>
-      <c r="N26" s="38">
-        <v>0</v>
-      </c>
-      <c r="O26" s="12" t="s">
-        <v>188</v>
+      <c r="K26" s="37">
+        <f t="shared" ref="K26:K88" si="1">AVERAGE(L26:N26)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L26" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M26" s="37">
+        <v>0</v>
+      </c>
+      <c r="N26" s="37">
+        <v>0</v>
       </c>
       <c r="P26" s="16"/>
-      <c r="Q26" s="16"/>
+      <c r="Q26" s="34" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="27" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="15">
+        <v>3111</v>
+      </c>
+      <c r="D27" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="D27" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="E27" s="37" t="s">
+      <c r="E27" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F27" s="12"/>
       <c r="G27" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="H27" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L27" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M27" s="37">
+        <v>0</v>
+      </c>
+      <c r="N27" s="37">
+        <v>0</v>
+      </c>
+      <c r="O27" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P27" s="16"/>
+      <c r="Q27" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B28" s="12" t="s">
         <v>381</v>
       </c>
-      <c r="H27" s="24" t="s">
+      <c r="C28" s="15">
+        <v>3128</v>
+      </c>
+      <c r="D28" s="12" t="s">
         <v>382</v>
       </c>
-      <c r="I27" s="14">
-        <v>46063</v>
-      </c>
-      <c r="J27" s="14"/>
-      <c r="K27" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L27" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M27" s="38">
-        <v>0</v>
-      </c>
-      <c r="N27" s="38">
-        <v>0</v>
-      </c>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="16"/>
-    </row>
-    <row r="28" spans="1:17" ht="105" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>384</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="E28" s="37" t="s">
+      <c r="E28" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F28" s="12"/>
       <c r="G28" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="H28" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L28" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M28" s="37">
+        <v>0</v>
+      </c>
+      <c r="N28" s="37">
+        <v>0</v>
+      </c>
+      <c r="O28" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
         <v>376</v>
       </c>
-      <c r="H28" s="24" t="s">
-        <v>377</v>
-      </c>
-      <c r="I28" s="14">
-        <v>46064</v>
-      </c>
-      <c r="J28" s="14"/>
-      <c r="K28" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L28" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M28" s="38">
-        <v>0</v>
-      </c>
-      <c r="N28" s="38">
-        <v>0</v>
-      </c>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="16"/>
-    </row>
-    <row r="29" spans="1:17" ht="105" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>148</v>
-      </c>
       <c r="B29" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>395</v>
+        <v>383</v>
+      </c>
+      <c r="C29" s="15">
+        <v>3153</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="E29" s="37" t="s">
+        <v>384</v>
+      </c>
+      <c r="E29" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F29" s="12"/>
       <c r="G29" s="12" t="s">
-        <v>153</v>
+        <v>310</v>
       </c>
       <c r="H29" s="24" t="s">
-        <v>397</v>
-      </c>
-      <c r="I29" s="14">
-        <v>46065</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="I29" s="14"/>
       <c r="J29" s="14"/>
-      <c r="K29" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L29" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M29" s="38">
-        <v>0</v>
-      </c>
-      <c r="N29" s="38">
+      <c r="K29" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L29" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M29" s="37">
+        <v>0</v>
+      </c>
+      <c r="N29" s="37">
         <v>0</v>
       </c>
       <c r="P29" s="16"/>
-      <c r="Q29" s="16"/>
+      <c r="Q29" s="34" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="30" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>281</v>
+        <v>385</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>398</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>399</v>
+        <v>386</v>
+      </c>
+      <c r="C30" s="15">
+        <v>3160</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="E30" s="37" t="s">
+        <v>387</v>
+      </c>
+      <c r="E30" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="H30" s="24" t="s">
         <v>284</v>
-      </c>
-      <c r="H30" s="24" t="s">
-        <v>283</v>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14"/>
-      <c r="K30" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L30" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M30" s="38">
-        <v>0</v>
-      </c>
-      <c r="N30" s="38">
+      <c r="K30" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L30" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M30" s="37">
+        <v>0</v>
+      </c>
+      <c r="N30" s="37">
         <v>0</v>
       </c>
       <c r="P30" s="16"/>
-      <c r="Q30" s="16"/>
+      <c r="Q30" s="34" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="31" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>403</v>
-      </c>
-      <c r="E31" s="37" t="s">
+        <v>390</v>
+      </c>
+      <c r="E31" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F31" s="12"/>
-      <c r="G31" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="H31" s="24" t="s">
-        <v>283</v>
+      <c r="G31" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="H31" s="25" t="s">
+        <v>285</v>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14"/>
-      <c r="K31" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L31" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M31" s="38">
-        <v>0</v>
-      </c>
-      <c r="N31" s="38">
+      <c r="K31" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L31" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M31" s="37">
+        <v>0</v>
+      </c>
+      <c r="N31" s="37">
         <v>0</v>
       </c>
       <c r="P31" s="16"/>
-      <c r="Q31" s="16"/>
+      <c r="Q31" s="34" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="32" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>404</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>405</v>
+        <v>391</v>
+      </c>
+      <c r="C32" s="15">
+        <v>3179</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="E32" s="37" t="s">
+        <v>392</v>
+      </c>
+      <c r="E32" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="12" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14"/>
-      <c r="K32" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L32" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M32" s="38">
-        <v>0</v>
-      </c>
-      <c r="N32" s="38">
+      <c r="K32" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L32" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M32" s="37">
+        <v>0</v>
+      </c>
+      <c r="N32" s="37">
         <v>0</v>
       </c>
       <c r="P32" s="16"/>
-      <c r="Q32" s="16"/>
-    </row>
-    <row r="33" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q32" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>51</v>
+        <v>261</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>407</v>
-      </c>
-      <c r="C33" s="15">
-        <v>2904</v>
+        <v>393</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>394</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>408</v>
-      </c>
-      <c r="E33" s="37" t="s">
+        <v>395</v>
+      </c>
+      <c r="E33" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F33" s="12"/>
       <c r="G33" s="12" t="s">
-        <v>53</v>
+        <v>286</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14"/>
-      <c r="K33" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L33" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M33" s="38">
-        <v>0</v>
-      </c>
-      <c r="N33" s="38">
+      <c r="K33" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L33" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M33" s="37">
+        <v>0</v>
+      </c>
+      <c r="N33" s="37">
         <v>0</v>
       </c>
       <c r="P33" s="16"/>
-      <c r="Q33" s="16"/>
-    </row>
-    <row r="34" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q33" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>409</v>
+        <v>376</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>411</v>
+        <v>396</v>
+      </c>
+      <c r="C34" s="15">
+        <v>3190</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E34" s="37" t="s">
+        <v>397</v>
+      </c>
+      <c r="E34" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F34" s="12"/>
       <c r="G34" s="12" t="s">
-        <v>185</v>
+        <v>310</v>
       </c>
       <c r="H34" s="24" t="s">
-        <v>412</v>
+        <v>311</v>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14"/>
-      <c r="K34" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L34" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M34" s="38">
-        <v>0</v>
-      </c>
-      <c r="N34" s="38">
+      <c r="K34" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L34" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M34" s="37">
+        <v>0</v>
+      </c>
+      <c r="N34" s="37">
         <v>0</v>
       </c>
       <c r="P34" s="16"/>
-      <c r="Q34" s="16"/>
+      <c r="Q34" s="34" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="35" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>274</v>
+        <v>385</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="C35" s="15">
-        <v>2912</v>
+        <v>3197</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="E35" s="37" t="s">
+        <v>399</v>
+      </c>
+      <c r="E35" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F35" s="12"/>
       <c r="G35" s="12" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="H35" s="24" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14"/>
-      <c r="K35" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L35" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M35" s="38">
-        <v>0</v>
-      </c>
-      <c r="N35" s="38">
+      <c r="K35" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L35" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M35" s="37">
+        <v>0</v>
+      </c>
+      <c r="N35" s="37">
         <v>0</v>
       </c>
       <c r="P35" s="16"/>
-      <c r="Q35" s="16"/>
-    </row>
-    <row r="36" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q35" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="105" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>91</v>
+        <v>293</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="C36" s="15">
-        <v>2913</v>
+        <v>400</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>401</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="E36" s="37" t="s">
+        <v>402</v>
+      </c>
+      <c r="E36" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="H36" s="24" t="s">
-        <v>341</v>
+      <c r="G36" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="H36" s="25" t="s">
+        <v>296</v>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14"/>
-      <c r="K36" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L36" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M36" s="38">
-        <v>0</v>
-      </c>
-      <c r="N36" s="38">
+      <c r="K36" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L36" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M36" s="37">
+        <v>0</v>
+      </c>
+      <c r="N36" s="37">
         <v>0</v>
       </c>
       <c r="P36" s="16"/>
-      <c r="Q36" s="16"/>
-    </row>
-    <row r="37" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q36" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>415</v>
+        <v>51</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="C37" s="15">
-        <v>2914</v>
+        <v>3213</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="E37" s="37" t="s">
+        <v>404</v>
+      </c>
+      <c r="E37" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F37" s="12"/>
       <c r="G37" s="12" t="s">
-        <v>417</v>
+        <v>53</v>
       </c>
       <c r="H37" s="24" t="s">
-        <v>418</v>
+        <v>281</v>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14"/>
-      <c r="K37" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L37" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M37" s="38">
-        <v>0</v>
-      </c>
-      <c r="N37" s="38">
+      <c r="K37" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L37" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M37" s="37">
+        <v>0</v>
+      </c>
+      <c r="N37" s="37">
         <v>0</v>
       </c>
       <c r="P37" s="16"/>
-      <c r="Q37" s="16"/>
+      <c r="Q37" s="34" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="38" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>419</v>
+        <v>91</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="C38" s="15">
-        <v>2917</v>
+        <v>3220</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="E38" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="E38" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F38" s="12"/>
       <c r="G38" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>423</v>
+        <v>157</v>
+      </c>
+      <c r="H38" s="24" t="s">
+        <v>288</v>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14"/>
-      <c r="K38" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L38" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M38" s="38">
-        <v>0</v>
-      </c>
-      <c r="N38" s="38">
-        <v>0</v>
-      </c>
-      <c r="P38" s="16"/>
-      <c r="Q38" s="16"/>
+      <c r="K38" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L38" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M38" s="37">
+        <v>0</v>
+      </c>
+      <c r="N38" s="37">
+        <v>0</v>
+      </c>
+      <c r="P38" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q38" s="34" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="39" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>255</v>
+        <v>407</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>424</v>
-      </c>
-      <c r="C39" s="15">
-        <v>2928</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="C39" s="15"/>
       <c r="D39" s="12" t="s">
-        <v>425</v>
-      </c>
-      <c r="E39" s="37" t="s">
+        <v>409</v>
+      </c>
+      <c r="E39" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F39" s="12"/>
       <c r="G39" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="H39" s="24" t="s">
-        <v>287</v>
+        <v>410</v>
+      </c>
+      <c r="H39" s="38" t="s">
+        <v>411</v>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14"/>
-      <c r="K39" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L39" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M39" s="38">
-        <v>0</v>
-      </c>
-      <c r="N39" s="38">
+      <c r="K39" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L39" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M39" s="37">
+        <v>0</v>
+      </c>
+      <c r="N39" s="37">
         <v>0</v>
       </c>
       <c r="P39" s="16"/>
-      <c r="Q39" s="16"/>
-    </row>
-    <row r="40" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q39" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>426</v>
+        <v>376</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="C40" s="15">
-        <v>5320</v>
+        <v>3226</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>428</v>
-      </c>
-      <c r="E40" s="37" t="s">
+        <v>413</v>
+      </c>
+      <c r="E40" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F40" s="12"/>
       <c r="G40" s="12" t="s">
-        <v>127</v>
+        <v>310</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>429</v>
+        <v>311</v>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14"/>
-      <c r="K40" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L40" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M40" s="38">
-        <v>0</v>
-      </c>
-      <c r="N40" s="38">
-        <v>0</v>
-      </c>
-      <c r="P40" s="16"/>
-      <c r="Q40" s="16"/>
-    </row>
-    <row r="41" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+      <c r="K40" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L40" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M40" s="37">
+        <v>0</v>
+      </c>
+      <c r="N40" s="37">
+        <v>0</v>
+      </c>
+      <c r="P40" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="Q40" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>426</v>
+        <v>255</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="C41" s="15">
-        <v>5320</v>
+        <v>3231</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="E41" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="E41" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F41" s="12"/>
       <c r="G41" s="12" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>429</v>
+        <v>279</v>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14"/>
-      <c r="K41" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L41" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M41" s="38">
-        <v>0</v>
-      </c>
-      <c r="N41" s="38">
-        <v>0</v>
-      </c>
-      <c r="P41" s="16"/>
-      <c r="Q41" s="16"/>
-    </row>
-    <row r="42" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="K41" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L41" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M41" s="37">
+        <v>0</v>
+      </c>
+      <c r="N41" s="37">
+        <v>0</v>
+      </c>
+      <c r="P41" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q41" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="C42" s="15">
-        <v>2940</v>
+        <v>3236</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>432</v>
-      </c>
-      <c r="E42" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="E42" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F42" s="12"/>
       <c r="G42" s="12" t="s">
-        <v>53</v>
+        <v>157</v>
       </c>
       <c r="H42" s="24" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14"/>
-      <c r="K42" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L42" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M42" s="38">
-        <v>0</v>
-      </c>
-      <c r="N42" s="38">
-        <v>0</v>
-      </c>
-      <c r="P42" s="16"/>
-      <c r="Q42" s="16"/>
-    </row>
-    <row r="43" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+      <c r="K42" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L42" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M42" s="37">
+        <v>0</v>
+      </c>
+      <c r="N42" s="37">
+        <v>0</v>
+      </c>
+      <c r="P42" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q42" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>426</v>
+        <v>298</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="C43" s="15">
-        <v>5321</v>
+        <v>3240</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>434</v>
-      </c>
-      <c r="E43" s="37" t="s">
+        <v>418</v>
+      </c>
+      <c r="E43" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F43" s="12"/>
       <c r="G43" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="H43" s="24" t="s">
-        <v>429</v>
+        <v>299</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>300</v>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14"/>
-      <c r="K43" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L43" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M43" s="38">
-        <v>0</v>
-      </c>
-      <c r="N43" s="38">
+      <c r="K43" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L43" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M43" s="37">
+        <v>0</v>
+      </c>
+      <c r="N43" s="37">
         <v>0</v>
       </c>
       <c r="P43" s="16"/>
-      <c r="Q43" s="16"/>
+      <c r="Q43" s="34" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="44" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>435</v>
+        <v>314</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="C44" s="15">
-        <v>2946</v>
+        <v>3242</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>437</v>
-      </c>
-      <c r="E44" s="37" t="s">
+        <v>420</v>
+      </c>
+      <c r="E44" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F44" s="12"/>
       <c r="G44" s="12" t="s">
-        <v>438</v>
+        <v>317</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>439</v>
+        <v>318</v>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14"/>
-      <c r="K44" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L44" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M44" s="38">
-        <v>0</v>
-      </c>
-      <c r="N44" s="38">
+      <c r="K44" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L44" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M44" s="37">
+        <v>0</v>
+      </c>
+      <c r="N44" s="37">
         <v>0</v>
       </c>
       <c r="P44" s="16"/>
-      <c r="Q44" s="16"/>
-    </row>
-    <row r="45" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q44" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" ht="105" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="C45" s="15">
-        <v>2963</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>441</v>
-      </c>
-      <c r="E45" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="B45" s="12"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F45" s="12"/>
       <c r="G45" s="12" t="s">
-        <v>157</v>
+        <v>421</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>341</v>
+        <v>422</v>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14"/>
-      <c r="K45" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L45" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M45" s="38">
-        <v>0</v>
-      </c>
-      <c r="N45" s="38">
+      <c r="K45" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L45" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M45" s="37">
+        <v>0</v>
+      </c>
+      <c r="N45" s="37">
         <v>0</v>
       </c>
       <c r="P45" s="16"/>
       <c r="Q45" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>443</v>
-      </c>
-      <c r="C46" s="15">
-        <v>2978</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>444</v>
-      </c>
-      <c r="E46" s="37" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+      <c r="A46" s="12"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F46" s="12"/>
       <c r="G46" s="12" t="s">
-        <v>445</v>
+        <v>423</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14"/>
-      <c r="K46" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L46" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M46" s="38">
-        <v>0</v>
-      </c>
-      <c r="N46" s="38">
-        <v>0</v>
-      </c>
-      <c r="O46" s="12" t="s">
-        <v>188</v>
+      <c r="K46" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L46" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M46" s="37">
+        <v>0</v>
+      </c>
+      <c r="N46" s="37">
+        <v>0</v>
       </c>
       <c r="P46" s="16"/>
       <c r="Q46" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>447</v>
+        <v>314</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>448</v>
-      </c>
-      <c r="C47" s="15" t="s">
-        <v>449</v>
+        <v>425</v>
+      </c>
+      <c r="C47" s="15">
+        <v>3241</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E47" s="37" t="s">
+        <v>426</v>
+      </c>
+      <c r="E47" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F47" s="12"/>
       <c r="G47" s="12" t="s">
-        <v>450</v>
+        <v>317</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>451</v>
+        <v>318</v>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14"/>
-      <c r="K47" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L47" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M47" s="38">
-        <v>0</v>
-      </c>
-      <c r="N47" s="38">
+      <c r="K47" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L47" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M47" s="37">
+        <v>0</v>
+      </c>
+      <c r="N47" s="37">
         <v>0</v>
       </c>
       <c r="P47" s="16"/>
       <c r="Q47" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>51</v>
+        <v>261</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>452</v>
-      </c>
-      <c r="C48" s="15">
-        <v>2976</v>
+        <v>427</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>428</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>453</v>
-      </c>
-      <c r="E48" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="E48" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F48" s="12"/>
       <c r="G48" s="12" t="s">
-        <v>53</v>
+        <v>286</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14"/>
-      <c r="K48" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L48" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M48" s="38">
-        <v>0</v>
-      </c>
-      <c r="N48" s="38">
+      <c r="K48" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L48" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M48" s="37">
+        <v>0</v>
+      </c>
+      <c r="N48" s="37">
         <v>0</v>
       </c>
       <c r="P48" s="16"/>
       <c r="Q48" s="34" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
     </row>
     <row r="49" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>91</v>
+        <v>376</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="C49" s="15">
-        <v>2986</v>
+        <v>3273</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>455</v>
-      </c>
-      <c r="E49" s="37" t="s">
+        <v>431</v>
+      </c>
+      <c r="E49" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F49" s="12"/>
       <c r="G49" s="12" t="s">
-        <v>157</v>
+        <v>310</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>341</v>
+        <v>311</v>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14"/>
-      <c r="K49" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L49" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M49" s="38">
-        <v>0</v>
-      </c>
-      <c r="N49" s="38">
-        <v>0</v>
-      </c>
-      <c r="O49" s="12" t="s">
-        <v>188</v>
+      <c r="K49" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L49" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M49" s="37">
+        <v>0</v>
+      </c>
+      <c r="N49" s="37">
+        <v>0</v>
       </c>
       <c r="P49" s="16"/>
       <c r="Q49" s="34" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
     </row>
     <row r="50" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>456</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>457</v>
+        <v>432</v>
+      </c>
+      <c r="C50" s="15">
+        <v>3276</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>458</v>
-      </c>
-      <c r="E50" s="37" t="s">
+        <v>433</v>
+      </c>
+      <c r="E50" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F50" s="12"/>
       <c r="G50" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="H50" s="24" t="s">
-        <v>283</v>
+        <v>299</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>300</v>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="14"/>
-      <c r="K50" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L50" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M50" s="38">
-        <v>0</v>
-      </c>
-      <c r="N50" s="38">
-        <v>0</v>
-      </c>
-      <c r="O50" s="12" t="s">
-        <v>188</v>
+      <c r="K50" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L50" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M50" s="37">
+        <v>0</v>
+      </c>
+      <c r="N50" s="37">
+        <v>0</v>
       </c>
       <c r="P50" s="16"/>
       <c r="Q50" s="34" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>459</v>
-      </c>
-      <c r="C51" s="15" t="s">
-        <v>460</v>
+        <v>434</v>
+      </c>
+      <c r="C51" s="15">
+        <v>3282</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>461</v>
-      </c>
-      <c r="E51" s="37" t="s">
+        <v>435</v>
+      </c>
+      <c r="E51" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F51" s="12"/>
       <c r="G51" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="H51" s="24" t="s">
-        <v>283</v>
+        <v>299</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>300</v>
       </c>
       <c r="I51" s="14"/>
       <c r="J51" s="14"/>
-      <c r="K51" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L51" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M51" s="38">
-        <v>0</v>
-      </c>
-      <c r="N51" s="38">
+      <c r="K51" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L51" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M51" s="37">
+        <v>0</v>
+      </c>
+      <c r="N51" s="37">
         <v>0</v>
       </c>
       <c r="P51" s="16"/>
       <c r="Q51" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>462</v>
+        <v>298</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>463</v>
-      </c>
-      <c r="C52" s="15" t="s">
-        <v>464</v>
+        <v>436</v>
+      </c>
+      <c r="C52" s="15">
+        <v>3283</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="E52" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="E52" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F52" s="12"/>
       <c r="G52" s="12" t="s">
-        <v>465</v>
+        <v>299</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>466</v>
+        <v>300</v>
       </c>
       <c r="I52" s="14"/>
       <c r="J52" s="14"/>
-      <c r="K52" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L52" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M52" s="38">
-        <v>0</v>
-      </c>
-      <c r="N52" s="38">
+      <c r="K52" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L52" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M52" s="37">
+        <v>0</v>
+      </c>
+      <c r="N52" s="37">
         <v>0</v>
       </c>
       <c r="P52" s="16"/>
       <c r="Q52" s="34" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>467</v>
-      </c>
-      <c r="C53" s="15">
-        <v>3023</v>
+        <v>437</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>438</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>468</v>
-      </c>
-      <c r="E53" s="37" t="s">
+        <v>439</v>
+      </c>
+      <c r="E53" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F53" s="12"/>
-      <c r="G53" s="12" t="s">
-        <v>304</v>
-      </c>
+      <c r="G53" s="12"/>
       <c r="H53" s="24" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="I53" s="14"/>
       <c r="J53" s="14"/>
-      <c r="K53" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L53" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M53" s="38">
-        <v>0</v>
-      </c>
-      <c r="N53" s="38">
-        <v>0</v>
-      </c>
-      <c r="O53" s="12" t="s">
-        <v>188</v>
+      <c r="K53" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L53" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M53" s="37">
+        <v>0</v>
+      </c>
+      <c r="N53" s="37">
+        <v>0</v>
       </c>
       <c r="P53" s="16"/>
       <c r="Q53" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D54" s="12" t="s">
         <v>442</v>
       </c>
-      <c r="B54" s="12" t="s">
-        <v>469</v>
-      </c>
-      <c r="C54" s="15">
-        <v>3030</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>470</v>
-      </c>
-      <c r="E54" s="37" t="s">
+      <c r="E54" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F54" s="12"/>
       <c r="G54" s="12" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="H54" s="24" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I54" s="14"/>
       <c r="J54" s="14"/>
-      <c r="K54" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L54" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M54" s="38">
-        <v>0</v>
-      </c>
-      <c r="N54" s="38">
+      <c r="K54" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L54" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M54" s="37">
+        <v>0</v>
+      </c>
+      <c r="N54" s="37">
         <v>0</v>
       </c>
       <c r="P54" s="16"/>
       <c r="Q54" s="34" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
     </row>
     <row r="55" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>472</v>
+        <v>445</v>
+      </c>
+      <c r="C55" s="15">
+        <v>3292</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="E55" s="37" t="s">
+        <v>446</v>
+      </c>
+      <c r="E55" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F55" s="12"/>
       <c r="G55" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="H55" s="24" t="s">
-        <v>335</v>
+        <v>299</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>300</v>
       </c>
       <c r="I55" s="14"/>
       <c r="J55" s="14"/>
-      <c r="K55" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L55" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M55" s="38">
-        <v>0</v>
-      </c>
-      <c r="N55" s="38">
+      <c r="K55" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L55" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M55" s="37">
+        <v>0</v>
+      </c>
+      <c r="N55" s="37">
         <v>0</v>
       </c>
       <c r="P55" s="16"/>
       <c r="Q55" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>426</v>
+        <v>376</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="C56" s="15">
-        <v>5333</v>
+        <v>3294</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>474</v>
-      </c>
-      <c r="E56" s="37" t="s">
+        <v>448</v>
+      </c>
+      <c r="E56" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F56" s="12"/>
       <c r="G56" s="12" t="s">
-        <v>127</v>
+        <v>310</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>429</v>
+        <v>311</v>
       </c>
       <c r="I56" s="14"/>
       <c r="J56" s="14"/>
-      <c r="K56" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L56" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M56" s="38">
-        <v>0</v>
-      </c>
-      <c r="N56" s="38">
+      <c r="K56" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L56" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M56" s="37">
+        <v>0</v>
+      </c>
+      <c r="N56" s="37">
         <v>0</v>
       </c>
       <c r="P56" s="16"/>
       <c r="Q56" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
-        <v>426</v>
+        <v>319</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>475</v>
-      </c>
-      <c r="C57" s="15">
-        <v>5333</v>
+        <v>449</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>450</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="E57" s="37" t="s">
+        <v>451</v>
+      </c>
+      <c r="E57" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F57" s="12"/>
       <c r="G57" s="12" t="s">
-        <v>127</v>
+        <v>322</v>
       </c>
       <c r="H57" s="24" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="I57" s="14"/>
       <c r="J57" s="14"/>
-      <c r="K57" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L57" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M57" s="38">
-        <v>0</v>
-      </c>
-      <c r="N57" s="38">
+      <c r="K57" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L57" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M57" s="37">
+        <v>0</v>
+      </c>
+      <c r="N57" s="37">
         <v>0</v>
       </c>
       <c r="P57" s="16"/>
       <c r="Q57" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>255</v>
+        <v>298</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="C58" s="15">
-        <v>3044</v>
+        <v>3300</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>478</v>
-      </c>
-      <c r="E58" s="37" t="s">
+        <v>454</v>
+      </c>
+      <c r="E58" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F58" s="12"/>
       <c r="G58" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="H58" s="24" t="s">
-        <v>287</v>
+        <v>299</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>300</v>
       </c>
       <c r="I58" s="14"/>
       <c r="J58" s="14"/>
-      <c r="K58" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L58" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M58" s="38">
-        <v>0</v>
-      </c>
-      <c r="N58" s="38">
-        <v>0</v>
-      </c>
-      <c r="P58" s="16" t="s">
-        <v>479</v>
-      </c>
+      <c r="K58" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L58" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M58" s="37">
+        <v>0</v>
+      </c>
+      <c r="N58" s="37">
+        <v>0</v>
+      </c>
+      <c r="P58" s="16"/>
       <c r="Q58" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
-        <v>480</v>
+        <v>261</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>481</v>
+        <v>455</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>483</v>
-      </c>
-      <c r="E59" s="37" t="s">
+        <v>457</v>
+      </c>
+      <c r="E59" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F59" s="12"/>
-      <c r="G59" s="12" t="s">
-        <v>484</v>
-      </c>
+      <c r="G59" s="12"/>
       <c r="H59" s="24" t="s">
-        <v>485</v>
+        <v>285</v>
       </c>
       <c r="I59" s="14"/>
       <c r="J59" s="14"/>
-      <c r="K59" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L59" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M59" s="38">
-        <v>0</v>
-      </c>
-      <c r="N59" s="38">
+      <c r="K59" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L59" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M59" s="37">
+        <v>0</v>
+      </c>
+      <c r="N59" s="37">
         <v>0</v>
       </c>
       <c r="P59" s="16"/>
       <c r="Q59" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>486</v>
+        <v>458</v>
       </c>
       <c r="C60" s="15">
-        <v>3090</v>
+        <v>3333</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>487</v>
-      </c>
-      <c r="E60" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="E60" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F60" s="12"/>
-      <c r="G60" s="12" t="s">
-        <v>155</v>
-      </c>
+      <c r="G60" s="12"/>
       <c r="H60" s="24" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="I60" s="14"/>
       <c r="J60" s="14"/>
-      <c r="K60" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L60" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M60" s="38">
-        <v>0</v>
-      </c>
-      <c r="N60" s="38">
-        <v>0</v>
-      </c>
-      <c r="O60" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="P60" s="16"/>
+      <c r="K60" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L60" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M60" s="37">
+        <v>0</v>
+      </c>
+      <c r="N60" s="37">
+        <v>0</v>
+      </c>
+      <c r="P60" s="16" t="s">
+        <v>459</v>
+      </c>
       <c r="Q60" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>488</v>
+        <v>460</v>
       </c>
       <c r="C61" s="15">
-        <v>3096</v>
+        <v>3336</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E61" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="E61" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F61" s="12"/>
-      <c r="G61" s="12" t="s">
-        <v>155</v>
-      </c>
+      <c r="G61" s="12"/>
       <c r="H61" s="24" t="s">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="I61" s="14"/>
       <c r="J61" s="14"/>
-      <c r="K61" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L61" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M61" s="38">
-        <v>0</v>
-      </c>
-      <c r="N61" s="38">
+      <c r="K61" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L61" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M61" s="37">
+        <v>0</v>
+      </c>
+      <c r="N61" s="37">
         <v>0</v>
       </c>
       <c r="P61" s="16"/>
       <c r="Q61" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
-        <v>261</v>
+        <v>461</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>489</v>
-      </c>
-      <c r="C62" s="15" t="s">
-        <v>490</v>
+        <v>462</v>
+      </c>
+      <c r="C62" s="15">
+        <v>3339</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>491</v>
-      </c>
-      <c r="E62" s="37" t="s">
+        <v>463</v>
+      </c>
+      <c r="E62" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F62" s="12"/>
-      <c r="G62" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="H62" s="24" t="s">
-        <v>335</v>
-      </c>
-      <c r="I62" s="14"/>
-      <c r="J62" s="14"/>
-      <c r="K62" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L62" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M62" s="38">
-        <v>0</v>
-      </c>
-      <c r="N62" s="38">
+      <c r="G62" s="12"/>
+      <c r="H62" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="I62"/>
+      <c r="J62"/>
+      <c r="K62" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L62" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M62" s="37">
+        <v>0</v>
+      </c>
+      <c r="N62" s="37">
         <v>0</v>
       </c>
       <c r="P62" s="16"/>
       <c r="Q62" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>492</v>
+        <v>278</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>493</v>
+        <v>465</v>
       </c>
       <c r="C63" s="15">
-        <v>10001</v>
+        <v>3341</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>494</v>
-      </c>
-      <c r="E63" s="37" t="s">
+        <v>466</v>
+      </c>
+      <c r="E63" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F63" s="12"/>
-      <c r="G63" s="12" t="s">
-        <v>495</v>
-      </c>
+      <c r="G63" s="12"/>
       <c r="H63" s="24" t="s">
-        <v>496</v>
+        <v>467</v>
       </c>
       <c r="I63" s="14"/>
       <c r="J63" s="14"/>
-      <c r="K63" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L63" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M63" s="38">
-        <v>0</v>
-      </c>
-      <c r="N63" s="38">
+      <c r="K63" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L63" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M63" s="37">
+        <v>0</v>
+      </c>
+      <c r="N63" s="37">
         <v>0</v>
       </c>
       <c r="P63" s="16"/>
       <c r="Q63" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
-        <v>492</v>
+        <v>314</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>497</v>
+        <v>468</v>
       </c>
       <c r="C64" s="15">
-        <v>10001</v>
+        <v>3356</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>498</v>
-      </c>
-      <c r="E64" s="37" t="s">
+        <v>469</v>
+      </c>
+      <c r="E64" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F64" s="12"/>
-      <c r="G64" s="12" t="s">
-        <v>495</v>
-      </c>
+      <c r="G64" s="12"/>
       <c r="H64" s="24" t="s">
-        <v>496</v>
+        <v>318</v>
       </c>
       <c r="I64" s="14"/>
       <c r="J64" s="14"/>
-      <c r="K64" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L64" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M64" s="38">
-        <v>0</v>
-      </c>
-      <c r="N64" s="38">
-        <v>0</v>
-      </c>
-      <c r="P64" s="16"/>
+      <c r="K64" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L64" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M64" s="37">
+        <v>0</v>
+      </c>
+      <c r="N64" s="37">
+        <v>0</v>
+      </c>
+      <c r="P64" s="34" t="s">
+        <v>470</v>
+      </c>
       <c r="Q64" s="34" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
     </row>
     <row r="65" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
-        <v>499</v>
+        <v>314</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>500</v>
+        <v>471</v>
       </c>
       <c r="C65" s="15">
-        <v>3107</v>
+        <v>3357</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>501</v>
-      </c>
-      <c r="E65" s="37" t="s">
+        <v>472</v>
+      </c>
+      <c r="E65" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F65" s="12"/>
-      <c r="G65" s="12" t="s">
-        <v>502</v>
-      </c>
+      <c r="G65" s="12"/>
       <c r="H65" s="24" t="s">
-        <v>503</v>
+        <v>276</v>
       </c>
       <c r="I65" s="14"/>
       <c r="J65" s="14"/>
-      <c r="K65" s="38">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L65" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M65" s="38">
-        <v>0</v>
-      </c>
-      <c r="N65" s="38">
+      <c r="K65" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L65" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M65" s="37">
+        <v>0</v>
+      </c>
+      <c r="N65" s="37">
         <v>0</v>
       </c>
       <c r="P65" s="16"/>
       <c r="Q65" s="34" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
-        <v>504</v>
+        <v>261</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>505</v>
-      </c>
-      <c r="C66" s="15">
-        <v>3110</v>
+        <v>473</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>474</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>506</v>
-      </c>
-      <c r="E66" s="37" t="s">
+        <v>475</v>
+      </c>
+      <c r="E66" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F66" s="12"/>
-      <c r="G66" s="12" t="s">
-        <v>438</v>
-      </c>
+      <c r="G66" s="12"/>
       <c r="H66" s="24" t="s">
-        <v>439</v>
+        <v>285</v>
       </c>
       <c r="I66" s="14"/>
       <c r="J66" s="14"/>
-      <c r="K66" s="38">
-        <f t="shared" ref="K66:K122" si="1">AVERAGE(L66:N66)</f>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L66" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M66" s="38">
-        <v>0</v>
-      </c>
-      <c r="N66" s="38">
+      <c r="K66" s="37">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L66" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M66" s="37">
+        <v>0</v>
+      </c>
+      <c r="N66" s="37">
         <v>0</v>
       </c>
       <c r="P66" s="16"/>
       <c r="Q66" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>504</v>
+        <v>461</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>507</v>
+        <v>476</v>
       </c>
       <c r="C67" s="15">
-        <v>3111</v>
+        <v>3374</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>508</v>
-      </c>
-      <c r="E67" s="37" t="s">
+        <v>477</v>
+      </c>
+      <c r="E67" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F67" s="12"/>
-      <c r="G67" s="12" t="s">
-        <v>438</v>
-      </c>
-      <c r="H67" s="24" t="s">
-        <v>439</v>
+      <c r="G67" s="12"/>
+      <c r="H67" s="2" t="s">
+        <v>464</v>
       </c>
       <c r="I67" s="14"/>
       <c r="J67" s="14"/>
-      <c r="K67" s="38">
+      <c r="K67" s="37">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L67" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M67" s="38">
-        <v>0</v>
-      </c>
-      <c r="N67" s="38">
-        <v>0</v>
-      </c>
-      <c r="O67" s="12" t="s">
-        <v>188</v>
+      <c r="L67" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M67" s="37">
+        <v>0</v>
+      </c>
+      <c r="N67" s="37">
+        <v>0</v>
       </c>
       <c r="P67" s="16"/>
       <c r="Q67" s="34" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
     </row>
     <row r="68" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>268</v>
+        <v>376</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>509</v>
+        <v>478</v>
       </c>
       <c r="C68" s="15">
-        <v>3128</v>
+        <v>3382</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>510</v>
-      </c>
-      <c r="E68" s="37" t="s">
+        <v>479</v>
+      </c>
+      <c r="E68" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F68" s="12"/>
       <c r="G68" s="12" t="s">
-        <v>269</v>
+        <v>310</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="I68" s="14"/>
       <c r="J68" s="14"/>
-      <c r="K68" s="38">
+      <c r="K68" s="37">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L68" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M68" s="38">
-        <v>0</v>
-      </c>
-      <c r="N68" s="38">
-        <v>0</v>
-      </c>
-      <c r="O68" s="12" t="s">
-        <v>188</v>
+      <c r="L68" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M68" s="37">
+        <v>0</v>
+      </c>
+      <c r="N68" s="37">
+        <v>0</v>
       </c>
       <c r="P68" s="16"/>
       <c r="Q68" s="34" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
     </row>
     <row r="69" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
-        <v>504</v>
+        <v>376</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>511</v>
+        <v>480</v>
       </c>
       <c r="C69" s="15">
-        <v>3153</v>
+        <v>3391</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>512</v>
-      </c>
-      <c r="E69" s="37" t="s">
+        <v>481</v>
+      </c>
+      <c r="E69" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F69" s="12"/>
       <c r="G69" s="12" t="s">
-        <v>438</v>
+        <v>310</v>
       </c>
       <c r="H69" s="24" t="s">
-        <v>439</v>
+        <v>311</v>
       </c>
       <c r="I69" s="14"/>
       <c r="J69" s="14"/>
-      <c r="K69" s="38">
+      <c r="K69" s="37">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L69" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M69" s="38">
-        <v>0</v>
-      </c>
-      <c r="N69" s="38">
+      <c r="L69" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M69" s="37">
+        <v>0</v>
+      </c>
+      <c r="N69" s="37">
         <v>0</v>
       </c>
       <c r="P69" s="16"/>
       <c r="Q69" s="34" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
     </row>
     <row r="70" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
-        <v>513</v>
+        <v>385</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>514</v>
+        <v>482</v>
       </c>
       <c r="C70" s="15">
-        <v>3160</v>
-      </c>
-      <c r="D70" s="12" t="s">
-        <v>515</v>
-      </c>
-      <c r="E70" s="37" t="s">
+        <v>3387</v>
+      </c>
+      <c r="D70" s="12"/>
+      <c r="E70" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F70" s="12"/>
-      <c r="G70" s="12" t="s">
-        <v>304</v>
-      </c>
+      <c r="G70" s="12"/>
       <c r="H70" s="24" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="I70" s="14"/>
       <c r="J70" s="14"/>
-      <c r="K70" s="38">
+      <c r="K70" s="37">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L70" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M70" s="38">
-        <v>0</v>
-      </c>
-      <c r="N70" s="38">
+      <c r="L70" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="M70" s="37">
+        <v>0</v>
+      </c>
+      <c r="N70" s="37">
         <v>0</v>
       </c>
       <c r="P70" s="16"/>
       <c r="Q70" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
-        <v>261</v>
+        <v>461</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>516</v>
-      </c>
-      <c r="C71" s="15" t="s">
-        <v>517</v>
-      </c>
-      <c r="D71" s="12" t="s">
-        <v>518</v>
-      </c>
-      <c r="E71" s="37" t="s">
+        <v>483</v>
+      </c>
+      <c r="C71" s="15">
+        <v>3396</v>
+      </c>
+      <c r="D71" s="12"/>
+      <c r="E71" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F71" s="12"/>
-      <c r="G71" s="20" t="s">
-        <v>336</v>
-      </c>
+      <c r="G71" s="20"/>
       <c r="H71" s="25" t="s">
-        <v>335</v>
+        <v>464</v>
       </c>
       <c r="I71" s="14"/>
       <c r="J71" s="14"/>
-      <c r="K71" s="38">
+      <c r="K71" s="32">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L71" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M71" s="38">
-        <v>0</v>
-      </c>
-      <c r="N71" s="38">
+      <c r="L71" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M71" s="32">
+        <v>0</v>
+      </c>
+      <c r="N71" s="32">
         <v>0</v>
       </c>
       <c r="P71" s="16"/>
       <c r="Q71" s="34" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
     </row>
     <row r="72" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>519</v>
-      </c>
-      <c r="C72" s="15">
-        <v>3179</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>520</v>
-      </c>
-      <c r="E72" s="37" t="s">
+        <v>484</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="D72" s="12"/>
+      <c r="E72" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F72" s="12"/>
-      <c r="G72" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="H72" s="24" t="s">
-        <v>295</v>
+      <c r="G72" s="12"/>
+      <c r="H72" s="26" t="s">
+        <v>285</v>
       </c>
       <c r="I72" s="14"/>
       <c r="J72" s="14"/>
-      <c r="K72" s="38">
+      <c r="K72" s="32">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L72" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M72" s="38">
-        <v>0</v>
-      </c>
-      <c r="N72" s="38">
+      <c r="L72" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M72" s="32">
+        <v>0</v>
+      </c>
+      <c r="N72" s="32">
         <v>0</v>
       </c>
       <c r="P72" s="16"/>
       <c r="Q72" s="34" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
     </row>
     <row r="73" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>261</v>
+        <v>371</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>521</v>
-      </c>
-      <c r="C73" s="15" t="s">
-        <v>522</v>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="E73" s="37" t="s">
+        <v>486</v>
+      </c>
+      <c r="C73" s="15">
+        <v>3414</v>
+      </c>
+      <c r="D73" s="12"/>
+      <c r="E73" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F73" s="12"/>
-      <c r="G73" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="H73" s="24" t="s">
-        <v>335</v>
+      <c r="G73" s="12"/>
+      <c r="H73" s="26" t="s">
+        <v>375</v>
       </c>
       <c r="I73" s="14"/>
       <c r="J73" s="14"/>
-      <c r="K73" s="38">
+      <c r="K73" s="32">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L73" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M73" s="38">
-        <v>0</v>
-      </c>
-      <c r="N73" s="38">
+      <c r="L73" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M73" s="32">
+        <v>0</v>
+      </c>
+      <c r="N73" s="32">
         <v>0</v>
       </c>
       <c r="P73" s="16"/>
       <c r="Q73" s="34" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
     </row>
     <row r="74" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>504</v>
+        <v>268</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>524</v>
+        <v>487</v>
       </c>
       <c r="C74" s="15">
-        <v>3190</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>525</v>
-      </c>
-      <c r="E74" s="37" t="s">
+        <v>3421</v>
+      </c>
+      <c r="D74" s="12"/>
+      <c r="E74" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F74" s="12"/>
-      <c r="G74" s="12" t="s">
-        <v>438</v>
-      </c>
-      <c r="H74" s="24" t="s">
-        <v>439</v>
+      <c r="G74" s="12"/>
+      <c r="H74" s="25" t="s">
+        <v>280</v>
       </c>
       <c r="I74" s="14"/>
       <c r="J74" s="14"/>
-      <c r="K74" s="38">
+      <c r="K74" s="32">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L74" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M74" s="38">
-        <v>0</v>
-      </c>
-      <c r="N74" s="38">
+      <c r="L74" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M74" s="32">
+        <v>0</v>
+      </c>
+      <c r="N74" s="32">
         <v>0</v>
       </c>
       <c r="P74" s="16"/>
       <c r="Q74" s="34" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
     </row>
     <row r="75" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>513</v>
+        <v>298</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>526</v>
+        <v>488</v>
       </c>
       <c r="C75" s="15">
-        <v>3197</v>
-      </c>
-      <c r="D75" s="12" t="s">
-        <v>527</v>
-      </c>
-      <c r="E75" s="37" t="s">
+        <v>3423</v>
+      </c>
+      <c r="D75" s="12"/>
+      <c r="E75" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F75" s="12"/>
-      <c r="G75" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="H75" s="24" t="s">
-        <v>305</v>
+      <c r="G75" s="12"/>
+      <c r="H75" s="26" t="s">
+        <v>300</v>
       </c>
       <c r="I75" s="14"/>
       <c r="J75" s="14"/>
-      <c r="K75" s="38">
+      <c r="K75" s="32">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L75" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M75" s="38">
-        <v>0</v>
-      </c>
-      <c r="N75" s="38">
+      <c r="L75" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M75" s="32">
+        <v>0</v>
+      </c>
+      <c r="N75" s="32">
         <v>0</v>
       </c>
       <c r="P75" s="16"/>
       <c r="Q75" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>528</v>
-      </c>
-      <c r="C76" s="15" t="s">
-        <v>529</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>530</v>
-      </c>
-      <c r="E76" s="37" t="s">
+        <v>489</v>
+      </c>
+      <c r="C76" s="15">
+        <v>3427</v>
+      </c>
+      <c r="D76" s="12"/>
+      <c r="E76" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F76" s="12"/>
-      <c r="G76" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="H76" s="25" t="s">
-        <v>377</v>
+      <c r="G76" s="12"/>
+      <c r="H76" s="26" t="s">
+        <v>311</v>
       </c>
       <c r="I76" s="14"/>
       <c r="J76" s="14"/>
-      <c r="K76" s="38">
+      <c r="K76" s="32">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L76" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M76" s="38">
-        <v>0</v>
-      </c>
-      <c r="N76" s="38">
+      <c r="L76" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M76" s="32">
+        <v>0</v>
+      </c>
+      <c r="N76" s="32">
         <v>0</v>
       </c>
       <c r="P76" s="16"/>
       <c r="Q76" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>51</v>
+        <v>376</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>531</v>
+        <v>490</v>
       </c>
       <c r="C77" s="15">
-        <v>3213</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>532</v>
-      </c>
-      <c r="E77" s="37" t="s">
+        <v>3433</v>
+      </c>
+      <c r="D77" s="12"/>
+      <c r="E77" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F77" s="12"/>
-      <c r="G77" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="H77" s="24" t="s">
-        <v>297</v>
+      <c r="G77" s="12"/>
+      <c r="H77" s="26" t="s">
+        <v>311</v>
       </c>
       <c r="I77" s="14"/>
       <c r="J77" s="14"/>
-      <c r="K77" s="38">
+      <c r="K77" s="32">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L77" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M77" s="38">
-        <v>0</v>
-      </c>
-      <c r="N77" s="38">
+      <c r="L77" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M77" s="32">
+        <v>0</v>
+      </c>
+      <c r="N77" s="32">
         <v>0</v>
       </c>
       <c r="P77" s="16"/>
       <c r="Q77" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A78" s="12" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="78" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A78" s="12" t="s">
-        <v>91</v>
-      </c>
       <c r="B78" s="12" t="s">
-        <v>533</v>
-      </c>
-      <c r="C78" s="15">
-        <v>3220</v>
-      </c>
-      <c r="D78" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="E78" s="37" t="s">
-        <v>3</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="C78" s="15"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="12"/>
       <c r="F78" s="12"/>
-      <c r="G78" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="H78" s="24" t="s">
-        <v>341</v>
-      </c>
+      <c r="G78" s="12"/>
+      <c r="H78" s="24"/>
       <c r="I78" s="14"/>
       <c r="J78" s="14"/>
-      <c r="K78" s="38">
+      <c r="K78" s="32">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L78" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M78" s="38">
-        <v>0</v>
-      </c>
-      <c r="N78" s="38">
-        <v>0</v>
-      </c>
-      <c r="P78" s="16" t="s">
-        <v>534</v>
-      </c>
+      <c r="L78" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M78" s="32">
+        <v>0</v>
+      </c>
+      <c r="N78" s="32">
+        <v>0</v>
+      </c>
+      <c r="P78" s="16"/>
       <c r="Q78" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
-        <v>535</v>
+        <v>376</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>536</v>
+        <v>492</v>
       </c>
       <c r="C79" s="15"/>
-      <c r="D79" s="12" t="s">
-        <v>537</v>
-      </c>
-      <c r="E79" s="37" t="s">
-        <v>3</v>
-      </c>
+      <c r="D79" s="12"/>
+      <c r="E79" s="12"/>
       <c r="F79" s="12"/>
-      <c r="G79" s="12" t="s">
-        <v>538</v>
-      </c>
-      <c r="H79" s="39" t="s">
-        <v>539</v>
-      </c>
+      <c r="G79" s="12"/>
+      <c r="H79" s="24"/>
       <c r="I79" s="14"/>
       <c r="J79" s="14"/>
-      <c r="K79" s="38">
+      <c r="K79" s="32">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L79" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M79" s="38">
-        <v>0</v>
-      </c>
-      <c r="N79" s="38">
+      <c r="L79" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M79" s="32">
+        <v>0</v>
+      </c>
+      <c r="N79" s="32">
         <v>0</v>
       </c>
       <c r="P79" s="16"/>
       <c r="Q79" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>504</v>
+        <v>255</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>540</v>
+        <v>493</v>
       </c>
       <c r="C80" s="15">
-        <v>3226</v>
+        <v>3461</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="E80" s="37" t="s">
+        <v>494</v>
+      </c>
+      <c r="E80" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F80" s="12"/>
-      <c r="G80" s="12" t="s">
-        <v>438</v>
-      </c>
+      <c r="G80" s="12"/>
       <c r="H80" s="24" t="s">
-        <v>439</v>
+        <v>279</v>
       </c>
       <c r="I80" s="14"/>
       <c r="J80" s="14"/>
-      <c r="K80" s="38">
+      <c r="K80" s="32">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L80" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M80" s="38">
-        <v>0</v>
-      </c>
-      <c r="N80" s="38">
-        <v>0</v>
-      </c>
-      <c r="P80" s="16" t="s">
-        <v>542</v>
-      </c>
+      <c r="L80" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M80" s="32">
+        <v>0</v>
+      </c>
+      <c r="N80" s="32">
+        <v>0</v>
+      </c>
+      <c r="P80" s="16"/>
       <c r="Q80" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>543</v>
-      </c>
-      <c r="C81" s="15">
-        <v>3231</v>
+        <v>495</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>496</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="E81" s="37" t="s">
+        <v>497</v>
+      </c>
+      <c r="E81" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F81" s="12"/>
-      <c r="G81" s="12" t="s">
-        <v>155</v>
-      </c>
+      <c r="G81" s="12"/>
       <c r="H81" s="24" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="I81" s="14"/>
       <c r="J81" s="14"/>
-      <c r="K81" s="38">
+      <c r="K81" s="32">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L81" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M81" s="38">
-        <v>0</v>
-      </c>
-      <c r="N81" s="38">
-        <v>0</v>
-      </c>
-      <c r="P81" s="16" t="s">
-        <v>479</v>
-      </c>
+      <c r="L81" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M81" s="32">
+        <v>0</v>
+      </c>
+      <c r="N81" s="32">
+        <v>0</v>
+      </c>
+      <c r="P81" s="16"/>
       <c r="Q81" s="34" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
     </row>
     <row r="82" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>91</v>
+        <v>298</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>544</v>
+        <v>498</v>
       </c>
       <c r="C82" s="15">
-        <v>3236</v>
+        <v>3487</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="E82" s="37" t="s">
+        <v>499</v>
+      </c>
+      <c r="E82" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F82" s="12"/>
-      <c r="G82" s="12" t="s">
-        <v>157</v>
-      </c>
+      <c r="G82" s="12"/>
       <c r="H82" s="24" t="s">
-        <v>341</v>
+        <v>300</v>
       </c>
       <c r="I82" s="14"/>
       <c r="J82" s="14"/>
-      <c r="K82" s="38">
+      <c r="K82" s="32">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L82" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M82" s="38">
-        <v>0</v>
-      </c>
-      <c r="N82" s="38">
-        <v>0</v>
-      </c>
-      <c r="P82" s="16" t="s">
-        <v>534</v>
-      </c>
-      <c r="Q82" s="34" t="s">
-        <v>385</v>
-      </c>
+      <c r="L82" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M82" s="32">
+        <v>0</v>
+      </c>
+      <c r="N82" s="32">
+        <v>0</v>
+      </c>
+      <c r="P82" s="16"/>
+      <c r="Q82" s="16"/>
     </row>
     <row r="83" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>419</v>
+        <v>314</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>545</v>
+        <v>500</v>
       </c>
       <c r="C83" s="15">
-        <v>3240</v>
+        <v>3495</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>546</v>
-      </c>
-      <c r="E83" s="37" t="s">
+        <v>501</v>
+      </c>
+      <c r="E83" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F83" s="12"/>
       <c r="G83" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>423</v>
+        <v>317</v>
+      </c>
+      <c r="H83" s="24" t="s">
+        <v>318</v>
       </c>
       <c r="I83" s="14"/>
       <c r="J83" s="14"/>
-      <c r="K83" s="38">
+      <c r="K83" s="32">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L83" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M83" s="38">
-        <v>0</v>
-      </c>
-      <c r="N83" s="38">
+      <c r="L83" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M83" s="32">
+        <v>0</v>
+      </c>
+      <c r="N83" s="32">
         <v>0</v>
       </c>
       <c r="P83" s="16"/>
-      <c r="Q83" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q83" s="16"/>
+    </row>
+    <row r="84" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>442</v>
+        <v>502</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>547</v>
-      </c>
-      <c r="C84" s="15">
-        <v>3242</v>
+        <v>503</v>
+      </c>
+      <c r="C84" s="15" t="s">
+        <v>504</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>548</v>
-      </c>
-      <c r="E84" s="37" t="s">
+        <v>505</v>
+      </c>
+      <c r="E84" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F84" s="12"/>
       <c r="G84" s="12" t="s">
-        <v>445</v>
+        <v>506</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>446</v>
+        <v>507</v>
       </c>
       <c r="I84" s="14"/>
       <c r="J84" s="14"/>
-      <c r="K84" s="38">
+      <c r="K84" s="32">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L84" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M84" s="38">
-        <v>0</v>
-      </c>
-      <c r="N84" s="38">
+      <c r="L84" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M84" s="32">
+        <v>0</v>
+      </c>
+      <c r="N84" s="32">
         <v>0</v>
       </c>
       <c r="P84" s="16"/>
-      <c r="Q84" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+      <c r="Q84" s="16"/>
+    </row>
+    <row r="85" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="B85" s="12"/>
-      <c r="C85" s="15"/>
-      <c r="D85" s="12"/>
-      <c r="E85" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>508</v>
+      </c>
+      <c r="C85" s="15">
+        <v>3505</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="E85" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F85" s="12"/>
-      <c r="G85" s="12" t="s">
-        <v>549</v>
-      </c>
+      <c r="G85" s="12"/>
       <c r="H85" s="24" t="s">
-        <v>550</v>
+        <v>311</v>
       </c>
       <c r="I85" s="14"/>
       <c r="J85" s="14"/>
-      <c r="K85" s="38">
+      <c r="K85" s="32">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L85" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M85" s="38">
-        <v>0</v>
-      </c>
-      <c r="N85" s="38">
+      <c r="L85" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M85" s="32">
+        <v>0</v>
+      </c>
+      <c r="N85" s="32">
         <v>0</v>
       </c>
       <c r="P85" s="16"/>
-      <c r="Q85" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" ht="105" x14ac:dyDescent="0.25">
-      <c r="A86" s="12"/>
-      <c r="B86" s="12"/>
-      <c r="C86" s="15"/>
-      <c r="D86" s="12"/>
-      <c r="E86" s="37" t="s">
+      <c r="Q85" s="16"/>
+    </row>
+    <row r="86" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A86" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="B86" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="C86" s="15">
+        <v>3508</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="E86" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F86" s="12"/>
-      <c r="G86" s="12" t="s">
-        <v>551</v>
-      </c>
+      <c r="G86" s="12"/>
       <c r="H86" s="24" t="s">
-        <v>552</v>
+        <v>300</v>
       </c>
       <c r="I86" s="14"/>
       <c r="J86" s="14"/>
-      <c r="K86" s="38">
+      <c r="K86" s="32">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L86" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M86" s="38">
-        <v>0</v>
-      </c>
-      <c r="N86" s="38">
+      <c r="L86" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M86" s="32">
+        <v>0</v>
+      </c>
+      <c r="N86" s="32">
         <v>0</v>
       </c>
       <c r="P86" s="16"/>
-      <c r="Q86" s="34" t="s">
-        <v>385</v>
-      </c>
+      <c r="Q86" s="16"/>
     </row>
     <row r="87" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>442</v>
+        <v>298</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>553</v>
+        <v>512</v>
       </c>
       <c r="C87" s="15">
-        <v>3241</v>
+        <v>3526</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>554</v>
-      </c>
-      <c r="E87" s="37" t="s">
-        <v>3</v>
+        <v>433</v>
+      </c>
+      <c r="E87" s="36" t="s">
+        <v>65</v>
       </c>
       <c r="F87" s="12"/>
-      <c r="G87" s="12" t="s">
-        <v>445</v>
-      </c>
+      <c r="G87" s="12"/>
       <c r="H87" s="24" t="s">
-        <v>446</v>
+        <v>300</v>
       </c>
       <c r="I87" s="14"/>
-      <c r="J87" s="14"/>
-      <c r="K87" s="38">
+      <c r="J87" s="14">
+        <v>46190</v>
+      </c>
+      <c r="K87" s="32">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L87" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M87" s="38">
-        <v>0</v>
-      </c>
-      <c r="N87" s="38">
+      <c r="L87" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M87" s="32">
+        <v>0</v>
+      </c>
+      <c r="N87" s="32">
         <v>0</v>
       </c>
       <c r="P87" s="16"/>
       <c r="Q87" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>261</v>
+        <v>513</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>555</v>
+        <v>514</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>556</v>
+        <v>515</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>557</v>
-      </c>
-      <c r="E88" s="37" t="s">
+        <v>516</v>
+      </c>
+      <c r="E88" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F88" s="12"/>
-      <c r="G88" s="12" t="s">
-        <v>336</v>
-      </c>
+      <c r="G88" s="12"/>
       <c r="H88" s="24" t="s">
-        <v>335</v>
+        <v>517</v>
       </c>
       <c r="I88" s="14"/>
       <c r="J88" s="14"/>
-      <c r="K88" s="38">
+      <c r="K88" s="32">
         <f t="shared" si="1"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L88" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M88" s="38">
-        <v>0</v>
-      </c>
-      <c r="N88" s="38">
+      <c r="L88" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M88" s="32">
+        <v>0</v>
+      </c>
+      <c r="N88" s="32">
         <v>0</v>
       </c>
       <c r="P88" s="16"/>
-      <c r="Q88" s="34" t="s">
-        <v>385</v>
-      </c>
+      <c r="Q88" s="16"/>
     </row>
     <row r="89" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>504</v>
+        <v>298</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>558</v>
+        <v>518</v>
       </c>
       <c r="C89" s="15">
-        <v>3273</v>
+        <v>3547</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>559</v>
-      </c>
-      <c r="E89" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="E89" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F89" s="12"/>
-      <c r="G89" s="12" t="s">
-        <v>438</v>
-      </c>
+      <c r="G89" s="12"/>
       <c r="H89" s="24" t="s">
-        <v>439</v>
+        <v>300</v>
       </c>
       <c r="I89" s="14"/>
       <c r="J89" s="14"/>
-      <c r="K89" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L89" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M89" s="38">
-        <v>0</v>
-      </c>
-      <c r="N89" s="38">
+      <c r="K89" s="32">
+        <f t="shared" ref="K89:K95" si="2">AVERAGE(L89:N89)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L89" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M89" s="32">
+        <v>0</v>
+      </c>
+      <c r="N89" s="32">
         <v>0</v>
       </c>
       <c r="P89" s="16"/>
-      <c r="Q89" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q89" s="16"/>
+    </row>
+    <row r="90" spans="1:17" ht="105" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>419</v>
+        <v>519</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>560</v>
-      </c>
-      <c r="C90" s="15">
-        <v>3276</v>
+        <v>520</v>
+      </c>
+      <c r="C90" s="15" t="s">
+        <v>67</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>561</v>
-      </c>
-      <c r="E90" s="37" t="s">
+        <v>521</v>
+      </c>
+      <c r="E90" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F90" s="12"/>
       <c r="G90" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="H90" s="2" t="s">
         <v>423</v>
+      </c>
+      <c r="H90" s="24" t="s">
+        <v>424</v>
       </c>
       <c r="I90" s="14"/>
       <c r="J90" s="14"/>
-      <c r="K90" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L90" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M90" s="38">
-        <v>0</v>
-      </c>
-      <c r="N90" s="38">
+      <c r="K90" s="32">
+        <f t="shared" si="2"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L90" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M90" s="32">
+        <v>0</v>
+      </c>
+      <c r="N90" s="32">
         <v>0</v>
       </c>
       <c r="P90" s="16"/>
-      <c r="Q90" s="34" t="s">
-        <v>385</v>
-      </c>
+      <c r="Q90" s="16"/>
     </row>
     <row r="91" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
-        <v>419</v>
+        <v>298</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>562</v>
+        <v>522</v>
       </c>
       <c r="C91" s="15">
-        <v>3282</v>
+        <v>3561</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>563</v>
-      </c>
-      <c r="E91" s="37" t="s">
+        <v>523</v>
+      </c>
+      <c r="E91" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F91" s="12"/>
-      <c r="G91" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>423</v>
+      <c r="G91" s="12"/>
+      <c r="H91" s="24" t="s">
+        <v>300</v>
       </c>
       <c r="I91" s="14"/>
       <c r="J91" s="14"/>
-      <c r="K91" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L91" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M91" s="38">
-        <v>0</v>
-      </c>
-      <c r="N91" s="38">
+      <c r="K91" s="32">
+        <f t="shared" si="2"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L91" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M91" s="32">
+        <v>0</v>
+      </c>
+      <c r="N91" s="32">
         <v>0</v>
       </c>
       <c r="P91" s="16"/>
-      <c r="Q91" s="34" t="s">
-        <v>385</v>
-      </c>
+      <c r="Q91" s="16"/>
     </row>
     <row r="92" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>419</v>
+        <v>97</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>564</v>
-      </c>
-      <c r="C92" s="15">
-        <v>3283</v>
+        <v>524</v>
+      </c>
+      <c r="C92" s="15" t="s">
+        <v>67</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="E92" s="37" t="s">
+        <v>525</v>
+      </c>
+      <c r="E92" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F92" s="12"/>
-      <c r="G92" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>423</v>
+      <c r="G92" s="12"/>
+      <c r="H92" s="24" t="s">
+        <v>526</v>
       </c>
       <c r="I92" s="14"/>
       <c r="J92" s="14"/>
-      <c r="K92" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L92" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M92" s="38">
-        <v>0</v>
-      </c>
-      <c r="N92" s="38">
+      <c r="K92" s="32">
+        <f t="shared" si="2"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L92" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M92" s="32">
+        <v>0</v>
+      </c>
+      <c r="N92" s="32">
         <v>0</v>
       </c>
       <c r="P92" s="16"/>
-      <c r="Q92" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q92" s="16"/>
+    </row>
+    <row r="93" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
-        <v>261</v>
+        <v>352</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>565</v>
+        <v>527</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>566</v>
+        <v>543</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>567</v>
-      </c>
-      <c r="E93" s="37" t="s">
+        <v>528</v>
+      </c>
+      <c r="E93" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F93" s="12"/>
-      <c r="G93" s="12"/>
+      <c r="G93" s="12" t="s">
+        <v>356</v>
+      </c>
       <c r="H93" s="24" t="s">
-        <v>335</v>
+        <v>529</v>
       </c>
       <c r="I93" s="14"/>
       <c r="J93" s="14"/>
-      <c r="K93" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L93" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M93" s="38">
-        <v>0</v>
-      </c>
-      <c r="N93" s="38">
+      <c r="K93" s="32">
+        <f t="shared" si="2"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L93" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M93" s="32">
+        <v>0</v>
+      </c>
+      <c r="N93" s="32">
         <v>0</v>
       </c>
       <c r="P93" s="16"/>
-      <c r="Q93" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q93" s="16"/>
+    </row>
+    <row r="94" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
-        <v>568</v>
+        <v>530</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>569</v>
+        <v>531</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>67</v>
+        <v>544</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>570</v>
-      </c>
-      <c r="E94" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="E94" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F94" s="12"/>
       <c r="G94" s="12" t="s">
-        <v>571</v>
+        <v>277</v>
       </c>
       <c r="H94" s="24" t="s">
-        <v>572</v>
+        <v>276</v>
       </c>
       <c r="I94" s="14"/>
       <c r="J94" s="14"/>
-      <c r="K94" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L94" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M94" s="38">
-        <v>0</v>
-      </c>
-      <c r="N94" s="38">
+      <c r="K94" s="32">
+        <f t="shared" si="2"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L94" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M94" s="32">
+        <v>0</v>
+      </c>
+      <c r="N94" s="32">
         <v>0</v>
       </c>
       <c r="P94" s="16"/>
-      <c r="Q94" s="34" t="s">
-        <v>385</v>
-      </c>
+      <c r="Q94" s="16"/>
     </row>
     <row r="95" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
-        <v>419</v>
+        <v>314</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>573</v>
+        <v>532</v>
       </c>
       <c r="C95" s="15">
-        <v>3292</v>
+        <v>3614</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>574</v>
-      </c>
-      <c r="E95" s="37" t="s">
+        <v>533</v>
+      </c>
+      <c r="E95" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F95" s="12"/>
-      <c r="G95" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>423</v>
+      <c r="G95" s="12"/>
+      <c r="H95" s="24" t="s">
+        <v>318</v>
       </c>
       <c r="I95" s="14"/>
       <c r="J95" s="14"/>
-      <c r="K95" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L95" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M95" s="38">
-        <v>0</v>
-      </c>
-      <c r="N95" s="38">
+      <c r="K95" s="32">
+        <f t="shared" si="2"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L95" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M95" s="32">
+        <v>0</v>
+      </c>
+      <c r="N95" s="32">
         <v>0</v>
       </c>
       <c r="P95" s="16"/>
-      <c r="Q95" s="34" t="s">
-        <v>385</v>
-      </c>
+      <c r="Q95" s="16"/>
     </row>
     <row r="96" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>504</v>
+        <v>376</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>575</v>
+        <v>534</v>
       </c>
       <c r="C96" s="15">
-        <v>3294</v>
+        <v>3623</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>576</v>
-      </c>
-      <c r="E96" s="37" t="s">
+        <v>538</v>
+      </c>
+      <c r="E96" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F96" s="12"/>
-      <c r="G96" s="12" t="s">
-        <v>438</v>
-      </c>
+      <c r="G96" s="12"/>
       <c r="H96" s="24" t="s">
-        <v>439</v>
+        <v>311</v>
       </c>
       <c r="I96" s="14"/>
       <c r="J96" s="14"/>
-      <c r="K96" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L96" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M96" s="38">
-        <v>0</v>
-      </c>
-      <c r="N96" s="38">
+      <c r="K96" s="32">
+        <f t="shared" ref="K96" si="3">AVERAGE(L96:N96)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L96" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M96" s="32">
+        <v>0</v>
+      </c>
+      <c r="N96" s="32">
         <v>0</v>
       </c>
       <c r="P96" s="16"/>
-      <c r="Q96" s="34" t="s">
+      <c r="Q96" s="16"/>
+    </row>
+    <row r="97" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A97" s="12" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="97" spans="1:17" ht="75" x14ac:dyDescent="0.25">
-      <c r="A97" s="12" t="s">
-        <v>447</v>
-      </c>
       <c r="B97" s="12" t="s">
-        <v>577</v>
-      </c>
-      <c r="C97" s="15" t="s">
-        <v>578</v>
+        <v>535</v>
+      </c>
+      <c r="C97" s="15">
+        <v>3634</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>579</v>
-      </c>
-      <c r="E97" s="37" t="s">
+        <v>539</v>
+      </c>
+      <c r="E97" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F97" s="12"/>
-      <c r="G97" s="12" t="s">
-        <v>450</v>
-      </c>
+      <c r="G97" s="12"/>
       <c r="H97" s="24" t="s">
-        <v>580</v>
+        <v>284</v>
       </c>
       <c r="I97" s="14"/>
       <c r="J97" s="14"/>
-      <c r="K97" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L97" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M97" s="38">
-        <v>0</v>
-      </c>
-      <c r="N97" s="38">
+      <c r="K97" s="32">
+        <f t="shared" ref="K97:K99" si="4">AVERAGE(L97:N97)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L97" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M97" s="32">
+        <v>0</v>
+      </c>
+      <c r="N97" s="32">
         <v>0</v>
       </c>
       <c r="P97" s="16"/>
-      <c r="Q97" s="34" t="s">
-        <v>385</v>
-      </c>
+      <c r="Q97" s="16"/>
     </row>
     <row r="98" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>419</v>
+        <v>376</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>581</v>
+        <v>536</v>
       </c>
       <c r="C98" s="15">
-        <v>3300</v>
+        <v>3650</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>582</v>
-      </c>
-      <c r="E98" s="37" t="s">
+        <v>540</v>
+      </c>
+      <c r="E98" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F98" s="12"/>
-      <c r="G98" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>423</v>
+      <c r="G98" s="12"/>
+      <c r="H98" s="24" t="s">
+        <v>311</v>
       </c>
       <c r="I98" s="14"/>
       <c r="J98" s="14"/>
-      <c r="K98" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L98" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M98" s="38">
-        <v>0</v>
-      </c>
-      <c r="N98" s="38">
+      <c r="K98" s="32">
+        <f t="shared" si="4"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L98" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M98" s="32">
+        <v>0</v>
+      </c>
+      <c r="N98" s="32">
         <v>0</v>
       </c>
       <c r="P98" s="16"/>
-      <c r="Q98" s="34" t="s">
-        <v>385</v>
-      </c>
+      <c r="Q98" s="16"/>
     </row>
     <row r="99" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
-        <v>261</v>
+        <v>91</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>583</v>
-      </c>
-      <c r="C99" s="15" t="s">
-        <v>584</v>
+        <v>537</v>
+      </c>
+      <c r="C99" s="15">
+        <v>3663</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>585</v>
-      </c>
-      <c r="E99" s="37" t="s">
+        <v>380</v>
+      </c>
+      <c r="E99" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F99" s="12"/>
       <c r="G99" s="12"/>
       <c r="H99" s="24" t="s">
-        <v>335</v>
+        <v>288</v>
       </c>
       <c r="I99" s="14"/>
       <c r="J99" s="14"/>
-      <c r="K99" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L99" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M99" s="38">
-        <v>0</v>
-      </c>
-      <c r="N99" s="38">
+      <c r="K99" s="32">
+        <f t="shared" si="4"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="L99" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="M99" s="32">
+        <v>0</v>
+      </c>
+      <c r="N99" s="32">
         <v>0</v>
       </c>
       <c r="P99" s="16"/>
-      <c r="Q99" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q99" s="16"/>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>586</v>
-      </c>
-      <c r="C100" s="15">
-        <v>3333</v>
-      </c>
-      <c r="D100" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E100" s="37" t="s">
-        <v>3</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="C100" s="15" t="s">
+        <v>541</v>
+      </c>
+      <c r="D100" s="12"/>
+      <c r="E100" s="36"/>
       <c r="F100" s="12"/>
       <c r="G100" s="12"/>
-      <c r="H100" s="24" t="s">
-        <v>295</v>
-      </c>
+      <c r="H100" s="24"/>
       <c r="I100" s="14"/>
       <c r="J100" s="14"/>
-      <c r="K100" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L100" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M100" s="38">
-        <v>0</v>
-      </c>
-      <c r="N100" s="38">
-        <v>0</v>
-      </c>
-      <c r="P100" s="16" t="s">
-        <v>587</v>
-      </c>
-      <c r="Q100" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A101" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="B101" s="12" t="s">
-        <v>588</v>
-      </c>
-      <c r="C101" s="15">
-        <v>3336</v>
-      </c>
-      <c r="D101" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="E101" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="12"/>
-      <c r="G101" s="12"/>
-      <c r="H101" s="24" t="s">
-        <v>446</v>
-      </c>
-      <c r="I101" s="14"/>
-      <c r="J101" s="14"/>
-      <c r="K101" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L101" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M101" s="38">
-        <v>0</v>
-      </c>
-      <c r="N101" s="38">
-        <v>0</v>
-      </c>
-      <c r="P101" s="16"/>
-      <c r="Q101" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" ht="75" x14ac:dyDescent="0.25">
-      <c r="A102" s="12" t="s">
-        <v>589</v>
-      </c>
-      <c r="B102" s="12" t="s">
-        <v>590</v>
-      </c>
-      <c r="C102" s="15">
-        <v>3339</v>
-      </c>
-      <c r="D102" s="12" t="s">
-        <v>591</v>
-      </c>
-      <c r="E102" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F102" s="12"/>
-      <c r="G102" s="12"/>
-      <c r="H102" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="I102"/>
-      <c r="J102"/>
-      <c r="K102" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L102" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M102" s="38">
-        <v>0</v>
-      </c>
-      <c r="N102" s="38">
-        <v>0</v>
-      </c>
-      <c r="P102" s="16"/>
-      <c r="Q102" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A103" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="B103" s="12" t="s">
-        <v>593</v>
-      </c>
-      <c r="C103" s="15">
-        <v>3341</v>
-      </c>
-      <c r="D103" s="12" t="s">
-        <v>594</v>
-      </c>
-      <c r="E103" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F103" s="12"/>
-      <c r="G103" s="12"/>
-      <c r="H103" s="24" t="s">
-        <v>595</v>
-      </c>
-      <c r="I103" s="14"/>
-      <c r="J103" s="14"/>
-      <c r="K103" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L103" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M103" s="38">
-        <v>0</v>
-      </c>
-      <c r="N103" s="38">
-        <v>0</v>
-      </c>
-      <c r="P103" s="16"/>
-      <c r="Q103" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A104" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="B104" s="12" t="s">
-        <v>596</v>
-      </c>
-      <c r="C104" s="15">
-        <v>3356</v>
-      </c>
-      <c r="D104" s="12" t="s">
-        <v>597</v>
-      </c>
-      <c r="E104" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F104" s="12"/>
-      <c r="G104" s="12"/>
-      <c r="H104" s="24" t="s">
-        <v>446</v>
-      </c>
-      <c r="I104" s="14"/>
-      <c r="J104" s="14"/>
-      <c r="K104" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L104" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M104" s="38">
-        <v>0</v>
-      </c>
-      <c r="N104" s="38">
-        <v>0</v>
-      </c>
-      <c r="P104" s="34" t="s">
-        <v>598</v>
-      </c>
-      <c r="Q104" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A105" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="B105" s="12" t="s">
-        <v>599</v>
-      </c>
-      <c r="C105" s="15">
-        <v>3357</v>
-      </c>
-      <c r="D105" s="12" t="s">
-        <v>600</v>
-      </c>
-      <c r="E105" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F105" s="12"/>
-      <c r="G105" s="12"/>
-      <c r="H105" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="I105" s="14"/>
-      <c r="J105" s="14"/>
-      <c r="K105" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L105" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M105" s="38">
-        <v>0</v>
-      </c>
-      <c r="N105" s="38">
-        <v>0</v>
-      </c>
-      <c r="P105" s="16"/>
-      <c r="Q105" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A106" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="B106" s="12" t="s">
-        <v>601</v>
-      </c>
-      <c r="C106" s="15" t="s">
-        <v>602</v>
-      </c>
-      <c r="D106" s="12" t="s">
-        <v>603</v>
-      </c>
-      <c r="E106" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F106" s="12"/>
-      <c r="G106" s="12"/>
-      <c r="H106" s="24" t="s">
-        <v>335</v>
-      </c>
-      <c r="I106" s="14"/>
-      <c r="J106" s="14"/>
-      <c r="K106" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L106" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M106" s="38">
-        <v>0</v>
-      </c>
-      <c r="N106" s="38">
-        <v>0</v>
-      </c>
-      <c r="P106" s="16"/>
-      <c r="Q106" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17" ht="75" x14ac:dyDescent="0.25">
-      <c r="A107" s="12" t="s">
-        <v>589</v>
-      </c>
-      <c r="B107" s="12" t="s">
-        <v>604</v>
-      </c>
-      <c r="C107" s="15">
-        <v>3374</v>
-      </c>
-      <c r="D107" s="12" t="s">
-        <v>605</v>
-      </c>
-      <c r="E107" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F107" s="12"/>
-      <c r="G107" s="12"/>
-      <c r="H107" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="I107" s="14"/>
-      <c r="J107" s="14"/>
-      <c r="K107" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L107" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M107" s="38">
-        <v>0</v>
-      </c>
-      <c r="N107" s="38">
-        <v>0</v>
-      </c>
-      <c r="P107" s="16"/>
-      <c r="Q107" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A108" s="12" t="s">
-        <v>504</v>
-      </c>
-      <c r="B108" s="12" t="s">
-        <v>606</v>
-      </c>
-      <c r="C108" s="15">
-        <v>3382</v>
-      </c>
-      <c r="D108" s="12" t="s">
-        <v>607</v>
-      </c>
-      <c r="E108" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F108" s="12"/>
-      <c r="G108" s="12" t="s">
-        <v>438</v>
-      </c>
-      <c r="H108" s="24" t="s">
-        <v>439</v>
-      </c>
-      <c r="I108" s="14"/>
-      <c r="J108" s="14"/>
-      <c r="K108" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L108" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M108" s="38">
-        <v>0</v>
-      </c>
-      <c r="N108" s="38">
-        <v>0</v>
-      </c>
-      <c r="P108" s="16"/>
-      <c r="Q108" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A109" s="12" t="s">
-        <v>504</v>
-      </c>
-      <c r="B109" s="12" t="s">
-        <v>608</v>
-      </c>
-      <c r="C109" s="15">
-        <v>3391</v>
-      </c>
-      <c r="D109" s="12" t="s">
-        <v>609</v>
-      </c>
-      <c r="E109" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F109" s="12"/>
-      <c r="G109" s="12" t="s">
-        <v>438</v>
-      </c>
-      <c r="H109" s="24" t="s">
-        <v>439</v>
-      </c>
-      <c r="I109" s="14"/>
-      <c r="J109" s="14"/>
-      <c r="K109" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L109" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M109" s="38">
-        <v>0</v>
-      </c>
-      <c r="N109" s="38">
-        <v>0</v>
-      </c>
-      <c r="P109" s="16"/>
-      <c r="Q109" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="110" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A110" s="12" t="s">
-        <v>513</v>
-      </c>
-      <c r="B110" s="12" t="s">
-        <v>610</v>
-      </c>
-      <c r="C110" s="15">
-        <v>3387</v>
-      </c>
-      <c r="D110" s="12"/>
-      <c r="E110" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F110" s="12"/>
-      <c r="G110" s="12"/>
-      <c r="H110" s="24" t="s">
-        <v>305</v>
-      </c>
-      <c r="I110" s="14"/>
-      <c r="J110" s="14"/>
-      <c r="K110" s="38">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L110" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="M110" s="38">
-        <v>0</v>
-      </c>
-      <c r="N110" s="38">
-        <v>0</v>
-      </c>
-      <c r="P110" s="16"/>
-      <c r="Q110" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" ht="75" x14ac:dyDescent="0.25">
-      <c r="A111" s="12" t="s">
-        <v>589</v>
-      </c>
-      <c r="B111" s="12" t="s">
-        <v>611</v>
-      </c>
-      <c r="C111" s="15">
-        <v>3396</v>
-      </c>
-      <c r="D111" s="12"/>
-      <c r="E111" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F111" s="12"/>
-      <c r="G111" s="20"/>
-      <c r="H111" s="25" t="s">
-        <v>592</v>
-      </c>
-      <c r="I111" s="14"/>
-      <c r="J111" s="14"/>
-      <c r="K111" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L111" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M111" s="32">
-        <v>0</v>
-      </c>
-      <c r="N111" s="32">
-        <v>0</v>
-      </c>
-      <c r="P111" s="16"/>
-      <c r="Q111" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="112" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A112" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="B112" s="12" t="s">
-        <v>612</v>
-      </c>
-      <c r="C112" s="15" t="s">
-        <v>613</v>
-      </c>
-      <c r="D112" s="12"/>
-      <c r="E112" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F112" s="12"/>
-      <c r="G112" s="12"/>
-      <c r="H112" s="26" t="s">
-        <v>335</v>
-      </c>
-      <c r="I112" s="14"/>
-      <c r="J112" s="14"/>
-      <c r="K112" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L112" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M112" s="32">
-        <v>0</v>
-      </c>
-      <c r="N112" s="32">
-        <v>0</v>
-      </c>
-      <c r="P112" s="16"/>
-      <c r="Q112" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="113" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A113" s="12" t="s">
-        <v>499</v>
-      </c>
-      <c r="B113" s="12" t="s">
-        <v>614</v>
-      </c>
-      <c r="C113" s="15">
-        <v>3414</v>
-      </c>
-      <c r="D113" s="12"/>
-      <c r="E113" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F113" s="12"/>
-      <c r="G113" s="12"/>
-      <c r="H113" s="26" t="s">
-        <v>503</v>
-      </c>
-      <c r="I113" s="14"/>
-      <c r="J113" s="14"/>
-      <c r="K113" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L113" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M113" s="32">
-        <v>0</v>
-      </c>
-      <c r="N113" s="32">
-        <v>0</v>
-      </c>
-      <c r="P113" s="16"/>
-      <c r="Q113" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A114" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="B114" s="12" t="s">
-        <v>615</v>
-      </c>
-      <c r="C114" s="15">
-        <v>3421</v>
-      </c>
-      <c r="D114" s="12"/>
-      <c r="E114" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F114" s="12"/>
-      <c r="G114" s="12"/>
-      <c r="H114" s="25" t="s">
-        <v>295</v>
-      </c>
-      <c r="I114" s="14"/>
-      <c r="J114" s="14"/>
-      <c r="K114" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L114" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M114" s="32">
-        <v>0</v>
-      </c>
-      <c r="N114" s="32">
-        <v>0</v>
-      </c>
-      <c r="P114" s="16"/>
-      <c r="Q114" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A115" s="12" t="s">
-        <v>419</v>
-      </c>
-      <c r="B115" s="12" t="s">
-        <v>616</v>
-      </c>
-      <c r="C115" s="15">
-        <v>3423</v>
-      </c>
-      <c r="D115" s="12"/>
-      <c r="E115" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F115" s="12"/>
-      <c r="G115" s="12"/>
-      <c r="H115" s="26" t="s">
-        <v>423</v>
-      </c>
-      <c r="I115" s="14"/>
-      <c r="J115" s="14"/>
-      <c r="K115" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L115" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M115" s="32">
-        <v>0</v>
-      </c>
-      <c r="N115" s="32">
-        <v>0</v>
-      </c>
-      <c r="P115" s="16"/>
-      <c r="Q115" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A116" s="12" t="s">
-        <v>504</v>
-      </c>
-      <c r="B116" s="12" t="s">
-        <v>617</v>
-      </c>
-      <c r="C116" s="15">
-        <v>3427</v>
-      </c>
-      <c r="D116" s="12"/>
-      <c r="E116" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F116" s="12"/>
-      <c r="G116" s="12"/>
-      <c r="H116" s="26" t="s">
-        <v>439</v>
-      </c>
-      <c r="I116" s="14"/>
-      <c r="J116" s="14"/>
-      <c r="K116" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L116" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M116" s="32">
-        <v>0</v>
-      </c>
-      <c r="N116" s="32">
-        <v>0</v>
-      </c>
-      <c r="P116" s="16"/>
-      <c r="Q116" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A117" s="12" t="s">
-        <v>504</v>
-      </c>
-      <c r="B117" s="12" t="s">
-        <v>618</v>
-      </c>
-      <c r="C117" s="15">
-        <v>3433</v>
-      </c>
-      <c r="D117" s="12"/>
-      <c r="E117" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F117" s="12"/>
-      <c r="G117" s="12"/>
-      <c r="H117" s="26" t="s">
-        <v>439</v>
-      </c>
-      <c r="I117" s="14"/>
-      <c r="J117" s="14"/>
-      <c r="K117" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L117" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M117" s="32">
-        <v>0</v>
-      </c>
-      <c r="N117" s="32">
-        <v>0</v>
-      </c>
-      <c r="P117" s="16"/>
-      <c r="Q117" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="118" spans="1:17" ht="30" x14ac:dyDescent="0.25">
-      <c r="A118" s="12" t="s">
-        <v>513</v>
-      </c>
-      <c r="B118" s="12" t="s">
-        <v>619</v>
-      </c>
-      <c r="C118" s="15"/>
-      <c r="D118" s="12"/>
-      <c r="E118" s="12"/>
-      <c r="F118" s="12"/>
-      <c r="G118" s="12"/>
-      <c r="H118" s="24"/>
-      <c r="I118" s="14"/>
-      <c r="J118" s="14"/>
-      <c r="K118" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L118" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M118" s="32">
-        <v>0</v>
-      </c>
-      <c r="N118" s="32">
-        <v>0</v>
-      </c>
-      <c r="P118" s="16"/>
-      <c r="Q118" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" ht="30" x14ac:dyDescent="0.25">
-      <c r="A119" s="12" t="s">
-        <v>504</v>
-      </c>
-      <c r="B119" s="12" t="s">
-        <v>620</v>
-      </c>
-      <c r="C119" s="15"/>
-      <c r="D119" s="12"/>
-      <c r="E119" s="12"/>
-      <c r="F119" s="12"/>
-      <c r="G119" s="12"/>
-      <c r="H119" s="24"/>
-      <c r="I119" s="14"/>
-      <c r="J119" s="14"/>
-      <c r="K119" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L119" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M119" s="32">
-        <v>0</v>
-      </c>
-      <c r="N119" s="32">
-        <v>0</v>
-      </c>
-      <c r="P119" s="16"/>
-      <c r="Q119" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" ht="30" x14ac:dyDescent="0.25">
-      <c r="A120" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B120" s="12" t="s">
-        <v>621</v>
-      </c>
-      <c r="C120" s="15"/>
-      <c r="D120" s="12"/>
-      <c r="E120" s="12"/>
-      <c r="F120" s="12"/>
-      <c r="G120" s="12"/>
-      <c r="H120" s="24"/>
-      <c r="I120" s="14"/>
-      <c r="J120" s="14"/>
-      <c r="K120" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L120" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M120" s="32">
-        <v>0</v>
-      </c>
-      <c r="N120" s="32">
-        <v>0</v>
-      </c>
-      <c r="P120" s="16"/>
-      <c r="Q120" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" ht="30" x14ac:dyDescent="0.25">
-      <c r="A121" s="12"/>
-      <c r="B121" s="12" t="s">
-        <v>622</v>
-      </c>
-      <c r="C121" s="15"/>
-      <c r="D121" s="12"/>
-      <c r="E121" s="12"/>
-      <c r="F121" s="12"/>
-      <c r="G121" s="12"/>
-      <c r="H121" s="24"/>
-      <c r="I121" s="14"/>
-      <c r="J121" s="14"/>
-      <c r="K121" s="16" t="e">
-        <f t="shared" si="1"/>
+      <c r="K100" s="37" t="e">
+        <f>AVERAGE(L100:N100)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L121" s="16"/>
-      <c r="M121" s="16"/>
-      <c r="N121" s="16"/>
-      <c r="P121" s="16"/>
-      <c r="Q121" s="34" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" ht="30" x14ac:dyDescent="0.25">
-      <c r="A122" s="12"/>
-      <c r="B122" s="12"/>
-      <c r="C122" s="15"/>
-      <c r="D122" s="12"/>
-      <c r="E122" s="12"/>
-      <c r="F122" s="12"/>
-      <c r="G122" s="12"/>
-      <c r="H122" s="24"/>
-      <c r="I122" s="14"/>
-      <c r="J122" s="14"/>
-      <c r="K122" s="16" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L122" s="16"/>
-      <c r="M122" s="16"/>
-      <c r="N122" s="16"/>
-      <c r="P122" s="16"/>
-      <c r="Q122" s="34" t="s">
-        <v>385</v>
-      </c>
+      <c r="L100" s="37"/>
+      <c r="M100" s="37"/>
+      <c r="N100" s="37"/>
+      <c r="P100" s="16"/>
+      <c r="Q100" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -9343,25 +8093,25 @@
     </row>
     <row r="12" spans="1:14" ht="120" x14ac:dyDescent="0.25">
       <c r="A12" s="35" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B12" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C12">
         <v>2547</v>
       </c>
       <c r="D12" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E12" t="s">
         <v>50</v>
       </c>
       <c r="G12" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="I12" s="3">
         <v>45993</v>

--- a/Client Information App.xlsx
+++ b/Client Information App.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\06 Operation\1. Operation Documents\3. Project Cordination\5. Data Analytics\Power Bi Projects\1. PB2401 Client Information\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D0425E-BBD9-42C4-B0C4-135CDED41D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74F4AD8-0D2F-4CA9-B2C5-1DDCFED2680B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="768" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="357">
   <si>
     <t>Ready to dispatch</t>
   </si>
@@ -1011,9 +1011,6 @@
     <t>Curved Flashings</t>
   </si>
   <si>
-    <t>CGY</t>
-  </si>
-  <si>
     <t>Drummond Street</t>
   </si>
   <si>
@@ -1063,12 +1060,6 @@
     <t>Critical Information</t>
   </si>
   <si>
-    <t>Broadway Central 2</t>
-  </si>
-  <si>
-    <t>G2 3BW</t>
-  </si>
-  <si>
     <t>Thurrock Power Limited
 Thurrock Flexible Generation
 Station Road
@@ -1089,51 +1080,6 @@
     <t>RM18 8QR</t>
   </si>
   <si>
-    <t>Aluworks</t>
-  </si>
-  <si>
-    <t>Aluworks Ltd.
- Gate 2 Chester House
- Bentails
- Basildon
- SS14 3BG
-Contact: Damian +44 (0)7574 403789</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SS14 3BG</t>
-  </si>
-  <si>
-    <t>Southbank Place</t>
-  </si>
-  <si>
-    <t>St George Plc
-,Camden Goods Yard,
-Chalk Farm Road, Chalk Farm
-,Camden Town,London, NW1 8EH
-Contact: Arek +44 (0) 7534 515 939</t>
-  </si>
-  <si>
-    <t>McAleer &amp; Rushe Contracts UK Ltd
- (For FCS Facades)
- ,Broadway Central, PBSA,
-200 Renfield Street,
- Glasgow, G2 3BW
-Contact: Jakub +44 (0) 7772 728 234</t>
-  </si>
-  <si>
-    <t>McAleer &amp; Rushe Contracts UK Ltd
-(For FCS Facades)
-Stroudley Walk
-E3 3EW
-Jakub - +44 (0) 7772 728 234</t>
-  </si>
-  <si>
-    <t>Melliss Avenue</t>
-  </si>
-  <si>
-    <t>TW9 4BZ</t>
-  </si>
-  <si>
     <t>McAleer &amp; Rushe Site
 (For FCS Facades)
 Mellis Avenue
@@ -1142,6 +1088,157 @@
 Piotr Slowiak +44 (0) 7968 773 582</t>
   </si>
   <si>
+    <t>order_id</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>timestamp</t>
+  </si>
+  <si>
+    <t>Delivery Address</t>
+  </si>
+  <si>
+    <t>11/02/2026
+8:55</t>
+  </si>
+  <si>
+    <t>Aberdeen Lane</t>
+  </si>
+  <si>
+    <t>McAleer &amp; Rushe Contracts UK Ltd
+(For FCS Facades)
+Aberdeen Lane
+Islington
+N5 2EJ
+Pawel +44 (0) 7971 679 193</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EW1 2SF</t>
+  </si>
+  <si>
+    <t>St George North london Ltd
+(For FCS Facades)
+London Dock
+St George Construction Site
+Pennington Street, EW1 2SF
+Arek 07534 515 939</t>
+  </si>
+  <si>
+    <t>Selly Oak</t>
+  </si>
+  <si>
+    <t>McAleer &amp; Rushe Site
+(For FCS Facades)
+1 Chapel Lane
+Selly Oak
+B29 6SJ
+Ruslan +44 (0) 7896 059 740</t>
+  </si>
+  <si>
+    <t>London Dock</t>
+  </si>
+  <si>
+    <t>Mellis Avenue</t>
+  </si>
+  <si>
+    <t>SO-2139</t>
+  </si>
+  <si>
+    <t>CW Spandrels &amp; Trays</t>
+  </si>
+  <si>
+    <t>Elm Lane Fire Station</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> O&amp;P Construction Ltd (Sparta Clad)
+Elm Lane Fire Station 
+Sheffield
+S5 7TW
+Gavin Bailey 07719711503</t>
+  </si>
+  <si>
+    <t>SO-2173</t>
+  </si>
+  <si>
+    <t>Arched Wall Panels</t>
+  </si>
+  <si>
+    <t>Astley Place</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46 MERRIAL STREET ST5 2AW 
+Astley Place  
+York Place  
+Newcastle-Under -Lyme  
+ST5 2AW 
+PETRICA- +44 (0) 7453 264 227 </t>
+  </si>
+  <si>
+    <t>SO-2204</t>
+  </si>
+  <si>
+    <t>SO-2210</t>
+  </si>
+  <si>
+    <t>SO-2214</t>
+  </si>
+  <si>
+    <t>SO-2216</t>
+  </si>
+  <si>
+    <t>SO-2217</t>
+  </si>
+  <si>
+    <t>SO-2218</t>
+  </si>
+  <si>
+    <t>SO-2219</t>
+  </si>
+  <si>
+    <t>SO-2222</t>
+  </si>
+  <si>
+    <t>SO-2227</t>
+  </si>
+  <si>
+    <t>SO-2229</t>
+  </si>
+  <si>
+    <t>SO-2230</t>
+  </si>
+  <si>
+    <t>SO-2232</t>
+  </si>
+  <si>
+    <t>SO-2233</t>
+  </si>
+  <si>
+    <t>SO-2234</t>
+  </si>
+  <si>
+    <t>SO-2235</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>SO-2236</t>
+  </si>
+  <si>
+    <t>Brickwork Pods</t>
+  </si>
+  <si>
+    <t>Brackets and rails call off for Castellated areas</t>
+  </si>
+  <si>
+    <t>Additional Profiles</t>
+  </si>
+  <si>
+    <t>Final Plenums</t>
+  </si>
+  <si>
     <t>AJE facades 
 C/O Formation 
 58 Cherry orchard 
@@ -1150,824 +1247,17 @@
 Dragos +44 (0) 7719 309 409</t>
   </si>
   <si>
-    <t>CR0 6BA</t>
-  </si>
-  <si>
-    <t>Cills</t>
-  </si>
-  <si>
-    <t>McAleer &amp; Rushe Contracts UK Ltd
-(For FCS Facades)
-1 Church Road
-Tunbridge Wells
-Kent, TN1 1PN
-Kontakt: Pawel +44(0) 7590 056 393 </t>
-  </si>
-  <si>
-    <t>order_id</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>timestamp</t>
-  </si>
-  <si>
-    <t>Delivery Address</t>
-  </si>
-  <si>
-    <t>Corinthian House</t>
-  </si>
-  <si>
-    <t>Perforated Panels</t>
-  </si>
-  <si>
-    <t>CR0 2BX</t>
-  </si>
-  <si>
-    <t>EK Construction Limited / TBL Roofing Limited
-Corinthian House
-17 Lansdowne Road
-Croydon
-CR0 2BX
-Sebastian, +44 (0) 7851 334 852</t>
-  </si>
-  <si>
-    <t>11/02/2026
-8:55</t>
-  </si>
-  <si>
-    <t>Aberdeen Lane</t>
-  </si>
-  <si>
-    <t>N5 2EJ</t>
-  </si>
-  <si>
-    <t>McAleer &amp; Rushe Contracts UK Ltd
-(For FCS Facades)
-Aberdeen Lane
-Islington
-N5 2EJ
-Pawel +44 (0) 7971 679 193</t>
-  </si>
-  <si>
-    <t>Talbot Mill</t>
-  </si>
-  <si>
-    <t>44 Ellesmere Street, Manchester, M15 4JY
-Contact: Callum +44 (0) 7787 155 920
- +44 (0) 1246 588 334</t>
-  </si>
-  <si>
-    <t>SO-2074</t>
-  </si>
-  <si>
-    <t>Damaged Panel</t>
-  </si>
-  <si>
-    <t>SO-2075</t>
-  </si>
-  <si>
-    <t>Termination Bar</t>
-  </si>
-  <si>
-    <t>London Duck</t>
-  </si>
-  <si>
-    <t>SO-2076</t>
-  </si>
-  <si>
-    <t>Sub-Frame New Building</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EW1 2SF</t>
-  </si>
-  <si>
-    <t>St George North london Ltd
-(For FCS Facades)
-London Dock
-St George Construction Site
-Pennington Street, EW1 2SF
-Arek 07534 515 939</t>
-  </si>
-  <si>
-    <t>SO-2077</t>
-  </si>
-  <si>
-    <t>Substation Flashing</t>
-  </si>
-  <si>
-    <t>Selly Oak</t>
-  </si>
-  <si>
-    <t>SO-2078</t>
-  </si>
-  <si>
-    <t>Block A Plenums</t>
-  </si>
-  <si>
-    <t>B29 6SJ</t>
-  </si>
-  <si>
-    <t>McAleer &amp; Rushe Site
-(For FCS Facades)
-1 Chapel Lane
-Selly Oak
-B29 6SJ
-Ruslan +44 (0) 7896 059 740</t>
-  </si>
-  <si>
-    <t>Richmond Mews</t>
-  </si>
-  <si>
-    <t>SO-2079</t>
-  </si>
-  <si>
-    <t>PO00504</t>
-  </si>
-  <si>
-    <t>SE6 3JH</t>
-  </si>
-  <si>
-    <t>1 – 8 Richmond Mews
-Fordmill Road
-London
-SE6 3JH
-Contact – Alfie 07908 701565</t>
-  </si>
-  <si>
-    <t>SO-2080</t>
-  </si>
-  <si>
-    <t>Spandrel Panels</t>
-  </si>
-  <si>
-    <t>SO-2081</t>
-  </si>
-  <si>
-    <t>Brackets &amp; Flashings</t>
-  </si>
-  <si>
-    <t>SO-2082</t>
-  </si>
-  <si>
-    <t>PO41325-740-BYS</t>
-  </si>
-  <si>
-    <t>Yellow Storage Brackets - Revision C04</t>
-  </si>
-  <si>
-    <t>SO-2083</t>
-  </si>
-  <si>
-    <t>PO41325-744-BYS</t>
-  </si>
-  <si>
-    <t>YS - Bracket and Flashing</t>
-  </si>
-  <si>
-    <t>Gun Wharf</t>
-  </si>
-  <si>
-    <t>SO-2084</t>
-  </si>
-  <si>
-    <t>PO00505</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PO1 3TZ</t>
-  </si>
-  <si>
-    <t>Gun Quays,
- Park Road,
- Portsmouth,
- PO1 3TZ
-Alan Davies +44 (0) 7834 198 845</t>
-  </si>
-  <si>
-    <t>SO-2085</t>
-  </si>
-  <si>
-    <t>Plenums for brick</t>
-  </si>
-  <si>
-    <t>SO-2086</t>
-  </si>
-  <si>
-    <t>Blk B Window Brackets</t>
-  </si>
-  <si>
-    <t>SO-2087</t>
-  </si>
-  <si>
-    <t>DT53</t>
-  </si>
-  <si>
-    <t>SO-2089</t>
-  </si>
-  <si>
-    <t>Panels Mill 1</t>
-  </si>
-  <si>
-    <t>SO-2089.1</t>
-  </si>
-  <si>
-    <t>Panels Mill 2</t>
-  </si>
-  <si>
-    <t>SO-2090</t>
-  </si>
-  <si>
-    <t>Last CW Flashings</t>
-  </si>
-  <si>
-    <t>V. Lema Prebook</t>
-  </si>
-  <si>
-    <t>Kennington</t>
-  </si>
-  <si>
-    <t>SO-2092</t>
-  </si>
-  <si>
-    <t>CP595</t>
-  </si>
-  <si>
-    <t>Panels</t>
-  </si>
-  <si>
-    <t>SE11 5SY</t>
-  </si>
-  <si>
-    <t>8A Harleyford Street
-Oval
-London
-SE11 5SY
-Richard +44 (0) 7854 920 942</t>
-  </si>
-  <si>
-    <t>SO-2094</t>
-  </si>
-  <si>
-    <t>External Flashings</t>
-  </si>
-  <si>
-    <t>SO-2095</t>
-  </si>
-  <si>
-    <t>SO-2096</t>
-  </si>
-  <si>
-    <t>DT66</t>
-  </si>
-  <si>
-    <t>Reveals Brackets</t>
-  </si>
-  <si>
-    <t>Bosden Stockport</t>
-  </si>
-  <si>
-    <t>SO-2097</t>
-  </si>
-  <si>
-    <t>Fins</t>
-  </si>
-  <si>
-    <t>SK3 8AB</t>
-  </si>
-  <si>
-    <t>Oak Construction 
-Delivery Gate
-Mulberry Mount Street
-Stockport
-SK3 8AB</t>
-  </si>
-  <si>
-    <t>SO-2097.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canopy </t>
-  </si>
-  <si>
-    <t>Greenwich Millennium Village</t>
-  </si>
-  <si>
-    <t>SO-2098</t>
-  </si>
-  <si>
-    <t>V-Groove Panels</t>
-  </si>
-  <si>
-    <t>SE10 0JT</t>
-  </si>
-  <si>
-    <t>McAleer &amp; Rushe Site
-(For FCS Facades)
-Greenwich Millennium Village
-Plots 401 &amp; 403
-SE10 0JT
-Piotr +44 (0) 7471 273 458</t>
-  </si>
-  <si>
-    <t>London Dock</t>
-  </si>
-  <si>
-    <t>SO-2099</t>
-  </si>
-  <si>
-    <t>BR14 Brackets</t>
-  </si>
-  <si>
-    <t>SO-2100</t>
-  </si>
-  <si>
-    <t>Plenums</t>
-  </si>
-  <si>
-    <t>SO-2101</t>
-  </si>
-  <si>
-    <t>Final Brackets</t>
-  </si>
-  <si>
-    <t>SO-2102</t>
-  </si>
-  <si>
-    <t>Door Brackets</t>
-  </si>
-  <si>
-    <t>Mellis Avenue</t>
-  </si>
-  <si>
-    <t>SO-2103</t>
-  </si>
-  <si>
-    <t>Plenums for Brick</t>
-  </si>
-  <si>
-    <t>SO-2104</t>
-  </si>
-  <si>
-    <t>DT78</t>
-  </si>
-  <si>
-    <t>Brackets Prod. 2</t>
-  </si>
-  <si>
-    <t>SO-2105</t>
-  </si>
-  <si>
-    <t>L2 Subframe</t>
-  </si>
-  <si>
-    <t>SO-2106</t>
-  </si>
-  <si>
-    <t>DT81</t>
-  </si>
-  <si>
-    <t>Brackets Prod. 3</t>
-  </si>
-  <si>
-    <t>SO-2107</t>
-  </si>
-  <si>
-    <t>Plates for Doors</t>
-  </si>
-  <si>
-    <t>SO-2108</t>
-  </si>
-  <si>
-    <t>Dummy Plenums</t>
-  </si>
-  <si>
-    <t>SO-2109</t>
-  </si>
-  <si>
-    <t>P.O.CHC009</t>
-  </si>
-  <si>
-    <t>Extra Panels &amp; Renew Corner</t>
-  </si>
-  <si>
-    <t>SO-2110</t>
-  </si>
-  <si>
-    <t>Coping</t>
-  </si>
-  <si>
-    <t>SO-2111</t>
-  </si>
-  <si>
-    <t>P. Klubowicz Prebook</t>
-  </si>
-  <si>
-    <t>Wensleydale Av</t>
-  </si>
-  <si>
-    <t>SO-2112</t>
-  </si>
-  <si>
-    <t>Flat panels</t>
-  </si>
-  <si>
-    <t>N1 5QJ</t>
-  </si>
-  <si>
-    <t>Flat 9
-28–36 Orsman Road
-London
-N1 5QJ
-Victor +44 (0) 7979 368 584</t>
-  </si>
-  <si>
-    <t>SO-2113</t>
-  </si>
-  <si>
-    <t>Brackets &amp; Shims</t>
-  </si>
-  <si>
-    <t>A.Szyposz &amp; W.Damski Prebook</t>
-  </si>
-  <si>
-    <t>SO-2114</t>
-  </si>
-  <si>
-    <t>SO-2115</t>
-  </si>
-  <si>
-    <t>SO-2116</t>
-  </si>
-  <si>
-    <t>Subframe -Brackets &amp; Top Hats</t>
-  </si>
-  <si>
-    <t>SO-2117</t>
-  </si>
-  <si>
-    <t>Block B HDPE Blocks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BS14 1FZ </t>
-  </si>
-  <si>
-    <t>MPB Facades Ltd
-BoKlok Housing Site Office
-Airport Road 
-Bristol 
-BS14 1FZ 
-What3words/// Maple.bronze.corner
-Martin 07725900420</t>
-  </si>
-  <si>
-    <t>UB8 2XW</t>
-  </si>
-  <si>
-    <t>Sarogirg Ltd
-Wellington House 
-4-10 Cowley Road 
-Uxbridge 
-UB8 2XW
-Contact: Andrian 07438888813</t>
-  </si>
-  <si>
-    <t>SO-2118</t>
-  </si>
-  <si>
-    <t>Block B HDPE Blocks Prod. 2</t>
-  </si>
-  <si>
-    <t>SO-2119</t>
-  </si>
-  <si>
-    <t>DT96</t>
-  </si>
-  <si>
-    <t>T-Rails</t>
-  </si>
-  <si>
-    <t>SO-2120</t>
-  </si>
-  <si>
-    <t>CW Brackets L5-7</t>
-  </si>
-  <si>
-    <t>SO-2121</t>
-  </si>
-  <si>
-    <t>Block C Copings</t>
-  </si>
-  <si>
-    <t>SO-2122</t>
-  </si>
-  <si>
-    <t>Block C Cladding</t>
-  </si>
-  <si>
-    <t>SO-2123</t>
-  </si>
-  <si>
-    <t>SO-2124</t>
-  </si>
-  <si>
-    <t>CA2919</t>
-  </si>
-  <si>
-    <t>Block B Panels</t>
-  </si>
-  <si>
-    <t>Lancelote Pl (Lancaster Road)</t>
-  </si>
-  <si>
-    <t>SO-2125</t>
-  </si>
-  <si>
-    <t>Lancaster Road Panels</t>
-  </si>
-  <si>
-    <t>W11 1QJ</t>
-  </si>
-  <si>
-    <t>39 Lancaster Road
-W11 1QJ
-Noel +44 (0) 7580 181 106</t>
-  </si>
-  <si>
-    <t>SO-2126</t>
-  </si>
-  <si>
-    <t>Block B Flat Wall Panels</t>
-  </si>
-  <si>
-    <t>SO-2127</t>
-  </si>
-  <si>
-    <t>Plenums Prod. 2</t>
-  </si>
-  <si>
-    <t>SO-2128</t>
-  </si>
-  <si>
-    <t>PO00519</t>
-  </si>
-  <si>
-    <t>Upstands</t>
-  </si>
-  <si>
-    <t>1 – 8 Richmond Mews
-Fordmill Road
-London
-SE6 3JH
-Contact – Peter 07309 102159</t>
-  </si>
-  <si>
-    <t>SO-2129</t>
-  </si>
-  <si>
-    <t>Slatted Panel Tubes</t>
-  </si>
-  <si>
-    <t>SO-2130</t>
-  </si>
-  <si>
-    <t>CA2920</t>
-  </si>
-  <si>
-    <t>Block B Panels Prod. 2</t>
-  </si>
-  <si>
-    <t>SO-2131</t>
-  </si>
-  <si>
-    <t>June Site</t>
-  </si>
-  <si>
-    <t>SO-2132</t>
-  </si>
-  <si>
-    <t>Gough Street</t>
-  </si>
-  <si>
-    <t>SO-2133</t>
-  </si>
-  <si>
-    <t>P1 Understructure</t>
-  </si>
-  <si>
-    <t>McAleer &amp; Rushe Site
-(For FCS Facades)
-Gough Street
-Birmingham, B1 1HN
-Ruslan +44 (0) 7896 059 740</t>
-  </si>
-  <si>
-    <t>SO-2134</t>
-  </si>
-  <si>
-    <t>Additional Coping</t>
-  </si>
-  <si>
-    <t>McAleer &amp; Rushe Contracts UK Ltd
-(For FCS Facades)
-Southbank Place, Building 5
-Belvedere Road
-Southbank SE1 7AF
-Tom Plago 07889 215 253</t>
-  </si>
-  <si>
-    <t>SO-2135</t>
-  </si>
-  <si>
-    <t>Blk B Plenums</t>
-  </si>
-  <si>
-    <t>Parts Delivery
-Level 1 Priority</t>
-  </si>
-  <si>
-    <t>SO-2136</t>
-  </si>
-  <si>
-    <t>Blk A CW Brackets</t>
-  </si>
-  <si>
-    <t>SO-2137</t>
-  </si>
-  <si>
-    <t>CA2922</t>
-  </si>
-  <si>
-    <t>Block B Panels Prod. 3</t>
-  </si>
-  <si>
-    <t>SO-2138</t>
-  </si>
-  <si>
-    <t>P2 Understructure</t>
-  </si>
-  <si>
-    <t>SO-2139</t>
-  </si>
-  <si>
-    <t>CW Spandrels &amp; Trays</t>
-  </si>
-  <si>
-    <t>SO-2140</t>
-  </si>
-  <si>
-    <t>G3&amp;G4 L0-3 Brackets</t>
-  </si>
-  <si>
-    <t>SO-2141</t>
-  </si>
-  <si>
-    <t>SO-2142</t>
-  </si>
-  <si>
-    <t>SO-2143</t>
-  </si>
-  <si>
-    <t>DT112</t>
-  </si>
-  <si>
-    <t>SO-2144</t>
-  </si>
-  <si>
-    <t>SO-2145</t>
-  </si>
-  <si>
-    <t>SO-2146</t>
-  </si>
-  <si>
-    <t>SO-2147</t>
-  </si>
-  <si>
-    <t>SO-2148</t>
-  </si>
-  <si>
-    <t>SO-2149</t>
-  </si>
-  <si>
-    <t>SO-2150</t>
-  </si>
-  <si>
-    <t>SO-2152</t>
-  </si>
-  <si>
-    <t>Various</t>
-  </si>
-  <si>
-    <t>SO-2153</t>
-  </si>
-  <si>
-    <t>DT127</t>
-  </si>
-  <si>
-    <t>Block B Panels Prod. 4</t>
-  </si>
-  <si>
-    <t>SO-2154</t>
-  </si>
-  <si>
-    <t>Block B Copings</t>
-  </si>
-  <si>
-    <t>SO-2155</t>
-  </si>
-  <si>
-    <t>Additional Plenums</t>
-  </si>
-  <si>
-    <t>White Lodge</t>
-  </si>
-  <si>
-    <t>SO-2156</t>
-  </si>
-  <si>
-    <t>CM.9662.0539</t>
-  </si>
-  <si>
-    <t>Spigot plates and brackets</t>
-  </si>
-  <si>
-    <t>NR4 6DG</t>
-  </si>
-  <si>
-    <t>Unit 45 
-White Lodge Trading Estate 
-NR4 6DG
-Chris Mann +44 (0) 1603 327 373</t>
-  </si>
-  <si>
-    <t>SO-2157</t>
-  </si>
-  <si>
-    <t>Window Brackets</t>
-  </si>
-  <si>
-    <t>SO-2158</t>
-  </si>
-  <si>
-    <t>Curved Wall Profiles &amp; 009</t>
-  </si>
-  <si>
-    <t>SO-2159</t>
-  </si>
-  <si>
-    <t>Elm Lane Fire Station</t>
-  </si>
-  <si>
-    <t>SO-2160</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> P1115 - 1006</t>
-  </si>
-  <si>
-    <t>Framing</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> O&amp;P Construction Ltd (Sparta Clad)
-Elm Lane Fire Station 
-Sheffield
-S5 7TW
-Gavin Bailey 07719711503</t>
-  </si>
-  <si>
-    <t>SO-2161</t>
-  </si>
-  <si>
-    <t>Wellington House</t>
-  </si>
-  <si>
-    <t>SO-2162</t>
-  </si>
-  <si>
-    <t>Claddings</t>
-  </si>
-  <si>
-    <t>SO-2163</t>
-  </si>
-  <si>
-    <t>Block C Additions Copings</t>
-  </si>
-  <si>
-    <t>SO-2164</t>
-  </si>
-  <si>
-    <t>Daniele Squarci &amp; Luisella Quirito</t>
-  </si>
-  <si>
-    <t>Bifold Door Factory Ltd.
-, Bingley The Common
-, West Drayton, 
-UB7 7HQ
-Contact: Contact: Harj +44 (0) 7951 893 719</t>
-  </si>
-  <si>
-    <t>SO-2165</t>
-  </si>
-  <si>
-    <t>Projection Window</t>
+    <t>St George Plc
+,Camden Goods Yard,
+Chalk Farm Road, Chalk Farm
+,Camden Town,London, NW1 8EH
+Contact: Arek +44 (0) 7534 515 939</t>
+  </si>
+  <si>
+    <t>CGY</t>
+  </si>
+  <si>
+    <t>Kennington Park</t>
   </si>
   <si>
     <t>8A Harleyford Street
@@ -1977,84 +1267,137 @@
 Cristi +44 (0)7743 949 805</t>
   </si>
   <si>
-    <t>Kings Road Park</t>
-  </si>
-  <si>
-    <t>SO-2166</t>
-  </si>
-  <si>
-    <t>SO-2167</t>
-  </si>
-  <si>
-    <t>Spandrels Block A CW</t>
-  </si>
-  <si>
-    <t>SO-2168</t>
-  </si>
-  <si>
-    <t>SO-2169</t>
-  </si>
-  <si>
-    <t>SO-2170</t>
-  </si>
-  <si>
-    <t>SO-2171</t>
-  </si>
-  <si>
-    <t>Additional Top Hats L5&amp;L6</t>
-  </si>
-  <si>
-    <t>Colonnade Soffit Panels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Windows Plenums </t>
-  </si>
-  <si>
-    <t>DT155</t>
-  </si>
-  <si>
-    <t>SO-2172</t>
-  </si>
-  <si>
-    <t>HM0321</t>
-  </si>
-  <si>
-    <t>PO58325-927-KRP</t>
-  </si>
-  <si>
-    <t>09/06/2026
-11:09</t>
-  </si>
-  <si>
-    <t>76d11:Sparta Clad0</t>
-  </si>
-  <si>
-    <t>097
-11:01</t>
-  </si>
-  <si>
-    <t>8C-11:i2</t>
-  </si>
-  <si>
-    <t>091
-11:03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   1Ce11:04</t>
-  </si>
-  <si>
-    <t>1
-11:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Pu11:06</t>
+    <t>SO-2237</t>
+  </si>
+  <si>
+    <t>Internal Cills</t>
+  </si>
+  <si>
+    <t>S5 7TW</t>
+  </si>
+  <si>
+    <t>TW9 4BZ</t>
+  </si>
+  <si>
+    <t>N5 2EJ</t>
+  </si>
+  <si>
+    <t>EW1 2SF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST5 2AW </t>
+  </si>
+  <si>
+    <t>SO-2238</t>
+  </si>
+  <si>
+    <t>SO-2239</t>
+  </si>
+  <si>
+    <t>SO-2240</t>
+  </si>
+  <si>
+    <t>SO-2241</t>
+  </si>
+  <si>
+    <t>SO-2242</t>
+  </si>
+  <si>
+    <t>SO-2243</t>
+  </si>
+  <si>
+    <t>SO-2244</t>
+  </si>
+  <si>
+    <t>SO-2245</t>
+  </si>
+  <si>
+    <t>SO-2247</t>
+  </si>
+  <si>
+    <t>SO-2248</t>
+  </si>
+  <si>
+    <t>SO-2249</t>
+  </si>
+  <si>
+    <t>SO-2251</t>
+  </si>
+  <si>
+    <t>SO-2253</t>
+  </si>
+  <si>
+    <t>SO-2255</t>
+  </si>
+  <si>
+    <t>SO-2256</t>
+  </si>
+  <si>
+    <t>SO-2257</t>
+  </si>
+  <si>
+    <t>SO-2258</t>
+  </si>
+  <si>
+    <t>Premier Inn Burgess Hill</t>
+  </si>
+  <si>
+    <t>Premier Inn - Burgess Hill
+West Sussex
+RH15 9AL
+Contact: Chris Mann +44 (0) 1603 327 373</t>
+  </si>
+  <si>
+    <t>East Ferry</t>
+  </si>
+  <si>
+    <t>12 East Ferry Road
+London
+E14 3LA
+Sohan +44 (0) 7874 878 675</t>
+  </si>
+  <si>
+    <t>https://what3words.com/cost.froze.shout</t>
+  </si>
+  <si>
+    <t>SO-2259</t>
+  </si>
+  <si>
+    <t>SO-2260</t>
+  </si>
+  <si>
+    <t>SO-2261</t>
+  </si>
+  <si>
+    <t>Broadway Central 2</t>
+  </si>
+  <si>
+    <t>SO2139</t>
+  </si>
+  <si>
+    <t>McAleer &amp; Rushe Contracts UK Ltd
+(For FCS Facades)
+Broadway Central PBSA
+200 Renfield Street
+Glasgow, G2 3BW
+Jakub +44 (0) 7772 728 234</t>
+  </si>
+  <si>
+    <t>SO-2265</t>
+  </si>
+  <si>
+    <t>Add to production</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-[$€-2]* #,##0.00_-;\-[$€-2]* #,##0.00_-;_-[$€-2]* &quot;-&quot;??_-"/>
+  </numFmts>
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2114,13 +1457,86 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C5700"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color indexed="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4" tint="-0.24994659260841701"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0DFF35"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2141,11 +1557,28 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59996337778862885"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59996337778862885"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -2199,10 +1632,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2297,15 +1763,28 @@
     <xf numFmtId="9" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" xfId="14" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Neutral" xfId="1" builtinId="28"/>
+  <cellStyles count="15">
+    <cellStyle name="Accent5 2" xfId="7" xr:uid="{E1A192BE-A70B-4CDE-B0C5-DBCC20E6465E}"/>
+    <cellStyle name="Akcent 5 2" xfId="10" xr:uid="{8F338B18-D819-46D2-A970-BA19C72B603F}"/>
+    <cellStyle name="Currency 2" xfId="4" xr:uid="{A659B78F-9AEA-4A41-A162-162C92F19117}"/>
+    <cellStyle name="Dobry 2" xfId="9" xr:uid="{4A1EFC97-54DC-47CA-B9FE-A2079D9E2AF8}"/>
+    <cellStyle name="Euro" xfId="1" xr:uid="{23BB7D0C-8687-47B3-B7BD-A89FE747966C}"/>
+    <cellStyle name="Galwanizacja" xfId="13" xr:uid="{330B12C1-0E97-4A24-8938-5E6BBB5B5D43}"/>
+    <cellStyle name="Good 2" xfId="6" xr:uid="{D08679CB-2C69-4BA0-BBE9-1FCABDF097BB}"/>
+    <cellStyle name="Hyperlink" xfId="14" builtinId="8"/>
+    <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{F51D2A67-306F-4297-AEE4-0F2BBE4AB55A}"/>
+    <cellStyle name="Lustro" xfId="12" xr:uid="{6F126DC3-F1C2-485E-BEDC-0CDBE8189302}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{EC29638F-E412-49F6-9267-C7D407625E73}"/>
+    <cellStyle name="Normal 3" xfId="5" xr:uid="{CE3B0A17-4803-48AD-BC26-379EFACACBB6}"/>
+    <cellStyle name="Normalny 2" xfId="8" xr:uid="{522C6CCC-2E85-47DF-9B48-C321C4FA81EB}"/>
+    <cellStyle name="Spawanie" xfId="11" xr:uid="{99AA20AB-74CF-442A-A961-6D0FDC7F049C}"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="23">
     <dxf>
       <font>
         <b/>
@@ -2564,8 +2043,73 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="mediumGray">
+          <fgColor theme="4"/>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="3" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Slicer Style 1" pivot="0" table="0" count="1" xr9:uid="{697A4B7A-E931-4F79-A46F-0646FCB4C2EE}">
+      <tableStyleElement type="wholeTable" dxfId="22"/>
+    </tableStyle>
+    <tableStyle name="Slicer Style 2" pivot="0" table="0" count="1" xr9:uid="{A8598257-55EA-43F2-A562-A1752488766E}">
+      <tableStyleElement type="wholeTable" dxfId="21"/>
+    </tableStyle>
+    <tableStyle name="SlicerStyleDark1 2" pivot="0" table="0" count="2" xr9:uid="{04587E0B-C3DA-4B36-9B29-95EE1643D9BF}">
+      <tableStyleElement type="wholeTable" dxfId="20"/>
+      <tableStyleElement type="headerRow" dxfId="19"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2578,8 +2122,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}" name="Table1" displayName="Table1" ref="A1:Q100" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:Q100" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}" name="Table1" displayName="Table1" ref="A1:Q42" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+  <autoFilter ref="A1:Q42" xr:uid="{D238CE20-76DC-4853-9E42-BB88690E3CED}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{867090DC-1FE0-4EF0-A0C0-448920317853}" name="Project" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{ED71812C-E204-4FE0-ADEA-0CD9B3ADA2A3}" name="Project SO" dataDxfId="15"/>
@@ -2871,7 +2415,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:Q100"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -2901,13 +2445,13 @@
         <v>35</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="D1" s="12" t="s">
         <v>33</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>31</v>
@@ -2916,7 +2460,7 @@
         <v>30</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>28</v>
@@ -2940,31 +2484,31 @@
         <v>187</v>
       </c>
       <c r="P1" s="12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q1" s="12" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>51</v>
+        <v>284</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="C2" s="15">
-        <v>2940</v>
+        <v>3382</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="E2" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12" t="s">
-        <v>53</v>
+        <v>280</v>
       </c>
       <c r="H2" s="24" t="s">
         <v>281</v>
@@ -2972,7 +2516,7 @@
       <c r="I2" s="14"/>
       <c r="J2" s="14"/>
       <c r="K2" s="37">
-        <f t="shared" ref="K2:K25" si="0">AVERAGE(L2:N2)</f>
+        <f t="shared" ref="K2" si="0">AVERAGE(L2:N2)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L2" s="37">
@@ -2985,44 +2529,44 @@
         <v>0</v>
       </c>
       <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-    </row>
-    <row r="3" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q2" s="34" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="C3" s="15">
-        <v>5321</v>
+        <v>3674</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="E3" s="36" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="12"/>
-      <c r="G3" s="12" t="s">
-        <v>127</v>
-      </c>
+      <c r="G3" s="12"/>
       <c r="H3" s="24" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="I3" s="14"/>
       <c r="J3" s="14"/>
-      <c r="K3" s="37">
-        <f t="shared" si="0"/>
+      <c r="K3" s="32">
+        <f t="shared" ref="K3" si="1">AVERAGE(L3:N3)</f>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="L3" s="37">
+      <c r="L3" s="32">
         <v>0.01</v>
       </c>
-      <c r="M3" s="37">
-        <v>0</v>
-      </c>
-      <c r="N3" s="37">
+      <c r="M3" s="32">
+        <v>0</v>
+      </c>
+      <c r="N3" s="32">
         <v>0</v>
       </c>
       <c r="P3" s="16"/>
@@ -3030,31 +2574,23 @@
     </row>
     <row r="4" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>307</v>
+        <v>278</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="C4" s="15">
-        <v>2946</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
       <c r="F4" s="12"/>
-      <c r="G4" s="12" t="s">
-        <v>310</v>
-      </c>
+      <c r="G4" s="12"/>
       <c r="H4" s="24" t="s">
-        <v>311</v>
+        <v>279</v>
       </c>
       <c r="I4" s="14"/>
       <c r="J4" s="14"/>
       <c r="K4" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="K4" si="2">AVERAGE(L4:N4)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L4" s="37">
@@ -3071,31 +2607,23 @@
     </row>
     <row r="5" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>91</v>
+        <v>260</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="C5" s="15">
-        <v>2963</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="E5" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="36"/>
       <c r="F5" s="12"/>
-      <c r="G5" s="12" t="s">
-        <v>157</v>
-      </c>
+      <c r="G5" s="12"/>
       <c r="H5" s="24" t="s">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="14"/>
       <c r="K5" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="K5:K18" si="3">AVERAGE(L5:N5)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L5" s="37">
@@ -3108,37 +2636,27 @@
         <v>0</v>
       </c>
       <c r="P5" s="16"/>
-      <c r="Q5" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="Q5" s="16"/>
     </row>
     <row r="6" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>314</v>
+        <v>278</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="C6" s="15">
-        <v>2978</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="E6" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
       <c r="F6" s="12"/>
-      <c r="G6" s="12" t="s">
-        <v>317</v>
-      </c>
+      <c r="G6" s="12"/>
       <c r="H6" s="24" t="s">
-        <v>318</v>
+        <v>279</v>
       </c>
       <c r="I6" s="14"/>
       <c r="J6" s="14"/>
       <c r="K6" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L6" s="37">
@@ -3150,41 +2668,28 @@
       <c r="N6" s="37">
         <v>0</v>
       </c>
-      <c r="O6" s="12" t="s">
-        <v>188</v>
-      </c>
       <c r="P6" s="16"/>
-      <c r="Q6" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="Q6" s="16"/>
     </row>
     <row r="7" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="24" t="s">
         <v>319</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>321</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="H7" s="24" t="s">
-        <v>323</v>
       </c>
       <c r="I7" s="14"/>
       <c r="J7" s="14"/>
       <c r="K7" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L7" s="37">
@@ -3197,37 +2702,27 @@
         <v>0</v>
       </c>
       <c r="P7" s="16"/>
-      <c r="Q7" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q7" s="16"/>
+    </row>
+    <row r="8" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>51</v>
+        <v>285</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>324</v>
-      </c>
-      <c r="C8" s="15">
-        <v>2976</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>325</v>
-      </c>
-      <c r="E8" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
       <c r="F8" s="12"/>
-      <c r="G8" s="12" t="s">
-        <v>53</v>
-      </c>
+      <c r="G8" s="12"/>
       <c r="H8" s="24" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L8" s="37">
@@ -3240,37 +2735,27 @@
         <v>0</v>
       </c>
       <c r="P8" s="16"/>
-      <c r="Q8" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="Q8" s="16"/>
     </row>
     <row r="9" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>91</v>
+        <v>285</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="C9" s="15">
-        <v>2986</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="E9" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
       <c r="F9" s="12"/>
-      <c r="G9" s="12" t="s">
-        <v>157</v>
-      </c>
+      <c r="G9" s="12"/>
       <c r="H9" s="24" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="I9" s="14"/>
       <c r="J9" s="14"/>
       <c r="K9" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L9" s="37">
@@ -3282,41 +2767,28 @@
       <c r="N9" s="37">
         <v>0</v>
       </c>
-      <c r="O9" s="12" t="s">
-        <v>188</v>
-      </c>
       <c r="P9" s="16"/>
-      <c r="Q9" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="Q9" s="16"/>
     </row>
     <row r="10" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>329</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="E10" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
       <c r="F10" s="12"/>
-      <c r="G10" s="12" t="s">
-        <v>277</v>
-      </c>
+      <c r="G10" s="12"/>
       <c r="H10" s="24" t="s">
-        <v>276</v>
+        <v>315</v>
       </c>
       <c r="I10" s="14"/>
       <c r="J10" s="14"/>
       <c r="K10" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L10" s="37">
@@ -3328,41 +2800,28 @@
       <c r="N10" s="37">
         <v>0</v>
       </c>
-      <c r="O10" s="12" t="s">
-        <v>188</v>
-      </c>
       <c r="P10" s="16"/>
-      <c r="Q10" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q10" s="16"/>
+    </row>
+    <row r="11" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>275</v>
+        <v>317</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>332</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
       <c r="F11" s="12"/>
-      <c r="G11" s="12" t="s">
-        <v>277</v>
-      </c>
+      <c r="G11" s="12"/>
       <c r="H11" s="24" t="s">
-        <v>276</v>
+        <v>316</v>
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
       <c r="K11" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L11" s="37">
@@ -3375,37 +2834,27 @@
         <v>0</v>
       </c>
       <c r="P11" s="16"/>
-      <c r="Q11" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q11" s="16"/>
+    </row>
+    <row r="12" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>334</v>
+        <v>260</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>336</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="E12" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
       <c r="F12" s="12"/>
-      <c r="G12" s="12" t="s">
-        <v>337</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>338</v>
+      <c r="G12" s="12"/>
+      <c r="H12" s="24" t="s">
+        <v>315</v>
       </c>
       <c r="I12" s="14"/>
       <c r="J12" s="14"/>
       <c r="K12" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L12" s="37">
@@ -3418,37 +2867,27 @@
         <v>0</v>
       </c>
       <c r="P12" s="16"/>
-      <c r="Q12" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="Q12" s="16"/>
     </row>
     <row r="13" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>282</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="C13" s="15">
-        <v>3023</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="E13" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
       <c r="F13" s="12"/>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="12"/>
+      <c r="H13" s="24" t="s">
         <v>283</v>
-      </c>
-      <c r="H13" s="24" t="s">
-        <v>284</v>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
       <c r="K13" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L13" s="37">
@@ -3460,41 +2899,30 @@
       <c r="N13" s="37">
         <v>0</v>
       </c>
-      <c r="O13" s="12" t="s">
-        <v>188</v>
-      </c>
       <c r="P13" s="16"/>
-      <c r="Q13" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q13" s="16"/>
+    </row>
+    <row r="14" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>314</v>
+        <v>288</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="C14" s="15">
-        <v>3030</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="E14" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
       <c r="F14" s="12"/>
       <c r="G14" s="12" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>318</v>
+        <v>289</v>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14"/>
       <c r="K14" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L14" s="37">
@@ -3507,37 +2935,29 @@
         <v>0</v>
       </c>
       <c r="P14" s="16"/>
-      <c r="Q14" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="Q14" s="16"/>
     </row>
     <row r="15" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>344</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="E15" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
       <c r="F15" s="12"/>
       <c r="G15" s="12" t="s">
-        <v>286</v>
+        <v>323</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14"/>
       <c r="K15" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L15" s="37">
@@ -3550,37 +2970,33 @@
         <v>0</v>
       </c>
       <c r="P15" s="16"/>
-      <c r="Q15" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q15" s="16"/>
+    </row>
+    <row r="16" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>345</v>
+        <v>306</v>
       </c>
       <c r="C16" s="15">
-        <v>5333</v>
+        <v>4070</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="E16" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="E16" s="12"/>
       <c r="F16" s="12"/>
       <c r="G16" s="12" t="s">
-        <v>127</v>
+        <v>324</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14"/>
       <c r="K16" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L16" s="37">
@@ -3593,37 +3009,33 @@
         <v>0</v>
       </c>
       <c r="P16" s="16"/>
-      <c r="Q16" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q16" s="16"/>
+    </row>
+    <row r="17" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>347</v>
+        <v>307</v>
       </c>
       <c r="C17" s="15">
-        <v>5333</v>
+        <v>4072</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>348</v>
-      </c>
-      <c r="E17" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="E17" s="12"/>
       <c r="F17" s="12"/>
       <c r="G17" s="12" t="s">
-        <v>127</v>
+        <v>325</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14"/>
       <c r="K17" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L17" s="37">
@@ -3636,37 +3048,33 @@
         <v>0</v>
       </c>
       <c r="P17" s="16"/>
-      <c r="Q17" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q17" s="16"/>
+    </row>
+    <row r="18" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>349</v>
+        <v>308</v>
       </c>
       <c r="C18" s="15">
-        <v>3044</v>
+        <v>12606</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="E18" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="E18" s="12"/>
       <c r="F18" s="12"/>
       <c r="G18" s="12" t="s">
-        <v>155</v>
+        <v>326</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14"/>
       <c r="K18" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L18" s="37">
@@ -3678,40 +3086,34 @@
       <c r="N18" s="37">
         <v>0</v>
       </c>
-      <c r="P18" s="16" t="s">
-        <v>351</v>
-      </c>
-      <c r="Q18" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+    </row>
+    <row r="19" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>352</v>
+        <v>285</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>354</v>
+        <v>310</v>
+      </c>
+      <c r="C19" s="15">
+        <v>4124</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="E19" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="E19" s="36"/>
       <c r="F19" s="12"/>
       <c r="G19" s="12" t="s">
-        <v>356</v>
+        <v>323</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>357</v>
+        <v>272</v>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14"/>
       <c r="K19" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="K19" si="4">AVERAGE(L19:N19)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L19" s="37">
@@ -3724,29 +3126,25 @@
         <v>0</v>
       </c>
       <c r="P19" s="16"/>
-      <c r="Q19" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q19" s="16"/>
+    </row>
+    <row r="20" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="C20" s="15">
-        <v>3090</v>
+        <v>4131</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="E20" s="36"/>
       <c r="F20" s="12"/>
       <c r="G20" s="12" t="s">
-        <v>155</v>
+        <v>324</v>
       </c>
       <c r="H20" s="24" t="s">
         <v>279</v>
@@ -3754,7 +3152,7 @@
       <c r="I20" s="14"/>
       <c r="J20" s="14"/>
       <c r="K20" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="K20" si="5">AVERAGE(L20:N20)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L20" s="37">
@@ -3766,41 +3164,30 @@
       <c r="N20" s="37">
         <v>0</v>
       </c>
-      <c r="O20" s="12" t="s">
-        <v>188</v>
-      </c>
       <c r="P20" s="16"/>
-      <c r="Q20" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q20" s="16"/>
+    </row>
+    <row r="21" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>360</v>
+        <v>327</v>
       </c>
       <c r="C21" s="15">
-        <v>3096</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>4097</v>
+      </c>
+      <c r="D21" s="12"/>
+      <c r="E21" s="36"/>
       <c r="F21" s="12"/>
-      <c r="G21" s="12" t="s">
-        <v>155</v>
-      </c>
+      <c r="G21" s="12"/>
       <c r="H21" s="24" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14"/>
       <c r="K21" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="K21:K24" si="6">AVERAGE(L21:N21)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L21" s="37">
@@ -3813,37 +3200,29 @@
         <v>0</v>
       </c>
       <c r="P21" s="16"/>
-      <c r="Q21" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="Q21" s="16"/>
     </row>
     <row r="22" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>362</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="E22" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="C22" s="15">
+        <v>12637</v>
+      </c>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
       <c r="F22" s="12"/>
-      <c r="G22" s="12" t="s">
-        <v>286</v>
-      </c>
+      <c r="G22" s="12"/>
       <c r="H22" s="24" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14"/>
       <c r="K22" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L22" s="37">
@@ -3856,37 +3235,29 @@
         <v>0</v>
       </c>
       <c r="P22" s="16"/>
-      <c r="Q22" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q22" s="16"/>
+    </row>
+    <row r="23" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>364</v>
+        <v>285</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>365</v>
+        <v>329</v>
       </c>
       <c r="C23" s="15">
-        <v>10001</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="E23" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>4148</v>
+      </c>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
       <c r="F23" s="12"/>
-      <c r="G23" s="12" t="s">
-        <v>367</v>
-      </c>
+      <c r="G23" s="12"/>
       <c r="H23" s="24" t="s">
-        <v>368</v>
+        <v>272</v>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14"/>
       <c r="K23" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L23" s="37">
@@ -3899,37 +3270,29 @@
         <v>0</v>
       </c>
       <c r="P23" s="16"/>
-      <c r="Q23" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q23" s="16"/>
+    </row>
+    <row r="24" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>364</v>
+        <v>282</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
       <c r="C24" s="15">
-        <v>10001</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="E24" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>4156</v>
+      </c>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
       <c r="F24" s="12"/>
-      <c r="G24" s="12" t="s">
-        <v>367</v>
-      </c>
+      <c r="G24" s="12"/>
       <c r="H24" s="24" t="s">
-        <v>368</v>
+        <v>283</v>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
       <c r="K24" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L24" s="37">
@@ -3942,37 +3305,29 @@
         <v>0</v>
       </c>
       <c r="P24" s="16"/>
-      <c r="Q24" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="Q24" s="16"/>
     </row>
     <row r="25" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>371</v>
+        <v>284</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>372</v>
+        <v>331</v>
       </c>
       <c r="C25" s="15">
-        <v>3107</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="E25" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>3382</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="36"/>
       <c r="F25" s="12"/>
-      <c r="G25" s="12" t="s">
-        <v>374</v>
-      </c>
+      <c r="G25" s="12"/>
       <c r="H25" s="24" t="s">
-        <v>375</v>
+        <v>281</v>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14"/>
       <c r="K25" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="K25:K29" si="7">AVERAGE(L25:N25)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L25" s="37">
@@ -3985,37 +3340,29 @@
         <v>0</v>
       </c>
       <c r="P25" s="16"/>
-      <c r="Q25" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="Q25" s="16"/>
     </row>
     <row r="26" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>376</v>
+        <v>284</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>377</v>
+        <v>332</v>
       </c>
       <c r="C26" s="15">
-        <v>3110</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="E26" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>3382</v>
+      </c>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
       <c r="F26" s="12"/>
-      <c r="G26" s="12" t="s">
-        <v>310</v>
-      </c>
+      <c r="G26" s="12"/>
       <c r="H26" s="24" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14"/>
       <c r="K26" s="37">
-        <f t="shared" ref="K26:K88" si="1">AVERAGE(L26:N26)</f>
+        <f t="shared" si="7"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L26" s="37">
@@ -4028,37 +3375,29 @@
         <v>0</v>
       </c>
       <c r="P26" s="16"/>
-      <c r="Q26" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="Q26" s="16"/>
     </row>
     <row r="27" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>376</v>
+        <v>284</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>379</v>
+        <v>333</v>
       </c>
       <c r="C27" s="15">
-        <v>3111</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="E27" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>3382</v>
+      </c>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
       <c r="F27" s="12"/>
-      <c r="G27" s="12" t="s">
-        <v>310</v>
-      </c>
+      <c r="G27" s="12"/>
       <c r="H27" s="24" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14"/>
       <c r="K27" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L27" s="37">
@@ -4070,41 +3409,30 @@
       <c r="N27" s="37">
         <v>0</v>
       </c>
-      <c r="O27" s="12" t="s">
-        <v>188</v>
-      </c>
       <c r="P27" s="16"/>
-      <c r="Q27" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="Q27" s="16"/>
     </row>
     <row r="28" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="C28" s="15">
-        <v>3128</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>382</v>
-      </c>
-      <c r="E28" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>3382</v>
+      </c>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
       <c r="F28" s="12"/>
-      <c r="G28" s="12" t="s">
-        <v>269</v>
-      </c>
+      <c r="G28" s="12"/>
       <c r="H28" s="24" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14"/>
       <c r="K28" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L28" s="37">
@@ -4116,41 +3444,30 @@
       <c r="N28" s="37">
         <v>0</v>
       </c>
-      <c r="O28" s="12" t="s">
-        <v>188</v>
-      </c>
       <c r="P28" s="16"/>
-      <c r="Q28" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="Q28" s="16"/>
     </row>
     <row r="29" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>376</v>
+        <v>285</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>383</v>
+        <v>335</v>
       </c>
       <c r="C29" s="15">
-        <v>3153</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="E29" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>4160</v>
+      </c>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
       <c r="F29" s="12"/>
-      <c r="G29" s="12" t="s">
-        <v>310</v>
-      </c>
+      <c r="G29" s="12"/>
       <c r="H29" s="24" t="s">
-        <v>311</v>
+        <v>272</v>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14"/>
       <c r="K29" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L29" s="37">
@@ -4163,37 +3480,29 @@
         <v>0</v>
       </c>
       <c r="P29" s="16"/>
-      <c r="Q29" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="Q29" s="16"/>
     </row>
     <row r="30" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>385</v>
+        <v>278</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>386</v>
+        <v>336</v>
       </c>
       <c r="C30" s="15">
-        <v>3160</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="E30" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>4166</v>
+      </c>
+      <c r="D30" s="12"/>
+      <c r="E30" s="36"/>
       <c r="F30" s="12"/>
-      <c r="G30" s="12" t="s">
-        <v>283</v>
-      </c>
+      <c r="G30" s="12"/>
       <c r="H30" s="24" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14"/>
       <c r="K30" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K30:K31" si="8">AVERAGE(L30:N30)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L30" s="37">
@@ -4206,37 +3515,29 @@
         <v>0</v>
       </c>
       <c r="P30" s="16"/>
-      <c r="Q30" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="Q30" s="16"/>
     </row>
     <row r="31" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>388</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>389</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>390</v>
-      </c>
-      <c r="E31" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="C31" s="15">
+        <v>4168</v>
+      </c>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
       <c r="F31" s="12"/>
-      <c r="G31" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="H31" s="25" t="s">
-        <v>285</v>
+      <c r="G31" s="12"/>
+      <c r="H31" s="24" t="s">
+        <v>272</v>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14"/>
       <c r="K31" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L31" s="37">
@@ -4249,37 +3550,27 @@
         <v>0</v>
       </c>
       <c r="P31" s="16"/>
-      <c r="Q31" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="Q31" s="16"/>
     </row>
     <row r="32" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="C32" s="15">
-        <v>3179</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="E32" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="C32" s="15"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
       <c r="F32" s="12"/>
-      <c r="G32" s="12" t="s">
-        <v>269</v>
-      </c>
+      <c r="G32" s="12"/>
       <c r="H32" s="24" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14"/>
       <c r="K32" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K32:K33" si="9">AVERAGE(L32:N32)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L32" s="37">
@@ -4292,37 +3583,27 @@
         <v>0</v>
       </c>
       <c r="P32" s="16"/>
-      <c r="Q32" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="Q32" s="16"/>
     </row>
     <row r="33" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="E33" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="C33" s="15"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
       <c r="F33" s="12"/>
-      <c r="G33" s="12" t="s">
-        <v>286</v>
-      </c>
+      <c r="G33" s="12"/>
       <c r="H33" s="24" t="s">
-        <v>285</v>
+        <v>315</v>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14"/>
       <c r="K33" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L33" s="37">
@@ -4335,37 +3616,27 @@
         <v>0</v>
       </c>
       <c r="P33" s="16"/>
-      <c r="Q33" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q33" s="16"/>
+    </row>
+    <row r="34" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="C34" s="15">
-        <v>3190</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>397</v>
-      </c>
-      <c r="E34" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="C34" s="15"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
       <c r="F34" s="12"/>
-      <c r="G34" s="12" t="s">
-        <v>310</v>
-      </c>
+      <c r="G34" s="12"/>
       <c r="H34" s="24" t="s">
-        <v>311</v>
+        <v>345</v>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14"/>
       <c r="K34" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K34:K37" si="10">AVERAGE(L34:N34)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L34" s="37">
@@ -4378,37 +3649,27 @@
         <v>0</v>
       </c>
       <c r="P34" s="16"/>
-      <c r="Q34" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q34" s="16"/>
+    </row>
+    <row r="35" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>385</v>
+        <v>346</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>398</v>
-      </c>
-      <c r="C35" s="15">
-        <v>3197</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>399</v>
-      </c>
-      <c r="E35" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="C35" s="15"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
       <c r="F35" s="12"/>
-      <c r="G35" s="12" t="s">
-        <v>283</v>
-      </c>
+      <c r="G35" s="12"/>
       <c r="H35" s="24" t="s">
-        <v>284</v>
+        <v>347</v>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14"/>
       <c r="K35" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L35" s="37">
@@ -4420,38 +3681,30 @@
       <c r="N35" s="37">
         <v>0</v>
       </c>
-      <c r="P35" s="16"/>
-      <c r="Q35" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+      <c r="P35" s="38" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q35" s="16"/>
+    </row>
+    <row r="36" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>293</v>
+        <v>260</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>402</v>
-      </c>
-      <c r="E36" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="C36" s="15"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
       <c r="F36" s="12"/>
-      <c r="G36" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="H36" s="25" t="s">
-        <v>296</v>
+      <c r="G36" s="12"/>
+      <c r="H36" s="24" t="s">
+        <v>315</v>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14"/>
       <c r="K36" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L36" s="37">
@@ -4464,37 +3717,27 @@
         <v>0</v>
       </c>
       <c r="P36" s="16"/>
-      <c r="Q36" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q36" s="16"/>
+    </row>
+    <row r="37" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>51</v>
+        <v>282</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>403</v>
-      </c>
-      <c r="C37" s="15">
-        <v>3213</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>404</v>
-      </c>
-      <c r="E37" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="C37" s="15"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
       <c r="F37" s="12"/>
-      <c r="G37" s="12" t="s">
-        <v>53</v>
-      </c>
+      <c r="G37" s="12"/>
       <c r="H37" s="24" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14"/>
       <c r="K37" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L37" s="37">
@@ -4507,37 +3750,27 @@
         <v>0</v>
       </c>
       <c r="P37" s="16"/>
-      <c r="Q37" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="Q37" s="16"/>
     </row>
     <row r="38" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>91</v>
+        <v>260</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>405</v>
-      </c>
-      <c r="C38" s="15">
-        <v>3220</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="E38" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="C38" s="15"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
       <c r="F38" s="12"/>
-      <c r="G38" s="12" t="s">
-        <v>157</v>
-      </c>
+      <c r="G38" s="12"/>
       <c r="H38" s="24" t="s">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14"/>
       <c r="K38" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K38" si="11">AVERAGE(L38:N38)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L38" s="37">
@@ -4549,38 +3782,28 @@
       <c r="N38" s="37">
         <v>0</v>
       </c>
-      <c r="P38" s="16" t="s">
-        <v>406</v>
-      </c>
-      <c r="Q38" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="P38" s="16"/>
+      <c r="Q38" s="16"/>
+    </row>
+    <row r="39" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>407</v>
+        <v>292</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>408</v>
+        <v>350</v>
       </c>
       <c r="C39" s="15"/>
-      <c r="D39" s="12" t="s">
-        <v>409</v>
-      </c>
-      <c r="E39" s="36" t="s">
-        <v>3</v>
-      </c>
+      <c r="D39" s="12"/>
+      <c r="E39" s="36"/>
       <c r="F39" s="12"/>
-      <c r="G39" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="H39" s="38" t="s">
-        <v>411</v>
+      <c r="G39" s="12"/>
+      <c r="H39" s="24" t="s">
+        <v>293</v>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14"/>
       <c r="K39" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K39:K40" si="12">AVERAGE(L39:N39)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L39" s="37">
@@ -4593,37 +3816,29 @@
         <v>0</v>
       </c>
       <c r="P39" s="16"/>
-      <c r="Q39" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="Q39" s="16"/>
     </row>
     <row r="40" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>412</v>
+        <v>351</v>
       </c>
       <c r="C40" s="15">
-        <v>3226</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="E40" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>4315</v>
+      </c>
+      <c r="D40" s="12"/>
+      <c r="E40" s="36"/>
       <c r="F40" s="12"/>
-      <c r="G40" s="12" t="s">
-        <v>310</v>
-      </c>
+      <c r="G40" s="12"/>
       <c r="H40" s="24" t="s">
-        <v>311</v>
+        <v>354</v>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14"/>
       <c r="K40" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L40" s="37">
@@ -4635,40 +3850,32 @@
       <c r="N40" s="37">
         <v>0</v>
       </c>
-      <c r="P40" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="Q40" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="P40" s="16"/>
+      <c r="Q40" s="16"/>
+    </row>
+    <row r="41" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>255</v>
+        <v>284</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>415</v>
+        <v>353</v>
       </c>
       <c r="C41" s="15">
-        <v>3231</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="E41" s="36" t="s">
-        <v>3</v>
-      </c>
+        <v>4310</v>
+      </c>
+      <c r="D41" s="12"/>
+      <c r="E41" s="36"/>
       <c r="F41" s="12"/>
-      <c r="G41" s="12" t="s">
-        <v>155</v>
-      </c>
+      <c r="G41" s="12"/>
       <c r="H41" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="I41" s="14"/>
+        <v>281</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>309</v>
+      </c>
       <c r="J41" s="14"/>
       <c r="K41" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K41:K42" si="13">AVERAGE(L41:N41)</f>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L41" s="37">
@@ -4680,40 +3887,38 @@
       <c r="N41" s="37">
         <v>0</v>
       </c>
-      <c r="P41" s="16" t="s">
-        <v>351</v>
-      </c>
-      <c r="Q41" s="34" t="s">
-        <v>297</v>
-      </c>
+      <c r="P41" s="16"/>
+      <c r="Q41" s="16"/>
     </row>
     <row r="42" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>91</v>
+        <v>292</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>416</v>
+        <v>355</v>
       </c>
       <c r="C42" s="15">
-        <v>3236</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>143</v>
-      </c>
+        <v>12858</v>
+      </c>
+      <c r="D42" s="12"/>
       <c r="E42" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12" t="s">
-        <v>157</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="F42" s="36" t="s">
+        <v>356</v>
+      </c>
+      <c r="G42" s="12"/>
       <c r="H42" s="24" t="s">
-        <v>288</v>
-      </c>
-      <c r="I42" s="14"/>
-      <c r="J42" s="14"/>
+        <v>293</v>
+      </c>
+      <c r="I42" s="14">
+        <v>46268</v>
+      </c>
+      <c r="J42" s="14" t="s">
+        <v>67</v>
+      </c>
       <c r="K42" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>3.3333333333333335E-3</v>
       </c>
       <c r="L42" s="37">
@@ -4725,2353 +3930,18 @@
       <c r="N42" s="37">
         <v>0</v>
       </c>
-      <c r="P42" s="16" t="s">
-        <v>406</v>
-      </c>
-      <c r="Q42" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>417</v>
-      </c>
-      <c r="C43" s="15">
-        <v>3240</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="E43" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="I43" s="14"/>
-      <c r="J43" s="14"/>
-      <c r="K43" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L43" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M43" s="37">
-        <v>0</v>
-      </c>
-      <c r="N43" s="37">
-        <v>0</v>
-      </c>
-      <c r="P43" s="16"/>
-      <c r="Q43" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>419</v>
-      </c>
-      <c r="C44" s="15">
-        <v>3242</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>420</v>
-      </c>
-      <c r="E44" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="H44" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="I44" s="14"/>
-      <c r="J44" s="14"/>
-      <c r="K44" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L44" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M44" s="37">
-        <v>0</v>
-      </c>
-      <c r="N44" s="37">
-        <v>0</v>
-      </c>
-      <c r="P44" s="16"/>
-      <c r="Q44" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" ht="105" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45" s="12"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="H45" s="24" t="s">
-        <v>422</v>
-      </c>
-      <c r="I45" s="14"/>
-      <c r="J45" s="14"/>
-      <c r="K45" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L45" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M45" s="37">
-        <v>0</v>
-      </c>
-      <c r="N45" s="37">
-        <v>0</v>
-      </c>
-      <c r="P45" s="16"/>
-      <c r="Q45" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" ht="105" x14ac:dyDescent="0.25">
-      <c r="A46" s="12"/>
-      <c r="B46" s="12"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="H46" s="24" t="s">
-        <v>424</v>
-      </c>
-      <c r="I46" s="14"/>
-      <c r="J46" s="14"/>
-      <c r="K46" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L46" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M46" s="37">
-        <v>0</v>
-      </c>
-      <c r="N46" s="37">
-        <v>0</v>
-      </c>
-      <c r="P46" s="16"/>
-      <c r="Q46" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A47" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>425</v>
-      </c>
-      <c r="C47" s="15">
-        <v>3241</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>426</v>
-      </c>
-      <c r="E47" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="H47" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="I47" s="14"/>
-      <c r="J47" s="14"/>
-      <c r="K47" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L47" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M47" s="37">
-        <v>0</v>
-      </c>
-      <c r="N47" s="37">
-        <v>0</v>
-      </c>
-      <c r="P47" s="16"/>
-      <c r="Q47" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>427</v>
-      </c>
-      <c r="C48" s="15" t="s">
-        <v>428</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>429</v>
-      </c>
-      <c r="E48" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="H48" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L48" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M48" s="37">
-        <v>0</v>
-      </c>
-      <c r="N48" s="37">
-        <v>0</v>
-      </c>
-      <c r="P48" s="16"/>
-      <c r="Q48" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="C49" s="15">
-        <v>3273</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>431</v>
-      </c>
-      <c r="E49" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="H49" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="I49" s="14"/>
-      <c r="J49" s="14"/>
-      <c r="K49" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L49" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M49" s="37">
-        <v>0</v>
-      </c>
-      <c r="N49" s="37">
-        <v>0</v>
-      </c>
-      <c r="P49" s="16"/>
-      <c r="Q49" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>432</v>
-      </c>
-      <c r="C50" s="15">
-        <v>3276</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="E50" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14"/>
-      <c r="K50" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L50" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M50" s="37">
-        <v>0</v>
-      </c>
-      <c r="N50" s="37">
-        <v>0</v>
-      </c>
-      <c r="P50" s="16"/>
-      <c r="Q50" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A51" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>434</v>
-      </c>
-      <c r="C51" s="15">
-        <v>3282</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>435</v>
-      </c>
-      <c r="E51" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14"/>
-      <c r="K51" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L51" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M51" s="37">
-        <v>0</v>
-      </c>
-      <c r="N51" s="37">
-        <v>0</v>
-      </c>
-      <c r="P51" s="16"/>
-      <c r="Q51" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>436</v>
-      </c>
-      <c r="C52" s="15">
-        <v>3283</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="E52" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="I52" s="14"/>
-      <c r="J52" s="14"/>
-      <c r="K52" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L52" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M52" s="37">
-        <v>0</v>
-      </c>
-      <c r="N52" s="37">
-        <v>0</v>
-      </c>
-      <c r="P52" s="16"/>
-      <c r="Q52" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A53" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>437</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>438</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>439</v>
-      </c>
-      <c r="E53" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="I53" s="14"/>
-      <c r="J53" s="14"/>
-      <c r="K53" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L53" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M53" s="37">
-        <v>0</v>
-      </c>
-      <c r="N53" s="37">
-        <v>0</v>
-      </c>
-      <c r="P53" s="16"/>
-      <c r="Q53" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" ht="45" x14ac:dyDescent="0.25">
-      <c r="A54" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="B54" s="12" t="s">
-        <v>441</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="E54" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12" t="s">
-        <v>443</v>
-      </c>
-      <c r="H54" s="24" t="s">
-        <v>444</v>
-      </c>
-      <c r="I54" s="14"/>
-      <c r="J54" s="14"/>
-      <c r="K54" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L54" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M54" s="37">
-        <v>0</v>
-      </c>
-      <c r="N54" s="37">
-        <v>0</v>
-      </c>
-      <c r="P54" s="16"/>
-      <c r="Q54" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A55" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="C55" s="15">
-        <v>3292</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>446</v>
-      </c>
-      <c r="E55" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="I55" s="14"/>
-      <c r="J55" s="14"/>
-      <c r="K55" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L55" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M55" s="37">
-        <v>0</v>
-      </c>
-      <c r="N55" s="37">
-        <v>0</v>
-      </c>
-      <c r="P55" s="16"/>
-      <c r="Q55" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A56" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="B56" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="C56" s="15">
-        <v>3294</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>448</v>
-      </c>
-      <c r="E56" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="H56" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="I56" s="14"/>
-      <c r="J56" s="14"/>
-      <c r="K56" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L56" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M56" s="37">
-        <v>0</v>
-      </c>
-      <c r="N56" s="37">
-        <v>0</v>
-      </c>
-      <c r="P56" s="16"/>
-      <c r="Q56" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" ht="75" x14ac:dyDescent="0.25">
-      <c r="A57" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>449</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>450</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>451</v>
-      </c>
-      <c r="E57" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="H57" s="24" t="s">
-        <v>452</v>
-      </c>
-      <c r="I57" s="14"/>
-      <c r="J57" s="14"/>
-      <c r="K57" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L57" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M57" s="37">
-        <v>0</v>
-      </c>
-      <c r="N57" s="37">
-        <v>0</v>
-      </c>
-      <c r="P57" s="16"/>
-      <c r="Q57" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="B58" s="12" t="s">
-        <v>453</v>
-      </c>
-      <c r="C58" s="15">
-        <v>3300</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="E58" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="I58" s="14"/>
-      <c r="J58" s="14"/>
-      <c r="K58" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L58" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M58" s="37">
-        <v>0</v>
-      </c>
-      <c r="N58" s="37">
-        <v>0</v>
-      </c>
-      <c r="P58" s="16"/>
-      <c r="Q58" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A59" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>455</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>456</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>457</v>
-      </c>
-      <c r="E59" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F59" s="12"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="I59" s="14"/>
-      <c r="J59" s="14"/>
-      <c r="K59" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L59" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M59" s="37">
-        <v>0</v>
-      </c>
-      <c r="N59" s="37">
-        <v>0</v>
-      </c>
-      <c r="P59" s="16"/>
-      <c r="Q59" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>458</v>
-      </c>
-      <c r="C60" s="15">
-        <v>3333</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E60" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F60" s="12"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="I60" s="14"/>
-      <c r="J60" s="14"/>
-      <c r="K60" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L60" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M60" s="37">
-        <v>0</v>
-      </c>
-      <c r="N60" s="37">
-        <v>0</v>
-      </c>
-      <c r="P60" s="16" t="s">
-        <v>459</v>
-      </c>
-      <c r="Q60" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A61" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="B61" s="12" t="s">
-        <v>460</v>
-      </c>
-      <c r="C61" s="15">
-        <v>3336</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="E61" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="I61" s="14"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L61" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M61" s="37">
-        <v>0</v>
-      </c>
-      <c r="N61" s="37">
-        <v>0</v>
-      </c>
-      <c r="P61" s="16"/>
-      <c r="Q61" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" ht="75" x14ac:dyDescent="0.25">
-      <c r="A62" s="12" t="s">
-        <v>461</v>
-      </c>
-      <c r="B62" s="12" t="s">
-        <v>462</v>
-      </c>
-      <c r="C62" s="15">
-        <v>3339</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>463</v>
-      </c>
-      <c r="E62" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F62" s="12"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="I62"/>
-      <c r="J62"/>
-      <c r="K62" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L62" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M62" s="37">
-        <v>0</v>
-      </c>
-      <c r="N62" s="37">
-        <v>0</v>
-      </c>
-      <c r="P62" s="16"/>
-      <c r="Q62" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A63" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>465</v>
-      </c>
-      <c r="C63" s="15">
-        <v>3341</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>466</v>
-      </c>
-      <c r="E63" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F63" s="12"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="24" t="s">
-        <v>467</v>
-      </c>
-      <c r="I63" s="14"/>
-      <c r="J63" s="14"/>
-      <c r="K63" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L63" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M63" s="37">
-        <v>0</v>
-      </c>
-      <c r="N63" s="37">
-        <v>0</v>
-      </c>
-      <c r="P63" s="16"/>
-      <c r="Q63" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A64" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="B64" s="12" t="s">
-        <v>468</v>
-      </c>
-      <c r="C64" s="15">
-        <v>3356</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>469</v>
-      </c>
-      <c r="E64" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12"/>
-      <c r="H64" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="I64" s="14"/>
-      <c r="J64" s="14"/>
-      <c r="K64" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L64" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M64" s="37">
-        <v>0</v>
-      </c>
-      <c r="N64" s="37">
-        <v>0</v>
-      </c>
-      <c r="P64" s="34" t="s">
-        <v>470</v>
-      </c>
-      <c r="Q64" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A65" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="B65" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="C65" s="15">
-        <v>3357</v>
-      </c>
-      <c r="D65" s="12" t="s">
-        <v>472</v>
-      </c>
-      <c r="E65" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="24" t="s">
-        <v>276</v>
-      </c>
-      <c r="I65" s="14"/>
-      <c r="J65" s="14"/>
-      <c r="K65" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L65" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M65" s="37">
-        <v>0</v>
-      </c>
-      <c r="N65" s="37">
-        <v>0</v>
-      </c>
-      <c r="P65" s="16"/>
-      <c r="Q65" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A66" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="B66" s="12" t="s">
-        <v>473</v>
-      </c>
-      <c r="C66" s="15" t="s">
-        <v>474</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>475</v>
-      </c>
-      <c r="E66" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="I66" s="14"/>
-      <c r="J66" s="14"/>
-      <c r="K66" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L66" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M66" s="37">
-        <v>0</v>
-      </c>
-      <c r="N66" s="37">
-        <v>0</v>
-      </c>
-      <c r="P66" s="16"/>
-      <c r="Q66" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" ht="75" x14ac:dyDescent="0.25">
-      <c r="A67" s="12" t="s">
-        <v>461</v>
-      </c>
-      <c r="B67" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="C67" s="15">
-        <v>3374</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>477</v>
-      </c>
-      <c r="E67" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F67" s="12"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="I67" s="14"/>
-      <c r="J67" s="14"/>
-      <c r="K67" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L67" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M67" s="37">
-        <v>0</v>
-      </c>
-      <c r="N67" s="37">
-        <v>0</v>
-      </c>
-      <c r="P67" s="16"/>
-      <c r="Q67" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A68" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="B68" s="12" t="s">
-        <v>478</v>
-      </c>
-      <c r="C68" s="15">
-        <v>3382</v>
-      </c>
-      <c r="D68" s="12" t="s">
-        <v>479</v>
-      </c>
-      <c r="E68" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F68" s="12"/>
-      <c r="G68" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="H68" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="I68" s="14"/>
-      <c r="J68" s="14"/>
-      <c r="K68" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L68" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M68" s="37">
-        <v>0</v>
-      </c>
-      <c r="N68" s="37">
-        <v>0</v>
-      </c>
-      <c r="P68" s="16"/>
-      <c r="Q68" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A69" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="B69" s="12" t="s">
-        <v>480</v>
-      </c>
-      <c r="C69" s="15">
-        <v>3391</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>481</v>
-      </c>
-      <c r="E69" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F69" s="12"/>
-      <c r="G69" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="H69" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="I69" s="14"/>
-      <c r="J69" s="14"/>
-      <c r="K69" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L69" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M69" s="37">
-        <v>0</v>
-      </c>
-      <c r="N69" s="37">
-        <v>0</v>
-      </c>
-      <c r="P69" s="16"/>
-      <c r="Q69" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A70" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="B70" s="12" t="s">
-        <v>482</v>
-      </c>
-      <c r="C70" s="15">
-        <v>3387</v>
-      </c>
-      <c r="D70" s="12"/>
-      <c r="E70" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F70" s="12"/>
-      <c r="G70" s="12"/>
-      <c r="H70" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="I70" s="14"/>
-      <c r="J70" s="14"/>
-      <c r="K70" s="37">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L70" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="M70" s="37">
-        <v>0</v>
-      </c>
-      <c r="N70" s="37">
-        <v>0</v>
-      </c>
-      <c r="P70" s="16"/>
-      <c r="Q70" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" ht="75" x14ac:dyDescent="0.25">
-      <c r="A71" s="12" t="s">
-        <v>461</v>
-      </c>
-      <c r="B71" s="12" t="s">
-        <v>483</v>
-      </c>
-      <c r="C71" s="15">
-        <v>3396</v>
-      </c>
-      <c r="D71" s="12"/>
-      <c r="E71" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F71" s="12"/>
-      <c r="G71" s="20"/>
-      <c r="H71" s="25" t="s">
-        <v>464</v>
-      </c>
-      <c r="I71" s="14"/>
-      <c r="J71" s="14"/>
-      <c r="K71" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L71" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M71" s="32">
-        <v>0</v>
-      </c>
-      <c r="N71" s="32">
-        <v>0</v>
-      </c>
-      <c r="P71" s="16"/>
-      <c r="Q71" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A72" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="B72" s="12" t="s">
-        <v>484</v>
-      </c>
-      <c r="C72" s="15" t="s">
-        <v>485</v>
-      </c>
-      <c r="D72" s="12"/>
-      <c r="E72" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F72" s="12"/>
-      <c r="G72" s="12"/>
-      <c r="H72" s="26" t="s">
-        <v>285</v>
-      </c>
-      <c r="I72" s="14"/>
-      <c r="J72" s="14"/>
-      <c r="K72" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L72" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M72" s="32">
-        <v>0</v>
-      </c>
-      <c r="N72" s="32">
-        <v>0</v>
-      </c>
-      <c r="P72" s="16"/>
-      <c r="Q72" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A73" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="B73" s="12" t="s">
-        <v>486</v>
-      </c>
-      <c r="C73" s="15">
-        <v>3414</v>
-      </c>
-      <c r="D73" s="12"/>
-      <c r="E73" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F73" s="12"/>
-      <c r="G73" s="12"/>
-      <c r="H73" s="26" t="s">
-        <v>375</v>
-      </c>
-      <c r="I73" s="14"/>
-      <c r="J73" s="14"/>
-      <c r="K73" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L73" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M73" s="32">
-        <v>0</v>
-      </c>
-      <c r="N73" s="32">
-        <v>0</v>
-      </c>
-      <c r="P73" s="16"/>
-      <c r="Q73" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A74" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="B74" s="12" t="s">
-        <v>487</v>
-      </c>
-      <c r="C74" s="15">
-        <v>3421</v>
-      </c>
-      <c r="D74" s="12"/>
-      <c r="E74" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F74" s="12"/>
-      <c r="G74" s="12"/>
-      <c r="H74" s="25" t="s">
-        <v>280</v>
-      </c>
-      <c r="I74" s="14"/>
-      <c r="J74" s="14"/>
-      <c r="K74" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L74" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M74" s="32">
-        <v>0</v>
-      </c>
-      <c r="N74" s="32">
-        <v>0</v>
-      </c>
-      <c r="P74" s="16"/>
-      <c r="Q74" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A75" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="B75" s="12" t="s">
-        <v>488</v>
-      </c>
-      <c r="C75" s="15">
-        <v>3423</v>
-      </c>
-      <c r="D75" s="12"/>
-      <c r="E75" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F75" s="12"/>
-      <c r="G75" s="12"/>
-      <c r="H75" s="26" t="s">
-        <v>300</v>
-      </c>
-      <c r="I75" s="14"/>
-      <c r="J75" s="14"/>
-      <c r="K75" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L75" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M75" s="32">
-        <v>0</v>
-      </c>
-      <c r="N75" s="32">
-        <v>0</v>
-      </c>
-      <c r="P75" s="16"/>
-      <c r="Q75" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A76" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="B76" s="12" t="s">
-        <v>489</v>
-      </c>
-      <c r="C76" s="15">
-        <v>3427</v>
-      </c>
-      <c r="D76" s="12"/>
-      <c r="E76" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F76" s="12"/>
-      <c r="G76" s="12"/>
-      <c r="H76" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="I76" s="14"/>
-      <c r="J76" s="14"/>
-      <c r="K76" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L76" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M76" s="32">
-        <v>0</v>
-      </c>
-      <c r="N76" s="32">
-        <v>0</v>
-      </c>
-      <c r="P76" s="16"/>
-      <c r="Q76" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A77" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="B77" s="12" t="s">
-        <v>490</v>
-      </c>
-      <c r="C77" s="15">
-        <v>3433</v>
-      </c>
-      <c r="D77" s="12"/>
-      <c r="E77" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F77" s="12"/>
-      <c r="G77" s="12"/>
-      <c r="H77" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="I77" s="14"/>
-      <c r="J77" s="14"/>
-      <c r="K77" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L77" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M77" s="32">
-        <v>0</v>
-      </c>
-      <c r="N77" s="32">
-        <v>0</v>
-      </c>
-      <c r="P77" s="16"/>
-      <c r="Q77" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" ht="30" x14ac:dyDescent="0.25">
-      <c r="A78" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="B78" s="12" t="s">
-        <v>491</v>
-      </c>
-      <c r="C78" s="15"/>
-      <c r="D78" s="12"/>
-      <c r="E78" s="12"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="12"/>
-      <c r="H78" s="24"/>
-      <c r="I78" s="14"/>
-      <c r="J78" s="14"/>
-      <c r="K78" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L78" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M78" s="32">
-        <v>0</v>
-      </c>
-      <c r="N78" s="32">
-        <v>0</v>
-      </c>
-      <c r="P78" s="16"/>
-      <c r="Q78" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" ht="30" x14ac:dyDescent="0.25">
-      <c r="A79" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="B79" s="12" t="s">
-        <v>492</v>
-      </c>
-      <c r="C79" s="15"/>
-      <c r="D79" s="12"/>
-      <c r="E79" s="12"/>
-      <c r="F79" s="12"/>
-      <c r="G79" s="12"/>
-      <c r="H79" s="24"/>
-      <c r="I79" s="14"/>
-      <c r="J79" s="14"/>
-      <c r="K79" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L79" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M79" s="32">
-        <v>0</v>
-      </c>
-      <c r="N79" s="32">
-        <v>0</v>
-      </c>
-      <c r="P79" s="16"/>
-      <c r="Q79" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" ht="75" x14ac:dyDescent="0.25">
-      <c r="A80" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="B80" s="12" t="s">
-        <v>493</v>
-      </c>
-      <c r="C80" s="15">
-        <v>3461</v>
-      </c>
-      <c r="D80" s="12" t="s">
-        <v>494</v>
-      </c>
-      <c r="E80" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F80" s="12"/>
-      <c r="G80" s="12"/>
-      <c r="H80" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="I80" s="14"/>
-      <c r="J80" s="14"/>
-      <c r="K80" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L80" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M80" s="32">
-        <v>0</v>
-      </c>
-      <c r="N80" s="32">
-        <v>0</v>
-      </c>
-      <c r="P80" s="16"/>
-      <c r="Q80" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A81" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="B81" s="12" t="s">
-        <v>495</v>
-      </c>
-      <c r="C81" s="15" t="s">
-        <v>496</v>
-      </c>
-      <c r="D81" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="E81" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F81" s="12"/>
-      <c r="G81" s="12"/>
-      <c r="H81" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="I81" s="14"/>
-      <c r="J81" s="14"/>
-      <c r="K81" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L81" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M81" s="32">
-        <v>0</v>
-      </c>
-      <c r="N81" s="32">
-        <v>0</v>
-      </c>
-      <c r="P81" s="16"/>
-      <c r="Q81" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A82" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="B82" s="12" t="s">
-        <v>498</v>
-      </c>
-      <c r="C82" s="15">
-        <v>3487</v>
-      </c>
-      <c r="D82" s="12" t="s">
-        <v>499</v>
-      </c>
-      <c r="E82" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F82" s="12"/>
-      <c r="G82" s="12"/>
-      <c r="H82" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="I82" s="14"/>
-      <c r="J82" s="14"/>
-      <c r="K82" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L82" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M82" s="32">
-        <v>0</v>
-      </c>
-      <c r="N82" s="32">
-        <v>0</v>
-      </c>
-      <c r="P82" s="16"/>
-      <c r="Q82" s="16"/>
-    </row>
-    <row r="83" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A83" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="B83" s="12" t="s">
-        <v>500</v>
-      </c>
-      <c r="C83" s="15">
-        <v>3495</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>501</v>
-      </c>
-      <c r="E83" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="12"/>
-      <c r="G83" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="H83" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="I83" s="14"/>
-      <c r="J83" s="14"/>
-      <c r="K83" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L83" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M83" s="32">
-        <v>0</v>
-      </c>
-      <c r="N83" s="32">
-        <v>0</v>
-      </c>
-      <c r="P83" s="16"/>
-      <c r="Q83" s="16"/>
-    </row>
-    <row r="84" spans="1:17" ht="60" x14ac:dyDescent="0.25">
-      <c r="A84" s="12" t="s">
-        <v>502</v>
-      </c>
-      <c r="B84" s="12" t="s">
-        <v>503</v>
-      </c>
-      <c r="C84" s="15" t="s">
-        <v>504</v>
-      </c>
-      <c r="D84" s="12" t="s">
-        <v>505</v>
-      </c>
-      <c r="E84" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F84" s="12"/>
-      <c r="G84" s="12" t="s">
-        <v>506</v>
-      </c>
-      <c r="H84" s="24" t="s">
-        <v>507</v>
-      </c>
-      <c r="I84" s="14"/>
-      <c r="J84" s="14"/>
-      <c r="K84" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L84" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M84" s="32">
-        <v>0</v>
-      </c>
-      <c r="N84" s="32">
-        <v>0</v>
-      </c>
-      <c r="P84" s="16"/>
-      <c r="Q84" s="16"/>
-    </row>
-    <row r="85" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A85" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="B85" s="12" t="s">
-        <v>508</v>
-      </c>
-      <c r="C85" s="15">
-        <v>3505</v>
-      </c>
-      <c r="D85" s="12" t="s">
-        <v>509</v>
-      </c>
-      <c r="E85" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F85" s="12"/>
-      <c r="G85" s="12"/>
-      <c r="H85" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="I85" s="14"/>
-      <c r="J85" s="14"/>
-      <c r="K85" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L85" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M85" s="32">
-        <v>0</v>
-      </c>
-      <c r="N85" s="32">
-        <v>0</v>
-      </c>
-      <c r="P85" s="16"/>
-      <c r="Q85" s="16"/>
-    </row>
-    <row r="86" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A86" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="B86" s="12" t="s">
-        <v>510</v>
-      </c>
-      <c r="C86" s="15">
-        <v>3508</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>511</v>
-      </c>
-      <c r="E86" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F86" s="12"/>
-      <c r="G86" s="12"/>
-      <c r="H86" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="I86" s="14"/>
-      <c r="J86" s="14"/>
-      <c r="K86" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L86" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M86" s="32">
-        <v>0</v>
-      </c>
-      <c r="N86" s="32">
-        <v>0</v>
-      </c>
-      <c r="P86" s="16"/>
-      <c r="Q86" s="16"/>
-    </row>
-    <row r="87" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A87" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="B87" s="12" t="s">
-        <v>512</v>
-      </c>
-      <c r="C87" s="15">
-        <v>3526</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="E87" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="F87" s="12"/>
-      <c r="G87" s="12"/>
-      <c r="H87" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="I87" s="14"/>
-      <c r="J87" s="14">
-        <v>46190</v>
-      </c>
-      <c r="K87" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L87" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M87" s="32">
-        <v>0</v>
-      </c>
-      <c r="N87" s="32">
-        <v>0</v>
-      </c>
-      <c r="P87" s="16"/>
-      <c r="Q87" s="34" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" ht="75" x14ac:dyDescent="0.25">
-      <c r="A88" s="12" t="s">
-        <v>513</v>
-      </c>
-      <c r="B88" s="12" t="s">
-        <v>514</v>
-      </c>
-      <c r="C88" s="15" t="s">
-        <v>515</v>
-      </c>
-      <c r="D88" s="12" t="s">
-        <v>516</v>
-      </c>
-      <c r="E88" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F88" s="12"/>
-      <c r="G88" s="12"/>
-      <c r="H88" s="24" t="s">
-        <v>517</v>
-      </c>
-      <c r="I88" s="14"/>
-      <c r="J88" s="14"/>
-      <c r="K88" s="32">
-        <f t="shared" si="1"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L88" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M88" s="32">
-        <v>0</v>
-      </c>
-      <c r="N88" s="32">
-        <v>0</v>
-      </c>
-      <c r="P88" s="16"/>
-      <c r="Q88" s="16"/>
-    </row>
-    <row r="89" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A89" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="B89" s="12" t="s">
-        <v>518</v>
-      </c>
-      <c r="C89" s="15">
-        <v>3547</v>
-      </c>
-      <c r="D89" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="E89" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F89" s="12"/>
-      <c r="G89" s="12"/>
-      <c r="H89" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="I89" s="14"/>
-      <c r="J89" s="14"/>
-      <c r="K89" s="32">
-        <f t="shared" ref="K89:K95" si="2">AVERAGE(L89:N89)</f>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L89" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M89" s="32">
-        <v>0</v>
-      </c>
-      <c r="N89" s="32">
-        <v>0</v>
-      </c>
-      <c r="P89" s="16"/>
-      <c r="Q89" s="16"/>
-    </row>
-    <row r="90" spans="1:17" ht="105" x14ac:dyDescent="0.25">
-      <c r="A90" s="12" t="s">
-        <v>519</v>
-      </c>
-      <c r="B90" s="12" t="s">
-        <v>520</v>
-      </c>
-      <c r="C90" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D90" s="12" t="s">
-        <v>521</v>
-      </c>
-      <c r="E90" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F90" s="12"/>
-      <c r="G90" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="H90" s="24" t="s">
-        <v>424</v>
-      </c>
-      <c r="I90" s="14"/>
-      <c r="J90" s="14"/>
-      <c r="K90" s="32">
-        <f t="shared" si="2"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L90" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M90" s="32">
-        <v>0</v>
-      </c>
-      <c r="N90" s="32">
-        <v>0</v>
-      </c>
-      <c r="P90" s="16"/>
-      <c r="Q90" s="16"/>
-    </row>
-    <row r="91" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A91" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="B91" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C91" s="15">
-        <v>3561</v>
-      </c>
-      <c r="D91" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="E91" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F91" s="12"/>
-      <c r="G91" s="12"/>
-      <c r="H91" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="I91" s="14"/>
-      <c r="J91" s="14"/>
-      <c r="K91" s="32">
-        <f t="shared" si="2"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L91" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M91" s="32">
-        <v>0</v>
-      </c>
-      <c r="N91" s="32">
-        <v>0</v>
-      </c>
-      <c r="P91" s="16"/>
-      <c r="Q91" s="16"/>
-    </row>
-    <row r="92" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A92" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="B92" s="12" t="s">
-        <v>524</v>
-      </c>
-      <c r="C92" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D92" s="12" t="s">
-        <v>525</v>
-      </c>
-      <c r="E92" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F92" s="12"/>
-      <c r="G92" s="12"/>
-      <c r="H92" s="24" t="s">
-        <v>526</v>
-      </c>
-      <c r="I92" s="14"/>
-      <c r="J92" s="14"/>
-      <c r="K92" s="32">
-        <f t="shared" si="2"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L92" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M92" s="32">
-        <v>0</v>
-      </c>
-      <c r="N92" s="32">
-        <v>0</v>
-      </c>
-      <c r="P92" s="16"/>
-      <c r="Q92" s="16"/>
-    </row>
-    <row r="93" spans="1:17" ht="75" x14ac:dyDescent="0.25">
-      <c r="A93" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="B93" s="12" t="s">
-        <v>527</v>
-      </c>
-      <c r="C93" s="15" t="s">
-        <v>543</v>
-      </c>
-      <c r="D93" s="12" t="s">
-        <v>528</v>
-      </c>
-      <c r="E93" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F93" s="12"/>
-      <c r="G93" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="H93" s="24" t="s">
-        <v>529</v>
-      </c>
-      <c r="I93" s="14"/>
-      <c r="J93" s="14"/>
-      <c r="K93" s="32">
-        <f t="shared" si="2"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L93" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M93" s="32">
-        <v>0</v>
-      </c>
-      <c r="N93" s="32">
-        <v>0</v>
-      </c>
-      <c r="P93" s="16"/>
-      <c r="Q93" s="16"/>
-    </row>
-    <row r="94" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A94" s="12" t="s">
-        <v>530</v>
-      </c>
-      <c r="B94" s="12" t="s">
-        <v>531</v>
-      </c>
-      <c r="C94" s="15" t="s">
-        <v>544</v>
-      </c>
-      <c r="D94" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="E94" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94" s="12"/>
-      <c r="G94" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="H94" s="24" t="s">
-        <v>276</v>
-      </c>
-      <c r="I94" s="14"/>
-      <c r="J94" s="14"/>
-      <c r="K94" s="32">
-        <f t="shared" si="2"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L94" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M94" s="32">
-        <v>0</v>
-      </c>
-      <c r="N94" s="32">
-        <v>0</v>
-      </c>
-      <c r="P94" s="16"/>
-      <c r="Q94" s="16"/>
-    </row>
-    <row r="95" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A95" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="B95" s="12" t="s">
-        <v>532</v>
-      </c>
-      <c r="C95" s="15">
-        <v>3614</v>
-      </c>
-      <c r="D95" s="12" t="s">
-        <v>533</v>
-      </c>
-      <c r="E95" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F95" s="12"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="I95" s="14"/>
-      <c r="J95" s="14"/>
-      <c r="K95" s="32">
-        <f t="shared" si="2"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L95" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M95" s="32">
-        <v>0</v>
-      </c>
-      <c r="N95" s="32">
-        <v>0</v>
-      </c>
-      <c r="P95" s="16"/>
-      <c r="Q95" s="16"/>
-    </row>
-    <row r="96" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A96" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="B96" s="12" t="s">
-        <v>534</v>
-      </c>
-      <c r="C96" s="15">
-        <v>3623</v>
-      </c>
-      <c r="D96" s="12" t="s">
-        <v>538</v>
-      </c>
-      <c r="E96" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F96" s="12"/>
-      <c r="G96" s="12"/>
-      <c r="H96" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="I96" s="14"/>
-      <c r="J96" s="14"/>
-      <c r="K96" s="32">
-        <f t="shared" ref="K96" si="3">AVERAGE(L96:N96)</f>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L96" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M96" s="32">
-        <v>0</v>
-      </c>
-      <c r="N96" s="32">
-        <v>0</v>
-      </c>
-      <c r="P96" s="16"/>
-      <c r="Q96" s="16"/>
-    </row>
-    <row r="97" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A97" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="B97" s="12" t="s">
-        <v>535</v>
-      </c>
-      <c r="C97" s="15">
-        <v>3634</v>
-      </c>
-      <c r="D97" s="12" t="s">
-        <v>539</v>
-      </c>
-      <c r="E97" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F97" s="12"/>
-      <c r="G97" s="12"/>
-      <c r="H97" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="I97" s="14"/>
-      <c r="J97" s="14"/>
-      <c r="K97" s="32">
-        <f t="shared" ref="K97:K99" si="4">AVERAGE(L97:N97)</f>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L97" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M97" s="32">
-        <v>0</v>
-      </c>
-      <c r="N97" s="32">
-        <v>0</v>
-      </c>
-      <c r="P97" s="16"/>
-      <c r="Q97" s="16"/>
-    </row>
-    <row r="98" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A98" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="B98" s="12" t="s">
-        <v>536</v>
-      </c>
-      <c r="C98" s="15">
-        <v>3650</v>
-      </c>
-      <c r="D98" s="12" t="s">
-        <v>540</v>
-      </c>
-      <c r="E98" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F98" s="12"/>
-      <c r="G98" s="12"/>
-      <c r="H98" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="I98" s="14"/>
-      <c r="J98" s="14"/>
-      <c r="K98" s="32">
-        <f t="shared" si="4"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L98" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M98" s="32">
-        <v>0</v>
-      </c>
-      <c r="N98" s="32">
-        <v>0</v>
-      </c>
-      <c r="P98" s="16"/>
-      <c r="Q98" s="16"/>
-    </row>
-    <row r="99" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A99" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B99" s="12" t="s">
-        <v>537</v>
-      </c>
-      <c r="C99" s="15">
-        <v>3663</v>
-      </c>
-      <c r="D99" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="E99" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F99" s="12"/>
-      <c r="G99" s="12"/>
-      <c r="H99" s="24" t="s">
-        <v>288</v>
-      </c>
-      <c r="I99" s="14"/>
-      <c r="J99" s="14"/>
-      <c r="K99" s="32">
-        <f t="shared" si="4"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="L99" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M99" s="32">
-        <v>0</v>
-      </c>
-      <c r="N99" s="32">
-        <v>0</v>
-      </c>
-      <c r="P99" s="16"/>
-      <c r="Q99" s="16"/>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A100" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="B100" s="12" t="s">
-        <v>542</v>
-      </c>
-      <c r="C100" s="15" t="s">
-        <v>541</v>
-      </c>
-      <c r="D100" s="12"/>
-      <c r="E100" s="36"/>
-      <c r="F100" s="12"/>
-      <c r="G100" s="12"/>
-      <c r="H100" s="24"/>
-      <c r="I100" s="14"/>
-      <c r="J100" s="14"/>
-      <c r="K100" s="37" t="e">
-        <f>AVERAGE(L100:N100)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L100" s="37"/>
-      <c r="M100" s="37"/>
-      <c r="N100" s="37"/>
-      <c r="P100" s="16"/>
-      <c r="Q100" s="16"/>
+      <c r="P42" s="16"/>
+      <c r="Q42" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="P35" r:id="rId1" xr:uid="{98105506-64B6-4747-95DC-0CED951FD614}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7281,24 +4151,24 @@
     </row>
     <row r="10" spans="1:14" ht="150" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>260</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="H10" s="25" t="s">
         <v>261</v>
       </c>
-      <c r="G10" s="20" t="s">
+    </row>
+    <row r="11" spans="1:14" ht="165" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>263</v>
       </c>
-      <c r="H10" s="25" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="180" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="G11" t="s">
+        <v>265</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="G11" t="s">
-        <v>266</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -8093,25 +4963,25 @@
     </row>
     <row r="12" spans="1:14" ht="120" x14ac:dyDescent="0.25">
       <c r="A12" s="35" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B12" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C12">
         <v>2547</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E12" t="s">
         <v>50</v>
       </c>
       <c r="G12" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="I12" s="3">
         <v>45993</v>
@@ -8543,13 +5413,13 @@
   <sheetData>
     <row r="1" spans="1:15" ht="150" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
+        <v>255</v>
+      </c>
+      <c r="B1" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="C1" s="19" t="s">
         <v>257</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>258</v>
       </c>
       <c r="D1" s="18" t="s">
         <v>254</v>
@@ -8559,10 +5429,10 @@
       </c>
       <c r="F1" s="18"/>
       <c r="G1" s="18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1" s="26" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I1" s="31">
         <v>45853</v>

--- a/Client Information App.xlsx
+++ b/Client Information App.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\06 Operation\1. Operation Documents\3. Project Cordination\5. Data Analytics\Power Bi Projects\1. PB2401 Client Information\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74F4AD8-0D2F-4CA9-B2C5-1DDCFED2680B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBFEAE4-A458-4002-88D6-860B73AE6FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="768" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1386,7 +1386,7 @@
     <t>SO-2265</t>
   </si>
   <si>
-    <t>Add to production</t>
+    <t>Add to Production</t>
   </si>
 </sst>
 </file>
